--- a/xlsx/dre/DRE_08_2026.xlsx
+++ b/xlsx/dre/DRE_08_2026.xlsx
@@ -477,6 +477,24 @@
     <t>ADM</t>
   </si>
   <si>
+    <t>1/7</t>
+  </si>
+  <si>
+    <t>MP Interiores e Serv Ltda</t>
+  </si>
+  <si>
+    <t>R$  511,90</t>
+  </si>
+  <si>
+    <t>27/02/26</t>
+  </si>
+  <si>
+    <t>18/08/26</t>
+  </si>
+  <si>
+    <t>Digisac MP 2026</t>
+  </si>
+  <si>
     <t>38/1</t>
   </si>
   <si>
@@ -490,24 +508,6 @@
   </si>
   <si>
     <t>INSS</t>
-  </si>
-  <si>
-    <t>1/7</t>
-  </si>
-  <si>
-    <t>MP Interiores e Serv Ltda</t>
-  </si>
-  <si>
-    <t>R$  511,90</t>
-  </si>
-  <si>
-    <t>27/02/26</t>
-  </si>
-  <si>
-    <t>18/08/26</t>
-  </si>
-  <si>
-    <t>Digisac MP 2026</t>
   </si>
   <si>
     <t>4 CUSTOS E DESPESAS</t>
@@ -1398,9 +1398,66 @@
     <t>PPC</t>
   </si>
   <si>
+    <t>R$  1.358,25</t>
+  </si>
+  <si>
+    <t>Jose Carlos de Carvalho</t>
+  </si>
+  <si>
+    <t>R$  432,60</t>
+  </si>
+  <si>
+    <t>FERNANDA DOCHVAT SILVA</t>
+  </si>
+  <si>
+    <t>R$  2.193,79</t>
+  </si>
+  <si>
+    <t>R$  369,25</t>
+  </si>
+  <si>
     <t>R$  159,90</t>
   </si>
   <si>
+    <t>R$  5,63</t>
+  </si>
+  <si>
+    <t>88201/1</t>
+  </si>
+  <si>
+    <t>R$  294,73</t>
+  </si>
+  <si>
+    <t>88201BRUNORV</t>
+  </si>
+  <si>
+    <t>90401/1</t>
+  </si>
+  <si>
+    <t>R$  3.395,45</t>
+  </si>
+  <si>
+    <t>89301JoaoMCC</t>
+  </si>
+  <si>
+    <t>97901/2</t>
+  </si>
+  <si>
+    <t>R$  364,20</t>
+  </si>
+  <si>
+    <t>79601/1</t>
+  </si>
+  <si>
+    <t>R$  534,37</t>
+  </si>
+  <si>
+    <t>79601EduardoMF</t>
+  </si>
+  <si>
+    <t>R$  610,94</t>
+  </si>
+  <si>
     <t>91001/1</t>
   </si>
   <si>
@@ -1410,40 +1467,7 @@
     <t>91001DABRURA</t>
   </si>
   <si>
-    <t>88201/1</t>
-  </si>
-  <si>
-    <t>R$  294,73</t>
-  </si>
-  <si>
-    <t>88201BRUNORV</t>
-  </si>
-  <si>
-    <t>R$  5,63</t>
-  </si>
-  <si>
-    <t>FERNANDA DOCHVAT SILVA</t>
-  </si>
-  <si>
-    <t>R$  369,25</t>
-  </si>
-  <si>
-    <t>79601/1</t>
-  </si>
-  <si>
-    <t>Jose Carlos de Carvalho</t>
-  </si>
-  <si>
-    <t>R$  534,37</t>
-  </si>
-  <si>
-    <t>79601EduardoMF</t>
-  </si>
-  <si>
-    <t>R$  432,60</t>
-  </si>
-  <si>
-    <t>R$  364,20</t>
+    <t>R$  92,96</t>
   </si>
   <si>
     <t>90501/1</t>
@@ -1455,18 +1479,12 @@
     <t>90501TARLEYSO</t>
   </si>
   <si>
-    <t>97901/2</t>
+    <t>R$  43,69</t>
   </si>
   <si>
     <t>R$  19,04</t>
   </si>
   <si>
-    <t>R$  43,69</t>
-  </si>
-  <si>
-    <t>R$  92,96</t>
-  </si>
-  <si>
     <t>56101/1</t>
   </si>
   <si>
@@ -1476,24 +1494,6 @@
     <t>56101FELIXHS</t>
   </si>
   <si>
-    <t>R$  2.193,79</t>
-  </si>
-  <si>
-    <t>90401/1</t>
-  </si>
-  <si>
-    <t>R$  3.395,45</t>
-  </si>
-  <si>
-    <t>89301JoaoMCC</t>
-  </si>
-  <si>
-    <t>R$  1.358,25</t>
-  </si>
-  <si>
-    <t>R$  610,94</t>
-  </si>
-  <si>
     <t>4.03.01.02.08 Comissões montagem - provisão</t>
   </si>
   <si>
@@ -1599,12 +1599,12 @@
     <t>4.03.03.02.05.02 Assistência técnica medição</t>
   </si>
   <si>
+    <t>PFP</t>
+  </si>
+  <si>
     <t>L E A Medicoes Tecnicas LTDA</t>
   </si>
   <si>
-    <t>PFP</t>
-  </si>
-  <si>
     <t>R$  360,00</t>
   </si>
   <si>
@@ -1659,9 +1659,30 @@
     <t>R$ 9.215,99</t>
   </si>
   <si>
+    <t>WEBGIGA SOLUCOES DIGITAIS LTDA</t>
+  </si>
+  <si>
+    <t>R$  4.642,50</t>
+  </si>
+  <si>
+    <t>18/02/26</t>
+  </si>
+  <si>
+    <t>Webgiga 2026</t>
+  </si>
+  <si>
     <t>12/8</t>
   </si>
   <si>
+    <t>Google</t>
+  </si>
+  <si>
+    <t>R$  14,99</t>
+  </si>
+  <si>
+    <t>Google 2026</t>
+  </si>
+  <si>
     <t>MARQUES MAIO MARKETING DIGITAL LTDA</t>
   </si>
   <si>
@@ -1674,27 +1695,6 @@
     <t>MHM - Honorários 2026</t>
   </si>
   <si>
-    <t>Google</t>
-  </si>
-  <si>
-    <t>R$  14,99</t>
-  </si>
-  <si>
-    <t>Google 2026</t>
-  </si>
-  <si>
-    <t>WEBGIGA SOLUCOES DIGITAIS LTDA</t>
-  </si>
-  <si>
-    <t>R$  4.642,50</t>
-  </si>
-  <si>
-    <t>18/02/26</t>
-  </si>
-  <si>
-    <t>Webgiga 2026</t>
-  </si>
-  <si>
     <t>1/6</t>
   </si>
   <si>
@@ -1752,6 +1752,102 @@
     <t>4.04.01.02.01.01 Salário fixo</t>
   </si>
   <si>
+    <t>SABRINA ALVES DE ABREU BRAUNBECK</t>
+  </si>
+  <si>
+    <t>R$  3.276,49</t>
+  </si>
+  <si>
+    <t>Sabrina Braunbeck - Pagamento 2026</t>
+  </si>
+  <si>
+    <t>Danielle Martins da Silva</t>
+  </si>
+  <si>
+    <t>R$  2.090,00</t>
+  </si>
+  <si>
+    <t>Danielle - Pagamento 2026</t>
+  </si>
+  <si>
+    <t>Rubens - Pagamento 2026</t>
+  </si>
+  <si>
+    <t>R$  2.536,00</t>
+  </si>
+  <si>
+    <t>19/02/26</t>
+  </si>
+  <si>
+    <t>Bianca Rodrigues - Salário fixo 2026</t>
+  </si>
+  <si>
+    <t>735/1</t>
+  </si>
+  <si>
+    <t>BIANCA RODRIGUES NASCIMENTO</t>
+  </si>
+  <si>
+    <t>Pemiação meta</t>
+  </si>
+  <si>
+    <t>GUTEMBERG DIAS GOMES</t>
+  </si>
+  <si>
+    <t>R$  6.500,00</t>
+  </si>
+  <si>
+    <t>Gutemberg Dias - Pagamento</t>
+  </si>
+  <si>
+    <t>R$  1.500,00</t>
+  </si>
+  <si>
+    <t>12/02/26</t>
+  </si>
+  <si>
+    <t>Fernanda Dochvat - Fixo 2026</t>
+  </si>
+  <si>
+    <t>Fixo ago26/1</t>
+  </si>
+  <si>
+    <t>R$  225,31</t>
+  </si>
+  <si>
+    <t>Estorno empréstimo</t>
+  </si>
+  <si>
+    <t>R$  2.365,00</t>
+  </si>
+  <si>
+    <t>Carina - Pagamento 2026</t>
+  </si>
+  <si>
+    <t>740/1</t>
+  </si>
+  <si>
+    <t>Eric Kevin de Souza Serpa</t>
+  </si>
+  <si>
+    <t>19/08/26</t>
+  </si>
+  <si>
+    <t>Salário Fixo -Eric Serpa 2026</t>
+  </si>
+  <si>
+    <t>Estorno empr ago26/1</t>
+  </si>
+  <si>
+    <t>R$  249,82</t>
+  </si>
+  <si>
+    <t>Teresinha Elvira Maximino de Menezes</t>
+  </si>
+  <si>
+    <t>Tucha - Fixo 2026</t>
+  </si>
+  <si>
     <t>Denny Lucas do Carmo Pereira</t>
   </si>
   <si>
@@ -1761,87 +1857,6 @@
     <t>Denny Lucas - Pagamento 2026</t>
   </si>
   <si>
-    <t>Rubens - Pagamento 2026</t>
-  </si>
-  <si>
-    <t>R$  1.500,00</t>
-  </si>
-  <si>
-    <t>12/02/26</t>
-  </si>
-  <si>
-    <t>Fernanda Dochvat - Fixo 2026</t>
-  </si>
-  <si>
-    <t>R$  2.536,00</t>
-  </si>
-  <si>
-    <t>19/02/26</t>
-  </si>
-  <si>
-    <t>Bianca Rodrigues - Salário fixo 2026</t>
-  </si>
-  <si>
-    <t>GUTEMBERG DIAS GOMES</t>
-  </si>
-  <si>
-    <t>R$  6.500,00</t>
-  </si>
-  <si>
-    <t>Gutemberg Dias - Pagamento</t>
-  </si>
-  <si>
-    <t>740/1</t>
-  </si>
-  <si>
-    <t>Teresinha Elvira Maximino de Menezes</t>
-  </si>
-  <si>
-    <t>Tucha - Fixo 2026</t>
-  </si>
-  <si>
-    <t>Eric Kevin de Souza Serpa</t>
-  </si>
-  <si>
-    <t>19/08/26</t>
-  </si>
-  <si>
-    <t>Salário Fixo -Eric Serpa 2026</t>
-  </si>
-  <si>
-    <t>Fixo ago26/1</t>
-  </si>
-  <si>
-    <t>R$  225,31</t>
-  </si>
-  <si>
-    <t>Estorno empréstimo</t>
-  </si>
-  <si>
-    <t>SABRINA ALVES DE ABREU BRAUNBECK</t>
-  </si>
-  <si>
-    <t>R$  3.276,49</t>
-  </si>
-  <si>
-    <t>Sabrina Braunbeck - Pagamento 2026</t>
-  </si>
-  <si>
-    <t>Estorno empr ago26/1</t>
-  </si>
-  <si>
-    <t>R$  249,82</t>
-  </si>
-  <si>
-    <t>Danielle Martins da Silva</t>
-  </si>
-  <si>
-    <t>R$  2.090,00</t>
-  </si>
-  <si>
-    <t>Danielle - Pagamento 2026</t>
-  </si>
-  <si>
     <t>R$  2.219,85</t>
   </si>
   <si>
@@ -1849,21 +1864,6 @@
   </si>
   <si>
     <t>Felipe Domingos - salário fixo 2026</t>
-  </si>
-  <si>
-    <t>735/1</t>
-  </si>
-  <si>
-    <t>BIANCA RODRIGUES NASCIMENTO</t>
-  </si>
-  <si>
-    <t>Pemiação meta</t>
-  </si>
-  <si>
-    <t>R$  2.365,00</t>
-  </si>
-  <si>
-    <t>Carina - Pagamento 2026</t>
   </si>
   <si>
     <t>4.04.01.02.05 IRRF sobre salários</t>
@@ -2118,6 +2118,18 @@
     <t xml:space="preserve">04/08/2026	•••• •••• •••• 0005497380066700654	SUPERMERCADO	Compra à vista		105,06	PAO DE ACUCAR 2409     	Materiais limpeza e pao de queijo
 25/08/2026	•••• •••• •••• 0005497380066700654	SUPERMERCADO	Compra à vista		307,33	PAO DE ACUCAR 2409	Materiais limpeza 
 </t>
+  </si>
+  <si>
+    <t>736/1</t>
+  </si>
+  <si>
+    <t>Casa de Bolos de Moema LTDA</t>
+  </si>
+  <si>
+    <t>R$  97,00</t>
+  </si>
+  <si>
+    <t>Bolo Bianca</t>
   </si>
   <si>
     <t>745/1</t>
@@ -2145,18 +2157,6 @@
     <t>R$  5,95</t>
   </si>
   <si>
-    <t>736/1</t>
-  </si>
-  <si>
-    <t>Casa de Bolos de Moema LTDA</t>
-  </si>
-  <si>
-    <t>R$  97,00</t>
-  </si>
-  <si>
-    <t>Bolo Bianca</t>
-  </si>
-  <si>
     <t>4.04.02.07 Informática</t>
   </si>
   <si>
@@ -2217,6 +2217,51 @@
     <t>4.04.02.08.03 Mensalidades e assinaturas - outros gastos</t>
   </si>
   <si>
+    <t>70/12</t>
+  </si>
+  <si>
+    <t>R$  188,22</t>
+  </si>
+  <si>
+    <t>Promob 26/5</t>
+  </si>
+  <si>
+    <t>63/3</t>
+  </si>
+  <si>
+    <t>R$  376,38</t>
+  </si>
+  <si>
+    <t>11/06/26</t>
+  </si>
+  <si>
+    <t>Promob 2026/4</t>
+  </si>
+  <si>
+    <t>R$  599,00</t>
+  </si>
+  <si>
+    <t>Promob 2026</t>
+  </si>
+  <si>
+    <t>62/3</t>
+  </si>
+  <si>
+    <t>R$  293,11</t>
+  </si>
+  <si>
+    <t>Promob 2026/3</t>
+  </si>
+  <si>
+    <t>D4 sign</t>
+  </si>
+  <si>
+    <t>R$  49,95</t>
+  </si>
+  <si>
+    <t>D4 sign 2026</t>
+  </si>
+  <si>
     <t>3/7</t>
   </si>
   <si>
@@ -2229,34 +2274,16 @@
     <t>Promob 2026/2</t>
   </si>
   <si>
-    <t>D4 sign</t>
-  </si>
-  <si>
-    <t>R$  49,95</t>
-  </si>
-  <si>
-    <t>D4 sign 2026</t>
-  </si>
-  <si>
-    <t>63/3</t>
-  </si>
-  <si>
-    <t>R$  376,38</t>
-  </si>
-  <si>
-    <t>11/06/26</t>
-  </si>
-  <si>
-    <t>Promob 2026/4</t>
-  </si>
-  <si>
-    <t>70/12</t>
-  </si>
-  <si>
-    <t>R$  188,22</t>
-  </si>
-  <si>
-    <t>Promob 26/5</t>
+    <t>61/4</t>
+  </si>
+  <si>
+    <t>Pipefy</t>
+  </si>
+  <si>
+    <t>R$  98,71</t>
+  </si>
+  <si>
+    <t>21/05/26</t>
   </si>
   <si>
     <t>64/3</t>
@@ -2275,33 +2302,6 @@
   </si>
   <si>
     <t>ISO Implantação -Saude ocupacional</t>
-  </si>
-  <si>
-    <t>62/3</t>
-  </si>
-  <si>
-    <t>R$  293,11</t>
-  </si>
-  <si>
-    <t>Promob 2026/3</t>
-  </si>
-  <si>
-    <t>R$  599,00</t>
-  </si>
-  <si>
-    <t>Promob 2026</t>
-  </si>
-  <si>
-    <t>61/4</t>
-  </si>
-  <si>
-    <t>Pipefy</t>
-  </si>
-  <si>
-    <t>R$  98,71</t>
-  </si>
-  <si>
-    <t>21/05/26</t>
   </si>
   <si>
     <t>4.04.02.11 Manutenção de predio e equipamentos</t>
@@ -2413,6 +2413,15 @@
     <t>R$ 400,33</t>
   </si>
   <si>
+    <t>Jackson Fernando de Araujo</t>
+  </si>
+  <si>
+    <t>R$  150,00</t>
+  </si>
+  <si>
+    <t>Segurança 2026</t>
+  </si>
+  <si>
     <t>VERISURE</t>
   </si>
   <si>
@@ -2420,15 +2429,6 @@
   </si>
   <si>
     <t>Verisure - Alarme 2026</t>
-  </si>
-  <si>
-    <t>Jackson Fernando de Araujo</t>
-  </si>
-  <si>
-    <t>R$  150,00</t>
-  </si>
-  <si>
-    <t>Segurança 2026</t>
   </si>
   <si>
     <t>4.04.02.14.08 Site e newsletter da loja</t>
@@ -4893,10 +4893,10 @@
         <v>157</v>
       </c>
       <c r="K49" t="s">
-        <v>88</v>
+        <v>158</v>
       </c>
       <c r="L49" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M49" t="s">
         <v>147</v>
@@ -4931,7 +4931,7 @@
         <v>34</v>
       </c>
       <c r="E50" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F50" t="s">
         <v>63</v>
@@ -4940,16 +4940,16 @@
         <v>41</v>
       </c>
       <c r="H50" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I50" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J50" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="K50" t="s">
-        <v>163</v>
+        <v>88</v>
       </c>
       <c r="L50" t="s">
         <v>164</v>
@@ -4964,7 +4964,7 @@
         <v>153</v>
       </c>
       <c r="P50" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q50" t="s">
         <v>45</v>
@@ -5211,7 +5211,7 @@
         <v>33</v>
       </c>
       <c r="E55" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="F55" t="s">
         <v>173</v>
@@ -7242,7 +7242,7 @@
         <v>294</v>
       </c>
       <c r="J91" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="K91" t="s">
         <v>88</v>
@@ -13107,7 +13107,7 @@
         <v>33</v>
       </c>
       <c r="E196" t="s">
-        <v>314</v>
+        <v>346</v>
       </c>
       <c r="F196" t="s">
         <v>457</v>
@@ -13122,10 +13122,10 @@
         <v>458</v>
       </c>
       <c r="J196" t="s">
-        <v>118</v>
+        <v>60</v>
       </c>
       <c r="K196" t="s">
-        <v>118</v>
+        <v>60</v>
       </c>
       <c r="L196" t="s">
         <v>34</v>
@@ -13163,7 +13163,7 @@
         <v>34</v>
       </c>
       <c r="E197" t="s">
-        <v>459</v>
+        <v>218</v>
       </c>
       <c r="F197" t="s">
         <v>213</v>
@@ -13172,7 +13172,7 @@
         <v>41</v>
       </c>
       <c r="H197" t="s">
-        <v>421</v>
+        <v>459</v>
       </c>
       <c r="I197" t="s">
         <v>460</v>
@@ -13193,7 +13193,7 @@
         <v>45</v>
       </c>
       <c r="O197" t="s">
-        <v>461</v>
+        <v>374</v>
       </c>
       <c r="P197" t="s">
         <v>460</v>
@@ -13219,7 +13219,7 @@
         <v>34</v>
       </c>
       <c r="E198" t="s">
-        <v>462</v>
+        <v>242</v>
       </c>
       <c r="F198" t="s">
         <v>213</v>
@@ -13228,10 +13228,10 @@
         <v>41</v>
       </c>
       <c r="H198" t="s">
-        <v>391</v>
+        <v>461</v>
       </c>
       <c r="I198" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="J198" t="s">
         <v>368</v>
@@ -13249,10 +13249,10 @@
         <v>45</v>
       </c>
       <c r="O198" t="s">
-        <v>464</v>
+        <v>247</v>
       </c>
       <c r="P198" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="Q198" t="s">
         <v>45</v>
@@ -13275,7 +13275,7 @@
         <v>34</v>
       </c>
       <c r="E199" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="F199" t="s">
         <v>213</v>
@@ -13284,10 +13284,10 @@
         <v>41</v>
       </c>
       <c r="H199" t="s">
-        <v>391</v>
+        <v>461</v>
       </c>
       <c r="I199" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="J199" t="s">
         <v>368</v>
@@ -13305,10 +13305,10 @@
         <v>45</v>
       </c>
       <c r="O199" t="s">
-        <v>399</v>
+        <v>324</v>
       </c>
       <c r="P199" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="Q199" t="s">
         <v>45</v>
@@ -13331,25 +13331,25 @@
         <v>34</v>
       </c>
       <c r="E200" t="s">
-        <v>212</v>
+        <v>318</v>
       </c>
       <c r="F200" t="s">
-        <v>213</v>
+        <v>457</v>
       </c>
       <c r="G200" t="s">
         <v>41</v>
       </c>
       <c r="H200" t="s">
-        <v>466</v>
+        <v>391</v>
       </c>
       <c r="I200" t="s">
-        <v>467</v>
+        <v>386</v>
       </c>
       <c r="J200" t="s">
-        <v>368</v>
+        <v>130</v>
       </c>
       <c r="K200" t="s">
-        <v>55</v>
+        <v>130</v>
       </c>
       <c r="L200" t="s">
         <v>34</v>
@@ -13361,13 +13361,13 @@
         <v>45</v>
       </c>
       <c r="O200" t="s">
-        <v>324</v>
+        <v>34</v>
       </c>
       <c r="P200" t="s">
-        <v>467</v>
+        <v>34</v>
       </c>
       <c r="Q200" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="R200" t="s">
         <v>34</v>
@@ -13387,25 +13387,25 @@
         <v>34</v>
       </c>
       <c r="E201" t="s">
-        <v>468</v>
+        <v>314</v>
       </c>
       <c r="F201" t="s">
-        <v>213</v>
+        <v>457</v>
       </c>
       <c r="G201" t="s">
         <v>41</v>
       </c>
       <c r="H201" t="s">
-        <v>469</v>
+        <v>206</v>
       </c>
       <c r="I201" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="J201" t="s">
-        <v>368</v>
+        <v>118</v>
       </c>
       <c r="K201" t="s">
-        <v>55</v>
+        <v>118</v>
       </c>
       <c r="L201" t="s">
         <v>34</v>
@@ -13417,13 +13417,13 @@
         <v>45</v>
       </c>
       <c r="O201" t="s">
-        <v>471</v>
+        <v>34</v>
       </c>
       <c r="P201" t="s">
-        <v>470</v>
+        <v>34</v>
       </c>
       <c r="Q201" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="R201" t="s">
         <v>34</v>
@@ -13443,7 +13443,7 @@
         <v>34</v>
       </c>
       <c r="E202" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="F202" t="s">
         <v>213</v>
@@ -13452,10 +13452,10 @@
         <v>41</v>
       </c>
       <c r="H202" t="s">
-        <v>469</v>
+        <v>391</v>
       </c>
       <c r="I202" t="s">
-        <v>472</v>
+        <v>465</v>
       </c>
       <c r="J202" t="s">
         <v>368</v>
@@ -13473,10 +13473,10 @@
         <v>45</v>
       </c>
       <c r="O202" t="s">
-        <v>374</v>
+        <v>399</v>
       </c>
       <c r="P202" t="s">
-        <v>472</v>
+        <v>465</v>
       </c>
       <c r="Q202" t="s">
         <v>45</v>
@@ -13499,7 +13499,7 @@
         <v>34</v>
       </c>
       <c r="E203" t="s">
-        <v>221</v>
+        <v>466</v>
       </c>
       <c r="F203" t="s">
         <v>213</v>
@@ -13508,10 +13508,10 @@
         <v>41</v>
       </c>
       <c r="H203" t="s">
-        <v>469</v>
+        <v>391</v>
       </c>
       <c r="I203" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="J203" t="s">
         <v>368</v>
@@ -13529,10 +13529,10 @@
         <v>45</v>
       </c>
       <c r="O203" t="s">
-        <v>327</v>
+        <v>468</v>
       </c>
       <c r="P203" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="Q203" t="s">
         <v>45</v>
@@ -13555,7 +13555,7 @@
         <v>34</v>
       </c>
       <c r="E204" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="F204" t="s">
         <v>213</v>
@@ -13564,10 +13564,10 @@
         <v>41</v>
       </c>
       <c r="H204" t="s">
-        <v>469</v>
+        <v>461</v>
       </c>
       <c r="I204" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="J204" t="s">
         <v>368</v>
@@ -13585,10 +13585,10 @@
         <v>45</v>
       </c>
       <c r="O204" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="P204" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="Q204" t="s">
         <v>45</v>
@@ -13611,7 +13611,7 @@
         <v>34</v>
       </c>
       <c r="E205" t="s">
-        <v>310</v>
+        <v>472</v>
       </c>
       <c r="F205" t="s">
         <v>457</v>
@@ -13623,13 +13623,13 @@
         <v>206</v>
       </c>
       <c r="I205" t="s">
-        <v>383</v>
+        <v>401</v>
       </c>
       <c r="J205" t="s">
-        <v>130</v>
+        <v>44</v>
       </c>
       <c r="K205" t="s">
-        <v>130</v>
+        <v>44</v>
       </c>
       <c r="L205" t="s">
         <v>34</v>
@@ -13723,25 +13723,25 @@
         <v>34</v>
       </c>
       <c r="E207" t="s">
-        <v>477</v>
+        <v>221</v>
       </c>
       <c r="F207" t="s">
-        <v>457</v>
+        <v>213</v>
       </c>
       <c r="G207" t="s">
         <v>41</v>
       </c>
       <c r="H207" t="s">
-        <v>206</v>
+        <v>459</v>
       </c>
       <c r="I207" t="s">
-        <v>401</v>
+        <v>473</v>
       </c>
       <c r="J207" t="s">
-        <v>44</v>
+        <v>368</v>
       </c>
       <c r="K207" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="L207" t="s">
         <v>34</v>
@@ -13753,13 +13753,13 @@
         <v>45</v>
       </c>
       <c r="O207" t="s">
-        <v>34</v>
+        <v>327</v>
       </c>
       <c r="P207" t="s">
-        <v>34</v>
+        <v>473</v>
       </c>
       <c r="Q207" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R207" t="s">
         <v>34</v>
@@ -13779,25 +13779,25 @@
         <v>34</v>
       </c>
       <c r="E208" t="s">
-        <v>338</v>
+        <v>474</v>
       </c>
       <c r="F208" t="s">
-        <v>457</v>
+        <v>213</v>
       </c>
       <c r="G208" t="s">
         <v>41</v>
       </c>
       <c r="H208" t="s">
-        <v>421</v>
+        <v>459</v>
       </c>
       <c r="I208" t="s">
-        <v>379</v>
+        <v>475</v>
       </c>
       <c r="J208" t="s">
-        <v>108</v>
+        <v>368</v>
       </c>
       <c r="K208" t="s">
-        <v>108</v>
+        <v>55</v>
       </c>
       <c r="L208" t="s">
         <v>34</v>
@@ -13809,13 +13809,13 @@
         <v>45</v>
       </c>
       <c r="O208" t="s">
-        <v>34</v>
+        <v>476</v>
       </c>
       <c r="P208" t="s">
-        <v>34</v>
+        <v>475</v>
       </c>
       <c r="Q208" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R208" t="s">
         <v>34</v>
@@ -13835,25 +13835,25 @@
         <v>34</v>
       </c>
       <c r="E209" t="s">
-        <v>445</v>
+        <v>223</v>
       </c>
       <c r="F209" t="s">
-        <v>213</v>
+        <v>457</v>
       </c>
       <c r="G209" t="s">
         <v>41</v>
       </c>
       <c r="H209" t="s">
-        <v>391</v>
+        <v>206</v>
       </c>
       <c r="I209" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="J209" t="s">
-        <v>368</v>
+        <v>60</v>
       </c>
       <c r="K209" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="L209" t="s">
         <v>34</v>
@@ -13865,13 +13865,13 @@
         <v>45</v>
       </c>
       <c r="O209" t="s">
-        <v>447</v>
+        <v>34</v>
       </c>
       <c r="P209" t="s">
-        <v>478</v>
+        <v>34</v>
       </c>
       <c r="Q209" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="R209" t="s">
         <v>34</v>
@@ -13891,7 +13891,7 @@
         <v>34</v>
       </c>
       <c r="E210" t="s">
-        <v>253</v>
+        <v>478</v>
       </c>
       <c r="F210" t="s">
         <v>213</v>
@@ -13900,7 +13900,7 @@
         <v>41</v>
       </c>
       <c r="H210" t="s">
-        <v>391</v>
+        <v>421</v>
       </c>
       <c r="I210" t="s">
         <v>479</v>
@@ -13921,7 +13921,7 @@
         <v>45</v>
       </c>
       <c r="O210" t="s">
-        <v>89</v>
+        <v>480</v>
       </c>
       <c r="P210" t="s">
         <v>479</v>
@@ -13947,25 +13947,25 @@
         <v>34</v>
       </c>
       <c r="E211" t="s">
-        <v>204</v>
+        <v>338</v>
       </c>
       <c r="F211" t="s">
-        <v>213</v>
+        <v>457</v>
       </c>
       <c r="G211" t="s">
         <v>41</v>
       </c>
       <c r="H211" t="s">
-        <v>391</v>
+        <v>421</v>
       </c>
       <c r="I211" t="s">
-        <v>480</v>
+        <v>379</v>
       </c>
       <c r="J211" t="s">
-        <v>368</v>
+        <v>108</v>
       </c>
       <c r="K211" t="s">
-        <v>55</v>
+        <v>108</v>
       </c>
       <c r="L211" t="s">
         <v>34</v>
@@ -13977,13 +13977,13 @@
         <v>45</v>
       </c>
       <c r="O211" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="P211" t="s">
-        <v>480</v>
+        <v>34</v>
       </c>
       <c r="Q211" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="R211" t="s">
         <v>34</v>
@@ -14003,25 +14003,25 @@
         <v>34</v>
       </c>
       <c r="E212" t="s">
-        <v>481</v>
+        <v>357</v>
       </c>
       <c r="F212" t="s">
-        <v>213</v>
+        <v>457</v>
       </c>
       <c r="G212" t="s">
         <v>41</v>
       </c>
       <c r="H212" t="s">
-        <v>469</v>
+        <v>206</v>
       </c>
       <c r="I212" t="s">
-        <v>482</v>
+        <v>370</v>
       </c>
       <c r="J212" t="s">
-        <v>368</v>
+        <v>60</v>
       </c>
       <c r="K212" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="L212" t="s">
         <v>34</v>
@@ -14033,13 +14033,13 @@
         <v>45</v>
       </c>
       <c r="O212" t="s">
-        <v>483</v>
+        <v>34</v>
       </c>
       <c r="P212" t="s">
-        <v>482</v>
+        <v>34</v>
       </c>
       <c r="Q212" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="R212" t="s">
         <v>34</v>
@@ -14059,7 +14059,7 @@
         <v>34</v>
       </c>
       <c r="E213" t="s">
-        <v>242</v>
+        <v>204</v>
       </c>
       <c r="F213" t="s">
         <v>213</v>
@@ -14068,10 +14068,10 @@
         <v>41</v>
       </c>
       <c r="H213" t="s">
-        <v>466</v>
+        <v>391</v>
       </c>
       <c r="I213" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="J213" t="s">
         <v>368</v>
@@ -14089,10 +14089,10 @@
         <v>45</v>
       </c>
       <c r="O213" t="s">
-        <v>247</v>
+        <v>51</v>
       </c>
       <c r="P213" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="Q213" t="s">
         <v>45</v>
@@ -14115,7 +14115,7 @@
         <v>34</v>
       </c>
       <c r="E214" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="F214" t="s">
         <v>213</v>
@@ -14124,10 +14124,10 @@
         <v>41</v>
       </c>
       <c r="H214" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
       <c r="I214" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="J214" t="s">
         <v>368</v>
@@ -14145,10 +14145,10 @@
         <v>45</v>
       </c>
       <c r="O214" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="P214" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="Q214" t="s">
         <v>45</v>
@@ -14171,7 +14171,7 @@
         <v>34</v>
       </c>
       <c r="E215" t="s">
-        <v>346</v>
+        <v>310</v>
       </c>
       <c r="F215" t="s">
         <v>457</v>
@@ -14183,13 +14183,13 @@
         <v>206</v>
       </c>
       <c r="I215" t="s">
-        <v>488</v>
+        <v>383</v>
       </c>
       <c r="J215" t="s">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="K215" t="s">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="L215" t="s">
         <v>34</v>
@@ -14227,25 +14227,25 @@
         <v>34</v>
       </c>
       <c r="E216" t="s">
-        <v>223</v>
+        <v>253</v>
       </c>
       <c r="F216" t="s">
-        <v>457</v>
+        <v>213</v>
       </c>
       <c r="G216" t="s">
         <v>41</v>
       </c>
       <c r="H216" t="s">
-        <v>206</v>
+        <v>391</v>
       </c>
       <c r="I216" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="J216" t="s">
-        <v>60</v>
+        <v>368</v>
       </c>
       <c r="K216" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="L216" t="s">
         <v>34</v>
@@ -14257,13 +14257,13 @@
         <v>45</v>
       </c>
       <c r="O216" t="s">
-        <v>34</v>
+        <v>89</v>
       </c>
       <c r="P216" t="s">
-        <v>34</v>
+        <v>485</v>
       </c>
       <c r="Q216" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R216" t="s">
         <v>34</v>
@@ -14283,25 +14283,25 @@
         <v>34</v>
       </c>
       <c r="E217" t="s">
-        <v>357</v>
+        <v>445</v>
       </c>
       <c r="F217" t="s">
-        <v>457</v>
+        <v>213</v>
       </c>
       <c r="G217" t="s">
         <v>41</v>
       </c>
       <c r="H217" t="s">
-        <v>206</v>
+        <v>391</v>
       </c>
       <c r="I217" t="s">
-        <v>370</v>
+        <v>486</v>
       </c>
       <c r="J217" t="s">
-        <v>60</v>
+        <v>368</v>
       </c>
       <c r="K217" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="L217" t="s">
         <v>34</v>
@@ -14313,13 +14313,13 @@
         <v>45</v>
       </c>
       <c r="O217" t="s">
-        <v>34</v>
+        <v>447</v>
       </c>
       <c r="P217" t="s">
-        <v>34</v>
+        <v>486</v>
       </c>
       <c r="Q217" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R217" t="s">
         <v>34</v>
@@ -14339,25 +14339,25 @@
         <v>34</v>
       </c>
       <c r="E218" t="s">
-        <v>318</v>
+        <v>487</v>
       </c>
       <c r="F218" t="s">
-        <v>457</v>
+        <v>213</v>
       </c>
       <c r="G218" t="s">
         <v>41</v>
       </c>
       <c r="H218" t="s">
-        <v>391</v>
+        <v>459</v>
       </c>
       <c r="I218" t="s">
-        <v>386</v>
+        <v>488</v>
       </c>
       <c r="J218" t="s">
-        <v>130</v>
+        <v>368</v>
       </c>
       <c r="K218" t="s">
-        <v>130</v>
+        <v>55</v>
       </c>
       <c r="L218" t="s">
         <v>34</v>
@@ -14369,13 +14369,13 @@
         <v>45</v>
       </c>
       <c r="O218" t="s">
-        <v>34</v>
+        <v>489</v>
       </c>
       <c r="P218" t="s">
-        <v>34</v>
+        <v>488</v>
       </c>
       <c r="Q218" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R218" t="s">
         <v>34</v>
@@ -15627,25 +15627,25 @@
         <v>33</v>
       </c>
       <c r="E241" t="s">
-        <v>221</v>
+        <v>240</v>
       </c>
       <c r="F241" t="s">
-        <v>173</v>
+        <v>525</v>
       </c>
       <c r="G241" t="s">
         <v>41</v>
       </c>
       <c r="H241" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="I241" t="s">
         <v>200</v>
       </c>
       <c r="J241" t="s">
-        <v>67</v>
+        <v>118</v>
       </c>
       <c r="K241" t="s">
-        <v>67</v>
+        <v>118</v>
       </c>
       <c r="L241" t="s">
         <v>34</v>
@@ -15657,13 +15657,13 @@
         <v>45</v>
       </c>
       <c r="O241" t="s">
-        <v>327</v>
+        <v>34</v>
       </c>
       <c r="P241" t="s">
-        <v>200</v>
+        <v>34</v>
       </c>
       <c r="Q241" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="R241" t="s">
         <v>34</v>
@@ -15683,25 +15683,25 @@
         <v>34</v>
       </c>
       <c r="E242" t="s">
-        <v>240</v>
+        <v>218</v>
       </c>
       <c r="F242" t="s">
+        <v>173</v>
+      </c>
+      <c r="G242" t="s">
+        <v>41</v>
+      </c>
+      <c r="H242" t="s">
         <v>526</v>
-      </c>
-      <c r="G242" t="s">
-        <v>41</v>
-      </c>
-      <c r="H242" t="s">
-        <v>525</v>
       </c>
       <c r="I242" t="s">
         <v>200</v>
       </c>
       <c r="J242" t="s">
-        <v>118</v>
+        <v>67</v>
       </c>
       <c r="K242" t="s">
-        <v>118</v>
+        <v>67</v>
       </c>
       <c r="L242" t="s">
         <v>34</v>
@@ -15713,13 +15713,13 @@
         <v>45</v>
       </c>
       <c r="O242" t="s">
-        <v>34</v>
+        <v>247</v>
       </c>
       <c r="P242" t="s">
-        <v>34</v>
+        <v>200</v>
       </c>
       <c r="Q242" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R242" t="s">
         <v>34</v>
@@ -15739,25 +15739,25 @@
         <v>34</v>
       </c>
       <c r="E243" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="F243" t="s">
-        <v>173</v>
+        <v>525</v>
       </c>
       <c r="G243" t="s">
         <v>41</v>
       </c>
       <c r="H243" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="I243" t="s">
         <v>200</v>
       </c>
       <c r="J243" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="K243" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="L243" t="s">
         <v>34</v>
@@ -15769,13 +15769,13 @@
         <v>45</v>
       </c>
       <c r="O243" t="s">
-        <v>247</v>
+        <v>34</v>
       </c>
       <c r="P243" t="s">
-        <v>200</v>
+        <v>34</v>
       </c>
       <c r="Q243" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="R243" t="s">
         <v>34</v>
@@ -15795,7 +15795,7 @@
         <v>34</v>
       </c>
       <c r="E244" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="F244" t="s">
         <v>173</v>
@@ -15804,16 +15804,16 @@
         <v>41</v>
       </c>
       <c r="H244" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="I244" t="s">
         <v>200</v>
       </c>
       <c r="J244" t="s">
-        <v>130</v>
+        <v>60</v>
       </c>
       <c r="K244" t="s">
-        <v>130</v>
+        <v>60</v>
       </c>
       <c r="L244" t="s">
         <v>34</v>
@@ -15825,7 +15825,7 @@
         <v>45</v>
       </c>
       <c r="O244" t="s">
-        <v>137</v>
+        <v>61</v>
       </c>
       <c r="P244" t="s">
         <v>200</v>
@@ -15851,7 +15851,7 @@
         <v>34</v>
       </c>
       <c r="E245" t="s">
-        <v>210</v>
+        <v>253</v>
       </c>
       <c r="F245" t="s">
         <v>173</v>
@@ -15860,16 +15860,16 @@
         <v>41</v>
       </c>
       <c r="H245" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="I245" t="s">
         <v>200</v>
       </c>
       <c r="J245" t="s">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="K245" t="s">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="L245" t="s">
         <v>34</v>
@@ -15881,7 +15881,7 @@
         <v>45</v>
       </c>
       <c r="O245" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="P245" t="s">
         <v>200</v>
@@ -15907,25 +15907,25 @@
         <v>34</v>
       </c>
       <c r="E246" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="F246" t="s">
-        <v>173</v>
+        <v>525</v>
       </c>
       <c r="G246" t="s">
         <v>41</v>
       </c>
       <c r="H246" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="I246" t="s">
         <v>200</v>
       </c>
       <c r="J246" t="s">
-        <v>108</v>
+        <v>130</v>
       </c>
       <c r="K246" t="s">
-        <v>108</v>
+        <v>130</v>
       </c>
       <c r="L246" t="s">
         <v>34</v>
@@ -15937,13 +15937,13 @@
         <v>45</v>
       </c>
       <c r="O246" t="s">
-        <v>380</v>
+        <v>34</v>
       </c>
       <c r="P246" t="s">
-        <v>200</v>
+        <v>34</v>
       </c>
       <c r="Q246" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="R246" t="s">
         <v>34</v>
@@ -15963,7 +15963,7 @@
         <v>34</v>
       </c>
       <c r="E247" t="s">
-        <v>242</v>
+        <v>212</v>
       </c>
       <c r="F247" t="s">
         <v>173</v>
@@ -15972,16 +15972,16 @@
         <v>41</v>
       </c>
       <c r="H247" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="I247" t="s">
-        <v>527</v>
+        <v>200</v>
       </c>
       <c r="J247" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="K247" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="L247" t="s">
         <v>34</v>
@@ -15993,10 +15993,10 @@
         <v>45</v>
       </c>
       <c r="O247" t="s">
-        <v>247</v>
+        <v>324</v>
       </c>
       <c r="P247" t="s">
-        <v>527</v>
+        <v>200</v>
       </c>
       <c r="Q247" t="s">
         <v>45</v>
@@ -16019,25 +16019,25 @@
         <v>34</v>
       </c>
       <c r="E248" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="F248" t="s">
+        <v>525</v>
+      </c>
+      <c r="G248" t="s">
+        <v>41</v>
+      </c>
+      <c r="H248" t="s">
         <v>526</v>
-      </c>
-      <c r="G248" t="s">
-        <v>41</v>
-      </c>
-      <c r="H248" t="s">
-        <v>525</v>
       </c>
       <c r="I248" t="s">
         <v>200</v>
       </c>
       <c r="J248" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="K248" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="L248" t="s">
         <v>34</v>
@@ -16075,25 +16075,25 @@
         <v>34</v>
       </c>
       <c r="E249" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F249" t="s">
-        <v>173</v>
+        <v>525</v>
       </c>
       <c r="G249" t="s">
         <v>41</v>
       </c>
       <c r="H249" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="I249" t="s">
         <v>200</v>
       </c>
       <c r="J249" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="K249" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="L249" t="s">
         <v>34</v>
@@ -16105,13 +16105,13 @@
         <v>45</v>
       </c>
       <c r="O249" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="P249" t="s">
-        <v>200</v>
+        <v>34</v>
       </c>
       <c r="Q249" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="R249" t="s">
         <v>34</v>
@@ -16131,25 +16131,25 @@
         <v>34</v>
       </c>
       <c r="E250" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="F250" t="s">
+        <v>173</v>
+      </c>
+      <c r="G250" t="s">
+        <v>41</v>
+      </c>
+      <c r="H250" t="s">
         <v>526</v>
-      </c>
-      <c r="G250" t="s">
-        <v>41</v>
-      </c>
-      <c r="H250" t="s">
-        <v>525</v>
       </c>
       <c r="I250" t="s">
         <v>200</v>
       </c>
       <c r="J250" t="s">
-        <v>130</v>
+        <v>108</v>
       </c>
       <c r="K250" t="s">
-        <v>130</v>
+        <v>108</v>
       </c>
       <c r="L250" t="s">
         <v>34</v>
@@ -16161,13 +16161,13 @@
         <v>45</v>
       </c>
       <c r="O250" t="s">
-        <v>34</v>
+        <v>380</v>
       </c>
       <c r="P250" t="s">
-        <v>34</v>
+        <v>200</v>
       </c>
       <c r="Q250" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R250" t="s">
         <v>34</v>
@@ -16187,25 +16187,25 @@
         <v>34</v>
       </c>
       <c r="E251" t="s">
-        <v>253</v>
+        <v>227</v>
       </c>
       <c r="F251" t="s">
-        <v>173</v>
+        <v>525</v>
       </c>
       <c r="G251" t="s">
         <v>41</v>
       </c>
       <c r="H251" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="I251" t="s">
         <v>200</v>
       </c>
       <c r="J251" t="s">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="K251" t="s">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="L251" t="s">
         <v>34</v>
@@ -16217,13 +16217,13 @@
         <v>45</v>
       </c>
       <c r="O251" t="s">
-        <v>89</v>
+        <v>34</v>
       </c>
       <c r="P251" t="s">
-        <v>200</v>
+        <v>34</v>
       </c>
       <c r="Q251" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="R251" t="s">
         <v>34</v>
@@ -16243,7 +16243,7 @@
         <v>34</v>
       </c>
       <c r="E252" t="s">
-        <v>212</v>
+        <v>242</v>
       </c>
       <c r="F252" t="s">
         <v>173</v>
@@ -16252,16 +16252,16 @@
         <v>41</v>
       </c>
       <c r="H252" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="I252" t="s">
-        <v>200</v>
+        <v>527</v>
       </c>
       <c r="J252" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="K252" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="L252" t="s">
         <v>34</v>
@@ -16273,10 +16273,10 @@
         <v>45</v>
       </c>
       <c r="O252" t="s">
-        <v>324</v>
+        <v>247</v>
       </c>
       <c r="P252" t="s">
-        <v>200</v>
+        <v>527</v>
       </c>
       <c r="Q252" t="s">
         <v>45</v>
@@ -16299,25 +16299,25 @@
         <v>34</v>
       </c>
       <c r="E253" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="F253" t="s">
+        <v>173</v>
+      </c>
+      <c r="G253" t="s">
+        <v>41</v>
+      </c>
+      <c r="H253" t="s">
         <v>526</v>
-      </c>
-      <c r="G253" t="s">
-        <v>41</v>
-      </c>
-      <c r="H253" t="s">
-        <v>525</v>
       </c>
       <c r="I253" t="s">
         <v>200</v>
       </c>
       <c r="J253" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="K253" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="L253" t="s">
         <v>34</v>
@@ -16329,13 +16329,13 @@
         <v>45</v>
       </c>
       <c r="O253" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="P253" t="s">
-        <v>34</v>
+        <v>200</v>
       </c>
       <c r="Q253" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R253" t="s">
         <v>34</v>
@@ -16355,25 +16355,25 @@
         <v>34</v>
       </c>
       <c r="E254" t="s">
-        <v>223</v>
+        <v>204</v>
       </c>
       <c r="F254" t="s">
+        <v>525</v>
+      </c>
+      <c r="G254" t="s">
+        <v>41</v>
+      </c>
+      <c r="H254" t="s">
         <v>526</v>
-      </c>
-      <c r="G254" t="s">
-        <v>41</v>
-      </c>
-      <c r="H254" t="s">
-        <v>525</v>
       </c>
       <c r="I254" t="s">
         <v>200</v>
       </c>
       <c r="J254" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="K254" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="L254" t="s">
         <v>34</v>
@@ -16411,25 +16411,25 @@
         <v>34</v>
       </c>
       <c r="E255" t="s">
-        <v>204</v>
+        <v>230</v>
       </c>
       <c r="F255" t="s">
+        <v>173</v>
+      </c>
+      <c r="G255" t="s">
+        <v>41</v>
+      </c>
+      <c r="H255" t="s">
         <v>526</v>
-      </c>
-      <c r="G255" t="s">
-        <v>41</v>
-      </c>
-      <c r="H255" t="s">
-        <v>525</v>
       </c>
       <c r="I255" t="s">
         <v>200</v>
       </c>
       <c r="J255" t="s">
-        <v>50</v>
+        <v>130</v>
       </c>
       <c r="K255" t="s">
-        <v>50</v>
+        <v>130</v>
       </c>
       <c r="L255" t="s">
         <v>34</v>
@@ -16441,13 +16441,13 @@
         <v>45</v>
       </c>
       <c r="O255" t="s">
-        <v>34</v>
+        <v>137</v>
       </c>
       <c r="P255" t="s">
-        <v>34</v>
+        <v>200</v>
       </c>
       <c r="Q255" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R255" t="s">
         <v>34</v>
@@ -16467,25 +16467,25 @@
         <v>34</v>
       </c>
       <c r="E256" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="F256" t="s">
+        <v>173</v>
+      </c>
+      <c r="G256" t="s">
+        <v>41</v>
+      </c>
+      <c r="H256" t="s">
         <v>526</v>
-      </c>
-      <c r="G256" t="s">
-        <v>41</v>
-      </c>
-      <c r="H256" t="s">
-        <v>525</v>
       </c>
       <c r="I256" t="s">
         <v>200</v>
       </c>
       <c r="J256" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="K256" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="L256" t="s">
         <v>34</v>
@@ -16497,13 +16497,13 @@
         <v>45</v>
       </c>
       <c r="O256" t="s">
-        <v>34</v>
+        <v>327</v>
       </c>
       <c r="P256" t="s">
-        <v>34</v>
+        <v>200</v>
       </c>
       <c r="Q256" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R256" t="s">
         <v>34</v>
@@ -16747,7 +16747,7 @@
         <v>33</v>
       </c>
       <c r="E261" t="s">
-        <v>545</v>
+        <v>154</v>
       </c>
       <c r="F261" t="s">
         <v>173</v>
@@ -16756,19 +16756,19 @@
         <v>41</v>
       </c>
       <c r="H261" t="s">
+        <v>545</v>
+      </c>
+      <c r="I261" t="s">
         <v>546</v>
       </c>
-      <c r="I261" t="s">
+      <c r="J261" t="s">
         <v>547</v>
       </c>
-      <c r="J261" t="s">
+      <c r="K261" t="s">
+        <v>158</v>
+      </c>
+      <c r="L261" t="s">
         <v>548</v>
-      </c>
-      <c r="K261" t="s">
-        <v>81</v>
-      </c>
-      <c r="L261" t="s">
-        <v>549</v>
       </c>
       <c r="M261" t="s">
         <v>543</v>
@@ -16780,7 +16780,7 @@
         <v>153</v>
       </c>
       <c r="P261" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="Q261" t="s">
         <v>45</v>
@@ -16803,7 +16803,7 @@
         <v>34</v>
       </c>
       <c r="E262" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="F262" t="s">
         <v>173</v>
@@ -16859,7 +16859,7 @@
         <v>34</v>
       </c>
       <c r="E263" t="s">
-        <v>159</v>
+        <v>549</v>
       </c>
       <c r="F263" t="s">
         <v>173</v>
@@ -16877,7 +16877,7 @@
         <v>555</v>
       </c>
       <c r="K263" t="s">
-        <v>163</v>
+        <v>81</v>
       </c>
       <c r="L263" t="s">
         <v>556</v>
@@ -17139,7 +17139,7 @@
         <v>33</v>
       </c>
       <c r="E268" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="F268" t="s">
         <v>173</v>
@@ -17154,7 +17154,7 @@
         <v>569</v>
       </c>
       <c r="J268" t="s">
-        <v>548</v>
+        <v>555</v>
       </c>
       <c r="K268" t="s">
         <v>266</v>
@@ -17307,7 +17307,7 @@
         <v>33</v>
       </c>
       <c r="E271" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="F271" t="s">
         <v>173</v>
@@ -17322,7 +17322,7 @@
         <v>577</v>
       </c>
       <c r="J271" t="s">
-        <v>548</v>
+        <v>555</v>
       </c>
       <c r="K271" t="s">
         <v>266</v>
@@ -17363,7 +17363,7 @@
         <v>34</v>
       </c>
       <c r="E272" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="F272" t="s">
         <v>173</v>
@@ -17372,19 +17372,19 @@
         <v>41</v>
       </c>
       <c r="H272" t="s">
-        <v>391</v>
+        <v>579</v>
       </c>
       <c r="I272" t="s">
-        <v>569</v>
+        <v>580</v>
       </c>
       <c r="J272" t="s">
-        <v>265</v>
+        <v>555</v>
       </c>
       <c r="K272" t="s">
         <v>266</v>
       </c>
       <c r="L272" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="M272" t="s">
         <v>575</v>
@@ -17396,7 +17396,7 @@
         <v>153</v>
       </c>
       <c r="P272" t="s">
-        <v>569</v>
+        <v>580</v>
       </c>
       <c r="Q272" t="s">
         <v>45</v>
@@ -17419,7 +17419,7 @@
         <v>34</v>
       </c>
       <c r="E273" t="s">
-        <v>159</v>
+        <v>549</v>
       </c>
       <c r="F273" t="s">
         <v>173</v>
@@ -17428,13 +17428,13 @@
         <v>41</v>
       </c>
       <c r="H273" t="s">
-        <v>466</v>
+        <v>391</v>
       </c>
       <c r="I273" t="s">
-        <v>580</v>
+        <v>569</v>
       </c>
       <c r="J273" t="s">
-        <v>581</v>
+        <v>265</v>
       </c>
       <c r="K273" t="s">
         <v>266</v>
@@ -17452,7 +17452,7 @@
         <v>153</v>
       </c>
       <c r="P273" t="s">
-        <v>580</v>
+        <v>569</v>
       </c>
       <c r="Q273" t="s">
         <v>45</v>
@@ -17475,7 +17475,7 @@
         <v>34</v>
       </c>
       <c r="E274" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="F274" t="s">
         <v>173</v>
@@ -17531,25 +17531,25 @@
         <v>34</v>
       </c>
       <c r="E275" t="s">
-        <v>545</v>
+        <v>586</v>
       </c>
       <c r="F275" t="s">
-        <v>173</v>
+        <v>198</v>
       </c>
       <c r="G275" t="s">
         <v>41</v>
       </c>
       <c r="H275" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="I275" t="s">
-        <v>587</v>
+        <v>569</v>
       </c>
       <c r="J275" t="s">
-        <v>548</v>
+        <v>121</v>
       </c>
       <c r="K275" t="s">
-        <v>266</v>
+        <v>146</v>
       </c>
       <c r="L275" t="s">
         <v>588</v>
@@ -17564,7 +17564,7 @@
         <v>153</v>
       </c>
       <c r="P275" t="s">
-        <v>587</v>
+        <v>569</v>
       </c>
       <c r="Q275" t="s">
         <v>45</v>
@@ -17587,28 +17587,28 @@
         <v>34</v>
       </c>
       <c r="E276" t="s">
+        <v>549</v>
+      </c>
+      <c r="F276" t="s">
+        <v>173</v>
+      </c>
+      <c r="G276" t="s">
+        <v>41</v>
+      </c>
+      <c r="H276" t="s">
         <v>589</v>
       </c>
-      <c r="F276" t="s">
-        <v>198</v>
-      </c>
-      <c r="G276" t="s">
-        <v>41</v>
-      </c>
-      <c r="H276" t="s">
-        <v>469</v>
-      </c>
       <c r="I276" t="s">
-        <v>569</v>
+        <v>590</v>
       </c>
       <c r="J276" t="s">
-        <v>368</v>
+        <v>555</v>
       </c>
       <c r="K276" t="s">
-        <v>188</v>
+        <v>266</v>
       </c>
       <c r="L276" t="s">
-        <v>34</v>
+        <v>591</v>
       </c>
       <c r="M276" t="s">
         <v>575</v>
@@ -17620,7 +17620,7 @@
         <v>153</v>
       </c>
       <c r="P276" t="s">
-        <v>569</v>
+        <v>590</v>
       </c>
       <c r="Q276" t="s">
         <v>45</v>
@@ -17643,7 +17643,7 @@
         <v>34</v>
       </c>
       <c r="E277" t="s">
-        <v>545</v>
+        <v>154</v>
       </c>
       <c r="F277" t="s">
         <v>173</v>
@@ -17652,19 +17652,19 @@
         <v>41</v>
       </c>
       <c r="H277" t="s">
-        <v>590</v>
+        <v>461</v>
       </c>
       <c r="I277" t="s">
-        <v>569</v>
+        <v>592</v>
       </c>
       <c r="J277" t="s">
-        <v>548</v>
+        <v>593</v>
       </c>
       <c r="K277" t="s">
         <v>266</v>
       </c>
       <c r="L277" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="M277" t="s">
         <v>575</v>
@@ -17676,7 +17676,7 @@
         <v>153</v>
       </c>
       <c r="P277" t="s">
-        <v>569</v>
+        <v>592</v>
       </c>
       <c r="Q277" t="s">
         <v>45</v>
@@ -17699,28 +17699,28 @@
         <v>34</v>
       </c>
       <c r="E278" t="s">
-        <v>159</v>
+        <v>595</v>
       </c>
       <c r="F278" t="s">
-        <v>173</v>
+        <v>198</v>
       </c>
       <c r="G278" t="s">
         <v>41</v>
       </c>
       <c r="H278" t="s">
-        <v>592</v>
+        <v>366</v>
       </c>
       <c r="I278" t="s">
-        <v>583</v>
+        <v>596</v>
       </c>
       <c r="J278" t="s">
-        <v>584</v>
+        <v>55</v>
       </c>
       <c r="K278" t="s">
-        <v>593</v>
+        <v>55</v>
       </c>
       <c r="L278" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="M278" t="s">
         <v>575</v>
@@ -17732,7 +17732,7 @@
         <v>153</v>
       </c>
       <c r="P278" t="s">
-        <v>583</v>
+        <v>596</v>
       </c>
       <c r="Q278" t="s">
         <v>45</v>
@@ -17755,28 +17755,28 @@
         <v>34</v>
       </c>
       <c r="E279" t="s">
-        <v>595</v>
+        <v>549</v>
       </c>
       <c r="F279" t="s">
-        <v>198</v>
+        <v>173</v>
       </c>
       <c r="G279" t="s">
         <v>41</v>
       </c>
       <c r="H279" t="s">
-        <v>366</v>
+        <v>442</v>
       </c>
       <c r="I279" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="J279" t="s">
-        <v>55</v>
+        <v>555</v>
       </c>
       <c r="K279" t="s">
-        <v>55</v>
+        <v>266</v>
       </c>
       <c r="L279" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="M279" t="s">
         <v>575</v>
@@ -17788,7 +17788,7 @@
         <v>153</v>
       </c>
       <c r="P279" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="Q279" t="s">
         <v>45</v>
@@ -17811,28 +17811,28 @@
         <v>34</v>
       </c>
       <c r="E280" t="s">
-        <v>545</v>
+        <v>600</v>
       </c>
       <c r="F280" t="s">
-        <v>173</v>
+        <v>198</v>
       </c>
       <c r="G280" t="s">
         <v>41</v>
       </c>
       <c r="H280" t="s">
-        <v>598</v>
+        <v>459</v>
       </c>
       <c r="I280" t="s">
-        <v>599</v>
+        <v>569</v>
       </c>
       <c r="J280" t="s">
-        <v>548</v>
+        <v>368</v>
       </c>
       <c r="K280" t="s">
-        <v>266</v>
+        <v>188</v>
       </c>
       <c r="L280" t="s">
-        <v>600</v>
+        <v>34</v>
       </c>
       <c r="M280" t="s">
         <v>575</v>
@@ -17844,7 +17844,7 @@
         <v>153</v>
       </c>
       <c r="P280" t="s">
-        <v>599</v>
+        <v>569</v>
       </c>
       <c r="Q280" t="s">
         <v>45</v>
@@ -17867,28 +17867,28 @@
         <v>34</v>
       </c>
       <c r="E281" t="s">
+        <v>154</v>
+      </c>
+      <c r="F281" t="s">
+        <v>173</v>
+      </c>
+      <c r="G281" t="s">
+        <v>41</v>
+      </c>
+      <c r="H281" t="s">
         <v>601</v>
       </c>
-      <c r="F281" t="s">
-        <v>198</v>
-      </c>
-      <c r="G281" t="s">
-        <v>41</v>
-      </c>
-      <c r="H281" t="s">
-        <v>512</v>
-      </c>
       <c r="I281" t="s">
+        <v>583</v>
+      </c>
+      <c r="J281" t="s">
+        <v>584</v>
+      </c>
+      <c r="K281" t="s">
         <v>602</v>
       </c>
-      <c r="J281" t="s">
-        <v>66</v>
-      </c>
-      <c r="K281" t="s">
-        <v>66</v>
-      </c>
       <c r="L281" t="s">
-        <v>34</v>
+        <v>603</v>
       </c>
       <c r="M281" t="s">
         <v>575</v>
@@ -17900,7 +17900,7 @@
         <v>153</v>
       </c>
       <c r="P281" t="s">
-        <v>602</v>
+        <v>583</v>
       </c>
       <c r="Q281" t="s">
         <v>45</v>
@@ -17923,28 +17923,28 @@
         <v>34</v>
       </c>
       <c r="E282" t="s">
-        <v>545</v>
+        <v>604</v>
       </c>
       <c r="F282" t="s">
-        <v>173</v>
+        <v>198</v>
       </c>
       <c r="G282" t="s">
         <v>41</v>
       </c>
       <c r="H282" t="s">
-        <v>603</v>
+        <v>512</v>
       </c>
       <c r="I282" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="J282" t="s">
-        <v>548</v>
+        <v>66</v>
       </c>
       <c r="K282" t="s">
-        <v>266</v>
+        <v>66</v>
       </c>
       <c r="L282" t="s">
-        <v>605</v>
+        <v>34</v>
       </c>
       <c r="M282" t="s">
         <v>575</v>
@@ -17956,7 +17956,7 @@
         <v>153</v>
       </c>
       <c r="P282" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="Q282" t="s">
         <v>45</v>
@@ -17979,7 +17979,7 @@
         <v>34</v>
       </c>
       <c r="E283" t="s">
-        <v>557</v>
+        <v>549</v>
       </c>
       <c r="F283" t="s">
         <v>173</v>
@@ -17988,19 +17988,19 @@
         <v>41</v>
       </c>
       <c r="H283" t="s">
-        <v>366</v>
+        <v>606</v>
       </c>
       <c r="I283" t="s">
-        <v>606</v>
+        <v>569</v>
       </c>
       <c r="J283" t="s">
-        <v>607</v>
+        <v>555</v>
       </c>
       <c r="K283" t="s">
         <v>266</v>
       </c>
       <c r="L283" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="M283" t="s">
         <v>575</v>
@@ -18012,7 +18012,7 @@
         <v>153</v>
       </c>
       <c r="P283" t="s">
-        <v>606</v>
+        <v>569</v>
       </c>
       <c r="Q283" t="s">
         <v>45</v>
@@ -18035,28 +18035,28 @@
         <v>34</v>
       </c>
       <c r="E284" t="s">
+        <v>549</v>
+      </c>
+      <c r="F284" t="s">
+        <v>173</v>
+      </c>
+      <c r="G284" t="s">
+        <v>41</v>
+      </c>
+      <c r="H284" t="s">
+        <v>608</v>
+      </c>
+      <c r="I284" t="s">
         <v>609</v>
       </c>
-      <c r="F284" t="s">
-        <v>198</v>
-      </c>
-      <c r="G284" t="s">
-        <v>41</v>
-      </c>
-      <c r="H284" t="s">
+      <c r="J284" t="s">
+        <v>555</v>
+      </c>
+      <c r="K284" t="s">
+        <v>266</v>
+      </c>
+      <c r="L284" t="s">
         <v>610</v>
-      </c>
-      <c r="I284" t="s">
-        <v>569</v>
-      </c>
-      <c r="J284" t="s">
-        <v>121</v>
-      </c>
-      <c r="K284" t="s">
-        <v>146</v>
-      </c>
-      <c r="L284" t="s">
-        <v>611</v>
       </c>
       <c r="M284" t="s">
         <v>575</v>
@@ -18068,7 +18068,7 @@
         <v>153</v>
       </c>
       <c r="P284" t="s">
-        <v>569</v>
+        <v>609</v>
       </c>
       <c r="Q284" t="s">
         <v>45</v>
@@ -18091,7 +18091,7 @@
         <v>34</v>
       </c>
       <c r="E285" t="s">
-        <v>545</v>
+        <v>557</v>
       </c>
       <c r="F285" t="s">
         <v>173</v>
@@ -18100,13 +18100,13 @@
         <v>41</v>
       </c>
       <c r="H285" t="s">
-        <v>442</v>
+        <v>366</v>
       </c>
       <c r="I285" t="s">
+        <v>611</v>
+      </c>
+      <c r="J285" t="s">
         <v>612</v>
-      </c>
-      <c r="J285" t="s">
-        <v>548</v>
       </c>
       <c r="K285" t="s">
         <v>266</v>
@@ -18124,7 +18124,7 @@
         <v>153</v>
       </c>
       <c r="P285" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="Q285" t="s">
         <v>45</v>
@@ -18324,10 +18324,10 @@
         <v>41</v>
       </c>
       <c r="H289" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="I289" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="J289" t="s">
         <v>176</v>
@@ -18348,7 +18348,7 @@
         <v>153</v>
       </c>
       <c r="P289" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="Q289" t="s">
         <v>45</v>
@@ -18890,7 +18890,7 @@
         <v>651</v>
       </c>
       <c r="J299" t="s">
-        <v>548</v>
+        <v>555</v>
       </c>
       <c r="K299" t="s">
         <v>81</v>
@@ -19155,7 +19155,7 @@
         <v>33</v>
       </c>
       <c r="E304" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="F304" t="s">
         <v>173</v>
@@ -19170,7 +19170,7 @@
         <v>670</v>
       </c>
       <c r="J304" t="s">
-        <v>548</v>
+        <v>555</v>
       </c>
       <c r="K304" t="s">
         <v>266</v>
@@ -19323,7 +19323,7 @@
         <v>33</v>
       </c>
       <c r="E307" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="F307" t="s">
         <v>173</v>
@@ -19338,7 +19338,7 @@
         <v>682</v>
       </c>
       <c r="J307" t="s">
-        <v>548</v>
+        <v>555</v>
       </c>
       <c r="K307" t="s">
         <v>683</v>
@@ -19450,7 +19450,7 @@
         <v>689</v>
       </c>
       <c r="J309" t="s">
-        <v>548</v>
+        <v>555</v>
       </c>
       <c r="K309" t="s">
         <v>81</v>
@@ -19618,10 +19618,10 @@
         <v>700</v>
       </c>
       <c r="J312" t="s">
-        <v>201</v>
+        <v>121</v>
       </c>
       <c r="K312" t="s">
-        <v>66</v>
+        <v>146</v>
       </c>
       <c r="L312" t="s">
         <v>701</v>
@@ -19680,7 +19680,7 @@
         <v>66</v>
       </c>
       <c r="L313" t="s">
-        <v>34</v>
+        <v>705</v>
       </c>
       <c r="M313" t="s">
         <v>693</v>
@@ -19715,7 +19715,7 @@
         <v>34</v>
       </c>
       <c r="E314" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="F314" t="s">
         <v>198</v>
@@ -19724,19 +19724,19 @@
         <v>41</v>
       </c>
       <c r="H314" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="I314" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="J314" t="s">
-        <v>121</v>
+        <v>201</v>
       </c>
       <c r="K314" t="s">
-        <v>146</v>
+        <v>66</v>
       </c>
       <c r="L314" t="s">
-        <v>708</v>
+        <v>34</v>
       </c>
       <c r="M314" t="s">
         <v>693</v>
@@ -19748,7 +19748,7 @@
         <v>153</v>
       </c>
       <c r="P314" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="Q314" t="s">
         <v>45</v>
@@ -19827,7 +19827,7 @@
         <v>33</v>
       </c>
       <c r="E316" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="F316" t="s">
         <v>173</v>
@@ -19842,7 +19842,7 @@
         <v>714</v>
       </c>
       <c r="J316" t="s">
-        <v>548</v>
+        <v>555</v>
       </c>
       <c r="K316" t="s">
         <v>266</v>
@@ -19895,7 +19895,7 @@
         <v>718</v>
       </c>
       <c r="I317" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="J317" t="s">
         <v>678</v>
@@ -19916,7 +19916,7 @@
         <v>153</v>
       </c>
       <c r="P317" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="Q317" t="s">
         <v>45</v>
@@ -20066,13 +20066,13 @@
         <v>730</v>
       </c>
       <c r="J320" t="s">
-        <v>731</v>
+        <v>201</v>
       </c>
       <c r="K320" t="s">
         <v>266</v>
       </c>
       <c r="L320" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="M320" t="s">
         <v>728</v>
@@ -20107,7 +20107,7 @@
         <v>34</v>
       </c>
       <c r="E321" t="s">
-        <v>545</v>
+        <v>732</v>
       </c>
       <c r="F321" t="s">
         <v>173</v>
@@ -20116,13 +20116,13 @@
         <v>41</v>
       </c>
       <c r="H321" t="s">
+        <v>723</v>
+      </c>
+      <c r="I321" t="s">
         <v>733</v>
       </c>
-      <c r="I321" t="s">
+      <c r="J321" t="s">
         <v>734</v>
-      </c>
-      <c r="J321" t="s">
-        <v>265</v>
       </c>
       <c r="K321" t="s">
         <v>266</v>
@@ -20140,7 +20140,7 @@
         <v>153</v>
       </c>
       <c r="P321" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="Q321" t="s">
         <v>45</v>
@@ -20163,7 +20163,7 @@
         <v>34</v>
       </c>
       <c r="E322" t="s">
-        <v>736</v>
+        <v>549</v>
       </c>
       <c r="F322" t="s">
         <v>173</v>
@@ -20175,16 +20175,16 @@
         <v>723</v>
       </c>
       <c r="I322" t="s">
+        <v>736</v>
+      </c>
+      <c r="J322" t="s">
+        <v>265</v>
+      </c>
+      <c r="K322" t="s">
+        <v>60</v>
+      </c>
+      <c r="L322" t="s">
         <v>737</v>
-      </c>
-      <c r="J322" t="s">
-        <v>738</v>
-      </c>
-      <c r="K322" t="s">
-        <v>266</v>
-      </c>
-      <c r="L322" t="s">
-        <v>739</v>
       </c>
       <c r="M322" t="s">
         <v>728</v>
@@ -20196,7 +20196,7 @@
         <v>153</v>
       </c>
       <c r="P322" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="Q322" t="s">
         <v>45</v>
@@ -20219,7 +20219,7 @@
         <v>34</v>
       </c>
       <c r="E323" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="F323" t="s">
         <v>173</v>
@@ -20231,16 +20231,16 @@
         <v>723</v>
       </c>
       <c r="I323" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="J323" t="s">
-        <v>201</v>
+        <v>734</v>
       </c>
       <c r="K323" t="s">
         <v>266</v>
       </c>
       <c r="L323" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="M323" t="s">
         <v>728</v>
@@ -20252,7 +20252,7 @@
         <v>153</v>
       </c>
       <c r="P323" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="Q323" t="s">
         <v>45</v>
@@ -20275,7 +20275,7 @@
         <v>34</v>
       </c>
       <c r="E324" t="s">
-        <v>743</v>
+        <v>549</v>
       </c>
       <c r="F324" t="s">
         <v>173</v>
@@ -20284,19 +20284,19 @@
         <v>41</v>
       </c>
       <c r="H324" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="I324" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="J324" t="s">
-        <v>746</v>
+        <v>265</v>
       </c>
       <c r="K324" t="s">
-        <v>747</v>
+        <v>266</v>
       </c>
       <c r="L324" t="s">
-        <v>748</v>
+        <v>743</v>
       </c>
       <c r="M324" t="s">
         <v>728</v>
@@ -20308,7 +20308,7 @@
         <v>153</v>
       </c>
       <c r="P324" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="Q324" t="s">
         <v>45</v>
@@ -20331,7 +20331,7 @@
         <v>34</v>
       </c>
       <c r="E325" t="s">
-        <v>749</v>
+        <v>744</v>
       </c>
       <c r="F325" t="s">
         <v>173</v>
@@ -20343,16 +20343,16 @@
         <v>723</v>
       </c>
       <c r="I325" t="s">
-        <v>750</v>
+        <v>745</v>
       </c>
       <c r="J325" t="s">
-        <v>738</v>
+        <v>746</v>
       </c>
       <c r="K325" t="s">
         <v>266</v>
       </c>
       <c r="L325" t="s">
-        <v>751</v>
+        <v>747</v>
       </c>
       <c r="M325" t="s">
         <v>728</v>
@@ -20364,7 +20364,7 @@
         <v>153</v>
       </c>
       <c r="P325" t="s">
-        <v>750</v>
+        <v>745</v>
       </c>
       <c r="Q325" t="s">
         <v>45</v>
@@ -20387,7 +20387,7 @@
         <v>34</v>
       </c>
       <c r="E326" t="s">
-        <v>545</v>
+        <v>748</v>
       </c>
       <c r="F326" t="s">
         <v>173</v>
@@ -20396,19 +20396,19 @@
         <v>41</v>
       </c>
       <c r="H326" t="s">
-        <v>723</v>
+        <v>749</v>
       </c>
       <c r="I326" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="J326" t="s">
-        <v>265</v>
+        <v>751</v>
       </c>
       <c r="K326" t="s">
-        <v>60</v>
+        <v>266</v>
       </c>
       <c r="L326" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="M326" t="s">
         <v>728</v>
@@ -20420,7 +20420,7 @@
         <v>153</v>
       </c>
       <c r="P326" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="Q326" t="s">
         <v>45</v>
@@ -20443,7 +20443,7 @@
         <v>34</v>
       </c>
       <c r="E327" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="F327" t="s">
         <v>173</v>
@@ -20452,19 +20452,19 @@
         <v>41</v>
       </c>
       <c r="H327" t="s">
+        <v>753</v>
+      </c>
+      <c r="I327" t="s">
+        <v>754</v>
+      </c>
+      <c r="J327" t="s">
         <v>755</v>
       </c>
-      <c r="I327" t="s">
+      <c r="K327" t="s">
         <v>756</v>
       </c>
-      <c r="J327" t="s">
+      <c r="L327" t="s">
         <v>757</v>
-      </c>
-      <c r="K327" t="s">
-        <v>266</v>
-      </c>
-      <c r="L327" t="s">
-        <v>755</v>
       </c>
       <c r="M327" t="s">
         <v>728</v>
@@ -20476,7 +20476,7 @@
         <v>153</v>
       </c>
       <c r="P327" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="Q327" t="s">
         <v>45</v>
@@ -20723,7 +20723,7 @@
         <v>33</v>
       </c>
       <c r="E332" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="F332" t="s">
         <v>173</v>
@@ -20738,7 +20738,7 @@
         <v>777</v>
       </c>
       <c r="J332" t="s">
-        <v>548</v>
+        <v>555</v>
       </c>
       <c r="K332" t="s">
         <v>266</v>
@@ -20947,7 +20947,7 @@
         <v>33</v>
       </c>
       <c r="E336" t="s">
-        <v>649</v>
+        <v>549</v>
       </c>
       <c r="F336" t="s">
         <v>173</v>
@@ -20965,7 +20965,7 @@
         <v>555</v>
       </c>
       <c r="K336" t="s">
-        <v>163</v>
+        <v>266</v>
       </c>
       <c r="L336" t="s">
         <v>796</v>
@@ -21003,7 +21003,7 @@
         <v>34</v>
       </c>
       <c r="E337" t="s">
-        <v>545</v>
+        <v>649</v>
       </c>
       <c r="F337" t="s">
         <v>173</v>
@@ -21018,10 +21018,10 @@
         <v>798</v>
       </c>
       <c r="J337" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="K337" t="s">
-        <v>266</v>
+        <v>158</v>
       </c>
       <c r="L337" t="s">
         <v>799</v>
@@ -21059,7 +21059,7 @@
         <v>33</v>
       </c>
       <c r="E338" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="F338" t="s">
         <v>173</v>
@@ -21074,7 +21074,7 @@
         <v>803</v>
       </c>
       <c r="J338" t="s">
-        <v>731</v>
+        <v>746</v>
       </c>
       <c r="K338" t="s">
         <v>266</v>
@@ -26285,7 +26285,7 @@
         <v>923</v>
       </c>
       <c r="K431" t="s">
-        <v>593</v>
+        <v>602</v>
       </c>
       <c r="L431" t="s">
         <v>924</v>
@@ -26397,7 +26397,7 @@
         <v>923</v>
       </c>
       <c r="K433" t="s">
-        <v>593</v>
+        <v>602</v>
       </c>
       <c r="L433" t="s">
         <v>930</v>
@@ -26562,10 +26562,10 @@
         <v>926</v>
       </c>
       <c r="J436" t="s">
-        <v>593</v>
+        <v>602</v>
       </c>
       <c r="K436" t="s">
-        <v>593</v>
+        <v>602</v>
       </c>
       <c r="L436" t="s">
         <v>924</v>

--- a/xlsx/dre/DRE_08_2026.xlsx
+++ b/xlsx/dre/DRE_08_2026.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7618" uniqueCount="940">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7618" uniqueCount="942">
   <si>
     <t>Movimentações Financeiras</t>
   </si>
@@ -477,6 +477,21 @@
     <t>ADM</t>
   </si>
   <si>
+    <t>38/1</t>
+  </si>
+  <si>
+    <t>INSS- Previdenciária</t>
+  </si>
+  <si>
+    <t>R$  1.607,30</t>
+  </si>
+  <si>
+    <t>21/09/26</t>
+  </si>
+  <si>
+    <t>INSS</t>
+  </si>
+  <si>
     <t>1/7</t>
   </si>
   <si>
@@ -495,25 +510,10 @@
     <t>Digisac MP 2026</t>
   </si>
   <si>
-    <t>38/1</t>
-  </si>
-  <si>
-    <t>INSS- Previdenciária</t>
-  </si>
-  <si>
-    <t>R$  1.607,30</t>
-  </si>
-  <si>
-    <t>21/09/26</t>
-  </si>
-  <si>
-    <t>INSS</t>
-  </si>
-  <si>
     <t>4 CUSTOS E DESPESAS</t>
   </si>
   <si>
-    <t>R$ 578.124,15</t>
+    <t>R$ 578.326,97</t>
   </si>
   <si>
     <t>4.01 DEDUÇÕES DE RECEITA</t>
@@ -588,7 +588,7 @@
     <t>4.02 CUSTOS</t>
   </si>
   <si>
-    <t>R$ 229.002,83</t>
+    <t>R$ 229.205,65</t>
   </si>
   <si>
     <t>4.02.01 CUSTO DAS MERCADORIAS VENDIDAS e SERVIÇOS</t>
@@ -918,7 +918,7 @@
     <t>4.02.02 CUSTO DE TRANSPORTE</t>
   </si>
   <si>
-    <t>R$ 32.808,91</t>
+    <t>R$ 33.011,73</t>
   </si>
   <si>
     <t>4.02.02.01 Fretes sobre compras</t>
@@ -933,7 +933,7 @@
     <t>RODAG TRANSPORTES LTDA*</t>
   </si>
   <si>
-    <t>R$  705,57</t>
+    <t>R$  807,94</t>
   </si>
   <si>
     <t>Título referente a Frete</t>
@@ -1041,7 +1041,7 @@
     <t>96101/2</t>
   </si>
   <si>
-    <t>R$  692,45</t>
+    <t>R$  792,90</t>
   </si>
   <si>
     <t>92401/3</t>
@@ -1500,6 +1500,15 @@
     <t>R$ 46.099,39</t>
   </si>
   <si>
+    <t>R$  731,91</t>
+  </si>
+  <si>
+    <t>92801/0</t>
+  </si>
+  <si>
+    <t>Antonio Jesus</t>
+  </si>
+  <si>
     <t>R$  1.821,02</t>
   </si>
   <si>
@@ -1515,7 +1524,7 @@
     <t>R$  10.968,96</t>
   </si>
   <si>
-    <t>R$  731,91</t>
+    <t>R$  3.054,69</t>
   </si>
   <si>
     <t>R$  1.734,08</t>
@@ -1524,30 +1533,27 @@
     <t>R$  6.791,26</t>
   </si>
   <si>
+    <t>R$  2.001,64</t>
+  </si>
+  <si>
+    <t>R$  1.984,53</t>
+  </si>
+  <si>
+    <t>R$  4.755,57</t>
+  </si>
+  <si>
+    <t>R$  799,51</t>
+  </si>
+  <si>
+    <t>R$  1.846,26</t>
+  </si>
+  <si>
+    <t>92401/0</t>
+  </si>
+  <si>
     <t>R$  2.163,00</t>
   </si>
   <si>
-    <t>R$  2.001,64</t>
-  </si>
-  <si>
-    <t>R$  1.984,53</t>
-  </si>
-  <si>
-    <t>R$  4.755,57</t>
-  </si>
-  <si>
-    <t>R$  799,51</t>
-  </si>
-  <si>
-    <t>Antonio Jesus</t>
-  </si>
-  <si>
-    <t>R$  1.846,26</t>
-  </si>
-  <si>
-    <t>R$  3.054,69</t>
-  </si>
-  <si>
     <t>4.03.01.02.13 DSR sobre comissões</t>
   </si>
   <si>
@@ -1599,12 +1605,12 @@
     <t>4.03.03.02.05.02 Assistência técnica medição</t>
   </si>
   <si>
+    <t>L E A Medicoes Tecnicas LTDA</t>
+  </si>
+  <si>
     <t>PFP</t>
   </si>
   <si>
-    <t>L E A Medicoes Tecnicas LTDA</t>
-  </si>
-  <si>
     <t>R$  360,00</t>
   </si>
   <si>
@@ -1659,6 +1665,30 @@
     <t>R$ 9.215,99</t>
   </si>
   <si>
+    <t>12/8</t>
+  </si>
+  <si>
+    <t>MARQUES MAIO MARKETING DIGITAL LTDA</t>
+  </si>
+  <si>
+    <t>R$  808,50</t>
+  </si>
+  <si>
+    <t>08/01/26</t>
+  </si>
+  <si>
+    <t>MHM - Honorários 2026</t>
+  </si>
+  <si>
+    <t>Google</t>
+  </si>
+  <si>
+    <t>R$  14,99</t>
+  </si>
+  <si>
+    <t>Google 2026</t>
+  </si>
+  <si>
     <t>WEBGIGA SOLUCOES DIGITAIS LTDA</t>
   </si>
   <si>
@@ -1669,30 +1699,6 @@
   </si>
   <si>
     <t>Webgiga 2026</t>
-  </si>
-  <si>
-    <t>12/8</t>
-  </si>
-  <si>
-    <t>Google</t>
-  </si>
-  <si>
-    <t>R$  14,99</t>
-  </si>
-  <si>
-    <t>Google 2026</t>
-  </si>
-  <si>
-    <t>MARQUES MAIO MARKETING DIGITAL LTDA</t>
-  </si>
-  <si>
-    <t>R$  808,50</t>
-  </si>
-  <si>
-    <t>08/01/26</t>
-  </si>
-  <si>
-    <t>MHM - Honorários 2026</t>
   </si>
   <si>
     <t>1/6</t>
@@ -2118,18 +2124,6 @@
     <t xml:space="preserve">04/08/2026	•••• •••• •••• 0005497380066700654	SUPERMERCADO	Compra à vista		105,06	PAO DE ACUCAR 2409     	Materiais limpeza e pao de queijo
 25/08/2026	•••• •••• •••• 0005497380066700654	SUPERMERCADO	Compra à vista		307,33	PAO DE ACUCAR 2409	Materiais limpeza 
 </t>
-  </si>
-  <si>
-    <t>736/1</t>
-  </si>
-  <si>
-    <t>Casa de Bolos de Moema LTDA</t>
-  </si>
-  <si>
-    <t>R$  97,00</t>
-  </si>
-  <si>
-    <t>Bolo Bianca</t>
   </si>
   <si>
     <t>745/1</t>
@@ -2157,6 +2151,18 @@
     <t>R$  5,95</t>
   </si>
   <si>
+    <t>736/1</t>
+  </si>
+  <si>
+    <t>Casa de Bolos de Moema LTDA</t>
+  </si>
+  <si>
+    <t>R$  97,00</t>
+  </si>
+  <si>
+    <t>Bolo Bianca</t>
+  </si>
+  <si>
     <t>4.04.02.07 Informática</t>
   </si>
   <si>
@@ -2217,6 +2223,39 @@
     <t>4.04.02.08.03 Mensalidades e assinaturas - outros gastos</t>
   </si>
   <si>
+    <t>3/7</t>
+  </si>
+  <si>
+    <t>R$  1.248,76</t>
+  </si>
+  <si>
+    <t>13/02/26</t>
+  </si>
+  <si>
+    <t>Promob 2026/2</t>
+  </si>
+  <si>
+    <t>D4 sign</t>
+  </si>
+  <si>
+    <t>R$  49,95</t>
+  </si>
+  <si>
+    <t>D4 sign 2026</t>
+  </si>
+  <si>
+    <t>63/3</t>
+  </si>
+  <si>
+    <t>R$  376,38</t>
+  </si>
+  <si>
+    <t>11/06/26</t>
+  </si>
+  <si>
+    <t>Promob 2026/4</t>
+  </si>
+  <si>
     <t>70/12</t>
   </si>
   <si>
@@ -2226,16 +2265,31 @@
     <t>Promob 26/5</t>
   </si>
   <si>
-    <t>63/3</t>
-  </si>
-  <si>
-    <t>R$  376,38</t>
-  </si>
-  <si>
-    <t>11/06/26</t>
-  </si>
-  <si>
-    <t>Promob 2026/4</t>
+    <t>64/3</t>
+  </si>
+  <si>
+    <t>ISO IMPLANTACAO EM SAUDE OCUPACIONAL LTDA</t>
+  </si>
+  <si>
+    <t>R$  146,67</t>
+  </si>
+  <si>
+    <t>24/06/26</t>
+  </si>
+  <si>
+    <t>22/08/26</t>
+  </si>
+  <si>
+    <t>ISO Implantação -Saude ocupacional</t>
+  </si>
+  <si>
+    <t>62/3</t>
+  </si>
+  <si>
+    <t>R$  293,11</t>
+  </si>
+  <si>
+    <t>Promob 2026/3</t>
   </si>
   <si>
     <t>R$  599,00</t>
@@ -2244,36 +2298,6 @@
     <t>Promob 2026</t>
   </si>
   <si>
-    <t>62/3</t>
-  </si>
-  <si>
-    <t>R$  293,11</t>
-  </si>
-  <si>
-    <t>Promob 2026/3</t>
-  </si>
-  <si>
-    <t>D4 sign</t>
-  </si>
-  <si>
-    <t>R$  49,95</t>
-  </si>
-  <si>
-    <t>D4 sign 2026</t>
-  </si>
-  <si>
-    <t>3/7</t>
-  </si>
-  <si>
-    <t>R$  1.248,76</t>
-  </si>
-  <si>
-    <t>13/02/26</t>
-  </si>
-  <si>
-    <t>Promob 2026/2</t>
-  </si>
-  <si>
     <t>61/4</t>
   </si>
   <si>
@@ -2284,24 +2308,6 @@
   </si>
   <si>
     <t>21/05/26</t>
-  </si>
-  <si>
-    <t>64/3</t>
-  </si>
-  <si>
-    <t>ISO IMPLANTACAO EM SAUDE OCUPACIONAL LTDA</t>
-  </si>
-  <si>
-    <t>R$  146,67</t>
-  </si>
-  <si>
-    <t>24/06/26</t>
-  </si>
-  <si>
-    <t>22/08/26</t>
-  </si>
-  <si>
-    <t>ISO Implantação -Saude ocupacional</t>
   </si>
   <si>
     <t>4.04.02.11 Manutenção de predio e equipamentos</t>
@@ -2413,6 +2419,15 @@
     <t>R$ 400,33</t>
   </si>
   <si>
+    <t>VERISURE</t>
+  </si>
+  <si>
+    <t>R$  250,33</t>
+  </si>
+  <si>
+    <t>Verisure - Alarme 2026</t>
+  </si>
+  <si>
     <t>Jackson Fernando de Araujo</t>
   </si>
   <si>
@@ -2422,15 +2437,6 @@
     <t>Segurança 2026</t>
   </si>
   <si>
-    <t>VERISURE</t>
-  </si>
-  <si>
-    <t>R$  250,33</t>
-  </si>
-  <si>
-    <t>Verisure - Alarme 2026</t>
-  </si>
-  <si>
     <t>4.04.02.14.08 Site e newsletter da loja</t>
   </si>
   <si>
@@ -2569,7 +2575,7 @@
     <t>7.05 = RESULTADO BRUTO</t>
   </si>
   <si>
-    <t>R$ 400.505,00</t>
+    <t>R$ 400.302,18</t>
   </si>
   <si>
     <t>7.06 (-) DESPESAS REGULARES</t>
@@ -2659,7 +2665,7 @@
     <t>7.07 = RESULTADO ANTES DAS DESPESAS E RECEITAS FINANCEIRAS</t>
   </si>
   <si>
-    <t>R$ 200.340,16</t>
+    <t>R$ 200.137,34</t>
   </si>
   <si>
     <t>7.08 (-) DESPESAS E RECEITAS FINANCEIRAS</t>
@@ -2683,7 +2689,7 @@
     <t>7.09 = RESULTADO OPERACIONAL</t>
   </si>
   <si>
-    <t>R$ 72.513,60</t>
+    <t>R$ 72.310,78</t>
   </si>
   <si>
     <t>7.11 = RESULTADO LÍQUIDO DO EXERCÍCIO</t>
@@ -2698,7 +2704,7 @@
     <t>7.50.02 TOTAL DOS CUSTOS VARIÁVEIS</t>
   </si>
   <si>
-    <t>R$ 507.390,42</t>
+    <t>R$ 507.593,24</t>
   </si>
   <si>
     <t>7.50.02.01 Deduções de receita</t>
@@ -2761,7 +2767,7 @@
     <t>7.70 BREAK-EVEN POINT</t>
   </si>
   <si>
-    <t>R$ 321.276,74</t>
+    <t>R$ 321.732,27</t>
   </si>
   <si>
     <t>7.80.01 Mark Up Negociado</t>
@@ -4893,10 +4899,10 @@
         <v>157</v>
       </c>
       <c r="K49" t="s">
+        <v>88</v>
+      </c>
+      <c r="L49" t="s">
         <v>158</v>
-      </c>
-      <c r="L49" t="s">
-        <v>159</v>
       </c>
       <c r="M49" t="s">
         <v>147</v>
@@ -4931,7 +4937,7 @@
         <v>34</v>
       </c>
       <c r="E50" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F50" t="s">
         <v>63</v>
@@ -4940,16 +4946,16 @@
         <v>41</v>
       </c>
       <c r="H50" t="s">
+        <v>160</v>
+      </c>
+      <c r="I50" t="s">
         <v>161</v>
       </c>
-      <c r="I50" t="s">
+      <c r="J50" t="s">
         <v>162</v>
       </c>
-      <c r="J50" t="s">
+      <c r="K50" t="s">
         <v>163</v>
-      </c>
-      <c r="K50" t="s">
-        <v>88</v>
       </c>
       <c r="L50" t="s">
         <v>164</v>
@@ -4964,7 +4970,7 @@
         <v>153</v>
       </c>
       <c r="P50" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="Q50" t="s">
         <v>45</v>
@@ -5211,7 +5217,7 @@
         <v>33</v>
       </c>
       <c r="E55" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="F55" t="s">
         <v>173</v>
@@ -7242,7 +7248,7 @@
         <v>294</v>
       </c>
       <c r="J91" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="K91" t="s">
         <v>88</v>
@@ -14395,7 +14401,7 @@
         <v>33</v>
       </c>
       <c r="E219" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="F219" t="s">
         <v>457</v>
@@ -14410,10 +14416,10 @@
         <v>492</v>
       </c>
       <c r="J219" t="s">
-        <v>67</v>
+        <v>130</v>
       </c>
       <c r="K219" t="s">
-        <v>67</v>
+        <v>130</v>
       </c>
       <c r="L219" t="s">
         <v>34</v>
@@ -14451,25 +14457,25 @@
         <v>34</v>
       </c>
       <c r="E220" t="s">
-        <v>253</v>
+        <v>493</v>
       </c>
       <c r="F220" t="s">
-        <v>457</v>
+        <v>198</v>
       </c>
       <c r="G220" t="s">
         <v>41</v>
       </c>
       <c r="H220" t="s">
-        <v>206</v>
+        <v>494</v>
       </c>
       <c r="I220" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="J220" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="K220" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="L220" t="s">
         <v>34</v>
@@ -14481,13 +14487,13 @@
         <v>45</v>
       </c>
       <c r="O220" t="s">
-        <v>34</v>
+        <v>327</v>
       </c>
       <c r="P220" t="s">
-        <v>34</v>
+        <v>495</v>
       </c>
       <c r="Q220" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R220" t="s">
         <v>34</v>
@@ -14507,7 +14513,7 @@
         <v>34</v>
       </c>
       <c r="E221" t="s">
-        <v>204</v>
+        <v>253</v>
       </c>
       <c r="F221" t="s">
         <v>457</v>
@@ -14519,13 +14525,13 @@
         <v>206</v>
       </c>
       <c r="I221" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="J221" t="s">
-        <v>50</v>
+        <v>88</v>
       </c>
       <c r="K221" t="s">
-        <v>50</v>
+        <v>88</v>
       </c>
       <c r="L221" t="s">
         <v>34</v>
@@ -14563,7 +14569,7 @@
         <v>34</v>
       </c>
       <c r="E222" t="s">
-        <v>227</v>
+        <v>204</v>
       </c>
       <c r="F222" t="s">
         <v>457</v>
@@ -14575,13 +14581,13 @@
         <v>206</v>
       </c>
       <c r="I222" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="J222" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="K222" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="L222" t="s">
         <v>34</v>
@@ -14619,7 +14625,7 @@
         <v>34</v>
       </c>
       <c r="E223" t="s">
-        <v>242</v>
+        <v>227</v>
       </c>
       <c r="F223" t="s">
         <v>457</v>
@@ -14631,13 +14637,13 @@
         <v>206</v>
       </c>
       <c r="I223" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="J223" t="s">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="K223" t="s">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="L223" t="s">
         <v>34</v>
@@ -14675,7 +14681,7 @@
         <v>34</v>
       </c>
       <c r="E224" t="s">
-        <v>230</v>
+        <v>242</v>
       </c>
       <c r="F224" t="s">
         <v>457</v>
@@ -14687,13 +14693,13 @@
         <v>206</v>
       </c>
       <c r="I224" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="J224" t="s">
-        <v>130</v>
+        <v>88</v>
       </c>
       <c r="K224" t="s">
-        <v>130</v>
+        <v>88</v>
       </c>
       <c r="L224" t="s">
         <v>34</v>
@@ -14731,7 +14737,7 @@
         <v>34</v>
       </c>
       <c r="E225" t="s">
-        <v>225</v>
+        <v>354</v>
       </c>
       <c r="F225" t="s">
         <v>457</v>
@@ -14743,7 +14749,7 @@
         <v>206</v>
       </c>
       <c r="I225" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="J225" t="s">
         <v>60</v>
@@ -14787,7 +14793,7 @@
         <v>34</v>
       </c>
       <c r="E226" t="s">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="F226" t="s">
         <v>457</v>
@@ -14799,7 +14805,7 @@
         <v>206</v>
       </c>
       <c r="I226" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="J226" t="s">
         <v>60</v>
@@ -14843,7 +14849,7 @@
         <v>34</v>
       </c>
       <c r="E227" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="F227" t="s">
         <v>457</v>
@@ -14855,13 +14861,13 @@
         <v>206</v>
       </c>
       <c r="I227" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="J227" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="K227" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="L227" t="s">
         <v>34</v>
@@ -14911,7 +14917,7 @@
         <v>206</v>
       </c>
       <c r="I228" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="J228" t="s">
         <v>108</v>
@@ -14967,7 +14973,7 @@
         <v>206</v>
       </c>
       <c r="I229" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="J229" t="s">
         <v>130</v>
@@ -15023,7 +15029,7 @@
         <v>206</v>
       </c>
       <c r="I230" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="J230" t="s">
         <v>130</v>
@@ -15079,7 +15085,7 @@
         <v>206</v>
       </c>
       <c r="I231" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="J231" t="s">
         <v>118</v>
@@ -15132,10 +15138,10 @@
         <v>41</v>
       </c>
       <c r="H232" t="s">
-        <v>505</v>
+        <v>494</v>
       </c>
       <c r="I232" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="J232" t="s">
         <v>81</v>
@@ -15156,7 +15162,7 @@
         <v>324</v>
       </c>
       <c r="P232" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="Q232" t="s">
         <v>45</v>
@@ -15179,25 +15185,25 @@
         <v>34</v>
       </c>
       <c r="E233" t="s">
-        <v>354</v>
+        <v>508</v>
       </c>
       <c r="F233" t="s">
-        <v>457</v>
+        <v>198</v>
       </c>
       <c r="G233" t="s">
         <v>41</v>
       </c>
       <c r="H233" t="s">
-        <v>206</v>
+        <v>494</v>
       </c>
       <c r="I233" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="J233" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="K233" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="L233" t="s">
         <v>34</v>
@@ -15209,13 +15215,13 @@
         <v>45</v>
       </c>
       <c r="O233" t="s">
-        <v>34</v>
+        <v>220</v>
       </c>
       <c r="P233" t="s">
-        <v>34</v>
+        <v>509</v>
       </c>
       <c r="Q233" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R233" t="s">
         <v>34</v>
@@ -15223,19 +15229,19 @@
     </row>
     <row r="234">
       <c r="A234" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="B234" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="C234" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="D234" t="s">
         <v>33</v>
       </c>
       <c r="E234" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="F234" t="s">
         <v>198</v>
@@ -15247,7 +15253,7 @@
         <v>366</v>
       </c>
       <c r="I234" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="J234" t="s">
         <v>55</v>
@@ -15259,7 +15265,7 @@
         <v>34</v>
       </c>
       <c r="M234" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="N234" t="s">
         <v>45</v>
@@ -15268,7 +15274,7 @@
         <v>153</v>
       </c>
       <c r="P234" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="Q234" t="s">
         <v>45</v>
@@ -15279,7 +15285,7 @@
     </row>
     <row r="235">
       <c r="A235" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="B235" t="s">
         <v>34</v>
@@ -15291,7 +15297,7 @@
         <v>34</v>
       </c>
       <c r="E235" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="F235" t="s">
         <v>198</v>
@@ -15300,10 +15306,10 @@
         <v>41</v>
       </c>
       <c r="H235" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="I235" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="J235" t="s">
         <v>66</v>
@@ -15315,7 +15321,7 @@
         <v>34</v>
       </c>
       <c r="M235" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="N235" t="s">
         <v>45</v>
@@ -15324,7 +15330,7 @@
         <v>153</v>
       </c>
       <c r="P235" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="Q235" t="s">
         <v>45</v>
@@ -15335,13 +15341,13 @@
     </row>
     <row r="236">
       <c r="A236" t="s" s="1">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="B236" t="s" s="1">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="C236" t="s" s="1">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="D236" t="s" s="1">
         <v>33</v>
@@ -15391,13 +15397,13 @@
     </row>
     <row r="237">
       <c r="A237" t="s" s="1">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B237" t="s" s="1">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="C237" t="s" s="1">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="D237" t="s" s="1">
         <v>33</v>
@@ -15447,13 +15453,13 @@
     </row>
     <row r="238">
       <c r="A238" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="B238" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="C238" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="D238" t="s">
         <v>33</v>
@@ -15468,10 +15474,10 @@
         <v>41</v>
       </c>
       <c r="H238" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="I238" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="J238" t="s">
         <v>88</v>
@@ -15483,7 +15489,7 @@
         <v>34</v>
       </c>
       <c r="M238" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="N238" t="s">
         <v>45</v>
@@ -15492,7 +15498,7 @@
         <v>93</v>
       </c>
       <c r="P238" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="Q238" t="s">
         <v>45</v>
@@ -15503,13 +15509,13 @@
     </row>
     <row r="239">
       <c r="A239" t="s" s="1">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="B239" t="s" s="1">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="C239" t="s" s="1">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="D239" t="s" s="1">
         <v>33</v>
@@ -15559,13 +15565,13 @@
     </row>
     <row r="240">
       <c r="A240" t="s" s="1">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="B240" t="s" s="1">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="C240" t="s" s="1">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="D240" t="s" s="1">
         <v>33</v>
@@ -15615,55 +15621,55 @@
     </row>
     <row r="241">
       <c r="A241" t="s">
+        <v>526</v>
+      </c>
+      <c r="B241" t="s">
         <v>524</v>
       </c>
-      <c r="B241" t="s">
-        <v>522</v>
-      </c>
       <c r="C241" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="D241" t="s">
         <v>33</v>
       </c>
       <c r="E241" t="s">
-        <v>240</v>
+        <v>221</v>
       </c>
       <c r="F241" t="s">
-        <v>525</v>
+        <v>173</v>
       </c>
       <c r="G241" t="s">
         <v>41</v>
       </c>
       <c r="H241" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="I241" t="s">
         <v>200</v>
       </c>
       <c r="J241" t="s">
-        <v>118</v>
+        <v>67</v>
       </c>
       <c r="K241" t="s">
-        <v>118</v>
+        <v>67</v>
       </c>
       <c r="L241" t="s">
         <v>34</v>
       </c>
       <c r="M241" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="N241" t="s">
         <v>45</v>
       </c>
       <c r="O241" t="s">
-        <v>34</v>
+        <v>327</v>
       </c>
       <c r="P241" t="s">
-        <v>34</v>
+        <v>200</v>
       </c>
       <c r="Q241" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R241" t="s">
         <v>34</v>
@@ -15671,7 +15677,7 @@
     </row>
     <row r="242">
       <c r="A242" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="B242" t="s">
         <v>34</v>
@@ -15683,43 +15689,43 @@
         <v>34</v>
       </c>
       <c r="E242" t="s">
-        <v>218</v>
+        <v>240</v>
       </c>
       <c r="F242" t="s">
-        <v>173</v>
+        <v>528</v>
       </c>
       <c r="G242" t="s">
         <v>41</v>
       </c>
       <c r="H242" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="I242" t="s">
         <v>200</v>
       </c>
       <c r="J242" t="s">
-        <v>67</v>
+        <v>118</v>
       </c>
       <c r="K242" t="s">
-        <v>67</v>
+        <v>118</v>
       </c>
       <c r="L242" t="s">
         <v>34</v>
       </c>
       <c r="M242" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="N242" t="s">
         <v>45</v>
       </c>
       <c r="O242" t="s">
-        <v>247</v>
+        <v>34</v>
       </c>
       <c r="P242" t="s">
-        <v>200</v>
+        <v>34</v>
       </c>
       <c r="Q242" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="R242" t="s">
         <v>34</v>
@@ -15727,7 +15733,7 @@
     </row>
     <row r="243">
       <c r="A243" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="B243" t="s">
         <v>34</v>
@@ -15739,43 +15745,43 @@
         <v>34</v>
       </c>
       <c r="E243" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="F243" t="s">
-        <v>525</v>
+        <v>173</v>
       </c>
       <c r="G243" t="s">
         <v>41</v>
       </c>
       <c r="H243" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="I243" t="s">
         <v>200</v>
       </c>
       <c r="J243" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="K243" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="L243" t="s">
         <v>34</v>
       </c>
       <c r="M243" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="N243" t="s">
         <v>45</v>
       </c>
       <c r="O243" t="s">
-        <v>34</v>
+        <v>247</v>
       </c>
       <c r="P243" t="s">
-        <v>34</v>
+        <v>200</v>
       </c>
       <c r="Q243" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R243" t="s">
         <v>34</v>
@@ -15783,7 +15789,7 @@
     </row>
     <row r="244">
       <c r="A244" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="B244" t="s">
         <v>34</v>
@@ -15795,7 +15801,7 @@
         <v>34</v>
       </c>
       <c r="E244" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="F244" t="s">
         <v>173</v>
@@ -15804,28 +15810,28 @@
         <v>41</v>
       </c>
       <c r="H244" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="I244" t="s">
         <v>200</v>
       </c>
       <c r="J244" t="s">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="K244" t="s">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="L244" t="s">
         <v>34</v>
       </c>
       <c r="M244" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="N244" t="s">
         <v>45</v>
       </c>
       <c r="O244" t="s">
-        <v>61</v>
+        <v>137</v>
       </c>
       <c r="P244" t="s">
         <v>200</v>
@@ -15839,7 +15845,7 @@
     </row>
     <row r="245">
       <c r="A245" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="B245" t="s">
         <v>34</v>
@@ -15851,7 +15857,7 @@
         <v>34</v>
       </c>
       <c r="E245" t="s">
-        <v>253</v>
+        <v>210</v>
       </c>
       <c r="F245" t="s">
         <v>173</v>
@@ -15860,28 +15866,28 @@
         <v>41</v>
       </c>
       <c r="H245" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="I245" t="s">
         <v>200</v>
       </c>
       <c r="J245" t="s">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="K245" t="s">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="L245" t="s">
         <v>34</v>
       </c>
       <c r="M245" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="N245" t="s">
         <v>45</v>
       </c>
       <c r="O245" t="s">
-        <v>89</v>
+        <v>46</v>
       </c>
       <c r="P245" t="s">
         <v>200</v>
@@ -15895,7 +15901,7 @@
     </row>
     <row r="246">
       <c r="A246" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="B246" t="s">
         <v>34</v>
@@ -15907,43 +15913,43 @@
         <v>34</v>
       </c>
       <c r="E246" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="F246" t="s">
-        <v>525</v>
+        <v>173</v>
       </c>
       <c r="G246" t="s">
         <v>41</v>
       </c>
       <c r="H246" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="I246" t="s">
         <v>200</v>
       </c>
       <c r="J246" t="s">
-        <v>130</v>
+        <v>108</v>
       </c>
       <c r="K246" t="s">
-        <v>130</v>
+        <v>108</v>
       </c>
       <c r="L246" t="s">
         <v>34</v>
       </c>
       <c r="M246" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="N246" t="s">
         <v>45</v>
       </c>
       <c r="O246" t="s">
-        <v>34</v>
+        <v>380</v>
       </c>
       <c r="P246" t="s">
-        <v>34</v>
+        <v>200</v>
       </c>
       <c r="Q246" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R246" t="s">
         <v>34</v>
@@ -15951,7 +15957,7 @@
     </row>
     <row r="247">
       <c r="A247" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="B247" t="s">
         <v>34</v>
@@ -15963,7 +15969,7 @@
         <v>34</v>
       </c>
       <c r="E247" t="s">
-        <v>212</v>
+        <v>242</v>
       </c>
       <c r="F247" t="s">
         <v>173</v>
@@ -15972,31 +15978,31 @@
         <v>41</v>
       </c>
       <c r="H247" t="s">
+        <v>527</v>
+      </c>
+      <c r="I247" t="s">
+        <v>529</v>
+      </c>
+      <c r="J247" t="s">
+        <v>88</v>
+      </c>
+      <c r="K247" t="s">
+        <v>88</v>
+      </c>
+      <c r="L247" t="s">
+        <v>34</v>
+      </c>
+      <c r="M247" t="s">
         <v>526</v>
       </c>
-      <c r="I247" t="s">
-        <v>200</v>
-      </c>
-      <c r="J247" t="s">
-        <v>81</v>
-      </c>
-      <c r="K247" t="s">
-        <v>81</v>
-      </c>
-      <c r="L247" t="s">
-        <v>34</v>
-      </c>
-      <c r="M247" t="s">
-        <v>524</v>
-      </c>
       <c r="N247" t="s">
         <v>45</v>
       </c>
       <c r="O247" t="s">
-        <v>324</v>
+        <v>247</v>
       </c>
       <c r="P247" t="s">
-        <v>200</v>
+        <v>529</v>
       </c>
       <c r="Q247" t="s">
         <v>45</v>
@@ -16007,7 +16013,7 @@
     </row>
     <row r="248">
       <c r="A248" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="B248" t="s">
         <v>34</v>
@@ -16019,31 +16025,31 @@
         <v>34</v>
       </c>
       <c r="E248" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="F248" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="G248" t="s">
         <v>41</v>
       </c>
       <c r="H248" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="I248" t="s">
         <v>200</v>
       </c>
       <c r="J248" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="K248" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="L248" t="s">
         <v>34</v>
       </c>
       <c r="M248" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="N248" t="s">
         <v>45</v>
@@ -16063,7 +16069,7 @@
     </row>
     <row r="249">
       <c r="A249" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="B249" t="s">
         <v>34</v>
@@ -16075,43 +16081,43 @@
         <v>34</v>
       </c>
       <c r="E249" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="F249" t="s">
-        <v>525</v>
+        <v>173</v>
       </c>
       <c r="G249" t="s">
         <v>41</v>
       </c>
       <c r="H249" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="I249" t="s">
         <v>200</v>
       </c>
       <c r="J249" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="K249" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="L249" t="s">
         <v>34</v>
       </c>
       <c r="M249" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="N249" t="s">
         <v>45</v>
       </c>
       <c r="O249" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="P249" t="s">
-        <v>34</v>
+        <v>200</v>
       </c>
       <c r="Q249" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R249" t="s">
         <v>34</v>
@@ -16119,7 +16125,7 @@
     </row>
     <row r="250">
       <c r="A250" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="B250" t="s">
         <v>34</v>
@@ -16131,43 +16137,43 @@
         <v>34</v>
       </c>
       <c r="E250" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="F250" t="s">
-        <v>173</v>
+        <v>528</v>
       </c>
       <c r="G250" t="s">
         <v>41</v>
       </c>
       <c r="H250" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="I250" t="s">
         <v>200</v>
       </c>
       <c r="J250" t="s">
-        <v>108</v>
+        <v>130</v>
       </c>
       <c r="K250" t="s">
-        <v>108</v>
+        <v>130</v>
       </c>
       <c r="L250" t="s">
         <v>34</v>
       </c>
       <c r="M250" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="N250" t="s">
         <v>45</v>
       </c>
       <c r="O250" t="s">
-        <v>380</v>
+        <v>34</v>
       </c>
       <c r="P250" t="s">
-        <v>200</v>
+        <v>34</v>
       </c>
       <c r="Q250" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="R250" t="s">
         <v>34</v>
@@ -16175,7 +16181,7 @@
     </row>
     <row r="251">
       <c r="A251" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="B251" t="s">
         <v>34</v>
@@ -16187,43 +16193,43 @@
         <v>34</v>
       </c>
       <c r="E251" t="s">
-        <v>227</v>
+        <v>253</v>
       </c>
       <c r="F251" t="s">
-        <v>525</v>
+        <v>173</v>
       </c>
       <c r="G251" t="s">
         <v>41</v>
       </c>
       <c r="H251" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="I251" t="s">
         <v>200</v>
       </c>
       <c r="J251" t="s">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="K251" t="s">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="L251" t="s">
         <v>34</v>
       </c>
       <c r="M251" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="N251" t="s">
         <v>45</v>
       </c>
       <c r="O251" t="s">
-        <v>34</v>
+        <v>89</v>
       </c>
       <c r="P251" t="s">
-        <v>34</v>
+        <v>200</v>
       </c>
       <c r="Q251" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R251" t="s">
         <v>34</v>
@@ -16231,7 +16237,7 @@
     </row>
     <row r="252">
       <c r="A252" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="B252" t="s">
         <v>34</v>
@@ -16243,7 +16249,7 @@
         <v>34</v>
       </c>
       <c r="E252" t="s">
-        <v>242</v>
+        <v>212</v>
       </c>
       <c r="F252" t="s">
         <v>173</v>
@@ -16252,31 +16258,31 @@
         <v>41</v>
       </c>
       <c r="H252" t="s">
+        <v>527</v>
+      </c>
+      <c r="I252" t="s">
+        <v>200</v>
+      </c>
+      <c r="J252" t="s">
+        <v>81</v>
+      </c>
+      <c r="K252" t="s">
+        <v>81</v>
+      </c>
+      <c r="L252" t="s">
+        <v>34</v>
+      </c>
+      <c r="M252" t="s">
         <v>526</v>
       </c>
-      <c r="I252" t="s">
-        <v>527</v>
-      </c>
-      <c r="J252" t="s">
-        <v>88</v>
-      </c>
-      <c r="K252" t="s">
-        <v>88</v>
-      </c>
-      <c r="L252" t="s">
-        <v>34</v>
-      </c>
-      <c r="M252" t="s">
-        <v>524</v>
-      </c>
       <c r="N252" t="s">
         <v>45</v>
       </c>
       <c r="O252" t="s">
-        <v>247</v>
+        <v>324</v>
       </c>
       <c r="P252" t="s">
-        <v>527</v>
+        <v>200</v>
       </c>
       <c r="Q252" t="s">
         <v>45</v>
@@ -16287,7 +16293,7 @@
     </row>
     <row r="253">
       <c r="A253" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="B253" t="s">
         <v>34</v>
@@ -16299,43 +16305,43 @@
         <v>34</v>
       </c>
       <c r="E253" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="F253" t="s">
-        <v>173</v>
+        <v>528</v>
       </c>
       <c r="G253" t="s">
         <v>41</v>
       </c>
       <c r="H253" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="I253" t="s">
         <v>200</v>
       </c>
       <c r="J253" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="K253" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="L253" t="s">
         <v>34</v>
       </c>
       <c r="M253" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="N253" t="s">
         <v>45</v>
       </c>
       <c r="O253" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="P253" t="s">
-        <v>200</v>
+        <v>34</v>
       </c>
       <c r="Q253" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="R253" t="s">
         <v>34</v>
@@ -16343,7 +16349,7 @@
     </row>
     <row r="254">
       <c r="A254" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="B254" t="s">
         <v>34</v>
@@ -16355,31 +16361,31 @@
         <v>34</v>
       </c>
       <c r="E254" t="s">
-        <v>204</v>
+        <v>223</v>
       </c>
       <c r="F254" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="G254" t="s">
         <v>41</v>
       </c>
       <c r="H254" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="I254" t="s">
         <v>200</v>
       </c>
       <c r="J254" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="K254" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="L254" t="s">
         <v>34</v>
       </c>
       <c r="M254" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="N254" t="s">
         <v>45</v>
@@ -16399,7 +16405,7 @@
     </row>
     <row r="255">
       <c r="A255" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="B255" t="s">
         <v>34</v>
@@ -16411,43 +16417,43 @@
         <v>34</v>
       </c>
       <c r="E255" t="s">
-        <v>230</v>
+        <v>204</v>
       </c>
       <c r="F255" t="s">
-        <v>173</v>
+        <v>528</v>
       </c>
       <c r="G255" t="s">
         <v>41</v>
       </c>
       <c r="H255" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="I255" t="s">
         <v>200</v>
       </c>
       <c r="J255" t="s">
-        <v>130</v>
+        <v>50</v>
       </c>
       <c r="K255" t="s">
-        <v>130</v>
+        <v>50</v>
       </c>
       <c r="L255" t="s">
         <v>34</v>
       </c>
       <c r="M255" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="N255" t="s">
         <v>45</v>
       </c>
       <c r="O255" t="s">
-        <v>137</v>
+        <v>34</v>
       </c>
       <c r="P255" t="s">
-        <v>200</v>
+        <v>34</v>
       </c>
       <c r="Q255" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="R255" t="s">
         <v>34</v>
@@ -16455,7 +16461,7 @@
     </row>
     <row r="256">
       <c r="A256" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="B256" t="s">
         <v>34</v>
@@ -16467,43 +16473,43 @@
         <v>34</v>
       </c>
       <c r="E256" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="F256" t="s">
-        <v>173</v>
+        <v>528</v>
       </c>
       <c r="G256" t="s">
         <v>41</v>
       </c>
       <c r="H256" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="I256" t="s">
         <v>200</v>
       </c>
       <c r="J256" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="K256" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="L256" t="s">
         <v>34</v>
       </c>
       <c r="M256" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="N256" t="s">
         <v>45</v>
       </c>
       <c r="O256" t="s">
-        <v>327</v>
+        <v>34</v>
       </c>
       <c r="P256" t="s">
-        <v>200</v>
+        <v>34</v>
       </c>
       <c r="Q256" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="R256" t="s">
         <v>34</v>
@@ -16511,13 +16517,13 @@
     </row>
     <row r="257">
       <c r="A257" t="s" s="1">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="B257" t="s" s="1">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="C257" t="s" s="1">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="D257" t="s" s="1">
         <v>33</v>
@@ -16567,19 +16573,19 @@
     </row>
     <row r="258">
       <c r="A258" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="B258" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="C258" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="D258" t="s">
         <v>33</v>
       </c>
       <c r="E258" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="F258" t="s">
         <v>173</v>
@@ -16588,10 +16594,10 @@
         <v>41</v>
       </c>
       <c r="H258" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="I258" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="J258" t="s">
         <v>274</v>
@@ -16600,10 +16606,10 @@
         <v>266</v>
       </c>
       <c r="L258" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="M258" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="N258" t="s">
         <v>45</v>
@@ -16612,7 +16618,7 @@
         <v>153</v>
       </c>
       <c r="P258" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="Q258" t="s">
         <v>45</v>
@@ -16623,13 +16629,13 @@
     </row>
     <row r="259">
       <c r="A259" t="s" s="1">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="B259" t="s" s="1">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="C259" t="s" s="1">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D259" t="s" s="1">
         <v>33</v>
@@ -16679,19 +16685,19 @@
     </row>
     <row r="260">
       <c r="A260" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="B260" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="C260" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="D260" t="s">
         <v>33</v>
       </c>
       <c r="E260" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="F260" t="s">
         <v>173</v>
@@ -16703,19 +16709,19 @@
         <v>214</v>
       </c>
       <c r="I260" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="J260" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K260" t="s">
         <v>121</v>
       </c>
       <c r="L260" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="M260" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="N260" t="s">
         <v>45</v>
@@ -16724,7 +16730,7 @@
         <v>153</v>
       </c>
       <c r="P260" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="Q260" t="s">
         <v>45</v>
@@ -16735,19 +16741,19 @@
     </row>
     <row r="261">
       <c r="A261" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="B261" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="C261" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="D261" t="s">
         <v>33</v>
       </c>
       <c r="E261" t="s">
-        <v>154</v>
+        <v>547</v>
       </c>
       <c r="F261" t="s">
         <v>173</v>
@@ -16756,22 +16762,22 @@
         <v>41</v>
       </c>
       <c r="H261" t="s">
+        <v>548</v>
+      </c>
+      <c r="I261" t="s">
+        <v>549</v>
+      </c>
+      <c r="J261" t="s">
+        <v>550</v>
+      </c>
+      <c r="K261" t="s">
+        <v>81</v>
+      </c>
+      <c r="L261" t="s">
+        <v>551</v>
+      </c>
+      <c r="M261" t="s">
         <v>545</v>
-      </c>
-      <c r="I261" t="s">
-        <v>546</v>
-      </c>
-      <c r="J261" t="s">
-        <v>547</v>
-      </c>
-      <c r="K261" t="s">
-        <v>158</v>
-      </c>
-      <c r="L261" t="s">
-        <v>548</v>
-      </c>
-      <c r="M261" t="s">
-        <v>543</v>
       </c>
       <c r="N261" t="s">
         <v>45</v>
@@ -16780,7 +16786,7 @@
         <v>153</v>
       </c>
       <c r="P261" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="Q261" t="s">
         <v>45</v>
@@ -16791,7 +16797,7 @@
     </row>
     <row r="262">
       <c r="A262" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="B262" t="s">
         <v>34</v>
@@ -16803,7 +16809,7 @@
         <v>34</v>
       </c>
       <c r="E262" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="F262" t="s">
         <v>173</v>
@@ -16812,10 +16818,10 @@
         <v>41</v>
       </c>
       <c r="H262" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="I262" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="J262" t="s">
         <v>265</v>
@@ -16824,10 +16830,10 @@
         <v>266</v>
       </c>
       <c r="L262" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="M262" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="N262" t="s">
         <v>45</v>
@@ -16836,7 +16842,7 @@
         <v>153</v>
       </c>
       <c r="P262" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="Q262" t="s">
         <v>45</v>
@@ -16847,7 +16853,7 @@
     </row>
     <row r="263">
       <c r="A263" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="B263" t="s">
         <v>34</v>
@@ -16859,7 +16865,7 @@
         <v>34</v>
       </c>
       <c r="E263" t="s">
-        <v>549</v>
+        <v>159</v>
       </c>
       <c r="F263" t="s">
         <v>173</v>
@@ -16868,22 +16874,22 @@
         <v>41</v>
       </c>
       <c r="H263" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="I263" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="J263" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="K263" t="s">
-        <v>81</v>
+        <v>163</v>
       </c>
       <c r="L263" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="M263" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="N263" t="s">
         <v>45</v>
@@ -16892,7 +16898,7 @@
         <v>153</v>
       </c>
       <c r="P263" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="Q263" t="s">
         <v>45</v>
@@ -16903,7 +16909,7 @@
     </row>
     <row r="264">
       <c r="A264" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="B264" t="s">
         <v>34</v>
@@ -16915,7 +16921,7 @@
         <v>34</v>
       </c>
       <c r="E264" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="F264" t="s">
         <v>173</v>
@@ -16924,22 +16930,22 @@
         <v>41</v>
       </c>
       <c r="H264" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="I264" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="J264" t="s">
         <v>182</v>
       </c>
       <c r="K264" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="L264" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="M264" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="N264" t="s">
         <v>45</v>
@@ -16948,7 +16954,7 @@
         <v>153</v>
       </c>
       <c r="P264" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="Q264" t="s">
         <v>45</v>
@@ -16959,13 +16965,13 @@
     </row>
     <row r="265">
       <c r="A265" t="s" s="1">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="B265" t="s" s="1">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="C265" t="s" s="1">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="D265" t="s" s="1">
         <v>33</v>
@@ -17015,13 +17021,13 @@
     </row>
     <row r="266">
       <c r="A266" t="s" s="1">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="B266" t="s" s="1">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="C266" t="s" s="1">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="D266" t="s" s="1">
         <v>33</v>
@@ -17071,13 +17077,13 @@
     </row>
     <row r="267">
       <c r="A267" t="s" s="1">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="B267" t="s" s="1">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="C267" t="s" s="1">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="D267" t="s" s="1">
         <v>33</v>
@@ -17127,19 +17133,19 @@
     </row>
     <row r="268">
       <c r="A268" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="B268" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="C268" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="D268" t="s">
         <v>33</v>
       </c>
       <c r="E268" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="F268" t="s">
         <v>173</v>
@@ -17151,19 +17157,19 @@
         <v>393</v>
       </c>
       <c r="I268" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="J268" t="s">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="K268" t="s">
         <v>266</v>
       </c>
       <c r="L268" t="s">
+        <v>572</v>
+      </c>
+      <c r="M268" t="s">
         <v>570</v>
-      </c>
-      <c r="M268" t="s">
-        <v>568</v>
       </c>
       <c r="N268" t="s">
         <v>45</v>
@@ -17172,7 +17178,7 @@
         <v>153</v>
       </c>
       <c r="P268" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="Q268" t="s">
         <v>45</v>
@@ -17183,13 +17189,13 @@
     </row>
     <row r="269">
       <c r="A269" t="s" s="1">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="B269" t="s" s="1">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="C269" t="s" s="1">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="D269" t="s" s="1">
         <v>33</v>
@@ -17239,13 +17245,13 @@
     </row>
     <row r="270">
       <c r="A270" t="s" s="1">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="B270" t="s" s="1">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="C270" t="s" s="1">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="D270" t="s" s="1">
         <v>33</v>
@@ -17295,19 +17301,19 @@
     </row>
     <row r="271">
       <c r="A271" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="B271" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="C271" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="D271" t="s">
         <v>33</v>
       </c>
       <c r="E271" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="F271" t="s">
         <v>173</v>
@@ -17316,22 +17322,22 @@
         <v>41</v>
       </c>
       <c r="H271" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="I271" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="J271" t="s">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="K271" t="s">
         <v>266</v>
       </c>
       <c r="L271" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="M271" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="N271" t="s">
         <v>45</v>
@@ -17340,7 +17346,7 @@
         <v>153</v>
       </c>
       <c r="P271" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="Q271" t="s">
         <v>45</v>
@@ -17351,7 +17357,7 @@
     </row>
     <row r="272">
       <c r="A272" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="B272" t="s">
         <v>34</v>
@@ -17363,7 +17369,7 @@
         <v>34</v>
       </c>
       <c r="E272" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="F272" t="s">
         <v>173</v>
@@ -17372,22 +17378,22 @@
         <v>41</v>
       </c>
       <c r="H272" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="I272" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="J272" t="s">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="K272" t="s">
         <v>266</v>
       </c>
       <c r="L272" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="M272" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="N272" t="s">
         <v>45</v>
@@ -17396,7 +17402,7 @@
         <v>153</v>
       </c>
       <c r="P272" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="Q272" t="s">
         <v>45</v>
@@ -17407,7 +17413,7 @@
     </row>
     <row r="273">
       <c r="A273" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="B273" t="s">
         <v>34</v>
@@ -17419,7 +17425,7 @@
         <v>34</v>
       </c>
       <c r="E273" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="F273" t="s">
         <v>173</v>
@@ -17431,7 +17437,7 @@
         <v>391</v>
       </c>
       <c r="I273" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="J273" t="s">
         <v>265</v>
@@ -17440,10 +17446,10 @@
         <v>266</v>
       </c>
       <c r="L273" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="M273" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="N273" t="s">
         <v>45</v>
@@ -17452,7 +17458,7 @@
         <v>153</v>
       </c>
       <c r="P273" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="Q273" t="s">
         <v>45</v>
@@ -17463,7 +17469,7 @@
     </row>
     <row r="274">
       <c r="A274" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="B274" t="s">
         <v>34</v>
@@ -17475,7 +17481,7 @@
         <v>34</v>
       </c>
       <c r="E274" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="F274" t="s">
         <v>173</v>
@@ -17487,19 +17493,19 @@
         <v>405</v>
       </c>
       <c r="I274" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="J274" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="K274" t="s">
         <v>266</v>
       </c>
       <c r="L274" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="M274" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="N274" t="s">
         <v>45</v>
@@ -17508,7 +17514,7 @@
         <v>153</v>
       </c>
       <c r="P274" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="Q274" t="s">
         <v>45</v>
@@ -17519,7 +17525,7 @@
     </row>
     <row r="275">
       <c r="A275" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="B275" t="s">
         <v>34</v>
@@ -17531,7 +17537,7 @@
         <v>34</v>
       </c>
       <c r="E275" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="F275" t="s">
         <v>198</v>
@@ -17540,10 +17546,10 @@
         <v>41</v>
       </c>
       <c r="H275" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="I275" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="J275" t="s">
         <v>121</v>
@@ -17552,10 +17558,10 @@
         <v>146</v>
       </c>
       <c r="L275" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="M275" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="N275" t="s">
         <v>45</v>
@@ -17564,7 +17570,7 @@
         <v>153</v>
       </c>
       <c r="P275" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="Q275" t="s">
         <v>45</v>
@@ -17575,7 +17581,7 @@
     </row>
     <row r="276">
       <c r="A276" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="B276" t="s">
         <v>34</v>
@@ -17587,7 +17593,7 @@
         <v>34</v>
       </c>
       <c r="E276" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="F276" t="s">
         <v>173</v>
@@ -17596,22 +17602,22 @@
         <v>41</v>
       </c>
       <c r="H276" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="I276" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="J276" t="s">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="K276" t="s">
         <v>266</v>
       </c>
       <c r="L276" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="M276" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="N276" t="s">
         <v>45</v>
@@ -17620,7 +17626,7 @@
         <v>153</v>
       </c>
       <c r="P276" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="Q276" t="s">
         <v>45</v>
@@ -17631,7 +17637,7 @@
     </row>
     <row r="277">
       <c r="A277" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="B277" t="s">
         <v>34</v>
@@ -17643,7 +17649,7 @@
         <v>34</v>
       </c>
       <c r="E277" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="F277" t="s">
         <v>173</v>
@@ -17655,19 +17661,19 @@
         <v>461</v>
       </c>
       <c r="I277" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="J277" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="K277" t="s">
         <v>266</v>
       </c>
       <c r="L277" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="M277" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="N277" t="s">
         <v>45</v>
@@ -17676,7 +17682,7 @@
         <v>153</v>
       </c>
       <c r="P277" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="Q277" t="s">
         <v>45</v>
@@ -17687,7 +17693,7 @@
     </row>
     <row r="278">
       <c r="A278" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="B278" t="s">
         <v>34</v>
@@ -17699,7 +17705,7 @@
         <v>34</v>
       </c>
       <c r="E278" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="F278" t="s">
         <v>198</v>
@@ -17711,7 +17717,7 @@
         <v>366</v>
       </c>
       <c r="I278" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="J278" t="s">
         <v>55</v>
@@ -17720,10 +17726,10 @@
         <v>55</v>
       </c>
       <c r="L278" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="M278" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="N278" t="s">
         <v>45</v>
@@ -17732,7 +17738,7 @@
         <v>153</v>
       </c>
       <c r="P278" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="Q278" t="s">
         <v>45</v>
@@ -17743,7 +17749,7 @@
     </row>
     <row r="279">
       <c r="A279" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="B279" t="s">
         <v>34</v>
@@ -17755,7 +17761,7 @@
         <v>34</v>
       </c>
       <c r="E279" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="F279" t="s">
         <v>173</v>
@@ -17767,19 +17773,19 @@
         <v>442</v>
       </c>
       <c r="I279" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="J279" t="s">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="K279" t="s">
         <v>266</v>
       </c>
       <c r="L279" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="M279" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="N279" t="s">
         <v>45</v>
@@ -17788,7 +17794,7 @@
         <v>153</v>
       </c>
       <c r="P279" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="Q279" t="s">
         <v>45</v>
@@ -17799,7 +17805,7 @@
     </row>
     <row r="280">
       <c r="A280" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="B280" t="s">
         <v>34</v>
@@ -17811,7 +17817,7 @@
         <v>34</v>
       </c>
       <c r="E280" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="F280" t="s">
         <v>198</v>
@@ -17823,7 +17829,7 @@
         <v>459</v>
       </c>
       <c r="I280" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="J280" t="s">
         <v>368</v>
@@ -17835,7 +17841,7 @@
         <v>34</v>
       </c>
       <c r="M280" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="N280" t="s">
         <v>45</v>
@@ -17844,7 +17850,7 @@
         <v>153</v>
       </c>
       <c r="P280" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="Q280" t="s">
         <v>45</v>
@@ -17855,7 +17861,7 @@
     </row>
     <row r="281">
       <c r="A281" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="B281" t="s">
         <v>34</v>
@@ -17867,7 +17873,7 @@
         <v>34</v>
       </c>
       <c r="E281" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="F281" t="s">
         <v>173</v>
@@ -17876,22 +17882,22 @@
         <v>41</v>
       </c>
       <c r="H281" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="I281" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="J281" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="K281" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="L281" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="M281" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="N281" t="s">
         <v>45</v>
@@ -17900,7 +17906,7 @@
         <v>153</v>
       </c>
       <c r="P281" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="Q281" t="s">
         <v>45</v>
@@ -17911,7 +17917,7 @@
     </row>
     <row r="282">
       <c r="A282" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="B282" t="s">
         <v>34</v>
@@ -17923,7 +17929,7 @@
         <v>34</v>
       </c>
       <c r="E282" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="F282" t="s">
         <v>198</v>
@@ -17932,10 +17938,10 @@
         <v>41</v>
       </c>
       <c r="H282" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="I282" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="J282" t="s">
         <v>66</v>
@@ -17947,7 +17953,7 @@
         <v>34</v>
       </c>
       <c r="M282" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="N282" t="s">
         <v>45</v>
@@ -17956,7 +17962,7 @@
         <v>153</v>
       </c>
       <c r="P282" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="Q282" t="s">
         <v>45</v>
@@ -17967,7 +17973,7 @@
     </row>
     <row r="283">
       <c r="A283" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="B283" t="s">
         <v>34</v>
@@ -17979,7 +17985,7 @@
         <v>34</v>
       </c>
       <c r="E283" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="F283" t="s">
         <v>173</v>
@@ -17988,22 +17994,22 @@
         <v>41</v>
       </c>
       <c r="H283" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="I283" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="J283" t="s">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="K283" t="s">
         <v>266</v>
       </c>
       <c r="L283" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="M283" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="N283" t="s">
         <v>45</v>
@@ -18012,7 +18018,7 @@
         <v>153</v>
       </c>
       <c r="P283" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="Q283" t="s">
         <v>45</v>
@@ -18023,7 +18029,7 @@
     </row>
     <row r="284">
       <c r="A284" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="B284" t="s">
         <v>34</v>
@@ -18035,7 +18041,7 @@
         <v>34</v>
       </c>
       <c r="E284" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="F284" t="s">
         <v>173</v>
@@ -18044,22 +18050,22 @@
         <v>41</v>
       </c>
       <c r="H284" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="I284" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="J284" t="s">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="K284" t="s">
         <v>266</v>
       </c>
       <c r="L284" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="M284" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="N284" t="s">
         <v>45</v>
@@ -18068,7 +18074,7 @@
         <v>153</v>
       </c>
       <c r="P284" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="Q284" t="s">
         <v>45</v>
@@ -18079,7 +18085,7 @@
     </row>
     <row r="285">
       <c r="A285" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="B285" t="s">
         <v>34</v>
@@ -18091,7 +18097,7 @@
         <v>34</v>
       </c>
       <c r="E285" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="F285" t="s">
         <v>173</v>
@@ -18103,19 +18109,19 @@
         <v>366</v>
       </c>
       <c r="I285" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="J285" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="K285" t="s">
         <v>266</v>
       </c>
       <c r="L285" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="M285" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="N285" t="s">
         <v>45</v>
@@ -18124,7 +18130,7 @@
         <v>153</v>
       </c>
       <c r="P285" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="Q285" t="s">
         <v>45</v>
@@ -18135,13 +18141,13 @@
     </row>
     <row r="286">
       <c r="A286" t="s" s="1">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="B286" t="s" s="1">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="C286" t="s" s="1">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="D286" t="s" s="1">
         <v>33</v>
@@ -18191,13 +18197,13 @@
     </row>
     <row r="287">
       <c r="A287" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="B287" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="C287" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="D287" t="s">
         <v>33</v>
@@ -18224,10 +18230,10 @@
         <v>121</v>
       </c>
       <c r="L287" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="M287" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="N287" t="s">
         <v>45</v>
@@ -18247,13 +18253,13 @@
     </row>
     <row r="288">
       <c r="A288" t="s" s="1">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="B288" t="s" s="1">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="C288" t="s" s="1">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="D288" t="s" s="1">
         <v>33</v>
@@ -18303,13 +18309,13 @@
     </row>
     <row r="289">
       <c r="A289" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="B289" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="C289" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="D289" t="s">
         <v>33</v>
@@ -18324,10 +18330,10 @@
         <v>41</v>
       </c>
       <c r="H289" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="I289" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="J289" t="s">
         <v>176</v>
@@ -18336,10 +18342,10 @@
         <v>121</v>
       </c>
       <c r="L289" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="M289" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="N289" t="s">
         <v>45</v>
@@ -18348,7 +18354,7 @@
         <v>153</v>
       </c>
       <c r="P289" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="Q289" t="s">
         <v>45</v>
@@ -18359,13 +18365,13 @@
     </row>
     <row r="290">
       <c r="A290" t="s" s="1">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="B290" t="s" s="1">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="C290" t="s" s="1">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="D290" t="s" s="1">
         <v>33</v>
@@ -18415,13 +18421,13 @@
     </row>
     <row r="291">
       <c r="A291" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="B291" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="C291" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="D291" t="s">
         <v>33</v>
@@ -18436,10 +18442,10 @@
         <v>41</v>
       </c>
       <c r="H291" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="I291" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="J291" t="s">
         <v>176</v>
@@ -18448,10 +18454,10 @@
         <v>121</v>
       </c>
       <c r="L291" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="M291" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="N291" t="s">
         <v>45</v>
@@ -18460,7 +18466,7 @@
         <v>153</v>
       </c>
       <c r="P291" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="Q291" t="s">
         <v>45</v>
@@ -18471,19 +18477,19 @@
     </row>
     <row r="292">
       <c r="A292" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="B292" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="C292" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="D292" t="s">
         <v>33</v>
       </c>
       <c r="E292" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="F292" t="s">
         <v>198</v>
@@ -18495,19 +18501,19 @@
         <v>442</v>
       </c>
       <c r="I292" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="J292" t="s">
         <v>266</v>
       </c>
       <c r="K292" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="L292" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="M292" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="N292" t="s">
         <v>45</v>
@@ -18516,7 +18522,7 @@
         <v>153</v>
       </c>
       <c r="P292" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="Q292" t="s">
         <v>45</v>
@@ -18527,13 +18533,13 @@
     </row>
     <row r="293">
       <c r="A293" t="s" s="1">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="B293" t="s" s="1">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="C293" t="s" s="1">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="D293" t="s" s="1">
         <v>33</v>
@@ -18583,13 +18589,13 @@
     </row>
     <row r="294">
       <c r="A294" t="s" s="1">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="B294" t="s" s="1">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="C294" t="s" s="1">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="D294" t="s" s="1">
         <v>33</v>
@@ -18639,19 +18645,19 @@
     </row>
     <row r="295">
       <c r="A295" t="s">
+        <v>640</v>
+      </c>
+      <c r="B295" t="s">
         <v>638</v>
       </c>
-      <c r="B295" t="s">
-        <v>636</v>
-      </c>
       <c r="C295" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="D295" t="s">
         <v>33</v>
       </c>
       <c r="E295" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="F295" t="s">
         <v>198</v>
@@ -18663,7 +18669,7 @@
         <v>366</v>
       </c>
       <c r="I295" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="J295" t="s">
         <v>55</v>
@@ -18675,7 +18681,7 @@
         <v>34</v>
       </c>
       <c r="M295" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="N295" t="s">
         <v>45</v>
@@ -18684,7 +18690,7 @@
         <v>153</v>
       </c>
       <c r="P295" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="Q295" t="s">
         <v>45</v>
@@ -18695,7 +18701,7 @@
     </row>
     <row r="296">
       <c r="A296" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="B296" t="s">
         <v>34</v>
@@ -18707,7 +18713,7 @@
         <v>34</v>
       </c>
       <c r="E296" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="F296" t="s">
         <v>198</v>
@@ -18716,13 +18722,13 @@
         <v>41</v>
       </c>
       <c r="H296" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="I296" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="J296" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="K296" t="s">
         <v>66</v>
@@ -18731,7 +18737,7 @@
         <v>34</v>
       </c>
       <c r="M296" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="N296" t="s">
         <v>45</v>
@@ -18740,7 +18746,7 @@
         <v>153</v>
       </c>
       <c r="P296" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="Q296" t="s">
         <v>45</v>
@@ -18751,13 +18757,13 @@
     </row>
     <row r="297">
       <c r="A297" t="s" s="1">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="B297" t="s" s="1">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="C297" t="s" s="1">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="D297" t="s" s="1">
         <v>33</v>
@@ -18807,13 +18813,13 @@
     </row>
     <row r="298">
       <c r="A298" t="s" s="1">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="B298" t="s" s="1">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="C298" t="s" s="1">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="D298" t="s" s="1">
         <v>33</v>
@@ -18863,19 +18869,19 @@
     </row>
     <row r="299">
       <c r="A299" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="B299" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="C299" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="D299" t="s">
         <v>33</v>
       </c>
       <c r="E299" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="F299" t="s">
         <v>173</v>
@@ -18884,22 +18890,22 @@
         <v>41</v>
       </c>
       <c r="H299" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="I299" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="J299" t="s">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="K299" t="s">
         <v>81</v>
       </c>
       <c r="L299" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="M299" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="N299" t="s">
         <v>45</v>
@@ -18908,7 +18914,7 @@
         <v>153</v>
       </c>
       <c r="P299" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="Q299" t="s">
         <v>45</v>
@@ -18919,19 +18925,19 @@
     </row>
     <row r="300">
       <c r="A300" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="B300" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="C300" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="D300" t="s">
         <v>33</v>
       </c>
       <c r="E300" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="F300" t="s">
         <v>198</v>
@@ -18943,7 +18949,7 @@
         <v>150</v>
       </c>
       <c r="I300" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="J300" t="s">
         <v>55</v>
@@ -18952,10 +18958,10 @@
         <v>55</v>
       </c>
       <c r="L300" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="M300" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="N300" t="s">
         <v>45</v>
@@ -18964,7 +18970,7 @@
         <v>153</v>
       </c>
       <c r="P300" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="Q300" t="s">
         <v>45</v>
@@ -18975,13 +18981,13 @@
     </row>
     <row r="301">
       <c r="A301" t="s" s="1">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="B301" t="s" s="1">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="C301" t="s" s="1">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="D301" t="s" s="1">
         <v>33</v>
@@ -19031,19 +19037,19 @@
     </row>
     <row r="302">
       <c r="A302" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="B302" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="C302" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="D302" t="s">
         <v>33</v>
       </c>
       <c r="E302" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="F302" t="s">
         <v>173</v>
@@ -19052,22 +19058,22 @@
         <v>41</v>
       </c>
       <c r="H302" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="I302" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="J302" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="K302" t="s">
         <v>88</v>
       </c>
       <c r="L302" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="M302" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="N302" t="s">
         <v>45</v>
@@ -19076,7 +19082,7 @@
         <v>153</v>
       </c>
       <c r="P302" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="Q302" t="s">
         <v>45</v>
@@ -19087,13 +19093,13 @@
     </row>
     <row r="303">
       <c r="A303" t="s" s="1">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="B303" t="s" s="1">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="C303" t="s" s="1">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="D303" t="s" s="1">
         <v>33</v>
@@ -19143,19 +19149,19 @@
     </row>
     <row r="304">
       <c r="A304" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="B304" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="C304" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="D304" t="s">
         <v>33</v>
       </c>
       <c r="E304" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="F304" t="s">
         <v>173</v>
@@ -19164,22 +19170,22 @@
         <v>41</v>
       </c>
       <c r="H304" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="I304" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="J304" t="s">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="K304" t="s">
         <v>266</v>
       </c>
       <c r="L304" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="M304" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="N304" t="s">
         <v>45</v>
@@ -19188,7 +19194,7 @@
         <v>153</v>
       </c>
       <c r="P304" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="Q304" t="s">
         <v>45</v>
@@ -19199,13 +19205,13 @@
     </row>
     <row r="305">
       <c r="A305" t="s" s="1">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="B305" t="s" s="1">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="C305" t="s" s="1">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="D305" t="s" s="1">
         <v>33</v>
@@ -19255,19 +19261,19 @@
     </row>
     <row r="306">
       <c r="A306" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="B306" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="C306" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="D306" t="s">
         <v>33</v>
       </c>
       <c r="E306" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="F306" t="s">
         <v>173</v>
@@ -19276,22 +19282,22 @@
         <v>41</v>
       </c>
       <c r="H306" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="I306" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="J306" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="K306" t="s">
         <v>146</v>
       </c>
       <c r="L306" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="M306" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="N306" t="s">
         <v>45</v>
@@ -19300,7 +19306,7 @@
         <v>153</v>
       </c>
       <c r="P306" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="Q306" t="s">
         <v>45</v>
@@ -19311,19 +19317,19 @@
     </row>
     <row r="307">
       <c r="A307" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="B307" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="C307" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="D307" t="s">
         <v>33</v>
       </c>
       <c r="E307" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="F307" t="s">
         <v>173</v>
@@ -19332,22 +19338,22 @@
         <v>41</v>
       </c>
       <c r="H307" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="I307" t="s">
+        <v>684</v>
+      </c>
+      <c r="J307" t="s">
+        <v>550</v>
+      </c>
+      <c r="K307" t="s">
+        <v>685</v>
+      </c>
+      <c r="L307" t="s">
+        <v>686</v>
+      </c>
+      <c r="M307" t="s">
         <v>682</v>
-      </c>
-      <c r="J307" t="s">
-        <v>555</v>
-      </c>
-      <c r="K307" t="s">
-        <v>683</v>
-      </c>
-      <c r="L307" t="s">
-        <v>684</v>
-      </c>
-      <c r="M307" t="s">
-        <v>680</v>
       </c>
       <c r="N307" t="s">
         <v>45</v>
@@ -19356,7 +19362,7 @@
         <v>153</v>
       </c>
       <c r="P307" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="Q307" t="s">
         <v>45</v>
@@ -19367,13 +19373,13 @@
     </row>
     <row r="308">
       <c r="A308" t="s" s="1">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="B308" t="s" s="1">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="C308" t="s" s="1">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="D308" t="s" s="1">
         <v>33</v>
@@ -19423,19 +19429,19 @@
     </row>
     <row r="309">
       <c r="A309" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="B309" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="C309" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="D309" t="s">
         <v>33</v>
       </c>
       <c r="E309" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="F309" t="s">
         <v>173</v>
@@ -19444,22 +19450,22 @@
         <v>41</v>
       </c>
       <c r="H309" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="I309" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="J309" t="s">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="K309" t="s">
         <v>81</v>
       </c>
       <c r="L309" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="M309" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="N309" t="s">
         <v>45</v>
@@ -19468,7 +19474,7 @@
         <v>153</v>
       </c>
       <c r="P309" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="Q309" t="s">
         <v>45</v>
@@ -19479,13 +19485,13 @@
     </row>
     <row r="310">
       <c r="A310" t="s" s="1">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="B310" t="s" s="1">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="C310" t="s" s="1">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="D310" t="s" s="1">
         <v>33</v>
@@ -19535,19 +19541,19 @@
     </row>
     <row r="311">
       <c r="A311" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="B311" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="C311" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="D311" t="s">
         <v>33</v>
       </c>
       <c r="E311" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="F311" t="s">
         <v>198</v>
@@ -19556,10 +19562,10 @@
         <v>41</v>
       </c>
       <c r="H311" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="I311" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="J311" t="s">
         <v>201</v>
@@ -19568,10 +19574,10 @@
         <v>66</v>
       </c>
       <c r="L311" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="M311" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="N311" t="s">
         <v>45</v>
@@ -19580,7 +19586,7 @@
         <v>153</v>
       </c>
       <c r="P311" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="Q311" t="s">
         <v>45</v>
@@ -19591,7 +19597,7 @@
     </row>
     <row r="312">
       <c r="A312" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="B312" t="s">
         <v>34</v>
@@ -19603,7 +19609,7 @@
         <v>34</v>
       </c>
       <c r="E312" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="F312" t="s">
         <v>198</v>
@@ -19612,22 +19618,22 @@
         <v>41</v>
       </c>
       <c r="H312" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="I312" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="J312" t="s">
-        <v>121</v>
+        <v>201</v>
       </c>
       <c r="K312" t="s">
-        <v>146</v>
+        <v>66</v>
       </c>
       <c r="L312" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="M312" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="N312" t="s">
         <v>45</v>
@@ -19636,7 +19642,7 @@
         <v>153</v>
       </c>
       <c r="P312" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="Q312" t="s">
         <v>45</v>
@@ -19647,7 +19653,7 @@
     </row>
     <row r="313">
       <c r="A313" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="B313" t="s">
         <v>34</v>
@@ -19659,7 +19665,7 @@
         <v>34</v>
       </c>
       <c r="E313" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="F313" t="s">
         <v>198</v>
@@ -19668,10 +19674,10 @@
         <v>41</v>
       </c>
       <c r="H313" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="I313" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="J313" t="s">
         <v>201</v>
@@ -19680,10 +19686,10 @@
         <v>66</v>
       </c>
       <c r="L313" t="s">
-        <v>705</v>
+        <v>34</v>
       </c>
       <c r="M313" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="N313" t="s">
         <v>45</v>
@@ -19692,7 +19698,7 @@
         <v>153</v>
       </c>
       <c r="P313" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="Q313" t="s">
         <v>45</v>
@@ -19703,7 +19709,7 @@
     </row>
     <row r="314">
       <c r="A314" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="B314" t="s">
         <v>34</v>
@@ -19715,7 +19721,7 @@
         <v>34</v>
       </c>
       <c r="E314" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="F314" t="s">
         <v>198</v>
@@ -19724,22 +19730,22 @@
         <v>41</v>
       </c>
       <c r="H314" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="I314" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="J314" t="s">
-        <v>201</v>
+        <v>121</v>
       </c>
       <c r="K314" t="s">
-        <v>66</v>
+        <v>146</v>
       </c>
       <c r="L314" t="s">
-        <v>34</v>
+        <v>710</v>
       </c>
       <c r="M314" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="N314" t="s">
         <v>45</v>
@@ -19748,7 +19754,7 @@
         <v>153</v>
       </c>
       <c r="P314" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="Q314" t="s">
         <v>45</v>
@@ -19759,13 +19765,13 @@
     </row>
     <row r="315">
       <c r="A315" t="s" s="1">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="B315" t="s" s="1">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="C315" t="s" s="1">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="D315" t="s" s="1">
         <v>33</v>
@@ -19815,19 +19821,19 @@
     </row>
     <row r="316">
       <c r="A316" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="B316" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="C316" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="D316" t="s">
         <v>33</v>
       </c>
       <c r="E316" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="F316" t="s">
         <v>173</v>
@@ -19836,22 +19842,22 @@
         <v>41</v>
       </c>
       <c r="H316" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="I316" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="J316" t="s">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="K316" t="s">
         <v>266</v>
       </c>
       <c r="L316" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="M316" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="N316" t="s">
         <v>45</v>
@@ -19860,7 +19866,7 @@
         <v>153</v>
       </c>
       <c r="P316" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="Q316" t="s">
         <v>45</v>
@@ -19871,19 +19877,19 @@
     </row>
     <row r="317">
       <c r="A317" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="B317" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="C317" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="D317" t="s">
         <v>33</v>
       </c>
       <c r="E317" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="F317" t="s">
         <v>173</v>
@@ -19892,22 +19898,22 @@
         <v>41</v>
       </c>
       <c r="H317" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="I317" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="J317" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="K317" t="s">
         <v>245</v>
       </c>
       <c r="L317" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="M317" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="N317" t="s">
         <v>45</v>
@@ -19916,7 +19922,7 @@
         <v>153</v>
       </c>
       <c r="P317" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="Q317" t="s">
         <v>45</v>
@@ -19927,19 +19933,19 @@
     </row>
     <row r="318">
       <c r="A318" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="B318" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="C318" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="D318" t="s">
         <v>33</v>
       </c>
       <c r="E318" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="F318" t="s">
         <v>173</v>
@@ -19948,22 +19954,22 @@
         <v>41</v>
       </c>
       <c r="H318" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="I318" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="J318" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="K318" t="s">
         <v>266</v>
       </c>
       <c r="L318" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="M318" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="N318" t="s">
         <v>45</v>
@@ -19972,7 +19978,7 @@
         <v>153</v>
       </c>
       <c r="P318" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="Q318" t="s">
         <v>45</v>
@@ -19983,13 +19989,13 @@
     </row>
     <row r="319">
       <c r="A319" t="s" s="1">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="B319" t="s" s="1">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="C319" t="s" s="1">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="D319" t="s" s="1">
         <v>33</v>
@@ -20039,19 +20045,19 @@
     </row>
     <row r="320">
       <c r="A320" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="B320" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="C320" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="D320" t="s">
         <v>33</v>
       </c>
       <c r="E320" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="F320" t="s">
         <v>173</v>
@@ -20060,22 +20066,22 @@
         <v>41</v>
       </c>
       <c r="H320" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="I320" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="J320" t="s">
-        <v>201</v>
+        <v>733</v>
       </c>
       <c r="K320" t="s">
         <v>266</v>
       </c>
       <c r="L320" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="M320" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="N320" t="s">
         <v>45</v>
@@ -20084,7 +20090,7 @@
         <v>153</v>
       </c>
       <c r="P320" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="Q320" t="s">
         <v>45</v>
@@ -20095,7 +20101,7 @@
     </row>
     <row r="321">
       <c r="A321" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="B321" t="s">
         <v>34</v>
@@ -20107,7 +20113,7 @@
         <v>34</v>
       </c>
       <c r="E321" t="s">
-        <v>732</v>
+        <v>547</v>
       </c>
       <c r="F321" t="s">
         <v>173</v>
@@ -20116,22 +20122,22 @@
         <v>41</v>
       </c>
       <c r="H321" t="s">
-        <v>723</v>
+        <v>735</v>
       </c>
       <c r="I321" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="J321" t="s">
-        <v>734</v>
+        <v>265</v>
       </c>
       <c r="K321" t="s">
         <v>266</v>
       </c>
       <c r="L321" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="M321" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="N321" t="s">
         <v>45</v>
@@ -20140,7 +20146,7 @@
         <v>153</v>
       </c>
       <c r="P321" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="Q321" t="s">
         <v>45</v>
@@ -20151,7 +20157,7 @@
     </row>
     <row r="322">
       <c r="A322" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="B322" t="s">
         <v>34</v>
@@ -20163,7 +20169,7 @@
         <v>34</v>
       </c>
       <c r="E322" t="s">
-        <v>549</v>
+        <v>738</v>
       </c>
       <c r="F322" t="s">
         <v>173</v>
@@ -20172,22 +20178,22 @@
         <v>41</v>
       </c>
       <c r="H322" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="I322" t="s">
-        <v>736</v>
+        <v>739</v>
       </c>
       <c r="J322" t="s">
-        <v>265</v>
+        <v>740</v>
       </c>
       <c r="K322" t="s">
-        <v>60</v>
+        <v>266</v>
       </c>
       <c r="L322" t="s">
-        <v>737</v>
+        <v>741</v>
       </c>
       <c r="M322" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="N322" t="s">
         <v>45</v>
@@ -20196,7 +20202,7 @@
         <v>153</v>
       </c>
       <c r="P322" t="s">
-        <v>736</v>
+        <v>739</v>
       </c>
       <c r="Q322" t="s">
         <v>45</v>
@@ -20207,7 +20213,7 @@
     </row>
     <row r="323">
       <c r="A323" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="B323" t="s">
         <v>34</v>
@@ -20219,7 +20225,7 @@
         <v>34</v>
       </c>
       <c r="E323" t="s">
-        <v>738</v>
+        <v>742</v>
       </c>
       <c r="F323" t="s">
         <v>173</v>
@@ -20228,22 +20234,22 @@
         <v>41</v>
       </c>
       <c r="H323" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="I323" t="s">
-        <v>739</v>
+        <v>743</v>
       </c>
       <c r="J323" t="s">
-        <v>734</v>
+        <v>201</v>
       </c>
       <c r="K323" t="s">
         <v>266</v>
       </c>
       <c r="L323" t="s">
-        <v>740</v>
+        <v>744</v>
       </c>
       <c r="M323" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="N323" t="s">
         <v>45</v>
@@ -20252,7 +20258,7 @@
         <v>153</v>
       </c>
       <c r="P323" t="s">
-        <v>739</v>
+        <v>743</v>
       </c>
       <c r="Q323" t="s">
         <v>45</v>
@@ -20263,7 +20269,7 @@
     </row>
     <row r="324">
       <c r="A324" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="B324" t="s">
         <v>34</v>
@@ -20275,7 +20281,7 @@
         <v>34</v>
       </c>
       <c r="E324" t="s">
-        <v>549</v>
+        <v>745</v>
       </c>
       <c r="F324" t="s">
         <v>173</v>
@@ -20284,22 +20290,22 @@
         <v>41</v>
       </c>
       <c r="H324" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="I324" t="s">
-        <v>742</v>
+        <v>747</v>
       </c>
       <c r="J324" t="s">
-        <v>265</v>
+        <v>748</v>
       </c>
       <c r="K324" t="s">
-        <v>266</v>
+        <v>749</v>
       </c>
       <c r="L324" t="s">
-        <v>743</v>
+        <v>750</v>
       </c>
       <c r="M324" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="N324" t="s">
         <v>45</v>
@@ -20308,7 +20314,7 @@
         <v>153</v>
       </c>
       <c r="P324" t="s">
-        <v>742</v>
+        <v>747</v>
       </c>
       <c r="Q324" t="s">
         <v>45</v>
@@ -20319,7 +20325,7 @@
     </row>
     <row r="325">
       <c r="A325" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="B325" t="s">
         <v>34</v>
@@ -20331,7 +20337,7 @@
         <v>34</v>
       </c>
       <c r="E325" t="s">
-        <v>744</v>
+        <v>751</v>
       </c>
       <c r="F325" t="s">
         <v>173</v>
@@ -20340,22 +20346,22 @@
         <v>41</v>
       </c>
       <c r="H325" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="I325" t="s">
-        <v>745</v>
+        <v>752</v>
       </c>
       <c r="J325" t="s">
-        <v>746</v>
+        <v>740</v>
       </c>
       <c r="K325" t="s">
         <v>266</v>
       </c>
       <c r="L325" t="s">
-        <v>747</v>
+        <v>753</v>
       </c>
       <c r="M325" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="N325" t="s">
         <v>45</v>
@@ -20364,7 +20370,7 @@
         <v>153</v>
       </c>
       <c r="P325" t="s">
-        <v>745</v>
+        <v>752</v>
       </c>
       <c r="Q325" t="s">
         <v>45</v>
@@ -20375,7 +20381,7 @@
     </row>
     <row r="326">
       <c r="A326" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="B326" t="s">
         <v>34</v>
@@ -20387,7 +20393,7 @@
         <v>34</v>
       </c>
       <c r="E326" t="s">
-        <v>748</v>
+        <v>547</v>
       </c>
       <c r="F326" t="s">
         <v>173</v>
@@ -20396,22 +20402,22 @@
         <v>41</v>
       </c>
       <c r="H326" t="s">
-        <v>749</v>
+        <v>725</v>
       </c>
       <c r="I326" t="s">
-        <v>750</v>
+        <v>754</v>
       </c>
       <c r="J326" t="s">
-        <v>751</v>
+        <v>265</v>
       </c>
       <c r="K326" t="s">
-        <v>266</v>
+        <v>60</v>
       </c>
       <c r="L326" t="s">
-        <v>749</v>
+        <v>755</v>
       </c>
       <c r="M326" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="N326" t="s">
         <v>45</v>
@@ -20420,7 +20426,7 @@
         <v>153</v>
       </c>
       <c r="P326" t="s">
-        <v>750</v>
+        <v>754</v>
       </c>
       <c r="Q326" t="s">
         <v>45</v>
@@ -20431,7 +20437,7 @@
     </row>
     <row r="327">
       <c r="A327" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="B327" t="s">
         <v>34</v>
@@ -20443,7 +20449,7 @@
         <v>34</v>
       </c>
       <c r="E327" t="s">
-        <v>752</v>
+        <v>756</v>
       </c>
       <c r="F327" t="s">
         <v>173</v>
@@ -20452,22 +20458,22 @@
         <v>41</v>
       </c>
       <c r="H327" t="s">
-        <v>753</v>
+        <v>757</v>
       </c>
       <c r="I327" t="s">
-        <v>754</v>
+        <v>758</v>
       </c>
       <c r="J327" t="s">
-        <v>755</v>
+        <v>759</v>
       </c>
       <c r="K327" t="s">
-        <v>756</v>
+        <v>266</v>
       </c>
       <c r="L327" t="s">
         <v>757</v>
       </c>
       <c r="M327" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="N327" t="s">
         <v>45</v>
@@ -20476,7 +20482,7 @@
         <v>153</v>
       </c>
       <c r="P327" t="s">
-        <v>754</v>
+        <v>758</v>
       </c>
       <c r="Q327" t="s">
         <v>45</v>
@@ -20487,13 +20493,13 @@
     </row>
     <row r="328">
       <c r="A328" t="s" s="1">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="B328" t="s" s="1">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="C328" t="s" s="1">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="D328" t="s" s="1">
         <v>33</v>
@@ -20543,19 +20549,19 @@
     </row>
     <row r="329">
       <c r="A329" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="B329" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="C329" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="D329" t="s">
         <v>33</v>
       </c>
       <c r="E329" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="F329" t="s">
         <v>198</v>
@@ -20564,22 +20570,22 @@
         <v>41</v>
       </c>
       <c r="H329" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="I329" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="J329" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="K329" t="s">
         <v>55</v>
       </c>
       <c r="L329" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="M329" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="N329" t="s">
         <v>45</v>
@@ -20588,7 +20594,7 @@
         <v>153</v>
       </c>
       <c r="P329" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="Q329" t="s">
         <v>45</v>
@@ -20599,19 +20605,19 @@
     </row>
     <row r="330">
       <c r="A330" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="B330" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="C330" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="D330" t="s">
         <v>33</v>
       </c>
       <c r="E330" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="F330" t="s">
         <v>198</v>
@@ -20620,22 +20626,22 @@
         <v>41</v>
       </c>
       <c r="H330" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="I330" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="J330" t="s">
         <v>266</v>
       </c>
       <c r="K330" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="L330" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="M330" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="N330" t="s">
         <v>45</v>
@@ -20644,7 +20650,7 @@
         <v>153</v>
       </c>
       <c r="P330" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="Q330" t="s">
         <v>45</v>
@@ -20655,13 +20661,13 @@
     </row>
     <row r="331">
       <c r="A331" t="s" s="1">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="B331" t="s" s="1">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="C331" t="s" s="1">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="D331" t="s" s="1">
         <v>33</v>
@@ -20711,19 +20717,19 @@
     </row>
     <row r="332">
       <c r="A332" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="B332" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="C332" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="D332" t="s">
         <v>33</v>
       </c>
       <c r="E332" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="F332" t="s">
         <v>173</v>
@@ -20732,22 +20738,22 @@
         <v>41</v>
       </c>
       <c r="H332" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="I332" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="J332" t="s">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="K332" t="s">
         <v>266</v>
       </c>
       <c r="L332" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="M332" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="N332" t="s">
         <v>45</v>
@@ -20756,7 +20762,7 @@
         <v>153</v>
       </c>
       <c r="P332" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="Q332" t="s">
         <v>45</v>
@@ -20767,13 +20773,13 @@
     </row>
     <row r="333">
       <c r="A333" t="s" s="1">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="B333" t="s" s="1">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="C333" t="s" s="1">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="D333" t="s" s="1">
         <v>33</v>
@@ -20823,13 +20829,13 @@
     </row>
     <row r="334">
       <c r="A334" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="B334" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="C334" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="D334" t="s">
         <v>33</v>
@@ -20844,10 +20850,10 @@
         <v>41</v>
       </c>
       <c r="H334" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="I334" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="J334" t="s">
         <v>176</v>
@@ -20856,10 +20862,10 @@
         <v>188</v>
       </c>
       <c r="L334" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="M334" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="N334" t="s">
         <v>45</v>
@@ -20868,7 +20874,7 @@
         <v>153</v>
       </c>
       <c r="P334" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="Q334" t="s">
         <v>45</v>
@@ -20879,19 +20885,19 @@
     </row>
     <row r="335">
       <c r="A335" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="B335" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="C335" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="D335" t="s">
         <v>33</v>
       </c>
       <c r="E335" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="F335" t="s">
         <v>173</v>
@@ -20900,10 +20906,10 @@
         <v>41</v>
       </c>
       <c r="H335" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="I335" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="J335" t="s">
         <v>266</v>
@@ -20912,10 +20918,10 @@
         <v>146</v>
       </c>
       <c r="L335" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="M335" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="N335" t="s">
         <v>45</v>
@@ -20924,7 +20930,7 @@
         <v>153</v>
       </c>
       <c r="P335" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="Q335" t="s">
         <v>45</v>
@@ -20935,19 +20941,19 @@
     </row>
     <row r="336">
       <c r="A336" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="B336" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="C336" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="D336" t="s">
         <v>33</v>
       </c>
       <c r="E336" t="s">
-        <v>549</v>
+        <v>651</v>
       </c>
       <c r="F336" t="s">
         <v>173</v>
@@ -20956,22 +20962,22 @@
         <v>41</v>
       </c>
       <c r="H336" t="s">
+        <v>796</v>
+      </c>
+      <c r="I336" t="s">
+        <v>797</v>
+      </c>
+      <c r="J336" t="s">
+        <v>557</v>
+      </c>
+      <c r="K336" t="s">
+        <v>163</v>
+      </c>
+      <c r="L336" t="s">
+        <v>798</v>
+      </c>
+      <c r="M336" t="s">
         <v>794</v>
-      </c>
-      <c r="I336" t="s">
-        <v>795</v>
-      </c>
-      <c r="J336" t="s">
-        <v>555</v>
-      </c>
-      <c r="K336" t="s">
-        <v>266</v>
-      </c>
-      <c r="L336" t="s">
-        <v>796</v>
-      </c>
-      <c r="M336" t="s">
-        <v>792</v>
       </c>
       <c r="N336" t="s">
         <v>45</v>
@@ -20980,7 +20986,7 @@
         <v>153</v>
       </c>
       <c r="P336" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="Q336" t="s">
         <v>45</v>
@@ -20991,7 +20997,7 @@
     </row>
     <row r="337">
       <c r="A337" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="B337" t="s">
         <v>34</v>
@@ -21003,7 +21009,7 @@
         <v>34</v>
       </c>
       <c r="E337" t="s">
-        <v>649</v>
+        <v>547</v>
       </c>
       <c r="F337" t="s">
         <v>173</v>
@@ -21012,22 +21018,22 @@
         <v>41</v>
       </c>
       <c r="H337" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="I337" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="J337" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="K337" t="s">
-        <v>158</v>
+        <v>266</v>
       </c>
       <c r="L337" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="M337" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="N337" t="s">
         <v>45</v>
@@ -21036,7 +21042,7 @@
         <v>153</v>
       </c>
       <c r="P337" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="Q337" t="s">
         <v>45</v>
@@ -21047,19 +21053,19 @@
     </row>
     <row r="338">
       <c r="A338" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="B338" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="C338" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="D338" t="s">
         <v>33</v>
       </c>
       <c r="E338" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="F338" t="s">
         <v>173</v>
@@ -21068,22 +21074,22 @@
         <v>41</v>
       </c>
       <c r="H338" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="I338" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="J338" t="s">
-        <v>746</v>
+        <v>733</v>
       </c>
       <c r="K338" t="s">
         <v>266</v>
       </c>
       <c r="L338" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="M338" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="N338" t="s">
         <v>45</v>
@@ -21092,7 +21098,7 @@
         <v>153</v>
       </c>
       <c r="P338" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="Q338" t="s">
         <v>45</v>
@@ -21103,13 +21109,13 @@
     </row>
     <row r="339">
       <c r="A339" t="s" s="1">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="B339" t="s" s="1">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="C339" t="s" s="1">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="D339" t="s" s="1">
         <v>33</v>
@@ -21159,13 +21165,13 @@
     </row>
     <row r="340">
       <c r="A340" t="s" s="1">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="B340" t="s" s="1">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="C340" t="s" s="1">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="D340" t="s" s="1">
         <v>33</v>
@@ -21215,13 +21221,13 @@
     </row>
     <row r="341">
       <c r="A341" t="s" s="1">
+        <v>810</v>
+      </c>
+      <c r="B341" t="s" s="1">
         <v>808</v>
       </c>
-      <c r="B341" t="s" s="1">
-        <v>806</v>
-      </c>
       <c r="C341" t="s" s="1">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="D341" t="s" s="1">
         <v>33</v>
@@ -21271,19 +21277,19 @@
     </row>
     <row r="342">
       <c r="A342" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="B342" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="C342" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="D342" t="s">
         <v>33</v>
       </c>
       <c r="E342" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="F342" t="s">
         <v>198</v>
@@ -21292,10 +21298,10 @@
         <v>41</v>
       </c>
       <c r="H342" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="I342" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="J342" t="s">
         <v>201</v>
@@ -21307,7 +21313,7 @@
         <v>34</v>
       </c>
       <c r="M342" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="N342" t="s">
         <v>45</v>
@@ -21316,7 +21322,7 @@
         <v>153</v>
       </c>
       <c r="P342" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="Q342" t="s">
         <v>45</v>
@@ -21327,13 +21333,13 @@
     </row>
     <row r="343">
       <c r="A343" t="s" s="1">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="B343" t="s" s="1">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="C343" t="s" s="1">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="D343" t="s" s="1">
         <v>33</v>
@@ -21383,13 +21389,13 @@
     </row>
     <row r="344">
       <c r="A344" t="s" s="1">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="B344" t="s" s="1">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="C344" t="s" s="1">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="D344" t="s" s="1">
         <v>33</v>
@@ -21439,13 +21445,13 @@
     </row>
     <row r="345">
       <c r="A345" t="s" s="1">
+        <v>818</v>
+      </c>
+      <c r="B345" t="s" s="1">
         <v>816</v>
       </c>
-      <c r="B345" t="s" s="1">
-        <v>814</v>
-      </c>
       <c r="C345" t="s" s="1">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="D345" t="s" s="1">
         <v>33</v>
@@ -21495,13 +21501,13 @@
     </row>
     <row r="346">
       <c r="A346" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="B346" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="C346" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="D346" t="s">
         <v>33</v>
@@ -21516,10 +21522,10 @@
         <v>41</v>
       </c>
       <c r="H346" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="I346" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="J346" t="s">
         <v>81</v>
@@ -21528,10 +21534,10 @@
         <v>81</v>
       </c>
       <c r="L346" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="M346" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="N346" t="s">
         <v>45</v>
@@ -21551,7 +21557,7 @@
     </row>
     <row r="347">
       <c r="A347" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="B347" t="s">
         <v>34</v>
@@ -21572,10 +21578,10 @@
         <v>41</v>
       </c>
       <c r="H347" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="I347" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="J347" t="s">
         <v>60</v>
@@ -21584,10 +21590,10 @@
         <v>60</v>
       </c>
       <c r="L347" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="M347" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="N347" t="s">
         <v>45</v>
@@ -21607,7 +21613,7 @@
     </row>
     <row r="348">
       <c r="A348" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="B348" t="s">
         <v>34</v>
@@ -21628,10 +21634,10 @@
         <v>41</v>
       </c>
       <c r="H348" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="I348" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="J348" t="s">
         <v>88</v>
@@ -21640,10 +21646,10 @@
         <v>88</v>
       </c>
       <c r="L348" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="M348" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="N348" t="s">
         <v>45</v>
@@ -21663,7 +21669,7 @@
     </row>
     <row r="349">
       <c r="A349" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="B349" t="s">
         <v>34</v>
@@ -21684,10 +21690,10 @@
         <v>41</v>
       </c>
       <c r="H349" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="I349" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="J349" t="s">
         <v>60</v>
@@ -21696,10 +21702,10 @@
         <v>60</v>
       </c>
       <c r="L349" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="M349" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="N349" t="s">
         <v>45</v>
@@ -21719,7 +21725,7 @@
     </row>
     <row r="350">
       <c r="A350" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="B350" t="s">
         <v>34</v>
@@ -21740,10 +21746,10 @@
         <v>41</v>
       </c>
       <c r="H350" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="I350" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="J350" t="s">
         <v>60</v>
@@ -21752,10 +21758,10 @@
         <v>60</v>
       </c>
       <c r="L350" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="M350" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="N350" t="s">
         <v>45</v>
@@ -21775,7 +21781,7 @@
     </row>
     <row r="351">
       <c r="A351" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="B351" t="s">
         <v>34</v>
@@ -21796,10 +21802,10 @@
         <v>41</v>
       </c>
       <c r="H351" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="I351" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="J351" t="s">
         <v>60</v>
@@ -21808,10 +21814,10 @@
         <v>60</v>
       </c>
       <c r="L351" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="M351" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="N351" t="s">
         <v>45</v>
@@ -21831,7 +21837,7 @@
     </row>
     <row r="352">
       <c r="A352" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="B352" t="s">
         <v>34</v>
@@ -21852,10 +21858,10 @@
         <v>41</v>
       </c>
       <c r="H352" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="I352" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="J352" t="s">
         <v>130</v>
@@ -21864,10 +21870,10 @@
         <v>130</v>
       </c>
       <c r="L352" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="M352" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="N352" t="s">
         <v>45</v>
@@ -21887,7 +21893,7 @@
     </row>
     <row r="353">
       <c r="A353" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="B353" t="s">
         <v>34</v>
@@ -21908,10 +21914,10 @@
         <v>41</v>
       </c>
       <c r="H353" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="I353" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="J353" t="s">
         <v>67</v>
@@ -21920,10 +21926,10 @@
         <v>67</v>
       </c>
       <c r="L353" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="M353" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="N353" t="s">
         <v>45</v>
@@ -21943,7 +21949,7 @@
     </row>
     <row r="354">
       <c r="A354" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="B354" t="s">
         <v>34</v>
@@ -21964,10 +21970,10 @@
         <v>41</v>
       </c>
       <c r="H354" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="I354" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="J354" t="s">
         <v>108</v>
@@ -21976,10 +21982,10 @@
         <v>108</v>
       </c>
       <c r="L354" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="M354" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="N354" t="s">
         <v>45</v>
@@ -21999,7 +22005,7 @@
     </row>
     <row r="355">
       <c r="A355" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="B355" t="s">
         <v>34</v>
@@ -22020,10 +22026,10 @@
         <v>41</v>
       </c>
       <c r="H355" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="I355" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="J355" t="s">
         <v>130</v>
@@ -22032,10 +22038,10 @@
         <v>130</v>
       </c>
       <c r="L355" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="M355" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="N355" t="s">
         <v>45</v>
@@ -22055,7 +22061,7 @@
     </row>
     <row r="356">
       <c r="A356" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="B356" t="s">
         <v>34</v>
@@ -22076,10 +22082,10 @@
         <v>41</v>
       </c>
       <c r="H356" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="I356" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="J356" t="s">
         <v>130</v>
@@ -22088,10 +22094,10 @@
         <v>130</v>
       </c>
       <c r="L356" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="M356" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="N356" t="s">
         <v>45</v>
@@ -22111,7 +22117,7 @@
     </row>
     <row r="357">
       <c r="A357" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="B357" t="s">
         <v>34</v>
@@ -22132,10 +22138,10 @@
         <v>41</v>
       </c>
       <c r="H357" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="I357" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="J357" t="s">
         <v>118</v>
@@ -22144,10 +22150,10 @@
         <v>118</v>
       </c>
       <c r="L357" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="M357" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="N357" t="s">
         <v>45</v>
@@ -22167,7 +22173,7 @@
     </row>
     <row r="358">
       <c r="A358" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="B358" t="s">
         <v>34</v>
@@ -22188,10 +22194,10 @@
         <v>41</v>
       </c>
       <c r="H358" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="I358" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="J358" t="s">
         <v>67</v>
@@ -22200,10 +22206,10 @@
         <v>67</v>
       </c>
       <c r="L358" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="M358" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="N358" t="s">
         <v>45</v>
@@ -22223,7 +22229,7 @@
     </row>
     <row r="359">
       <c r="A359" t="s" s="1">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="B359" t="s" s="1">
         <v>32</v>
@@ -22279,7 +22285,7 @@
     </row>
     <row r="360">
       <c r="A360" t="s" s="1">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="B360" t="s" s="1">
         <v>32</v>
@@ -22335,7 +22341,7 @@
     </row>
     <row r="361">
       <c r="A361" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="B361" t="s">
         <v>32</v>
@@ -22391,7 +22397,7 @@
     </row>
     <row r="362">
       <c r="A362" t="s" s="1">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="B362" t="s" s="1">
         <v>168</v>
@@ -22447,7 +22453,7 @@
     </row>
     <row r="363">
       <c r="A363" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="B363" t="s">
         <v>168</v>
@@ -22503,13 +22509,13 @@
     </row>
     <row r="364">
       <c r="A364" t="s" s="1">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="B364" t="s" s="1">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="C364" t="s" s="1">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="D364" t="s" s="1">
         <v>33</v>
@@ -22559,7 +22565,7 @@
     </row>
     <row r="365">
       <c r="A365" t="s" s="1">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="B365" t="s" s="1">
         <v>191</v>
@@ -22615,7 +22621,7 @@
     </row>
     <row r="366">
       <c r="A366" t="s" s="1">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="B366" t="s" s="1">
         <v>193</v>
@@ -22671,7 +22677,7 @@
     </row>
     <row r="367">
       <c r="A367" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="B367" t="s">
         <v>193</v>
@@ -22727,7 +22733,7 @@
     </row>
     <row r="368">
       <c r="A368" t="s" s="1">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="B368" t="s" s="1">
         <v>298</v>
@@ -22783,7 +22789,7 @@
     </row>
     <row r="369">
       <c r="A369" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="B369" t="s">
         <v>298</v>
@@ -22839,13 +22845,13 @@
     </row>
     <row r="370">
       <c r="A370" t="s" s="1">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="B370" t="s" s="1">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="C370" t="s" s="1">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="D370" t="s" s="1">
         <v>33</v>
@@ -22895,13 +22901,13 @@
     </row>
     <row r="371">
       <c r="A371" t="s" s="1">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="B371" t="s" s="1">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="C371" t="s" s="1">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="D371" t="s" s="1">
         <v>33</v>
@@ -22951,7 +22957,7 @@
     </row>
     <row r="372">
       <c r="A372" t="s" s="1">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="B372" t="s" s="1">
         <v>359</v>
@@ -23007,7 +23013,7 @@
     </row>
     <row r="373">
       <c r="A373" t="s" s="1">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="B373" t="s" s="1">
         <v>361</v>
@@ -23063,7 +23069,7 @@
     </row>
     <row r="374">
       <c r="A374" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="B374" t="s">
         <v>361</v>
@@ -23119,13 +23125,13 @@
     </row>
     <row r="375">
       <c r="A375" t="s" s="1">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="B375" t="s" s="1">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="C375" t="s" s="1">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="D375" t="s" s="1">
         <v>33</v>
@@ -23175,13 +23181,13 @@
     </row>
     <row r="376">
       <c r="A376" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="B376" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="C376" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="D376" t="s">
         <v>33</v>
@@ -23231,13 +23237,13 @@
     </row>
     <row r="377">
       <c r="A377" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="B377" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="C377" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="D377" t="s">
         <v>33</v>
@@ -23287,13 +23293,13 @@
     </row>
     <row r="378">
       <c r="A378" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="B378" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="C378" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="D378" t="s">
         <v>33</v>
@@ -23343,13 +23349,13 @@
     </row>
     <row r="379">
       <c r="A379" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="B379" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="C379" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D379" t="s">
         <v>33</v>
@@ -23399,13 +23405,13 @@
     </row>
     <row r="380">
       <c r="A380" t="s" s="1">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="B380" t="s" s="1">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="C380" t="s" s="1">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="D380" t="s" s="1">
         <v>33</v>
@@ -23455,13 +23461,13 @@
     </row>
     <row r="381">
       <c r="A381" t="s" s="1">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="B381" t="s" s="1">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="C381" t="s" s="1">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="D381" t="s" s="1">
         <v>33</v>
@@ -23511,13 +23517,13 @@
     </row>
     <row r="382">
       <c r="A382" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="B382" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="C382" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="D382" t="s">
         <v>33</v>
@@ -23567,13 +23573,13 @@
     </row>
     <row r="383">
       <c r="A383" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="B383" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="C383" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="D383" t="s">
         <v>33</v>
@@ -23623,13 +23629,13 @@
     </row>
     <row r="384">
       <c r="A384" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="B384" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="C384" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="D384" t="s">
         <v>33</v>
@@ -23679,13 +23685,13 @@
     </row>
     <row r="385">
       <c r="A385" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="B385" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="C385" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="D385" t="s">
         <v>33</v>
@@ -23735,13 +23741,13 @@
     </row>
     <row r="386">
       <c r="A386" t="s" s="1">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="B386" t="s" s="1">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="C386" t="s" s="1">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="D386" t="s" s="1">
         <v>33</v>
@@ -23791,13 +23797,13 @@
     </row>
     <row r="387">
       <c r="A387" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="B387" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="C387" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="D387" t="s">
         <v>33</v>
@@ -23847,13 +23853,13 @@
     </row>
     <row r="388">
       <c r="A388" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="B388" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="C388" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="D388" t="s">
         <v>33</v>
@@ -23903,13 +23909,13 @@
     </row>
     <row r="389">
       <c r="A389" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="B389" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="C389" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="D389" t="s">
         <v>33</v>
@@ -23959,13 +23965,13 @@
     </row>
     <row r="390">
       <c r="A390" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="B390" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="C390" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="D390" t="s">
         <v>33</v>
@@ -24015,13 +24021,13 @@
     </row>
     <row r="391">
       <c r="A391" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="B391" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="C391" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="D391" t="s">
         <v>33</v>
@@ -24071,13 +24077,13 @@
     </row>
     <row r="392">
       <c r="A392" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="B392" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="C392" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="D392" t="s">
         <v>33</v>
@@ -24127,13 +24133,13 @@
     </row>
     <row r="393">
       <c r="A393" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="B393" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="C393" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="D393" t="s">
         <v>33</v>
@@ -24183,13 +24189,13 @@
     </row>
     <row r="394">
       <c r="A394" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="B394" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="C394" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="D394" t="s">
         <v>33</v>
@@ -24239,13 +24245,13 @@
     </row>
     <row r="395">
       <c r="A395" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="B395" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="C395" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="D395" t="s">
         <v>33</v>
@@ -24295,13 +24301,13 @@
     </row>
     <row r="396">
       <c r="A396" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="B396" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="C396" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="D396" t="s">
         <v>33</v>
@@ -24351,13 +24357,13 @@
     </row>
     <row r="397">
       <c r="A397" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="B397" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="C397" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="D397" t="s">
         <v>33</v>
@@ -24407,13 +24413,13 @@
     </row>
     <row r="398">
       <c r="A398" t="s" s="1">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="B398" t="s" s="1">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="C398" t="s" s="1">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="D398" t="s" s="1">
         <v>33</v>
@@ -24463,13 +24469,13 @@
     </row>
     <row r="399">
       <c r="A399" t="s" s="1">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="B399" t="s" s="1">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="C399" t="s" s="1">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="D399" t="s" s="1">
         <v>33</v>
@@ -24519,13 +24525,13 @@
     </row>
     <row r="400">
       <c r="A400" t="s" s="1">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="B400" t="s" s="1">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="C400" t="s" s="1">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="D400" t="s" s="1">
         <v>33</v>
@@ -24575,13 +24581,13 @@
     </row>
     <row r="401">
       <c r="A401" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="B401" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="C401" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="D401" t="s">
         <v>33</v>
@@ -24631,13 +24637,13 @@
     </row>
     <row r="402">
       <c r="A402" t="s" s="1">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="B402" t="s" s="1">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="C402" t="s" s="1">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="D402" t="s" s="1">
         <v>33</v>
@@ -24687,13 +24693,13 @@
     </row>
     <row r="403">
       <c r="A403" t="s">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="B403" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="C403" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="D403" t="s">
         <v>33</v>
@@ -24743,13 +24749,13 @@
     </row>
     <row r="404">
       <c r="A404" t="s" s="1">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="B404" t="s" s="1">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="C404" t="s" s="1">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="D404" t="s" s="1">
         <v>33</v>
@@ -24799,13 +24805,13 @@
     </row>
     <row r="405">
       <c r="A405" t="s" s="1">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="B405" t="s" s="1">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="C405" t="s" s="1">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="D405" t="s" s="1">
         <v>33</v>
@@ -24855,13 +24861,13 @@
     </row>
     <row r="406">
       <c r="A406" t="s" s="1">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="B406" t="s" s="1">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="C406" t="s" s="1">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="D406" t="s" s="1">
         <v>33</v>
@@ -24911,7 +24917,7 @@
     </row>
     <row r="407">
       <c r="A407" t="s" s="1">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="B407" t="s" s="1">
         <v>32</v>
@@ -24967,13 +24973,13 @@
     </row>
     <row r="408">
       <c r="A408" t="s" s="1">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B408" t="s" s="1">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="C408" t="s" s="1">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="D408" t="s" s="1">
         <v>33</v>
@@ -25023,7 +25029,7 @@
     </row>
     <row r="409">
       <c r="A409" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="B409" t="s">
         <v>168</v>
@@ -25079,7 +25085,7 @@
     </row>
     <row r="410">
       <c r="A410" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="B410" t="s">
         <v>191</v>
@@ -25135,7 +25141,7 @@
     </row>
     <row r="411">
       <c r="A411" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="B411" t="s">
         <v>359</v>
@@ -25191,13 +25197,13 @@
     </row>
     <row r="412">
       <c r="A412" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="B412" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="C412" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="D412" t="s">
         <v>33</v>
@@ -25247,13 +25253,13 @@
     </row>
     <row r="413">
       <c r="A413" t="s" s="1">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="B413" t="s" s="1">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="C413" t="s" s="1">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="D413" t="s" s="1">
         <v>33</v>
@@ -25303,13 +25309,13 @@
     </row>
     <row r="414">
       <c r="A414" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="B414" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="C414" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="D414" t="s">
         <v>33</v>
@@ -25359,13 +25365,13 @@
     </row>
     <row r="415">
       <c r="A415" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="B415" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="C415" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="D415" t="s">
         <v>33</v>
@@ -25415,7 +25421,7 @@
     </row>
     <row r="416">
       <c r="A416" t="s">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="B416" t="s">
         <v>32</v>
@@ -25471,13 +25477,13 @@
     </row>
     <row r="417">
       <c r="A417" t="s">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="B417" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="C417" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="D417" t="s">
         <v>33</v>
@@ -25527,13 +25533,13 @@
     </row>
     <row r="418">
       <c r="A418" t="s">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="B418" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="C418" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="D418" t="s">
         <v>33</v>
@@ -25583,7 +25589,7 @@
     </row>
     <row r="419">
       <c r="A419" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="B419" t="s">
         <v>193</v>
@@ -25639,7 +25645,7 @@
     </row>
     <row r="420">
       <c r="A420" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="B420" t="s">
         <v>361</v>
@@ -25695,13 +25701,13 @@
     </row>
     <row r="421">
       <c r="A421" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="B421" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="C421" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="D421" t="s">
         <v>33</v>
@@ -25751,13 +25757,13 @@
     </row>
     <row r="422">
       <c r="A422" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="B422" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="C422" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="D422" t="s">
         <v>33</v>
@@ -25807,7 +25813,7 @@
     </row>
     <row r="423">
       <c r="A423" t="s">
-        <v>906</v>
+        <v>908</v>
       </c>
       <c r="B423" t="s">
         <v>168</v>
@@ -25863,13 +25869,13 @@
     </row>
     <row r="424">
       <c r="A424" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="B424" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="C424" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="D424" t="s">
         <v>33</v>
@@ -25919,13 +25925,13 @@
     </row>
     <row r="425">
       <c r="A425" t="s">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="B425" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="C425" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="D425" t="s">
         <v>33</v>
@@ -25975,13 +25981,13 @@
     </row>
     <row r="426">
       <c r="A426" t="s" s="1">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="B426" t="s" s="1">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="C426" t="s" s="1">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="D426" t="s" s="1">
         <v>33</v>
@@ -26031,16 +26037,16 @@
     </row>
     <row r="427">
       <c r="A427" t="s" s="1">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="B427" t="s" s="1">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="C427" t="s" s="1">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="D427" t="s" s="1">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="E427" t="s" s="1">
         <v>34</v>
@@ -26087,16 +26093,16 @@
     </row>
     <row r="428">
       <c r="A428" t="s" s="1">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="B428" t="s" s="1">
+        <v>917</v>
+      </c>
+      <c r="C428" t="s" s="1">
+        <v>917</v>
+      </c>
+      <c r="D428" t="s" s="1">
         <v>915</v>
-      </c>
-      <c r="C428" t="s" s="1">
-        <v>915</v>
-      </c>
-      <c r="D428" t="s" s="1">
-        <v>913</v>
       </c>
       <c r="E428" t="s" s="1">
         <v>34</v>
@@ -26143,16 +26149,16 @@
     </row>
     <row r="429">
       <c r="A429" t="s" s="1">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="B429" t="s" s="1">
+        <v>917</v>
+      </c>
+      <c r="C429" t="s" s="1">
+        <v>917</v>
+      </c>
+      <c r="D429" t="s" s="1">
         <v>915</v>
-      </c>
-      <c r="C429" t="s" s="1">
-        <v>915</v>
-      </c>
-      <c r="D429" t="s" s="1">
-        <v>913</v>
       </c>
       <c r="E429" t="s" s="1">
         <v>34</v>
@@ -26199,13 +26205,13 @@
     </row>
     <row r="430">
       <c r="A430" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="B430" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="C430" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="D430" t="s">
         <v>33</v>
@@ -26255,19 +26261,19 @@
     </row>
     <row r="431">
       <c r="A431" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="B431" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="C431" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="D431" t="s">
         <v>33</v>
       </c>
       <c r="E431" t="s">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="F431" t="s">
         <v>63</v>
@@ -26276,22 +26282,22 @@
         <v>41</v>
       </c>
       <c r="H431" t="s">
+        <v>923</v>
+      </c>
+      <c r="I431" t="s">
+        <v>924</v>
+      </c>
+      <c r="J431" t="s">
+        <v>925</v>
+      </c>
+      <c r="K431" t="s">
+        <v>604</v>
+      </c>
+      <c r="L431" t="s">
+        <v>926</v>
+      </c>
+      <c r="M431" t="s">
         <v>921</v>
-      </c>
-      <c r="I431" t="s">
-        <v>922</v>
-      </c>
-      <c r="J431" t="s">
-        <v>923</v>
-      </c>
-      <c r="K431" t="s">
-        <v>602</v>
-      </c>
-      <c r="L431" t="s">
-        <v>924</v>
-      </c>
-      <c r="M431" t="s">
-        <v>919</v>
       </c>
       <c r="N431" t="s">
         <v>45</v>
@@ -26300,7 +26306,7 @@
         <v>153</v>
       </c>
       <c r="P431" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="Q431" t="s">
         <v>45</v>
@@ -26311,7 +26317,7 @@
     </row>
     <row r="432">
       <c r="A432" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="B432" t="s">
         <v>34</v>
@@ -26323,7 +26329,7 @@
         <v>34</v>
       </c>
       <c r="E432" t="s">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="F432" t="s">
         <v>63</v>
@@ -26332,10 +26338,10 @@
         <v>41</v>
       </c>
       <c r="H432" t="s">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="I432" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="J432" t="s">
         <v>67</v>
@@ -26347,7 +26353,7 @@
         <v>34</v>
       </c>
       <c r="M432" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="N432" t="s">
         <v>45</v>
@@ -26356,7 +26362,7 @@
         <v>153</v>
       </c>
       <c r="P432" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="Q432" t="s">
         <v>45</v>
@@ -26367,7 +26373,7 @@
     </row>
     <row r="433">
       <c r="A433" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="B433" t="s">
         <v>34</v>
@@ -26379,7 +26385,7 @@
         <v>34</v>
       </c>
       <c r="E433" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="F433" t="s">
         <v>198</v>
@@ -26388,22 +26394,22 @@
         <v>41</v>
       </c>
       <c r="H433" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="I433" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="J433" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="K433" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="L433" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="M433" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="N433" t="s">
         <v>45</v>
@@ -26412,7 +26418,7 @@
         <v>153</v>
       </c>
       <c r="P433" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="Q433" t="s">
         <v>45</v>
@@ -26423,7 +26429,7 @@
     </row>
     <row r="434">
       <c r="A434" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="B434" t="s">
         <v>34</v>
@@ -26435,7 +26441,7 @@
         <v>34</v>
       </c>
       <c r="E434" t="s">
-        <v>931</v>
+        <v>933</v>
       </c>
       <c r="F434" t="s">
         <v>63</v>
@@ -26444,10 +26450,10 @@
         <v>41</v>
       </c>
       <c r="H434" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="I434" t="s">
-        <v>933</v>
+        <v>935</v>
       </c>
       <c r="J434" t="s">
         <v>108</v>
@@ -26456,10 +26462,10 @@
         <v>118</v>
       </c>
       <c r="L434" t="s">
-        <v>924</v>
+        <v>926</v>
       </c>
       <c r="M434" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="N434" t="s">
         <v>45</v>
@@ -26468,7 +26474,7 @@
         <v>153</v>
       </c>
       <c r="P434" t="s">
-        <v>933</v>
+        <v>935</v>
       </c>
       <c r="Q434" t="s">
         <v>45</v>
@@ -26479,7 +26485,7 @@
     </row>
     <row r="435">
       <c r="A435" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="B435" t="s">
         <v>34</v>
@@ -26491,7 +26497,7 @@
         <v>34</v>
       </c>
       <c r="E435" t="s">
-        <v>934</v>
+        <v>936</v>
       </c>
       <c r="F435" t="s">
         <v>63</v>
@@ -26500,10 +26506,10 @@
         <v>41</v>
       </c>
       <c r="H435" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="I435" t="s">
-        <v>935</v>
+        <v>937</v>
       </c>
       <c r="J435" t="s">
         <v>121</v>
@@ -26512,10 +26518,10 @@
         <v>146</v>
       </c>
       <c r="L435" t="s">
-        <v>936</v>
+        <v>938</v>
       </c>
       <c r="M435" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="N435" t="s">
         <v>45</v>
@@ -26524,7 +26530,7 @@
         <v>153</v>
       </c>
       <c r="P435" t="s">
-        <v>935</v>
+        <v>937</v>
       </c>
       <c r="Q435" t="s">
         <v>45</v>
@@ -26535,7 +26541,7 @@
     </row>
     <row r="436">
       <c r="A436" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="B436" t="s">
         <v>34</v>
@@ -26547,7 +26553,7 @@
         <v>34</v>
       </c>
       <c r="E436" t="s">
-        <v>937</v>
+        <v>939</v>
       </c>
       <c r="F436" t="s">
         <v>63</v>
@@ -26556,22 +26562,22 @@
         <v>41</v>
       </c>
       <c r="H436" t="s">
+        <v>923</v>
+      </c>
+      <c r="I436" t="s">
+        <v>928</v>
+      </c>
+      <c r="J436" t="s">
+        <v>604</v>
+      </c>
+      <c r="K436" t="s">
+        <v>604</v>
+      </c>
+      <c r="L436" t="s">
+        <v>926</v>
+      </c>
+      <c r="M436" t="s">
         <v>921</v>
-      </c>
-      <c r="I436" t="s">
-        <v>926</v>
-      </c>
-      <c r="J436" t="s">
-        <v>602</v>
-      </c>
-      <c r="K436" t="s">
-        <v>602</v>
-      </c>
-      <c r="L436" t="s">
-        <v>924</v>
-      </c>
-      <c r="M436" t="s">
-        <v>919</v>
       </c>
       <c r="N436" t="s">
         <v>45</v>
@@ -26580,7 +26586,7 @@
         <v>153</v>
       </c>
       <c r="P436" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="Q436" t="s">
         <v>45</v>
@@ -26591,7 +26597,7 @@
     </row>
     <row r="437">
       <c r="A437" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="B437" t="s">
         <v>34</v>
@@ -26603,7 +26609,7 @@
         <v>34</v>
       </c>
       <c r="E437" t="s">
-        <v>938</v>
+        <v>940</v>
       </c>
       <c r="F437" t="s">
         <v>198</v>
@@ -26612,10 +26618,10 @@
         <v>41</v>
       </c>
       <c r="H437" t="s">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="I437" t="s">
-        <v>939</v>
+        <v>941</v>
       </c>
       <c r="J437" t="s">
         <v>66</v>
@@ -26627,7 +26633,7 @@
         <v>34</v>
       </c>
       <c r="M437" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="N437" t="s">
         <v>45</v>
@@ -26636,7 +26642,7 @@
         <v>153</v>
       </c>
       <c r="P437" t="s">
-        <v>939</v>
+        <v>941</v>
       </c>
       <c r="Q437" t="s">
         <v>45</v>

--- a/xlsx/dre/DRE_08_2026.xlsx
+++ b/xlsx/dre/DRE_08_2026.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7618" uniqueCount="942">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7618" uniqueCount="943">
   <si>
     <t>Movimentações Financeiras</t>
   </si>
@@ -477,6 +477,24 @@
     <t>ADM</t>
   </si>
   <si>
+    <t>1/7</t>
+  </si>
+  <si>
+    <t>MP Interiores e Serv Ltda</t>
+  </si>
+  <si>
+    <t>R$  511,90</t>
+  </si>
+  <si>
+    <t>27/02/26</t>
+  </si>
+  <si>
+    <t>18/08/26</t>
+  </si>
+  <si>
+    <t>Digisac MP 2026</t>
+  </si>
+  <si>
     <t>38/1</t>
   </si>
   <si>
@@ -490,24 +508,6 @@
   </si>
   <si>
     <t>INSS</t>
-  </si>
-  <si>
-    <t>1/7</t>
-  </si>
-  <si>
-    <t>MP Interiores e Serv Ltda</t>
-  </si>
-  <si>
-    <t>R$  511,90</t>
-  </si>
-  <si>
-    <t>27/02/26</t>
-  </si>
-  <si>
-    <t>18/08/26</t>
-  </si>
-  <si>
-    <t>Digisac MP 2026</t>
   </si>
   <si>
     <t>4 CUSTOS E DESPESAS</t>
@@ -1605,12 +1605,12 @@
     <t>4.03.03.02.05.02 Assistência técnica medição</t>
   </si>
   <si>
+    <t>PFP</t>
+  </si>
+  <si>
     <t>L E A Medicoes Tecnicas LTDA</t>
   </si>
   <si>
-    <t>PFP</t>
-  </si>
-  <si>
     <t>R$  360,00</t>
   </si>
   <si>
@@ -1665,9 +1665,30 @@
     <t>R$ 9.215,99</t>
   </si>
   <si>
+    <t>WEBGIGA SOLUCOES DIGITAIS LTDA</t>
+  </si>
+  <si>
+    <t>R$  4.642,50</t>
+  </si>
+  <si>
+    <t>18/02/26</t>
+  </si>
+  <si>
+    <t>Webgiga 2026</t>
+  </si>
+  <si>
     <t>12/8</t>
   </si>
   <si>
+    <t>Google</t>
+  </si>
+  <si>
+    <t>R$  14,99</t>
+  </si>
+  <si>
+    <t>Google 2026</t>
+  </si>
+  <si>
     <t>MARQUES MAIO MARKETING DIGITAL LTDA</t>
   </si>
   <si>
@@ -1680,27 +1701,6 @@
     <t>MHM - Honorários 2026</t>
   </si>
   <si>
-    <t>Google</t>
-  </si>
-  <si>
-    <t>R$  14,99</t>
-  </si>
-  <si>
-    <t>Google 2026</t>
-  </si>
-  <si>
-    <t>WEBGIGA SOLUCOES DIGITAIS LTDA</t>
-  </si>
-  <si>
-    <t>R$  4.642,50</t>
-  </si>
-  <si>
-    <t>18/02/26</t>
-  </si>
-  <si>
-    <t>Webgiga 2026</t>
-  </si>
-  <si>
     <t>1/6</t>
   </si>
   <si>
@@ -1822,6 +1822,9 @@
   </si>
   <si>
     <t>Estorno empréstimo</t>
+  </si>
+  <si>
+    <t>CARINA PEREIRA</t>
   </si>
   <si>
     <t>R$  2.365,00</t>
@@ -2124,6 +2127,18 @@
     <t xml:space="preserve">04/08/2026	•••• •••• •••• 0005497380066700654	SUPERMERCADO	Compra à vista		105,06	PAO DE ACUCAR 2409     	Materiais limpeza e pao de queijo
 25/08/2026	•••• •••• •••• 0005497380066700654	SUPERMERCADO	Compra à vista		307,33	PAO DE ACUCAR 2409	Materiais limpeza 
 </t>
+  </si>
+  <si>
+    <t>736/1</t>
+  </si>
+  <si>
+    <t>Casa de Bolos de Moema LTDA</t>
+  </si>
+  <si>
+    <t>R$  97,00</t>
+  </si>
+  <si>
+    <t>Bolo Bianca</t>
   </si>
   <si>
     <t>745/1</t>
@@ -2151,18 +2166,6 @@
     <t>R$  5,95</t>
   </si>
   <si>
-    <t>736/1</t>
-  </si>
-  <si>
-    <t>Casa de Bolos de Moema LTDA</t>
-  </si>
-  <si>
-    <t>R$  97,00</t>
-  </si>
-  <si>
-    <t>Bolo Bianca</t>
-  </si>
-  <si>
     <t>4.04.02.07 Informática</t>
   </si>
   <si>
@@ -2223,6 +2226,51 @@
     <t>4.04.02.08.03 Mensalidades e assinaturas - outros gastos</t>
   </si>
   <si>
+    <t>70/12</t>
+  </si>
+  <si>
+    <t>R$  188,22</t>
+  </si>
+  <si>
+    <t>Promob 26/5</t>
+  </si>
+  <si>
+    <t>63/3</t>
+  </si>
+  <si>
+    <t>R$  376,38</t>
+  </si>
+  <si>
+    <t>11/06/26</t>
+  </si>
+  <si>
+    <t>Promob 2026/4</t>
+  </si>
+  <si>
+    <t>R$  599,00</t>
+  </si>
+  <si>
+    <t>Promob 2026</t>
+  </si>
+  <si>
+    <t>62/3</t>
+  </si>
+  <si>
+    <t>R$  293,11</t>
+  </si>
+  <si>
+    <t>Promob 2026/3</t>
+  </si>
+  <si>
+    <t>D4 sign</t>
+  </si>
+  <si>
+    <t>R$  49,95</t>
+  </si>
+  <si>
+    <t>D4 sign 2026</t>
+  </si>
+  <si>
     <t>3/7</t>
   </si>
   <si>
@@ -2235,34 +2283,16 @@
     <t>Promob 2026/2</t>
   </si>
   <si>
-    <t>D4 sign</t>
-  </si>
-  <si>
-    <t>R$  49,95</t>
-  </si>
-  <si>
-    <t>D4 sign 2026</t>
-  </si>
-  <si>
-    <t>63/3</t>
-  </si>
-  <si>
-    <t>R$  376,38</t>
-  </si>
-  <si>
-    <t>11/06/26</t>
-  </si>
-  <si>
-    <t>Promob 2026/4</t>
-  </si>
-  <si>
-    <t>70/12</t>
-  </si>
-  <si>
-    <t>R$  188,22</t>
-  </si>
-  <si>
-    <t>Promob 26/5</t>
+    <t>61/4</t>
+  </si>
+  <si>
+    <t>Pipefy</t>
+  </si>
+  <si>
+    <t>R$  98,71</t>
+  </si>
+  <si>
+    <t>21/05/26</t>
   </si>
   <si>
     <t>64/3</t>
@@ -2281,33 +2311,6 @@
   </si>
   <si>
     <t>ISO Implantação -Saude ocupacional</t>
-  </si>
-  <si>
-    <t>62/3</t>
-  </si>
-  <si>
-    <t>R$  293,11</t>
-  </si>
-  <si>
-    <t>Promob 2026/3</t>
-  </si>
-  <si>
-    <t>R$  599,00</t>
-  </si>
-  <si>
-    <t>Promob 2026</t>
-  </si>
-  <si>
-    <t>61/4</t>
-  </si>
-  <si>
-    <t>Pipefy</t>
-  </si>
-  <si>
-    <t>R$  98,71</t>
-  </si>
-  <si>
-    <t>21/05/26</t>
   </si>
   <si>
     <t>4.04.02.11 Manutenção de predio e equipamentos</t>
@@ -2419,6 +2422,15 @@
     <t>R$ 400,33</t>
   </si>
   <si>
+    <t>Jackson Fernando de Araujo</t>
+  </si>
+  <si>
+    <t>R$  150,00</t>
+  </si>
+  <si>
+    <t>Segurança 2026</t>
+  </si>
+  <si>
     <t>VERISURE</t>
   </si>
   <si>
@@ -2426,15 +2438,6 @@
   </si>
   <si>
     <t>Verisure - Alarme 2026</t>
-  </si>
-  <si>
-    <t>Jackson Fernando de Araujo</t>
-  </si>
-  <si>
-    <t>R$  150,00</t>
-  </si>
-  <si>
-    <t>Segurança 2026</t>
   </si>
   <si>
     <t>4.04.02.14.08 Site e newsletter da loja</t>
@@ -4899,10 +4902,10 @@
         <v>157</v>
       </c>
       <c r="K49" t="s">
-        <v>88</v>
+        <v>158</v>
       </c>
       <c r="L49" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M49" t="s">
         <v>147</v>
@@ -4937,7 +4940,7 @@
         <v>34</v>
       </c>
       <c r="E50" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F50" t="s">
         <v>63</v>
@@ -4946,16 +4949,16 @@
         <v>41</v>
       </c>
       <c r="H50" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I50" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J50" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="K50" t="s">
-        <v>163</v>
+        <v>88</v>
       </c>
       <c r="L50" t="s">
         <v>164</v>
@@ -4970,7 +4973,7 @@
         <v>153</v>
       </c>
       <c r="P50" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q50" t="s">
         <v>45</v>
@@ -5217,7 +5220,7 @@
         <v>33</v>
       </c>
       <c r="E55" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="F55" t="s">
         <v>173</v>
@@ -7248,7 +7251,7 @@
         <v>294</v>
       </c>
       <c r="J91" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="K91" t="s">
         <v>88</v>
@@ -15633,25 +15636,25 @@
         <v>33</v>
       </c>
       <c r="E241" t="s">
-        <v>221</v>
+        <v>240</v>
       </c>
       <c r="F241" t="s">
-        <v>173</v>
+        <v>527</v>
       </c>
       <c r="G241" t="s">
         <v>41</v>
       </c>
       <c r="H241" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I241" t="s">
         <v>200</v>
       </c>
       <c r="J241" t="s">
-        <v>67</v>
+        <v>118</v>
       </c>
       <c r="K241" t="s">
-        <v>67</v>
+        <v>118</v>
       </c>
       <c r="L241" t="s">
         <v>34</v>
@@ -15663,13 +15666,13 @@
         <v>45</v>
       </c>
       <c r="O241" t="s">
-        <v>327</v>
+        <v>34</v>
       </c>
       <c r="P241" t="s">
-        <v>200</v>
+        <v>34</v>
       </c>
       <c r="Q241" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="R241" t="s">
         <v>34</v>
@@ -15689,25 +15692,25 @@
         <v>34</v>
       </c>
       <c r="E242" t="s">
-        <v>240</v>
+        <v>218</v>
       </c>
       <c r="F242" t="s">
+        <v>173</v>
+      </c>
+      <c r="G242" t="s">
+        <v>41</v>
+      </c>
+      <c r="H242" t="s">
         <v>528</v>
-      </c>
-      <c r="G242" t="s">
-        <v>41</v>
-      </c>
-      <c r="H242" t="s">
-        <v>527</v>
       </c>
       <c r="I242" t="s">
         <v>200</v>
       </c>
       <c r="J242" t="s">
-        <v>118</v>
+        <v>67</v>
       </c>
       <c r="K242" t="s">
-        <v>118</v>
+        <v>67</v>
       </c>
       <c r="L242" t="s">
         <v>34</v>
@@ -15719,13 +15722,13 @@
         <v>45</v>
       </c>
       <c r="O242" t="s">
-        <v>34</v>
+        <v>247</v>
       </c>
       <c r="P242" t="s">
-        <v>34</v>
+        <v>200</v>
       </c>
       <c r="Q242" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R242" t="s">
         <v>34</v>
@@ -15745,25 +15748,25 @@
         <v>34</v>
       </c>
       <c r="E243" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="F243" t="s">
-        <v>173</v>
+        <v>527</v>
       </c>
       <c r="G243" t="s">
         <v>41</v>
       </c>
       <c r="H243" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I243" t="s">
         <v>200</v>
       </c>
       <c r="J243" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="K243" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="L243" t="s">
         <v>34</v>
@@ -15775,13 +15778,13 @@
         <v>45</v>
       </c>
       <c r="O243" t="s">
-        <v>247</v>
+        <v>34</v>
       </c>
       <c r="P243" t="s">
-        <v>200</v>
+        <v>34</v>
       </c>
       <c r="Q243" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="R243" t="s">
         <v>34</v>
@@ -15801,7 +15804,7 @@
         <v>34</v>
       </c>
       <c r="E244" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="F244" t="s">
         <v>173</v>
@@ -15810,16 +15813,16 @@
         <v>41</v>
       </c>
       <c r="H244" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I244" t="s">
         <v>200</v>
       </c>
       <c r="J244" t="s">
-        <v>130</v>
+        <v>60</v>
       </c>
       <c r="K244" t="s">
-        <v>130</v>
+        <v>60</v>
       </c>
       <c r="L244" t="s">
         <v>34</v>
@@ -15831,7 +15834,7 @@
         <v>45</v>
       </c>
       <c r="O244" t="s">
-        <v>137</v>
+        <v>61</v>
       </c>
       <c r="P244" t="s">
         <v>200</v>
@@ -15857,7 +15860,7 @@
         <v>34</v>
       </c>
       <c r="E245" t="s">
-        <v>210</v>
+        <v>253</v>
       </c>
       <c r="F245" t="s">
         <v>173</v>
@@ -15866,16 +15869,16 @@
         <v>41</v>
       </c>
       <c r="H245" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I245" t="s">
         <v>200</v>
       </c>
       <c r="J245" t="s">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="K245" t="s">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="L245" t="s">
         <v>34</v>
@@ -15887,7 +15890,7 @@
         <v>45</v>
       </c>
       <c r="O245" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="P245" t="s">
         <v>200</v>
@@ -15913,25 +15916,25 @@
         <v>34</v>
       </c>
       <c r="E246" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="F246" t="s">
-        <v>173</v>
+        <v>527</v>
       </c>
       <c r="G246" t="s">
         <v>41</v>
       </c>
       <c r="H246" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I246" t="s">
         <v>200</v>
       </c>
       <c r="J246" t="s">
-        <v>108</v>
+        <v>130</v>
       </c>
       <c r="K246" t="s">
-        <v>108</v>
+        <v>130</v>
       </c>
       <c r="L246" t="s">
         <v>34</v>
@@ -15943,13 +15946,13 @@
         <v>45</v>
       </c>
       <c r="O246" t="s">
-        <v>380</v>
+        <v>34</v>
       </c>
       <c r="P246" t="s">
-        <v>200</v>
+        <v>34</v>
       </c>
       <c r="Q246" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="R246" t="s">
         <v>34</v>
@@ -15969,7 +15972,7 @@
         <v>34</v>
       </c>
       <c r="E247" t="s">
-        <v>242</v>
+        <v>212</v>
       </c>
       <c r="F247" t="s">
         <v>173</v>
@@ -15978,16 +15981,16 @@
         <v>41</v>
       </c>
       <c r="H247" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I247" t="s">
-        <v>529</v>
+        <v>200</v>
       </c>
       <c r="J247" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="K247" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="L247" t="s">
         <v>34</v>
@@ -15999,10 +16002,10 @@
         <v>45</v>
       </c>
       <c r="O247" t="s">
-        <v>247</v>
+        <v>324</v>
       </c>
       <c r="P247" t="s">
-        <v>529</v>
+        <v>200</v>
       </c>
       <c r="Q247" t="s">
         <v>45</v>
@@ -16025,25 +16028,25 @@
         <v>34</v>
       </c>
       <c r="E248" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="F248" t="s">
+        <v>527</v>
+      </c>
+      <c r="G248" t="s">
+        <v>41</v>
+      </c>
+      <c r="H248" t="s">
         <v>528</v>
-      </c>
-      <c r="G248" t="s">
-        <v>41</v>
-      </c>
-      <c r="H248" t="s">
-        <v>527</v>
       </c>
       <c r="I248" t="s">
         <v>200</v>
       </c>
       <c r="J248" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="K248" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="L248" t="s">
         <v>34</v>
@@ -16081,25 +16084,25 @@
         <v>34</v>
       </c>
       <c r="E249" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F249" t="s">
-        <v>173</v>
+        <v>527</v>
       </c>
       <c r="G249" t="s">
         <v>41</v>
       </c>
       <c r="H249" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I249" t="s">
         <v>200</v>
       </c>
       <c r="J249" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="K249" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="L249" t="s">
         <v>34</v>
@@ -16111,13 +16114,13 @@
         <v>45</v>
       </c>
       <c r="O249" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="P249" t="s">
-        <v>200</v>
+        <v>34</v>
       </c>
       <c r="Q249" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="R249" t="s">
         <v>34</v>
@@ -16137,25 +16140,25 @@
         <v>34</v>
       </c>
       <c r="E250" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="F250" t="s">
+        <v>173</v>
+      </c>
+      <c r="G250" t="s">
+        <v>41</v>
+      </c>
+      <c r="H250" t="s">
         <v>528</v>
-      </c>
-      <c r="G250" t="s">
-        <v>41</v>
-      </c>
-      <c r="H250" t="s">
-        <v>527</v>
       </c>
       <c r="I250" t="s">
         <v>200</v>
       </c>
       <c r="J250" t="s">
-        <v>130</v>
+        <v>108</v>
       </c>
       <c r="K250" t="s">
-        <v>130</v>
+        <v>108</v>
       </c>
       <c r="L250" t="s">
         <v>34</v>
@@ -16167,13 +16170,13 @@
         <v>45</v>
       </c>
       <c r="O250" t="s">
-        <v>34</v>
+        <v>380</v>
       </c>
       <c r="P250" t="s">
-        <v>34</v>
+        <v>200</v>
       </c>
       <c r="Q250" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R250" t="s">
         <v>34</v>
@@ -16193,25 +16196,25 @@
         <v>34</v>
       </c>
       <c r="E251" t="s">
-        <v>253</v>
+        <v>227</v>
       </c>
       <c r="F251" t="s">
-        <v>173</v>
+        <v>527</v>
       </c>
       <c r="G251" t="s">
         <v>41</v>
       </c>
       <c r="H251" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I251" t="s">
         <v>200</v>
       </c>
       <c r="J251" t="s">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="K251" t="s">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="L251" t="s">
         <v>34</v>
@@ -16223,13 +16226,13 @@
         <v>45</v>
       </c>
       <c r="O251" t="s">
-        <v>89</v>
+        <v>34</v>
       </c>
       <c r="P251" t="s">
-        <v>200</v>
+        <v>34</v>
       </c>
       <c r="Q251" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="R251" t="s">
         <v>34</v>
@@ -16249,7 +16252,7 @@
         <v>34</v>
       </c>
       <c r="E252" t="s">
-        <v>212</v>
+        <v>242</v>
       </c>
       <c r="F252" t="s">
         <v>173</v>
@@ -16258,16 +16261,16 @@
         <v>41</v>
       </c>
       <c r="H252" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I252" t="s">
-        <v>200</v>
+        <v>529</v>
       </c>
       <c r="J252" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="K252" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="L252" t="s">
         <v>34</v>
@@ -16279,10 +16282,10 @@
         <v>45</v>
       </c>
       <c r="O252" t="s">
-        <v>324</v>
+        <v>247</v>
       </c>
       <c r="P252" t="s">
-        <v>200</v>
+        <v>529</v>
       </c>
       <c r="Q252" t="s">
         <v>45</v>
@@ -16305,25 +16308,25 @@
         <v>34</v>
       </c>
       <c r="E253" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="F253" t="s">
+        <v>173</v>
+      </c>
+      <c r="G253" t="s">
+        <v>41</v>
+      </c>
+      <c r="H253" t="s">
         <v>528</v>
-      </c>
-      <c r="G253" t="s">
-        <v>41</v>
-      </c>
-      <c r="H253" t="s">
-        <v>527</v>
       </c>
       <c r="I253" t="s">
         <v>200</v>
       </c>
       <c r="J253" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="K253" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="L253" t="s">
         <v>34</v>
@@ -16335,13 +16338,13 @@
         <v>45</v>
       </c>
       <c r="O253" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="P253" t="s">
-        <v>34</v>
+        <v>200</v>
       </c>
       <c r="Q253" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R253" t="s">
         <v>34</v>
@@ -16361,25 +16364,25 @@
         <v>34</v>
       </c>
       <c r="E254" t="s">
-        <v>223</v>
+        <v>204</v>
       </c>
       <c r="F254" t="s">
+        <v>527</v>
+      </c>
+      <c r="G254" t="s">
+        <v>41</v>
+      </c>
+      <c r="H254" t="s">
         <v>528</v>
-      </c>
-      <c r="G254" t="s">
-        <v>41</v>
-      </c>
-      <c r="H254" t="s">
-        <v>527</v>
       </c>
       <c r="I254" t="s">
         <v>200</v>
       </c>
       <c r="J254" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="K254" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="L254" t="s">
         <v>34</v>
@@ -16417,25 +16420,25 @@
         <v>34</v>
       </c>
       <c r="E255" t="s">
-        <v>204</v>
+        <v>230</v>
       </c>
       <c r="F255" t="s">
+        <v>173</v>
+      </c>
+      <c r="G255" t="s">
+        <v>41</v>
+      </c>
+      <c r="H255" t="s">
         <v>528</v>
-      </c>
-      <c r="G255" t="s">
-        <v>41</v>
-      </c>
-      <c r="H255" t="s">
-        <v>527</v>
       </c>
       <c r="I255" t="s">
         <v>200</v>
       </c>
       <c r="J255" t="s">
-        <v>50</v>
+        <v>130</v>
       </c>
       <c r="K255" t="s">
-        <v>50</v>
+        <v>130</v>
       </c>
       <c r="L255" t="s">
         <v>34</v>
@@ -16447,13 +16450,13 @@
         <v>45</v>
       </c>
       <c r="O255" t="s">
-        <v>34</v>
+        <v>137</v>
       </c>
       <c r="P255" t="s">
-        <v>34</v>
+        <v>200</v>
       </c>
       <c r="Q255" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R255" t="s">
         <v>34</v>
@@ -16473,25 +16476,25 @@
         <v>34</v>
       </c>
       <c r="E256" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="F256" t="s">
+        <v>173</v>
+      </c>
+      <c r="G256" t="s">
+        <v>41</v>
+      </c>
+      <c r="H256" t="s">
         <v>528</v>
-      </c>
-      <c r="G256" t="s">
-        <v>41</v>
-      </c>
-      <c r="H256" t="s">
-        <v>527</v>
       </c>
       <c r="I256" t="s">
         <v>200</v>
       </c>
       <c r="J256" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="K256" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="L256" t="s">
         <v>34</v>
@@ -16503,13 +16506,13 @@
         <v>45</v>
       </c>
       <c r="O256" t="s">
-        <v>34</v>
+        <v>327</v>
       </c>
       <c r="P256" t="s">
-        <v>34</v>
+        <v>200</v>
       </c>
       <c r="Q256" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R256" t="s">
         <v>34</v>
@@ -16753,7 +16756,7 @@
         <v>33</v>
       </c>
       <c r="E261" t="s">
-        <v>547</v>
+        <v>154</v>
       </c>
       <c r="F261" t="s">
         <v>173</v>
@@ -16762,19 +16765,19 @@
         <v>41</v>
       </c>
       <c r="H261" t="s">
+        <v>547</v>
+      </c>
+      <c r="I261" t="s">
         <v>548</v>
       </c>
-      <c r="I261" t="s">
+      <c r="J261" t="s">
         <v>549</v>
       </c>
-      <c r="J261" t="s">
+      <c r="K261" t="s">
+        <v>158</v>
+      </c>
+      <c r="L261" t="s">
         <v>550</v>
-      </c>
-      <c r="K261" t="s">
-        <v>81</v>
-      </c>
-      <c r="L261" t="s">
-        <v>551</v>
       </c>
       <c r="M261" t="s">
         <v>545</v>
@@ -16786,7 +16789,7 @@
         <v>153</v>
       </c>
       <c r="P261" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="Q261" t="s">
         <v>45</v>
@@ -16809,7 +16812,7 @@
         <v>34</v>
       </c>
       <c r="E262" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="F262" t="s">
         <v>173</v>
@@ -16865,7 +16868,7 @@
         <v>34</v>
       </c>
       <c r="E263" t="s">
-        <v>159</v>
+        <v>551</v>
       </c>
       <c r="F263" t="s">
         <v>173</v>
@@ -16883,7 +16886,7 @@
         <v>557</v>
       </c>
       <c r="K263" t="s">
-        <v>163</v>
+        <v>81</v>
       </c>
       <c r="L263" t="s">
         <v>558</v>
@@ -17145,7 +17148,7 @@
         <v>33</v>
       </c>
       <c r="E268" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="F268" t="s">
         <v>173</v>
@@ -17160,7 +17163,7 @@
         <v>571</v>
       </c>
       <c r="J268" t="s">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="K268" t="s">
         <v>266</v>
@@ -17313,7 +17316,7 @@
         <v>33</v>
       </c>
       <c r="E271" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="F271" t="s">
         <v>173</v>
@@ -17328,7 +17331,7 @@
         <v>579</v>
       </c>
       <c r="J271" t="s">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="K271" t="s">
         <v>266</v>
@@ -17369,7 +17372,7 @@
         <v>34</v>
       </c>
       <c r="E272" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="F272" t="s">
         <v>173</v>
@@ -17384,7 +17387,7 @@
         <v>582</v>
       </c>
       <c r="J272" t="s">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="K272" t="s">
         <v>266</v>
@@ -17425,7 +17428,7 @@
         <v>34</v>
       </c>
       <c r="E273" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="F273" t="s">
         <v>173</v>
@@ -17481,7 +17484,7 @@
         <v>34</v>
       </c>
       <c r="E274" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="F274" t="s">
         <v>173</v>
@@ -17593,7 +17596,7 @@
         <v>34</v>
       </c>
       <c r="E276" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="F276" t="s">
         <v>173</v>
@@ -17608,7 +17611,7 @@
         <v>592</v>
       </c>
       <c r="J276" t="s">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="K276" t="s">
         <v>266</v>
@@ -17649,7 +17652,7 @@
         <v>34</v>
       </c>
       <c r="E277" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="F277" t="s">
         <v>173</v>
@@ -17761,7 +17764,7 @@
         <v>34</v>
       </c>
       <c r="E279" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="F279" t="s">
         <v>173</v>
@@ -17770,19 +17773,19 @@
         <v>41</v>
       </c>
       <c r="H279" t="s">
-        <v>442</v>
+        <v>600</v>
       </c>
       <c r="I279" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="J279" t="s">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="K279" t="s">
         <v>266</v>
       </c>
       <c r="L279" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="M279" t="s">
         <v>577</v>
@@ -17794,7 +17797,7 @@
         <v>153</v>
       </c>
       <c r="P279" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="Q279" t="s">
         <v>45</v>
@@ -17817,7 +17820,7 @@
         <v>34</v>
       </c>
       <c r="E280" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="F280" t="s">
         <v>198</v>
@@ -17873,7 +17876,7 @@
         <v>34</v>
       </c>
       <c r="E281" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="F281" t="s">
         <v>173</v>
@@ -17882,7 +17885,7 @@
         <v>41</v>
       </c>
       <c r="H281" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="I281" t="s">
         <v>585</v>
@@ -17891,10 +17894,10 @@
         <v>586</v>
       </c>
       <c r="K281" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="L281" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="M281" t="s">
         <v>577</v>
@@ -17929,7 +17932,7 @@
         <v>34</v>
       </c>
       <c r="E282" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="F282" t="s">
         <v>198</v>
@@ -17941,7 +17944,7 @@
         <v>514</v>
       </c>
       <c r="I282" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="J282" t="s">
         <v>66</v>
@@ -17962,7 +17965,7 @@
         <v>153</v>
       </c>
       <c r="P282" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="Q282" t="s">
         <v>45</v>
@@ -17985,7 +17988,7 @@
         <v>34</v>
       </c>
       <c r="E283" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="F283" t="s">
         <v>173</v>
@@ -17994,19 +17997,19 @@
         <v>41</v>
       </c>
       <c r="H283" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="I283" t="s">
         <v>571</v>
       </c>
       <c r="J283" t="s">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="K283" t="s">
         <v>266</v>
       </c>
       <c r="L283" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="M283" t="s">
         <v>577</v>
@@ -18041,7 +18044,7 @@
         <v>34</v>
       </c>
       <c r="E284" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="F284" t="s">
         <v>173</v>
@@ -18050,19 +18053,19 @@
         <v>41</v>
       </c>
       <c r="H284" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="I284" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="J284" t="s">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="K284" t="s">
         <v>266</v>
       </c>
       <c r="L284" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="M284" t="s">
         <v>577</v>
@@ -18074,7 +18077,7 @@
         <v>153</v>
       </c>
       <c r="P284" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="Q284" t="s">
         <v>45</v>
@@ -18109,16 +18112,16 @@
         <v>366</v>
       </c>
       <c r="I285" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="J285" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="K285" t="s">
         <v>266</v>
       </c>
       <c r="L285" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="M285" t="s">
         <v>577</v>
@@ -18130,7 +18133,7 @@
         <v>153</v>
       </c>
       <c r="P285" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="Q285" t="s">
         <v>45</v>
@@ -18141,13 +18144,13 @@
     </row>
     <row r="286">
       <c r="A286" t="s" s="1">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B286" t="s" s="1">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C286" t="s" s="1">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="D286" t="s" s="1">
         <v>33</v>
@@ -18197,13 +18200,13 @@
     </row>
     <row r="287">
       <c r="A287" t="s">
+        <v>619</v>
+      </c>
+      <c r="B287" t="s">
         <v>618</v>
       </c>
-      <c r="B287" t="s">
-        <v>617</v>
-      </c>
       <c r="C287" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="D287" t="s">
         <v>33</v>
@@ -18230,10 +18233,10 @@
         <v>121</v>
       </c>
       <c r="L287" t="s">
+        <v>620</v>
+      </c>
+      <c r="M287" t="s">
         <v>619</v>
-      </c>
-      <c r="M287" t="s">
-        <v>618</v>
       </c>
       <c r="N287" t="s">
         <v>45</v>
@@ -18253,13 +18256,13 @@
     </row>
     <row r="288">
       <c r="A288" t="s" s="1">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B288" t="s" s="1">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C288" t="s" s="1">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="D288" t="s" s="1">
         <v>33</v>
@@ -18309,13 +18312,13 @@
     </row>
     <row r="289">
       <c r="A289" t="s">
+        <v>623</v>
+      </c>
+      <c r="B289" t="s">
         <v>622</v>
       </c>
-      <c r="B289" t="s">
-        <v>621</v>
-      </c>
       <c r="C289" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="D289" t="s">
         <v>33</v>
@@ -18330,10 +18333,10 @@
         <v>41</v>
       </c>
       <c r="H289" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="I289" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="J289" t="s">
         <v>176</v>
@@ -18342,10 +18345,10 @@
         <v>121</v>
       </c>
       <c r="L289" t="s">
+        <v>624</v>
+      </c>
+      <c r="M289" t="s">
         <v>623</v>
-      </c>
-      <c r="M289" t="s">
-        <v>622</v>
       </c>
       <c r="N289" t="s">
         <v>45</v>
@@ -18354,7 +18357,7 @@
         <v>153</v>
       </c>
       <c r="P289" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="Q289" t="s">
         <v>45</v>
@@ -18365,13 +18368,13 @@
     </row>
     <row r="290">
       <c r="A290" t="s" s="1">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B290" t="s" s="1">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C290" t="s" s="1">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="D290" t="s" s="1">
         <v>33</v>
@@ -18421,13 +18424,13 @@
     </row>
     <row r="291">
       <c r="A291" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B291" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C291" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="D291" t="s">
         <v>33</v>
@@ -18442,10 +18445,10 @@
         <v>41</v>
       </c>
       <c r="H291" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="I291" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="J291" t="s">
         <v>176</v>
@@ -18454,10 +18457,10 @@
         <v>121</v>
       </c>
       <c r="L291" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="M291" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="N291" t="s">
         <v>45</v>
@@ -18466,7 +18469,7 @@
         <v>153</v>
       </c>
       <c r="P291" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="Q291" t="s">
         <v>45</v>
@@ -18477,19 +18480,19 @@
     </row>
     <row r="292">
       <c r="A292" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B292" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C292" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="D292" t="s">
         <v>33</v>
       </c>
       <c r="E292" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="F292" t="s">
         <v>198</v>
@@ -18498,22 +18501,22 @@
         <v>41</v>
       </c>
       <c r="H292" t="s">
-        <v>442</v>
+        <v>600</v>
       </c>
       <c r="I292" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="J292" t="s">
         <v>266</v>
       </c>
       <c r="K292" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="L292" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="M292" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="N292" t="s">
         <v>45</v>
@@ -18522,7 +18525,7 @@
         <v>153</v>
       </c>
       <c r="P292" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="Q292" t="s">
         <v>45</v>
@@ -18533,13 +18536,13 @@
     </row>
     <row r="293">
       <c r="A293" t="s" s="1">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B293" t="s" s="1">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C293" t="s" s="1">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="D293" t="s" s="1">
         <v>33</v>
@@ -18589,13 +18592,13 @@
     </row>
     <row r="294">
       <c r="A294" t="s" s="1">
+        <v>640</v>
+      </c>
+      <c r="B294" t="s" s="1">
         <v>639</v>
       </c>
-      <c r="B294" t="s" s="1">
-        <v>638</v>
-      </c>
       <c r="C294" t="s" s="1">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="D294" t="s" s="1">
         <v>33</v>
@@ -18645,19 +18648,19 @@
     </row>
     <row r="295">
       <c r="A295" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B295" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C295" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="D295" t="s">
         <v>33</v>
       </c>
       <c r="E295" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="F295" t="s">
         <v>198</v>
@@ -18669,7 +18672,7 @@
         <v>366</v>
       </c>
       <c r="I295" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="J295" t="s">
         <v>55</v>
@@ -18681,7 +18684,7 @@
         <v>34</v>
       </c>
       <c r="M295" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="N295" t="s">
         <v>45</v>
@@ -18690,7 +18693,7 @@
         <v>153</v>
       </c>
       <c r="P295" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="Q295" t="s">
         <v>45</v>
@@ -18701,7 +18704,7 @@
     </row>
     <row r="296">
       <c r="A296" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B296" t="s">
         <v>34</v>
@@ -18713,7 +18716,7 @@
         <v>34</v>
       </c>
       <c r="E296" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="F296" t="s">
         <v>198</v>
@@ -18725,10 +18728,10 @@
         <v>514</v>
       </c>
       <c r="I296" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="J296" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="K296" t="s">
         <v>66</v>
@@ -18737,7 +18740,7 @@
         <v>34</v>
       </c>
       <c r="M296" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="N296" t="s">
         <v>45</v>
@@ -18746,7 +18749,7 @@
         <v>153</v>
       </c>
       <c r="P296" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="Q296" t="s">
         <v>45</v>
@@ -18757,13 +18760,13 @@
     </row>
     <row r="297">
       <c r="A297" t="s" s="1">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B297" t="s" s="1">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="C297" t="s" s="1">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="D297" t="s" s="1">
         <v>33</v>
@@ -18813,13 +18816,13 @@
     </row>
     <row r="298">
       <c r="A298" t="s" s="1">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B298" t="s" s="1">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C298" t="s" s="1">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="D298" t="s" s="1">
         <v>33</v>
@@ -18869,19 +18872,19 @@
     </row>
     <row r="299">
       <c r="A299" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B299" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C299" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="D299" t="s">
         <v>33</v>
       </c>
       <c r="E299" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="F299" t="s">
         <v>173</v>
@@ -18890,22 +18893,22 @@
         <v>41</v>
       </c>
       <c r="H299" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="I299" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="J299" t="s">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="K299" t="s">
         <v>81</v>
       </c>
       <c r="L299" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="M299" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="N299" t="s">
         <v>45</v>
@@ -18914,7 +18917,7 @@
         <v>153</v>
       </c>
       <c r="P299" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="Q299" t="s">
         <v>45</v>
@@ -18925,19 +18928,19 @@
     </row>
     <row r="300">
       <c r="A300" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B300" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="C300" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="D300" t="s">
         <v>33</v>
       </c>
       <c r="E300" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="F300" t="s">
         <v>198</v>
@@ -18949,7 +18952,7 @@
         <v>150</v>
       </c>
       <c r="I300" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="J300" t="s">
         <v>55</v>
@@ -18958,10 +18961,10 @@
         <v>55</v>
       </c>
       <c r="L300" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="M300" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="N300" t="s">
         <v>45</v>
@@ -18970,7 +18973,7 @@
         <v>153</v>
       </c>
       <c r="P300" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="Q300" t="s">
         <v>45</v>
@@ -18981,13 +18984,13 @@
     </row>
     <row r="301">
       <c r="A301" t="s" s="1">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B301" t="s" s="1">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C301" t="s" s="1">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="D301" t="s" s="1">
         <v>33</v>
@@ -19037,19 +19040,19 @@
     </row>
     <row r="302">
       <c r="A302" t="s">
+        <v>663</v>
+      </c>
+      <c r="B302" t="s">
         <v>662</v>
       </c>
-      <c r="B302" t="s">
-        <v>661</v>
-      </c>
       <c r="C302" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="D302" t="s">
         <v>33</v>
       </c>
       <c r="E302" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="F302" t="s">
         <v>173</v>
@@ -19058,22 +19061,22 @@
         <v>41</v>
       </c>
       <c r="H302" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="I302" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="J302" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="K302" t="s">
         <v>88</v>
       </c>
       <c r="L302" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="M302" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="N302" t="s">
         <v>45</v>
@@ -19082,7 +19085,7 @@
         <v>153</v>
       </c>
       <c r="P302" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="Q302" t="s">
         <v>45</v>
@@ -19093,13 +19096,13 @@
     </row>
     <row r="303">
       <c r="A303" t="s" s="1">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B303" t="s" s="1">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C303" t="s" s="1">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="D303" t="s" s="1">
         <v>33</v>
@@ -19149,19 +19152,19 @@
     </row>
     <row r="304">
       <c r="A304" t="s">
+        <v>671</v>
+      </c>
+      <c r="B304" t="s">
         <v>670</v>
       </c>
-      <c r="B304" t="s">
-        <v>669</v>
-      </c>
       <c r="C304" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="D304" t="s">
         <v>33</v>
       </c>
       <c r="E304" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="F304" t="s">
         <v>173</v>
@@ -19170,22 +19173,22 @@
         <v>41</v>
       </c>
       <c r="H304" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="I304" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="J304" t="s">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="K304" t="s">
         <v>266</v>
       </c>
       <c r="L304" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="M304" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="N304" t="s">
         <v>45</v>
@@ -19194,7 +19197,7 @@
         <v>153</v>
       </c>
       <c r="P304" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="Q304" t="s">
         <v>45</v>
@@ -19205,13 +19208,13 @@
     </row>
     <row r="305">
       <c r="A305" t="s" s="1">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B305" t="s" s="1">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C305" t="s" s="1">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="D305" t="s" s="1">
         <v>33</v>
@@ -19261,19 +19264,19 @@
     </row>
     <row r="306">
       <c r="A306" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B306" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C306" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="D306" t="s">
         <v>33</v>
       </c>
       <c r="E306" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="F306" t="s">
         <v>173</v>
@@ -19282,22 +19285,22 @@
         <v>41</v>
       </c>
       <c r="H306" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="I306" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="J306" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="K306" t="s">
         <v>146</v>
       </c>
       <c r="L306" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="M306" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="N306" t="s">
         <v>45</v>
@@ -19306,7 +19309,7 @@
         <v>153</v>
       </c>
       <c r="P306" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="Q306" t="s">
         <v>45</v>
@@ -19317,19 +19320,19 @@
     </row>
     <row r="307">
       <c r="A307" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B307" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="C307" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="D307" t="s">
         <v>33</v>
       </c>
       <c r="E307" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="F307" t="s">
         <v>173</v>
@@ -19338,22 +19341,22 @@
         <v>41</v>
       </c>
       <c r="H307" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="I307" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="J307" t="s">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="K307" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="L307" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="M307" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="N307" t="s">
         <v>45</v>
@@ -19362,7 +19365,7 @@
         <v>153</v>
       </c>
       <c r="P307" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="Q307" t="s">
         <v>45</v>
@@ -19373,13 +19376,13 @@
     </row>
     <row r="308">
       <c r="A308" t="s" s="1">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B308" t="s" s="1">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C308" t="s" s="1">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="D308" t="s" s="1">
         <v>33</v>
@@ -19429,19 +19432,19 @@
     </row>
     <row r="309">
       <c r="A309" t="s">
+        <v>690</v>
+      </c>
+      <c r="B309" t="s">
         <v>689</v>
       </c>
-      <c r="B309" t="s">
-        <v>688</v>
-      </c>
       <c r="C309" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="D309" t="s">
         <v>33</v>
       </c>
       <c r="E309" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="F309" t="s">
         <v>173</v>
@@ -19450,22 +19453,22 @@
         <v>41</v>
       </c>
       <c r="H309" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="I309" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="J309" t="s">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="K309" t="s">
         <v>81</v>
       </c>
       <c r="L309" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="M309" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="N309" t="s">
         <v>45</v>
@@ -19474,7 +19477,7 @@
         <v>153</v>
       </c>
       <c r="P309" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="Q309" t="s">
         <v>45</v>
@@ -19485,13 +19488,13 @@
     </row>
     <row r="310">
       <c r="A310" t="s" s="1">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B310" t="s" s="1">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C310" t="s" s="1">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="D310" t="s" s="1">
         <v>33</v>
@@ -19541,19 +19544,19 @@
     </row>
     <row r="311">
       <c r="A311" t="s">
+        <v>696</v>
+      </c>
+      <c r="B311" t="s">
         <v>695</v>
       </c>
-      <c r="B311" t="s">
-        <v>694</v>
-      </c>
       <c r="C311" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="D311" t="s">
         <v>33</v>
       </c>
       <c r="E311" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="F311" t="s">
         <v>198</v>
@@ -19562,10 +19565,10 @@
         <v>41</v>
       </c>
       <c r="H311" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="I311" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="J311" t="s">
         <v>201</v>
@@ -19574,10 +19577,10 @@
         <v>66</v>
       </c>
       <c r="L311" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="M311" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="N311" t="s">
         <v>45</v>
@@ -19586,7 +19589,7 @@
         <v>153</v>
       </c>
       <c r="P311" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="Q311" t="s">
         <v>45</v>
@@ -19597,7 +19600,7 @@
     </row>
     <row r="312">
       <c r="A312" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B312" t="s">
         <v>34</v>
@@ -19609,7 +19612,7 @@
         <v>34</v>
       </c>
       <c r="E312" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="F312" t="s">
         <v>198</v>
@@ -19618,22 +19621,22 @@
         <v>41</v>
       </c>
       <c r="H312" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="I312" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="J312" t="s">
-        <v>201</v>
+        <v>121</v>
       </c>
       <c r="K312" t="s">
-        <v>66</v>
+        <v>146</v>
       </c>
       <c r="L312" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="M312" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="N312" t="s">
         <v>45</v>
@@ -19642,7 +19645,7 @@
         <v>153</v>
       </c>
       <c r="P312" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="Q312" t="s">
         <v>45</v>
@@ -19653,7 +19656,7 @@
     </row>
     <row r="313">
       <c r="A313" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B313" t="s">
         <v>34</v>
@@ -19665,7 +19668,7 @@
         <v>34</v>
       </c>
       <c r="E313" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="F313" t="s">
         <v>198</v>
@@ -19674,10 +19677,10 @@
         <v>41</v>
       </c>
       <c r="H313" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="I313" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="J313" t="s">
         <v>201</v>
@@ -19686,10 +19689,10 @@
         <v>66</v>
       </c>
       <c r="L313" t="s">
-        <v>34</v>
+        <v>708</v>
       </c>
       <c r="M313" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="N313" t="s">
         <v>45</v>
@@ -19698,7 +19701,7 @@
         <v>153</v>
       </c>
       <c r="P313" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="Q313" t="s">
         <v>45</v>
@@ -19709,7 +19712,7 @@
     </row>
     <row r="314">
       <c r="A314" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B314" t="s">
         <v>34</v>
@@ -19721,7 +19724,7 @@
         <v>34</v>
       </c>
       <c r="E314" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="F314" t="s">
         <v>198</v>
@@ -19730,22 +19733,22 @@
         <v>41</v>
       </c>
       <c r="H314" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="I314" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="J314" t="s">
-        <v>121</v>
+        <v>201</v>
       </c>
       <c r="K314" t="s">
-        <v>146</v>
+        <v>66</v>
       </c>
       <c r="L314" t="s">
-        <v>710</v>
+        <v>34</v>
       </c>
       <c r="M314" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="N314" t="s">
         <v>45</v>
@@ -19754,7 +19757,7 @@
         <v>153</v>
       </c>
       <c r="P314" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="Q314" t="s">
         <v>45</v>
@@ -19765,13 +19768,13 @@
     </row>
     <row r="315">
       <c r="A315" t="s" s="1">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="B315" t="s" s="1">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="C315" t="s" s="1">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="D315" t="s" s="1">
         <v>33</v>
@@ -19821,19 +19824,19 @@
     </row>
     <row r="316">
       <c r="A316" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="B316" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="C316" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="D316" t="s">
         <v>33</v>
       </c>
       <c r="E316" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="F316" t="s">
         <v>173</v>
@@ -19842,22 +19845,22 @@
         <v>41</v>
       </c>
       <c r="H316" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="I316" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="J316" t="s">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="K316" t="s">
         <v>266</v>
       </c>
       <c r="L316" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="M316" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="N316" t="s">
         <v>45</v>
@@ -19866,7 +19869,7 @@
         <v>153</v>
       </c>
       <c r="P316" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="Q316" t="s">
         <v>45</v>
@@ -19877,19 +19880,19 @@
     </row>
     <row r="317">
       <c r="A317" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B317" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C317" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="D317" t="s">
         <v>33</v>
       </c>
       <c r="E317" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="F317" t="s">
         <v>173</v>
@@ -19898,22 +19901,22 @@
         <v>41</v>
       </c>
       <c r="H317" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="I317" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="J317" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="K317" t="s">
         <v>245</v>
       </c>
       <c r="L317" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="M317" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="N317" t="s">
         <v>45</v>
@@ -19922,7 +19925,7 @@
         <v>153</v>
       </c>
       <c r="P317" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="Q317" t="s">
         <v>45</v>
@@ -19933,19 +19936,19 @@
     </row>
     <row r="318">
       <c r="A318" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="B318" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="C318" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="D318" t="s">
         <v>33</v>
       </c>
       <c r="E318" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="F318" t="s">
         <v>173</v>
@@ -19954,22 +19957,22 @@
         <v>41</v>
       </c>
       <c r="H318" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="I318" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="J318" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="K318" t="s">
         <v>266</v>
       </c>
       <c r="L318" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="M318" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="N318" t="s">
         <v>45</v>
@@ -19978,7 +19981,7 @@
         <v>153</v>
       </c>
       <c r="P318" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="Q318" t="s">
         <v>45</v>
@@ -19989,13 +19992,13 @@
     </row>
     <row r="319">
       <c r="A319" t="s" s="1">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B319" t="s" s="1">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C319" t="s" s="1">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="D319" t="s" s="1">
         <v>33</v>
@@ -20045,19 +20048,19 @@
     </row>
     <row r="320">
       <c r="A320" t="s">
+        <v>731</v>
+      </c>
+      <c r="B320" t="s">
         <v>730</v>
       </c>
-      <c r="B320" t="s">
-        <v>729</v>
-      </c>
       <c r="C320" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="D320" t="s">
         <v>33</v>
       </c>
       <c r="E320" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="F320" t="s">
         <v>173</v>
@@ -20066,13 +20069,13 @@
         <v>41</v>
       </c>
       <c r="H320" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="I320" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="J320" t="s">
-        <v>733</v>
+        <v>201</v>
       </c>
       <c r="K320" t="s">
         <v>266</v>
@@ -20081,7 +20084,7 @@
         <v>734</v>
       </c>
       <c r="M320" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="N320" t="s">
         <v>45</v>
@@ -20090,7 +20093,7 @@
         <v>153</v>
       </c>
       <c r="P320" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="Q320" t="s">
         <v>45</v>
@@ -20101,7 +20104,7 @@
     </row>
     <row r="321">
       <c r="A321" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="B321" t="s">
         <v>34</v>
@@ -20113,7 +20116,7 @@
         <v>34</v>
       </c>
       <c r="E321" t="s">
-        <v>547</v>
+        <v>735</v>
       </c>
       <c r="F321" t="s">
         <v>173</v>
@@ -20122,22 +20125,22 @@
         <v>41</v>
       </c>
       <c r="H321" t="s">
-        <v>735</v>
+        <v>726</v>
       </c>
       <c r="I321" t="s">
         <v>736</v>
       </c>
       <c r="J321" t="s">
-        <v>265</v>
+        <v>737</v>
       </c>
       <c r="K321" t="s">
         <v>266</v>
       </c>
       <c r="L321" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="M321" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="N321" t="s">
         <v>45</v>
@@ -20157,7 +20160,7 @@
     </row>
     <row r="322">
       <c r="A322" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="B322" t="s">
         <v>34</v>
@@ -20169,7 +20172,7 @@
         <v>34</v>
       </c>
       <c r="E322" t="s">
-        <v>738</v>
+        <v>551</v>
       </c>
       <c r="F322" t="s">
         <v>173</v>
@@ -20178,22 +20181,22 @@
         <v>41</v>
       </c>
       <c r="H322" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="I322" t="s">
         <v>739</v>
       </c>
       <c r="J322" t="s">
+        <v>265</v>
+      </c>
+      <c r="K322" t="s">
+        <v>60</v>
+      </c>
+      <c r="L322" t="s">
         <v>740</v>
       </c>
-      <c r="K322" t="s">
-        <v>266</v>
-      </c>
-      <c r="L322" t="s">
-        <v>741</v>
-      </c>
       <c r="M322" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="N322" t="s">
         <v>45</v>
@@ -20213,7 +20216,7 @@
     </row>
     <row r="323">
       <c r="A323" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="B323" t="s">
         <v>34</v>
@@ -20225,7 +20228,7 @@
         <v>34</v>
       </c>
       <c r="E323" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="F323" t="s">
         <v>173</v>
@@ -20234,22 +20237,22 @@
         <v>41</v>
       </c>
       <c r="H323" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="I323" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="J323" t="s">
-        <v>201</v>
+        <v>737</v>
       </c>
       <c r="K323" t="s">
         <v>266</v>
       </c>
       <c r="L323" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="M323" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="N323" t="s">
         <v>45</v>
@@ -20258,7 +20261,7 @@
         <v>153</v>
       </c>
       <c r="P323" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="Q323" t="s">
         <v>45</v>
@@ -20269,7 +20272,7 @@
     </row>
     <row r="324">
       <c r="A324" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="B324" t="s">
         <v>34</v>
@@ -20281,7 +20284,7 @@
         <v>34</v>
       </c>
       <c r="E324" t="s">
-        <v>745</v>
+        <v>551</v>
       </c>
       <c r="F324" t="s">
         <v>173</v>
@@ -20290,22 +20293,22 @@
         <v>41</v>
       </c>
       <c r="H324" t="s">
+        <v>744</v>
+      </c>
+      <c r="I324" t="s">
+        <v>745</v>
+      </c>
+      <c r="J324" t="s">
+        <v>265</v>
+      </c>
+      <c r="K324" t="s">
+        <v>266</v>
+      </c>
+      <c r="L324" t="s">
         <v>746</v>
       </c>
-      <c r="I324" t="s">
-        <v>747</v>
-      </c>
-      <c r="J324" t="s">
-        <v>748</v>
-      </c>
-      <c r="K324" t="s">
-        <v>749</v>
-      </c>
-      <c r="L324" t="s">
-        <v>750</v>
-      </c>
       <c r="M324" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="N324" t="s">
         <v>45</v>
@@ -20314,7 +20317,7 @@
         <v>153</v>
       </c>
       <c r="P324" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="Q324" t="s">
         <v>45</v>
@@ -20325,7 +20328,7 @@
     </row>
     <row r="325">
       <c r="A325" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="B325" t="s">
         <v>34</v>
@@ -20337,7 +20340,7 @@
         <v>34</v>
       </c>
       <c r="E325" t="s">
-        <v>751</v>
+        <v>747</v>
       </c>
       <c r="F325" t="s">
         <v>173</v>
@@ -20346,22 +20349,22 @@
         <v>41</v>
       </c>
       <c r="H325" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="I325" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
       <c r="J325" t="s">
-        <v>740</v>
+        <v>749</v>
       </c>
       <c r="K325" t="s">
         <v>266</v>
       </c>
       <c r="L325" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="M325" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="N325" t="s">
         <v>45</v>
@@ -20370,7 +20373,7 @@
         <v>153</v>
       </c>
       <c r="P325" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
       <c r="Q325" t="s">
         <v>45</v>
@@ -20381,7 +20384,7 @@
     </row>
     <row r="326">
       <c r="A326" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="B326" t="s">
         <v>34</v>
@@ -20393,7 +20396,7 @@
         <v>34</v>
       </c>
       <c r="E326" t="s">
-        <v>547</v>
+        <v>751</v>
       </c>
       <c r="F326" t="s">
         <v>173</v>
@@ -20402,22 +20405,22 @@
         <v>41</v>
       </c>
       <c r="H326" t="s">
-        <v>725</v>
+        <v>752</v>
       </c>
       <c r="I326" t="s">
+        <v>753</v>
+      </c>
+      <c r="J326" t="s">
         <v>754</v>
       </c>
-      <c r="J326" t="s">
-        <v>265</v>
-      </c>
       <c r="K326" t="s">
-        <v>60</v>
+        <v>266</v>
       </c>
       <c r="L326" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="M326" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="N326" t="s">
         <v>45</v>
@@ -20426,7 +20429,7 @@
         <v>153</v>
       </c>
       <c r="P326" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="Q326" t="s">
         <v>45</v>
@@ -20437,7 +20440,7 @@
     </row>
     <row r="327">
       <c r="A327" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="B327" t="s">
         <v>34</v>
@@ -20449,7 +20452,7 @@
         <v>34</v>
       </c>
       <c r="E327" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="F327" t="s">
         <v>173</v>
@@ -20458,22 +20461,22 @@
         <v>41</v>
       </c>
       <c r="H327" t="s">
+        <v>756</v>
+      </c>
+      <c r="I327" t="s">
         <v>757</v>
       </c>
-      <c r="I327" t="s">
+      <c r="J327" t="s">
         <v>758</v>
       </c>
-      <c r="J327" t="s">
+      <c r="K327" t="s">
         <v>759</v>
       </c>
-      <c r="K327" t="s">
-        <v>266</v>
-      </c>
       <c r="L327" t="s">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="M327" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="N327" t="s">
         <v>45</v>
@@ -20482,7 +20485,7 @@
         <v>153</v>
       </c>
       <c r="P327" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="Q327" t="s">
         <v>45</v>
@@ -20493,13 +20496,13 @@
     </row>
     <row r="328">
       <c r="A328" t="s" s="1">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="B328" t="s" s="1">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C328" t="s" s="1">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="D328" t="s" s="1">
         <v>33</v>
@@ -20549,19 +20552,19 @@
     </row>
     <row r="329">
       <c r="A329" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="B329" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="C329" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="D329" t="s">
         <v>33</v>
       </c>
       <c r="E329" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="F329" t="s">
         <v>198</v>
@@ -20570,22 +20573,22 @@
         <v>41</v>
       </c>
       <c r="H329" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="I329" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="J329" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="K329" t="s">
         <v>55</v>
       </c>
       <c r="L329" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="M329" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="N329" t="s">
         <v>45</v>
@@ -20594,7 +20597,7 @@
         <v>153</v>
       </c>
       <c r="P329" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="Q329" t="s">
         <v>45</v>
@@ -20605,19 +20608,19 @@
     </row>
     <row r="330">
       <c r="A330" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="B330" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="C330" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="D330" t="s">
         <v>33</v>
       </c>
       <c r="E330" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="F330" t="s">
         <v>198</v>
@@ -20626,22 +20629,22 @@
         <v>41</v>
       </c>
       <c r="H330" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="I330" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="J330" t="s">
         <v>266</v>
       </c>
       <c r="K330" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="L330" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="M330" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="N330" t="s">
         <v>45</v>
@@ -20650,7 +20653,7 @@
         <v>153</v>
       </c>
       <c r="P330" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="Q330" t="s">
         <v>45</v>
@@ -20661,13 +20664,13 @@
     </row>
     <row r="331">
       <c r="A331" t="s" s="1">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="B331" t="s" s="1">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="C331" t="s" s="1">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="D331" t="s" s="1">
         <v>33</v>
@@ -20717,19 +20720,19 @@
     </row>
     <row r="332">
       <c r="A332" t="s">
+        <v>778</v>
+      </c>
+      <c r="B332" t="s">
         <v>777</v>
       </c>
-      <c r="B332" t="s">
-        <v>776</v>
-      </c>
       <c r="C332" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="D332" t="s">
         <v>33</v>
       </c>
       <c r="E332" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="F332" t="s">
         <v>173</v>
@@ -20738,22 +20741,22 @@
         <v>41</v>
       </c>
       <c r="H332" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="I332" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="J332" t="s">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="K332" t="s">
         <v>266</v>
       </c>
       <c r="L332" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="M332" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="N332" t="s">
         <v>45</v>
@@ -20762,7 +20765,7 @@
         <v>153</v>
       </c>
       <c r="P332" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="Q332" t="s">
         <v>45</v>
@@ -20773,13 +20776,13 @@
     </row>
     <row r="333">
       <c r="A333" t="s" s="1">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="B333" t="s" s="1">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="C333" t="s" s="1">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="D333" t="s" s="1">
         <v>33</v>
@@ -20829,13 +20832,13 @@
     </row>
     <row r="334">
       <c r="A334" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B334" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="C334" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="D334" t="s">
         <v>33</v>
@@ -20850,10 +20853,10 @@
         <v>41</v>
       </c>
       <c r="H334" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="I334" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="J334" t="s">
         <v>176</v>
@@ -20862,10 +20865,10 @@
         <v>188</v>
       </c>
       <c r="L334" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="M334" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="N334" t="s">
         <v>45</v>
@@ -20874,7 +20877,7 @@
         <v>153</v>
       </c>
       <c r="P334" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="Q334" t="s">
         <v>45</v>
@@ -20885,19 +20888,19 @@
     </row>
     <row r="335">
       <c r="A335" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="B335" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="C335" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="D335" t="s">
         <v>33</v>
       </c>
       <c r="E335" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="F335" t="s">
         <v>173</v>
@@ -20906,10 +20909,10 @@
         <v>41</v>
       </c>
       <c r="H335" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="I335" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="J335" t="s">
         <v>266</v>
@@ -20918,10 +20921,10 @@
         <v>146</v>
       </c>
       <c r="L335" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="M335" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="N335" t="s">
         <v>45</v>
@@ -20930,7 +20933,7 @@
         <v>153</v>
       </c>
       <c r="P335" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="Q335" t="s">
         <v>45</v>
@@ -20941,19 +20944,19 @@
     </row>
     <row r="336">
       <c r="A336" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="B336" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="C336" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="D336" t="s">
         <v>33</v>
       </c>
       <c r="E336" t="s">
-        <v>651</v>
+        <v>551</v>
       </c>
       <c r="F336" t="s">
         <v>173</v>
@@ -20962,22 +20965,22 @@
         <v>41</v>
       </c>
       <c r="H336" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="I336" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="J336" t="s">
         <v>557</v>
       </c>
       <c r="K336" t="s">
-        <v>163</v>
+        <v>266</v>
       </c>
       <c r="L336" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="M336" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="N336" t="s">
         <v>45</v>
@@ -20986,7 +20989,7 @@
         <v>153</v>
       </c>
       <c r="P336" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="Q336" t="s">
         <v>45</v>
@@ -20997,7 +21000,7 @@
     </row>
     <row r="337">
       <c r="A337" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="B337" t="s">
         <v>34</v>
@@ -21009,7 +21012,7 @@
         <v>34</v>
       </c>
       <c r="E337" t="s">
-        <v>547</v>
+        <v>652</v>
       </c>
       <c r="F337" t="s">
         <v>173</v>
@@ -21018,22 +21021,22 @@
         <v>41</v>
       </c>
       <c r="H337" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="I337" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="J337" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="K337" t="s">
-        <v>266</v>
+        <v>158</v>
       </c>
       <c r="L337" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="M337" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="N337" t="s">
         <v>45</v>
@@ -21042,7 +21045,7 @@
         <v>153</v>
       </c>
       <c r="P337" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="Q337" t="s">
         <v>45</v>
@@ -21053,19 +21056,19 @@
     </row>
     <row r="338">
       <c r="A338" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="B338" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="C338" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="D338" t="s">
         <v>33</v>
       </c>
       <c r="E338" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="F338" t="s">
         <v>173</v>
@@ -21074,22 +21077,22 @@
         <v>41</v>
       </c>
       <c r="H338" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="I338" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="J338" t="s">
-        <v>733</v>
+        <v>749</v>
       </c>
       <c r="K338" t="s">
         <v>266</v>
       </c>
       <c r="L338" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="M338" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="N338" t="s">
         <v>45</v>
@@ -21098,7 +21101,7 @@
         <v>153</v>
       </c>
       <c r="P338" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="Q338" t="s">
         <v>45</v>
@@ -21109,13 +21112,13 @@
     </row>
     <row r="339">
       <c r="A339" t="s" s="1">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="B339" t="s" s="1">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="C339" t="s" s="1">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="D339" t="s" s="1">
         <v>33</v>
@@ -21165,13 +21168,13 @@
     </row>
     <row r="340">
       <c r="A340" t="s" s="1">
+        <v>810</v>
+      </c>
+      <c r="B340" t="s" s="1">
         <v>809</v>
       </c>
-      <c r="B340" t="s" s="1">
-        <v>808</v>
-      </c>
       <c r="C340" t="s" s="1">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="D340" t="s" s="1">
         <v>33</v>
@@ -21221,13 +21224,13 @@
     </row>
     <row r="341">
       <c r="A341" t="s" s="1">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="B341" t="s" s="1">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="C341" t="s" s="1">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="D341" t="s" s="1">
         <v>33</v>
@@ -21277,19 +21280,19 @@
     </row>
     <row r="342">
       <c r="A342" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="B342" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="C342" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="D342" t="s">
         <v>33</v>
       </c>
       <c r="E342" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="F342" t="s">
         <v>198</v>
@@ -21298,10 +21301,10 @@
         <v>41</v>
       </c>
       <c r="H342" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="I342" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="J342" t="s">
         <v>201</v>
@@ -21313,7 +21316,7 @@
         <v>34</v>
       </c>
       <c r="M342" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="N342" t="s">
         <v>45</v>
@@ -21322,7 +21325,7 @@
         <v>153</v>
       </c>
       <c r="P342" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="Q342" t="s">
         <v>45</v>
@@ -21333,13 +21336,13 @@
     </row>
     <row r="343">
       <c r="A343" t="s" s="1">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="B343" t="s" s="1">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="C343" t="s" s="1">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="D343" t="s" s="1">
         <v>33</v>
@@ -21389,13 +21392,13 @@
     </row>
     <row r="344">
       <c r="A344" t="s" s="1">
+        <v>818</v>
+      </c>
+      <c r="B344" t="s" s="1">
         <v>817</v>
       </c>
-      <c r="B344" t="s" s="1">
-        <v>816</v>
-      </c>
       <c r="C344" t="s" s="1">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="D344" t="s" s="1">
         <v>33</v>
@@ -21445,13 +21448,13 @@
     </row>
     <row r="345">
       <c r="A345" t="s" s="1">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="B345" t="s" s="1">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="C345" t="s" s="1">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="D345" t="s" s="1">
         <v>33</v>
@@ -21501,13 +21504,13 @@
     </row>
     <row r="346">
       <c r="A346" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="B346" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="C346" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="D346" t="s">
         <v>33</v>
@@ -21522,10 +21525,10 @@
         <v>41</v>
       </c>
       <c r="H346" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="I346" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="J346" t="s">
         <v>81</v>
@@ -21534,10 +21537,10 @@
         <v>81</v>
       </c>
       <c r="L346" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="M346" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="N346" t="s">
         <v>45</v>
@@ -21557,7 +21560,7 @@
     </row>
     <row r="347">
       <c r="A347" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="B347" t="s">
         <v>34</v>
@@ -21578,10 +21581,10 @@
         <v>41</v>
       </c>
       <c r="H347" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="I347" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="J347" t="s">
         <v>60</v>
@@ -21590,10 +21593,10 @@
         <v>60</v>
       </c>
       <c r="L347" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="M347" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="N347" t="s">
         <v>45</v>
@@ -21613,7 +21616,7 @@
     </row>
     <row r="348">
       <c r="A348" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="B348" t="s">
         <v>34</v>
@@ -21634,10 +21637,10 @@
         <v>41</v>
       </c>
       <c r="H348" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="I348" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="J348" t="s">
         <v>88</v>
@@ -21646,10 +21649,10 @@
         <v>88</v>
       </c>
       <c r="L348" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="M348" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="N348" t="s">
         <v>45</v>
@@ -21669,7 +21672,7 @@
     </row>
     <row r="349">
       <c r="A349" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="B349" t="s">
         <v>34</v>
@@ -21690,10 +21693,10 @@
         <v>41</v>
       </c>
       <c r="H349" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="I349" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="J349" t="s">
         <v>60</v>
@@ -21702,10 +21705,10 @@
         <v>60</v>
       </c>
       <c r="L349" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="M349" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="N349" t="s">
         <v>45</v>
@@ -21725,7 +21728,7 @@
     </row>
     <row r="350">
       <c r="A350" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="B350" t="s">
         <v>34</v>
@@ -21746,10 +21749,10 @@
         <v>41</v>
       </c>
       <c r="H350" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="I350" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="J350" t="s">
         <v>60</v>
@@ -21758,10 +21761,10 @@
         <v>60</v>
       </c>
       <c r="L350" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="M350" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="N350" t="s">
         <v>45</v>
@@ -21781,7 +21784,7 @@
     </row>
     <row r="351">
       <c r="A351" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="B351" t="s">
         <v>34</v>
@@ -21802,10 +21805,10 @@
         <v>41</v>
       </c>
       <c r="H351" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="I351" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="J351" t="s">
         <v>60</v>
@@ -21814,10 +21817,10 @@
         <v>60</v>
       </c>
       <c r="L351" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="M351" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="N351" t="s">
         <v>45</v>
@@ -21837,7 +21840,7 @@
     </row>
     <row r="352">
       <c r="A352" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="B352" t="s">
         <v>34</v>
@@ -21858,10 +21861,10 @@
         <v>41</v>
       </c>
       <c r="H352" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="I352" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="J352" t="s">
         <v>130</v>
@@ -21870,10 +21873,10 @@
         <v>130</v>
       </c>
       <c r="L352" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="M352" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="N352" t="s">
         <v>45</v>
@@ -21893,7 +21896,7 @@
     </row>
     <row r="353">
       <c r="A353" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="B353" t="s">
         <v>34</v>
@@ -21914,10 +21917,10 @@
         <v>41</v>
       </c>
       <c r="H353" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="I353" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="J353" t="s">
         <v>67</v>
@@ -21926,10 +21929,10 @@
         <v>67</v>
       </c>
       <c r="L353" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="M353" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="N353" t="s">
         <v>45</v>
@@ -21949,7 +21952,7 @@
     </row>
     <row r="354">
       <c r="A354" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="B354" t="s">
         <v>34</v>
@@ -21970,10 +21973,10 @@
         <v>41</v>
       </c>
       <c r="H354" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="I354" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="J354" t="s">
         <v>108</v>
@@ -21982,10 +21985,10 @@
         <v>108</v>
       </c>
       <c r="L354" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="M354" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="N354" t="s">
         <v>45</v>
@@ -22005,7 +22008,7 @@
     </row>
     <row r="355">
       <c r="A355" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="B355" t="s">
         <v>34</v>
@@ -22026,10 +22029,10 @@
         <v>41</v>
       </c>
       <c r="H355" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="I355" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="J355" t="s">
         <v>130</v>
@@ -22038,10 +22041,10 @@
         <v>130</v>
       </c>
       <c r="L355" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="M355" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="N355" t="s">
         <v>45</v>
@@ -22061,7 +22064,7 @@
     </row>
     <row r="356">
       <c r="A356" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="B356" t="s">
         <v>34</v>
@@ -22082,10 +22085,10 @@
         <v>41</v>
       </c>
       <c r="H356" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="I356" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="J356" t="s">
         <v>130</v>
@@ -22094,10 +22097,10 @@
         <v>130</v>
       </c>
       <c r="L356" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="M356" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="N356" t="s">
         <v>45</v>
@@ -22117,7 +22120,7 @@
     </row>
     <row r="357">
       <c r="A357" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="B357" t="s">
         <v>34</v>
@@ -22138,10 +22141,10 @@
         <v>41</v>
       </c>
       <c r="H357" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="I357" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="J357" t="s">
         <v>118</v>
@@ -22150,10 +22153,10 @@
         <v>118</v>
       </c>
       <c r="L357" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="M357" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="N357" t="s">
         <v>45</v>
@@ -22173,7 +22176,7 @@
     </row>
     <row r="358">
       <c r="A358" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="B358" t="s">
         <v>34</v>
@@ -22194,10 +22197,10 @@
         <v>41</v>
       </c>
       <c r="H358" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="I358" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="J358" t="s">
         <v>67</v>
@@ -22206,10 +22209,10 @@
         <v>67</v>
       </c>
       <c r="L358" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="M358" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="N358" t="s">
         <v>45</v>
@@ -22229,7 +22232,7 @@
     </row>
     <row r="359">
       <c r="A359" t="s" s="1">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="B359" t="s" s="1">
         <v>32</v>
@@ -22285,7 +22288,7 @@
     </row>
     <row r="360">
       <c r="A360" t="s" s="1">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="B360" t="s" s="1">
         <v>32</v>
@@ -22341,7 +22344,7 @@
     </row>
     <row r="361">
       <c r="A361" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="B361" t="s">
         <v>32</v>
@@ -22397,7 +22400,7 @@
     </row>
     <row r="362">
       <c r="A362" t="s" s="1">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B362" t="s" s="1">
         <v>168</v>
@@ -22453,7 +22456,7 @@
     </row>
     <row r="363">
       <c r="A363" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="B363" t="s">
         <v>168</v>
@@ -22509,13 +22512,13 @@
     </row>
     <row r="364">
       <c r="A364" t="s" s="1">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="B364" t="s" s="1">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="C364" t="s" s="1">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="D364" t="s" s="1">
         <v>33</v>
@@ -22565,7 +22568,7 @@
     </row>
     <row r="365">
       <c r="A365" t="s" s="1">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B365" t="s" s="1">
         <v>191</v>
@@ -22621,7 +22624,7 @@
     </row>
     <row r="366">
       <c r="A366" t="s" s="1">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="B366" t="s" s="1">
         <v>193</v>
@@ -22677,7 +22680,7 @@
     </row>
     <row r="367">
       <c r="A367" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="B367" t="s">
         <v>193</v>
@@ -22733,7 +22736,7 @@
     </row>
     <row r="368">
       <c r="A368" t="s" s="1">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="B368" t="s" s="1">
         <v>298</v>
@@ -22789,7 +22792,7 @@
     </row>
     <row r="369">
       <c r="A369" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="B369" t="s">
         <v>298</v>
@@ -22845,13 +22848,13 @@
     </row>
     <row r="370">
       <c r="A370" t="s" s="1">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="B370" t="s" s="1">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="C370" t="s" s="1">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="D370" t="s" s="1">
         <v>33</v>
@@ -22901,13 +22904,13 @@
     </row>
     <row r="371">
       <c r="A371" t="s" s="1">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="B371" t="s" s="1">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="C371" t="s" s="1">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="D371" t="s" s="1">
         <v>33</v>
@@ -22957,7 +22960,7 @@
     </row>
     <row r="372">
       <c r="A372" t="s" s="1">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="B372" t="s" s="1">
         <v>359</v>
@@ -23013,7 +23016,7 @@
     </row>
     <row r="373">
       <c r="A373" t="s" s="1">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="B373" t="s" s="1">
         <v>361</v>
@@ -23069,7 +23072,7 @@
     </row>
     <row r="374">
       <c r="A374" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="B374" t="s">
         <v>361</v>
@@ -23125,7 +23128,7 @@
     </row>
     <row r="375">
       <c r="A375" t="s" s="1">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="B375" t="s" s="1">
         <v>517</v>
@@ -23181,7 +23184,7 @@
     </row>
     <row r="376">
       <c r="A376" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="B376" t="s">
         <v>519</v>
@@ -23237,7 +23240,7 @@
     </row>
     <row r="377">
       <c r="A377" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="B377" t="s">
         <v>524</v>
@@ -23293,7 +23296,7 @@
     </row>
     <row r="378">
       <c r="A378" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="B378" t="s">
         <v>531</v>
@@ -23349,7 +23352,7 @@
     </row>
     <row r="379">
       <c r="A379" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="B379" t="s">
         <v>538</v>
@@ -23405,7 +23408,7 @@
     </row>
     <row r="380">
       <c r="A380" t="s" s="1">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="B380" t="s" s="1">
         <v>565</v>
@@ -23461,7 +23464,7 @@
     </row>
     <row r="381">
       <c r="A381" t="s" s="1">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="B381" t="s" s="1">
         <v>567</v>
@@ -23517,7 +23520,7 @@
     </row>
     <row r="382">
       <c r="A382" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="B382" t="s">
         <v>569</v>
@@ -23573,7 +23576,7 @@
     </row>
     <row r="383">
       <c r="A383" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="B383" t="s">
         <v>574</v>
@@ -23629,13 +23632,13 @@
     </row>
     <row r="384">
       <c r="A384" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="B384" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C384" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="D384" t="s">
         <v>33</v>
@@ -23685,13 +23688,13 @@
     </row>
     <row r="385">
       <c r="A385" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="B385" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C385" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="D385" t="s">
         <v>33</v>
@@ -23741,13 +23744,13 @@
     </row>
     <row r="386">
       <c r="A386" t="s" s="1">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B386" t="s" s="1">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="C386" t="s" s="1">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="D386" t="s" s="1">
         <v>33</v>
@@ -23797,13 +23800,13 @@
     </row>
     <row r="387">
       <c r="A387" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="B387" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C387" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="D387" t="s">
         <v>33</v>
@@ -23853,13 +23856,13 @@
     </row>
     <row r="388">
       <c r="A388" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="B388" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C388" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="D388" t="s">
         <v>33</v>
@@ -23909,13 +23912,13 @@
     </row>
     <row r="389">
       <c r="A389" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="B389" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C389" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="D389" t="s">
         <v>33</v>
@@ -23965,13 +23968,13 @@
     </row>
     <row r="390">
       <c r="A390" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B390" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C390" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="D390" t="s">
         <v>33</v>
@@ -24021,13 +24024,13 @@
     </row>
     <row r="391">
       <c r="A391" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="B391" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C391" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="D391" t="s">
         <v>33</v>
@@ -24077,13 +24080,13 @@
     </row>
     <row r="392">
       <c r="A392" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="B392" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C392" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="D392" t="s">
         <v>33</v>
@@ -24133,13 +24136,13 @@
     </row>
     <row r="393">
       <c r="A393" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B393" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="C393" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="D393" t="s">
         <v>33</v>
@@ -24189,13 +24192,13 @@
     </row>
     <row r="394">
       <c r="A394" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="B394" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C394" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="D394" t="s">
         <v>33</v>
@@ -24245,13 +24248,13 @@
     </row>
     <row r="395">
       <c r="A395" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="B395" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C395" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="D395" t="s">
         <v>33</v>
@@ -24301,13 +24304,13 @@
     </row>
     <row r="396">
       <c r="A396" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="B396" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="C396" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="D396" t="s">
         <v>33</v>
@@ -24357,13 +24360,13 @@
     </row>
     <row r="397">
       <c r="A397" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="B397" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="C397" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="D397" t="s">
         <v>33</v>
@@ -24413,13 +24416,13 @@
     </row>
     <row r="398">
       <c r="A398" t="s" s="1">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="B398" t="s" s="1">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="C398" t="s" s="1">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="D398" t="s" s="1">
         <v>33</v>
@@ -24469,13 +24472,13 @@
     </row>
     <row r="399">
       <c r="A399" t="s" s="1">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="B399" t="s" s="1">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="C399" t="s" s="1">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="D399" t="s" s="1">
         <v>33</v>
@@ -24525,13 +24528,13 @@
     </row>
     <row r="400">
       <c r="A400" t="s" s="1">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="B400" t="s" s="1">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="C400" t="s" s="1">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="D400" t="s" s="1">
         <v>33</v>
@@ -24581,13 +24584,13 @@
     </row>
     <row r="401">
       <c r="A401" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="B401" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="C401" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="D401" t="s">
         <v>33</v>
@@ -24637,13 +24640,13 @@
     </row>
     <row r="402">
       <c r="A402" t="s" s="1">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="B402" t="s" s="1">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="C402" t="s" s="1">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="D402" t="s" s="1">
         <v>33</v>
@@ -24693,13 +24696,13 @@
     </row>
     <row r="403">
       <c r="A403" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="B403" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="C403" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="D403" t="s">
         <v>33</v>
@@ -24749,13 +24752,13 @@
     </row>
     <row r="404">
       <c r="A404" t="s" s="1">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="B404" t="s" s="1">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="C404" t="s" s="1">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="D404" t="s" s="1">
         <v>33</v>
@@ -24805,13 +24808,13 @@
     </row>
     <row r="405">
       <c r="A405" t="s" s="1">
+        <v>888</v>
+      </c>
+      <c r="B405" t="s" s="1">
         <v>887</v>
       </c>
-      <c r="B405" t="s" s="1">
-        <v>886</v>
-      </c>
       <c r="C405" t="s" s="1">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="D405" t="s" s="1">
         <v>33</v>
@@ -24861,13 +24864,13 @@
     </row>
     <row r="406">
       <c r="A406" t="s" s="1">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="B406" t="s" s="1">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="C406" t="s" s="1">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="D406" t="s" s="1">
         <v>33</v>
@@ -24917,7 +24920,7 @@
     </row>
     <row r="407">
       <c r="A407" t="s" s="1">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="B407" t="s" s="1">
         <v>32</v>
@@ -24973,13 +24976,13 @@
     </row>
     <row r="408">
       <c r="A408" t="s" s="1">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="B408" t="s" s="1">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="C408" t="s" s="1">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="D408" t="s" s="1">
         <v>33</v>
@@ -25029,7 +25032,7 @@
     </row>
     <row r="409">
       <c r="A409" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="B409" t="s">
         <v>168</v>
@@ -25085,7 +25088,7 @@
     </row>
     <row r="410">
       <c r="A410" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="B410" t="s">
         <v>191</v>
@@ -25141,7 +25144,7 @@
     </row>
     <row r="411">
       <c r="A411" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="B411" t="s">
         <v>359</v>
@@ -25197,13 +25200,13 @@
     </row>
     <row r="412">
       <c r="A412" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="B412" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="C412" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="D412" t="s">
         <v>33</v>
@@ -25253,13 +25256,13 @@
     </row>
     <row r="413">
       <c r="A413" t="s" s="1">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="B413" t="s" s="1">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="C413" t="s" s="1">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="D413" t="s" s="1">
         <v>33</v>
@@ -25309,7 +25312,7 @@
     </row>
     <row r="414">
       <c r="A414" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="B414" t="s">
         <v>565</v>
@@ -25365,13 +25368,13 @@
     </row>
     <row r="415">
       <c r="A415" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="B415" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="C415" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="D415" t="s">
         <v>33</v>
@@ -25421,7 +25424,7 @@
     </row>
     <row r="416">
       <c r="A416" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="B416" t="s">
         <v>32</v>
@@ -25477,13 +25480,13 @@
     </row>
     <row r="417">
       <c r="A417" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="B417" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="C417" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="D417" t="s">
         <v>33</v>
@@ -25533,13 +25536,13 @@
     </row>
     <row r="418">
       <c r="A418" t="s">
+        <v>904</v>
+      </c>
+      <c r="B418" t="s">
         <v>903</v>
       </c>
-      <c r="B418" t="s">
-        <v>902</v>
-      </c>
       <c r="C418" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="D418" t="s">
         <v>33</v>
@@ -25589,7 +25592,7 @@
     </row>
     <row r="419">
       <c r="A419" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="B419" t="s">
         <v>193</v>
@@ -25645,7 +25648,7 @@
     </row>
     <row r="420">
       <c r="A420" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="B420" t="s">
         <v>361</v>
@@ -25701,7 +25704,7 @@
     </row>
     <row r="421">
       <c r="A421" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="B421" t="s">
         <v>567</v>
@@ -25757,13 +25760,13 @@
     </row>
     <row r="422">
       <c r="A422" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="B422" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C422" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="D422" t="s">
         <v>33</v>
@@ -25813,7 +25816,7 @@
     </row>
     <row r="423">
       <c r="A423" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="B423" t="s">
         <v>168</v>
@@ -25869,13 +25872,13 @@
     </row>
     <row r="424">
       <c r="A424" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="B424" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="C424" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="D424" t="s">
         <v>33</v>
@@ -25925,13 +25928,13 @@
     </row>
     <row r="425">
       <c r="A425" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="B425" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="C425" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="D425" t="s">
         <v>33</v>
@@ -25981,13 +25984,13 @@
     </row>
     <row r="426">
       <c r="A426" t="s" s="1">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="B426" t="s" s="1">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="C426" t="s" s="1">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="D426" t="s" s="1">
         <v>33</v>
@@ -26037,16 +26040,16 @@
     </row>
     <row r="427">
       <c r="A427" t="s" s="1">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="B427" t="s" s="1">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="C427" t="s" s="1">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="D427" t="s" s="1">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="E427" t="s" s="1">
         <v>34</v>
@@ -26093,16 +26096,16 @@
     </row>
     <row r="428">
       <c r="A428" t="s" s="1">
+        <v>917</v>
+      </c>
+      <c r="B428" t="s" s="1">
+        <v>918</v>
+      </c>
+      <c r="C428" t="s" s="1">
+        <v>918</v>
+      </c>
+      <c r="D428" t="s" s="1">
         <v>916</v>
-      </c>
-      <c r="B428" t="s" s="1">
-        <v>917</v>
-      </c>
-      <c r="C428" t="s" s="1">
-        <v>917</v>
-      </c>
-      <c r="D428" t="s" s="1">
-        <v>915</v>
       </c>
       <c r="E428" t="s" s="1">
         <v>34</v>
@@ -26149,16 +26152,16 @@
     </row>
     <row r="429">
       <c r="A429" t="s" s="1">
+        <v>919</v>
+      </c>
+      <c r="B429" t="s" s="1">
         <v>918</v>
       </c>
-      <c r="B429" t="s" s="1">
-        <v>917</v>
-      </c>
       <c r="C429" t="s" s="1">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="D429" t="s" s="1">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="E429" t="s" s="1">
         <v>34</v>
@@ -26205,13 +26208,13 @@
     </row>
     <row r="430">
       <c r="A430" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="B430" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="C430" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="D430" t="s">
         <v>33</v>
@@ -26261,19 +26264,19 @@
     </row>
     <row r="431">
       <c r="A431" t="s">
+        <v>922</v>
+      </c>
+      <c r="B431" t="s">
         <v>921</v>
       </c>
-      <c r="B431" t="s">
-        <v>920</v>
-      </c>
       <c r="C431" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="D431" t="s">
         <v>33</v>
       </c>
       <c r="E431" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="F431" t="s">
         <v>63</v>
@@ -26282,22 +26285,22 @@
         <v>41</v>
       </c>
       <c r="H431" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="I431" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="J431" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="K431" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="L431" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="M431" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="N431" t="s">
         <v>45</v>
@@ -26306,7 +26309,7 @@
         <v>153</v>
       </c>
       <c r="P431" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="Q431" t="s">
         <v>45</v>
@@ -26317,7 +26320,7 @@
     </row>
     <row r="432">
       <c r="A432" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="B432" t="s">
         <v>34</v>
@@ -26329,7 +26332,7 @@
         <v>34</v>
       </c>
       <c r="E432" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="F432" t="s">
         <v>63</v>
@@ -26338,10 +26341,10 @@
         <v>41</v>
       </c>
       <c r="H432" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="I432" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="J432" t="s">
         <v>67</v>
@@ -26353,7 +26356,7 @@
         <v>34</v>
       </c>
       <c r="M432" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="N432" t="s">
         <v>45</v>
@@ -26362,7 +26365,7 @@
         <v>153</v>
       </c>
       <c r="P432" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="Q432" t="s">
         <v>45</v>
@@ -26373,7 +26376,7 @@
     </row>
     <row r="433">
       <c r="A433" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="B433" t="s">
         <v>34</v>
@@ -26385,7 +26388,7 @@
         <v>34</v>
       </c>
       <c r="E433" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="F433" t="s">
         <v>198</v>
@@ -26394,22 +26397,22 @@
         <v>41</v>
       </c>
       <c r="H433" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="I433" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="J433" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="K433" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="L433" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="M433" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="N433" t="s">
         <v>45</v>
@@ -26418,7 +26421,7 @@
         <v>153</v>
       </c>
       <c r="P433" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="Q433" t="s">
         <v>45</v>
@@ -26429,7 +26432,7 @@
     </row>
     <row r="434">
       <c r="A434" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="B434" t="s">
         <v>34</v>
@@ -26441,7 +26444,7 @@
         <v>34</v>
       </c>
       <c r="E434" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="F434" t="s">
         <v>63</v>
@@ -26450,10 +26453,10 @@
         <v>41</v>
       </c>
       <c r="H434" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="I434" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="J434" t="s">
         <v>108</v>
@@ -26462,10 +26465,10 @@
         <v>118</v>
       </c>
       <c r="L434" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="M434" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="N434" t="s">
         <v>45</v>
@@ -26474,7 +26477,7 @@
         <v>153</v>
       </c>
       <c r="P434" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="Q434" t="s">
         <v>45</v>
@@ -26485,7 +26488,7 @@
     </row>
     <row r="435">
       <c r="A435" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="B435" t="s">
         <v>34</v>
@@ -26497,7 +26500,7 @@
         <v>34</v>
       </c>
       <c r="E435" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="F435" t="s">
         <v>63</v>
@@ -26506,10 +26509,10 @@
         <v>41</v>
       </c>
       <c r="H435" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="I435" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="J435" t="s">
         <v>121</v>
@@ -26518,10 +26521,10 @@
         <v>146</v>
       </c>
       <c r="L435" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="M435" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="N435" t="s">
         <v>45</v>
@@ -26530,7 +26533,7 @@
         <v>153</v>
       </c>
       <c r="P435" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="Q435" t="s">
         <v>45</v>
@@ -26541,7 +26544,7 @@
     </row>
     <row r="436">
       <c r="A436" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="B436" t="s">
         <v>34</v>
@@ -26553,7 +26556,7 @@
         <v>34</v>
       </c>
       <c r="E436" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="F436" t="s">
         <v>63</v>
@@ -26562,22 +26565,22 @@
         <v>41</v>
       </c>
       <c r="H436" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="I436" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="J436" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="K436" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="L436" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="M436" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="N436" t="s">
         <v>45</v>
@@ -26586,7 +26589,7 @@
         <v>153</v>
       </c>
       <c r="P436" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="Q436" t="s">
         <v>45</v>
@@ -26597,7 +26600,7 @@
     </row>
     <row r="437">
       <c r="A437" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="B437" t="s">
         <v>34</v>
@@ -26609,7 +26612,7 @@
         <v>34</v>
       </c>
       <c r="E437" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="F437" t="s">
         <v>198</v>
@@ -26618,10 +26621,10 @@
         <v>41</v>
       </c>
       <c r="H437" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="I437" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="J437" t="s">
         <v>66</v>
@@ -26633,7 +26636,7 @@
         <v>34</v>
       </c>
       <c r="M437" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="N437" t="s">
         <v>45</v>
@@ -26642,7 +26645,7 @@
         <v>153</v>
       </c>
       <c r="P437" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="Q437" t="s">
         <v>45</v>

--- a/xlsx/dre/DRE_08_2026.xlsx
+++ b/xlsx/dre/DRE_08_2026.xlsx
@@ -477,6 +477,21 @@
     <t>ADM</t>
   </si>
   <si>
+    <t>38/1</t>
+  </si>
+  <si>
+    <t>INSS- Previdenciária</t>
+  </si>
+  <si>
+    <t>R$  1.607,30</t>
+  </si>
+  <si>
+    <t>21/09/26</t>
+  </si>
+  <si>
+    <t>INSS</t>
+  </si>
+  <si>
     <t>1/7</t>
   </si>
   <si>
@@ -493,21 +508,6 @@
   </si>
   <si>
     <t>Digisac MP 2026</t>
-  </si>
-  <si>
-    <t>38/1</t>
-  </si>
-  <si>
-    <t>INSS- Previdenciária</t>
-  </si>
-  <si>
-    <t>R$  1.607,30</t>
-  </si>
-  <si>
-    <t>21/09/26</t>
-  </si>
-  <si>
-    <t>INSS</t>
   </si>
   <si>
     <t>4 CUSTOS E DESPESAS</t>
@@ -1608,12 +1608,12 @@
     <t>4.03.03.02.05.02 Assistência técnica medição</t>
   </si>
   <si>
+    <t>L E A Medicoes Tecnicas LTDA</t>
+  </si>
+  <si>
     <t>PFP</t>
   </si>
   <si>
-    <t>L E A Medicoes Tecnicas LTDA</t>
-  </si>
-  <si>
     <t>R$  360,00</t>
   </si>
   <si>
@@ -1668,6 +1668,30 @@
     <t>R$ 9.215,99</t>
   </si>
   <si>
+    <t>12/8</t>
+  </si>
+  <si>
+    <t>MARQUES MAIO MARKETING DIGITAL LTDA</t>
+  </si>
+  <si>
+    <t>R$  808,50</t>
+  </si>
+  <si>
+    <t>08/01/26</t>
+  </si>
+  <si>
+    <t>MHM - Honorários 2026</t>
+  </si>
+  <si>
+    <t>Google</t>
+  </si>
+  <si>
+    <t>R$  14,99</t>
+  </si>
+  <si>
+    <t>Google 2026</t>
+  </si>
+  <si>
     <t>WEBGIGA SOLUCOES DIGITAIS LTDA</t>
   </si>
   <si>
@@ -1678,30 +1702,6 @@
   </si>
   <si>
     <t>Webgiga 2026</t>
-  </si>
-  <si>
-    <t>12/8</t>
-  </si>
-  <si>
-    <t>Google</t>
-  </si>
-  <si>
-    <t>R$  14,99</t>
-  </si>
-  <si>
-    <t>Google 2026</t>
-  </si>
-  <si>
-    <t>MARQUES MAIO MARKETING DIGITAL LTDA</t>
-  </si>
-  <si>
-    <t>R$  808,50</t>
-  </si>
-  <si>
-    <t>08/01/26</t>
-  </si>
-  <si>
-    <t>MHM - Honorários 2026</t>
   </si>
   <si>
     <t>1/6</t>
@@ -2130,18 +2130,6 @@
     <t xml:space="preserve">04/08/2026	•••• •••• •••• 0005497380066700654	SUPERMERCADO	Compra à vista		105,06	PAO DE ACUCAR 2409     	Materiais limpeza e pao de queijo
 25/08/2026	•••• •••• •••• 0005497380066700654	SUPERMERCADO	Compra à vista		307,33	PAO DE ACUCAR 2409	Materiais limpeza 
 </t>
-  </si>
-  <si>
-    <t>736/1</t>
-  </si>
-  <si>
-    <t>Casa de Bolos de Moema LTDA</t>
-  </si>
-  <si>
-    <t>R$  97,00</t>
-  </si>
-  <si>
-    <t>Bolo Bianca</t>
   </si>
   <si>
     <t>745/1</t>
@@ -2169,6 +2157,18 @@
     <t>R$  5,95</t>
   </si>
   <si>
+    <t>736/1</t>
+  </si>
+  <si>
+    <t>Casa de Bolos de Moema LTDA</t>
+  </si>
+  <si>
+    <t>R$  97,00</t>
+  </si>
+  <si>
+    <t>Bolo Bianca</t>
+  </si>
+  <si>
     <t>4.04.02.07 Informática</t>
   </si>
   <si>
@@ -2229,6 +2229,39 @@
     <t>4.04.02.08.03 Mensalidades e assinaturas - outros gastos</t>
   </si>
   <si>
+    <t>3/7</t>
+  </si>
+  <si>
+    <t>R$  1.248,76</t>
+  </si>
+  <si>
+    <t>13/02/26</t>
+  </si>
+  <si>
+    <t>Promob 2026/2</t>
+  </si>
+  <si>
+    <t>D4 sign</t>
+  </si>
+  <si>
+    <t>R$  49,95</t>
+  </si>
+  <si>
+    <t>D4 sign 2026</t>
+  </si>
+  <si>
+    <t>63/3</t>
+  </si>
+  <si>
+    <t>R$  376,38</t>
+  </si>
+  <si>
+    <t>11/06/26</t>
+  </si>
+  <si>
+    <t>Promob 2026/4</t>
+  </si>
+  <si>
     <t>70/12</t>
   </si>
   <si>
@@ -2238,16 +2271,31 @@
     <t>Promob 26/5</t>
   </si>
   <si>
-    <t>63/3</t>
-  </si>
-  <si>
-    <t>R$  376,38</t>
-  </si>
-  <si>
-    <t>11/06/26</t>
-  </si>
-  <si>
-    <t>Promob 2026/4</t>
+    <t>64/3</t>
+  </si>
+  <si>
+    <t>ISO IMPLANTACAO EM SAUDE OCUPACIONAL LTDA</t>
+  </si>
+  <si>
+    <t>R$  146,67</t>
+  </si>
+  <si>
+    <t>24/06/26</t>
+  </si>
+  <si>
+    <t>22/08/26</t>
+  </si>
+  <si>
+    <t>ISO Implantação -Saude ocupacional</t>
+  </si>
+  <si>
+    <t>62/3</t>
+  </si>
+  <si>
+    <t>R$  293,11</t>
+  </si>
+  <si>
+    <t>Promob 2026/3</t>
   </si>
   <si>
     <t>R$  599,00</t>
@@ -2256,36 +2304,6 @@
     <t>Promob 2026</t>
   </si>
   <si>
-    <t>62/3</t>
-  </si>
-  <si>
-    <t>R$  293,11</t>
-  </si>
-  <si>
-    <t>Promob 2026/3</t>
-  </si>
-  <si>
-    <t>D4 sign</t>
-  </si>
-  <si>
-    <t>R$  49,95</t>
-  </si>
-  <si>
-    <t>D4 sign 2026</t>
-  </si>
-  <si>
-    <t>3/7</t>
-  </si>
-  <si>
-    <t>R$  1.248,76</t>
-  </si>
-  <si>
-    <t>13/02/26</t>
-  </si>
-  <si>
-    <t>Promob 2026/2</t>
-  </si>
-  <si>
     <t>61/4</t>
   </si>
   <si>
@@ -2296,24 +2314,6 @@
   </si>
   <si>
     <t>21/05/26</t>
-  </si>
-  <si>
-    <t>64/3</t>
-  </si>
-  <si>
-    <t>ISO IMPLANTACAO EM SAUDE OCUPACIONAL LTDA</t>
-  </si>
-  <si>
-    <t>R$  146,67</t>
-  </si>
-  <si>
-    <t>24/06/26</t>
-  </si>
-  <si>
-    <t>22/08/26</t>
-  </si>
-  <si>
-    <t>ISO Implantação -Saude ocupacional</t>
   </si>
   <si>
     <t>4.04.02.11 Manutenção de predio e equipamentos</t>
@@ -2425,6 +2425,15 @@
     <t>R$ 400,33</t>
   </si>
   <si>
+    <t>VERISURE</t>
+  </si>
+  <si>
+    <t>R$  250,33</t>
+  </si>
+  <si>
+    <t>Verisure - Alarme 2026</t>
+  </si>
+  <si>
     <t>Jackson Fernando de Araujo</t>
   </si>
   <si>
@@ -2432,15 +2441,6 @@
   </si>
   <si>
     <t>Segurança 2026</t>
-  </si>
-  <si>
-    <t>VERISURE</t>
-  </si>
-  <si>
-    <t>R$  250,33</t>
-  </si>
-  <si>
-    <t>Verisure - Alarme 2026</t>
   </si>
   <si>
     <t>4.04.02.14.08 Site e newsletter da loja</t>
@@ -4905,10 +4905,10 @@
         <v>157</v>
       </c>
       <c r="K49" t="s">
+        <v>88</v>
+      </c>
+      <c r="L49" t="s">
         <v>158</v>
-      </c>
-      <c r="L49" t="s">
-        <v>159</v>
       </c>
       <c r="M49" t="s">
         <v>147</v>
@@ -4943,7 +4943,7 @@
         <v>34</v>
       </c>
       <c r="E50" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F50" t="s">
         <v>63</v>
@@ -4952,16 +4952,16 @@
         <v>41</v>
       </c>
       <c r="H50" t="s">
+        <v>160</v>
+      </c>
+      <c r="I50" t="s">
         <v>161</v>
       </c>
-      <c r="I50" t="s">
+      <c r="J50" t="s">
         <v>162</v>
       </c>
-      <c r="J50" t="s">
+      <c r="K50" t="s">
         <v>163</v>
-      </c>
-      <c r="K50" t="s">
-        <v>88</v>
       </c>
       <c r="L50" t="s">
         <v>164</v>
@@ -4976,7 +4976,7 @@
         <v>153</v>
       </c>
       <c r="P50" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="Q50" t="s">
         <v>45</v>
@@ -5223,7 +5223,7 @@
         <v>33</v>
       </c>
       <c r="E55" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="F55" t="s">
         <v>173</v>
@@ -7366,7 +7366,7 @@
         <v>297</v>
       </c>
       <c r="J93" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="K93" t="s">
         <v>88</v>
@@ -15639,25 +15639,25 @@
         <v>33</v>
       </c>
       <c r="E241" t="s">
-        <v>237</v>
+        <v>219</v>
       </c>
       <c r="F241" t="s">
+        <v>173</v>
+      </c>
+      <c r="G241" t="s">
+        <v>41</v>
+      </c>
+      <c r="H241" t="s">
         <v>528</v>
-      </c>
-      <c r="G241" t="s">
-        <v>41</v>
-      </c>
-      <c r="H241" t="s">
-        <v>529</v>
       </c>
       <c r="I241" t="s">
         <v>251</v>
       </c>
       <c r="J241" t="s">
-        <v>118</v>
+        <v>67</v>
       </c>
       <c r="K241" t="s">
-        <v>118</v>
+        <v>67</v>
       </c>
       <c r="L241" t="s">
         <v>34</v>
@@ -15669,13 +15669,13 @@
         <v>45</v>
       </c>
       <c r="O241" t="s">
-        <v>34</v>
+        <v>329</v>
       </c>
       <c r="P241" t="s">
-        <v>34</v>
+        <v>251</v>
       </c>
       <c r="Q241" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R241" t="s">
         <v>34</v>
@@ -15695,25 +15695,25 @@
         <v>34</v>
       </c>
       <c r="E242" t="s">
-        <v>216</v>
+        <v>237</v>
       </c>
       <c r="F242" t="s">
-        <v>173</v>
+        <v>529</v>
       </c>
       <c r="G242" t="s">
         <v>41</v>
       </c>
       <c r="H242" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="I242" t="s">
         <v>251</v>
       </c>
       <c r="J242" t="s">
-        <v>67</v>
+        <v>118</v>
       </c>
       <c r="K242" t="s">
-        <v>67</v>
+        <v>118</v>
       </c>
       <c r="L242" t="s">
         <v>34</v>
@@ -15725,13 +15725,13 @@
         <v>45</v>
       </c>
       <c r="O242" t="s">
-        <v>243</v>
+        <v>34</v>
       </c>
       <c r="P242" t="s">
-        <v>251</v>
+        <v>34</v>
       </c>
       <c r="Q242" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="R242" t="s">
         <v>34</v>
@@ -15751,25 +15751,25 @@
         <v>34</v>
       </c>
       <c r="E243" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="F243" t="s">
+        <v>173</v>
+      </c>
+      <c r="G243" t="s">
+        <v>41</v>
+      </c>
+      <c r="H243" t="s">
         <v>528</v>
-      </c>
-      <c r="G243" t="s">
-        <v>41</v>
-      </c>
-      <c r="H243" t="s">
-        <v>529</v>
       </c>
       <c r="I243" t="s">
         <v>251</v>
       </c>
       <c r="J243" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="K243" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="L243" t="s">
         <v>34</v>
@@ -15781,13 +15781,13 @@
         <v>45</v>
       </c>
       <c r="O243" t="s">
-        <v>34</v>
+        <v>243</v>
       </c>
       <c r="P243" t="s">
-        <v>34</v>
+        <v>251</v>
       </c>
       <c r="Q243" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R243" t="s">
         <v>34</v>
@@ -15807,7 +15807,7 @@
         <v>34</v>
       </c>
       <c r="E244" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="F244" t="s">
         <v>173</v>
@@ -15816,16 +15816,16 @@
         <v>41</v>
       </c>
       <c r="H244" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="I244" t="s">
         <v>251</v>
       </c>
       <c r="J244" t="s">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="K244" t="s">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="L244" t="s">
         <v>34</v>
@@ -15837,7 +15837,7 @@
         <v>45</v>
       </c>
       <c r="O244" t="s">
-        <v>61</v>
+        <v>137</v>
       </c>
       <c r="P244" t="s">
         <v>251</v>
@@ -15863,7 +15863,7 @@
         <v>34</v>
       </c>
       <c r="E245" t="s">
-        <v>255</v>
+        <v>208</v>
       </c>
       <c r="F245" t="s">
         <v>173</v>
@@ -15872,16 +15872,16 @@
         <v>41</v>
       </c>
       <c r="H245" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="I245" t="s">
         <v>251</v>
       </c>
       <c r="J245" t="s">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="K245" t="s">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="L245" t="s">
         <v>34</v>
@@ -15893,7 +15893,7 @@
         <v>45</v>
       </c>
       <c r="O245" t="s">
-        <v>89</v>
+        <v>46</v>
       </c>
       <c r="P245" t="s">
         <v>251</v>
@@ -15919,25 +15919,25 @@
         <v>34</v>
       </c>
       <c r="E246" t="s">
-        <v>234</v>
+        <v>197</v>
       </c>
       <c r="F246" t="s">
+        <v>173</v>
+      </c>
+      <c r="G246" t="s">
+        <v>41</v>
+      </c>
+      <c r="H246" t="s">
         <v>528</v>
-      </c>
-      <c r="G246" t="s">
-        <v>41</v>
-      </c>
-      <c r="H246" t="s">
-        <v>529</v>
       </c>
       <c r="I246" t="s">
         <v>251</v>
       </c>
       <c r="J246" t="s">
-        <v>130</v>
+        <v>108</v>
       </c>
       <c r="K246" t="s">
-        <v>130</v>
+        <v>108</v>
       </c>
       <c r="L246" t="s">
         <v>34</v>
@@ -15949,13 +15949,13 @@
         <v>45</v>
       </c>
       <c r="O246" t="s">
-        <v>34</v>
+        <v>201</v>
       </c>
       <c r="P246" t="s">
-        <v>34</v>
+        <v>251</v>
       </c>
       <c r="Q246" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R246" t="s">
         <v>34</v>
@@ -15975,7 +15975,7 @@
         <v>34</v>
       </c>
       <c r="E247" t="s">
-        <v>210</v>
+        <v>239</v>
       </c>
       <c r="F247" t="s">
         <v>173</v>
@@ -15984,16 +15984,16 @@
         <v>41</v>
       </c>
       <c r="H247" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="I247" t="s">
-        <v>251</v>
+        <v>530</v>
       </c>
       <c r="J247" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="K247" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="L247" t="s">
         <v>34</v>
@@ -16005,10 +16005,10 @@
         <v>45</v>
       </c>
       <c r="O247" t="s">
-        <v>326</v>
+        <v>243</v>
       </c>
       <c r="P247" t="s">
-        <v>251</v>
+        <v>530</v>
       </c>
       <c r="Q247" t="s">
         <v>45</v>
@@ -16031,25 +16031,25 @@
         <v>34</v>
       </c>
       <c r="E248" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="F248" t="s">
+        <v>529</v>
+      </c>
+      <c r="G248" t="s">
+        <v>41</v>
+      </c>
+      <c r="H248" t="s">
         <v>528</v>
-      </c>
-      <c r="G248" t="s">
-        <v>41</v>
-      </c>
-      <c r="H248" t="s">
-        <v>529</v>
       </c>
       <c r="I248" t="s">
         <v>251</v>
       </c>
       <c r="J248" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="K248" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="L248" t="s">
         <v>34</v>
@@ -16087,25 +16087,25 @@
         <v>34</v>
       </c>
       <c r="E249" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="F249" t="s">
+        <v>173</v>
+      </c>
+      <c r="G249" t="s">
+        <v>41</v>
+      </c>
+      <c r="H249" t="s">
         <v>528</v>
-      </c>
-      <c r="G249" t="s">
-        <v>41</v>
-      </c>
-      <c r="H249" t="s">
-        <v>529</v>
       </c>
       <c r="I249" t="s">
         <v>251</v>
       </c>
       <c r="J249" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="K249" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="L249" t="s">
         <v>34</v>
@@ -16117,13 +16117,13 @@
         <v>45</v>
       </c>
       <c r="O249" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="P249" t="s">
-        <v>34</v>
+        <v>251</v>
       </c>
       <c r="Q249" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R249" t="s">
         <v>34</v>
@@ -16143,25 +16143,25 @@
         <v>34</v>
       </c>
       <c r="E250" t="s">
-        <v>197</v>
+        <v>234</v>
       </c>
       <c r="F250" t="s">
-        <v>173</v>
+        <v>529</v>
       </c>
       <c r="G250" t="s">
         <v>41</v>
       </c>
       <c r="H250" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="I250" t="s">
         <v>251</v>
       </c>
       <c r="J250" t="s">
-        <v>108</v>
+        <v>130</v>
       </c>
       <c r="K250" t="s">
-        <v>108</v>
+        <v>130</v>
       </c>
       <c r="L250" t="s">
         <v>34</v>
@@ -16173,13 +16173,13 @@
         <v>45</v>
       </c>
       <c r="O250" t="s">
-        <v>201</v>
+        <v>34</v>
       </c>
       <c r="P250" t="s">
-        <v>251</v>
+        <v>34</v>
       </c>
       <c r="Q250" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="R250" t="s">
         <v>34</v>
@@ -16199,25 +16199,25 @@
         <v>34</v>
       </c>
       <c r="E251" t="s">
-        <v>225</v>
+        <v>255</v>
       </c>
       <c r="F251" t="s">
+        <v>173</v>
+      </c>
+      <c r="G251" t="s">
+        <v>41</v>
+      </c>
+      <c r="H251" t="s">
         <v>528</v>
-      </c>
-      <c r="G251" t="s">
-        <v>41</v>
-      </c>
-      <c r="H251" t="s">
-        <v>529</v>
       </c>
       <c r="I251" t="s">
         <v>251</v>
       </c>
       <c r="J251" t="s">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="K251" t="s">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="L251" t="s">
         <v>34</v>
@@ -16229,13 +16229,13 @@
         <v>45</v>
       </c>
       <c r="O251" t="s">
-        <v>34</v>
+        <v>89</v>
       </c>
       <c r="P251" t="s">
-        <v>34</v>
+        <v>251</v>
       </c>
       <c r="Q251" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R251" t="s">
         <v>34</v>
@@ -16255,7 +16255,7 @@
         <v>34</v>
       </c>
       <c r="E252" t="s">
-        <v>239</v>
+        <v>210</v>
       </c>
       <c r="F252" t="s">
         <v>173</v>
@@ -16264,16 +16264,16 @@
         <v>41</v>
       </c>
       <c r="H252" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="I252" t="s">
-        <v>530</v>
+        <v>251</v>
       </c>
       <c r="J252" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="K252" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="L252" t="s">
         <v>34</v>
@@ -16285,10 +16285,10 @@
         <v>45</v>
       </c>
       <c r="O252" t="s">
-        <v>243</v>
+        <v>326</v>
       </c>
       <c r="P252" t="s">
-        <v>530</v>
+        <v>251</v>
       </c>
       <c r="Q252" t="s">
         <v>45</v>
@@ -16311,25 +16311,25 @@
         <v>34</v>
       </c>
       <c r="E253" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="F253" t="s">
-        <v>173</v>
+        <v>529</v>
       </c>
       <c r="G253" t="s">
         <v>41</v>
       </c>
       <c r="H253" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="I253" t="s">
         <v>251</v>
       </c>
       <c r="J253" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="K253" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="L253" t="s">
         <v>34</v>
@@ -16341,13 +16341,13 @@
         <v>45</v>
       </c>
       <c r="O253" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="P253" t="s">
-        <v>251</v>
+        <v>34</v>
       </c>
       <c r="Q253" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="R253" t="s">
         <v>34</v>
@@ -16367,25 +16367,25 @@
         <v>34</v>
       </c>
       <c r="E254" t="s">
-        <v>202</v>
+        <v>221</v>
       </c>
       <c r="F254" t="s">
+        <v>529</v>
+      </c>
+      <c r="G254" t="s">
+        <v>41</v>
+      </c>
+      <c r="H254" t="s">
         <v>528</v>
-      </c>
-      <c r="G254" t="s">
-        <v>41</v>
-      </c>
-      <c r="H254" t="s">
-        <v>529</v>
       </c>
       <c r="I254" t="s">
         <v>251</v>
       </c>
       <c r="J254" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="K254" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="L254" t="s">
         <v>34</v>
@@ -16423,25 +16423,25 @@
         <v>34</v>
       </c>
       <c r="E255" t="s">
-        <v>228</v>
+        <v>202</v>
       </c>
       <c r="F255" t="s">
-        <v>173</v>
+        <v>529</v>
       </c>
       <c r="G255" t="s">
         <v>41</v>
       </c>
       <c r="H255" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="I255" t="s">
         <v>251</v>
       </c>
       <c r="J255" t="s">
-        <v>130</v>
+        <v>50</v>
       </c>
       <c r="K255" t="s">
-        <v>130</v>
+        <v>50</v>
       </c>
       <c r="L255" t="s">
         <v>34</v>
@@ -16453,13 +16453,13 @@
         <v>45</v>
       </c>
       <c r="O255" t="s">
-        <v>137</v>
+        <v>34</v>
       </c>
       <c r="P255" t="s">
-        <v>251</v>
+        <v>34</v>
       </c>
       <c r="Q255" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="R255" t="s">
         <v>34</v>
@@ -16479,25 +16479,25 @@
         <v>34</v>
       </c>
       <c r="E256" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="F256" t="s">
-        <v>173</v>
+        <v>529</v>
       </c>
       <c r="G256" t="s">
         <v>41</v>
       </c>
       <c r="H256" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="I256" t="s">
         <v>251</v>
       </c>
       <c r="J256" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="K256" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="L256" t="s">
         <v>34</v>
@@ -16509,13 +16509,13 @@
         <v>45</v>
       </c>
       <c r="O256" t="s">
-        <v>329</v>
+        <v>34</v>
       </c>
       <c r="P256" t="s">
-        <v>251</v>
+        <v>34</v>
       </c>
       <c r="Q256" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="R256" t="s">
         <v>34</v>
@@ -16759,7 +16759,7 @@
         <v>33</v>
       </c>
       <c r="E261" t="s">
-        <v>154</v>
+        <v>548</v>
       </c>
       <c r="F261" t="s">
         <v>173</v>
@@ -16768,19 +16768,19 @@
         <v>41</v>
       </c>
       <c r="H261" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="I261" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="J261" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="K261" t="s">
-        <v>158</v>
+        <v>81</v>
       </c>
       <c r="L261" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="M261" t="s">
         <v>546</v>
@@ -16792,7 +16792,7 @@
         <v>153</v>
       </c>
       <c r="P261" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="Q261" t="s">
         <v>45</v>
@@ -16815,7 +16815,7 @@
         <v>34</v>
       </c>
       <c r="E262" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="F262" t="s">
         <v>173</v>
@@ -16871,7 +16871,7 @@
         <v>34</v>
       </c>
       <c r="E263" t="s">
-        <v>552</v>
+        <v>159</v>
       </c>
       <c r="F263" t="s">
         <v>173</v>
@@ -16889,7 +16889,7 @@
         <v>558</v>
       </c>
       <c r="K263" t="s">
-        <v>81</v>
+        <v>163</v>
       </c>
       <c r="L263" t="s">
         <v>559</v>
@@ -17151,7 +17151,7 @@
         <v>33</v>
       </c>
       <c r="E268" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="F268" t="s">
         <v>173</v>
@@ -17166,7 +17166,7 @@
         <v>572</v>
       </c>
       <c r="J268" t="s">
-        <v>558</v>
+        <v>551</v>
       </c>
       <c r="K268" t="s">
         <v>271</v>
@@ -17319,7 +17319,7 @@
         <v>33</v>
       </c>
       <c r="E271" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="F271" t="s">
         <v>173</v>
@@ -17334,7 +17334,7 @@
         <v>580</v>
       </c>
       <c r="J271" t="s">
-        <v>558</v>
+        <v>551</v>
       </c>
       <c r="K271" t="s">
         <v>271</v>
@@ -17375,7 +17375,7 @@
         <v>34</v>
       </c>
       <c r="E272" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="F272" t="s">
         <v>173</v>
@@ -17431,7 +17431,7 @@
         <v>34</v>
       </c>
       <c r="E273" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="F273" t="s">
         <v>173</v>
@@ -17446,7 +17446,7 @@
         <v>586</v>
       </c>
       <c r="J273" t="s">
-        <v>558</v>
+        <v>551</v>
       </c>
       <c r="K273" t="s">
         <v>271</v>
@@ -17487,7 +17487,7 @@
         <v>34</v>
       </c>
       <c r="E274" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="F274" t="s">
         <v>173</v>
@@ -17543,7 +17543,7 @@
         <v>34</v>
       </c>
       <c r="E275" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="F275" t="s">
         <v>173</v>
@@ -17558,7 +17558,7 @@
         <v>590</v>
       </c>
       <c r="J275" t="s">
-        <v>558</v>
+        <v>551</v>
       </c>
       <c r="K275" t="s">
         <v>271</v>
@@ -17599,7 +17599,7 @@
         <v>34</v>
       </c>
       <c r="E276" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="F276" t="s">
         <v>173</v>
@@ -17614,7 +17614,7 @@
         <v>593</v>
       </c>
       <c r="J276" t="s">
-        <v>558</v>
+        <v>551</v>
       </c>
       <c r="K276" t="s">
         <v>271</v>
@@ -17767,7 +17767,7 @@
         <v>34</v>
       </c>
       <c r="E279" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="F279" t="s">
         <v>173</v>
@@ -17782,7 +17782,7 @@
         <v>601</v>
       </c>
       <c r="J279" t="s">
-        <v>558</v>
+        <v>551</v>
       </c>
       <c r="K279" t="s">
         <v>271</v>
@@ -17823,7 +17823,7 @@
         <v>34</v>
       </c>
       <c r="E280" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="F280" t="s">
         <v>173</v>
@@ -17991,7 +17991,7 @@
         <v>34</v>
       </c>
       <c r="E283" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="F283" t="s">
         <v>173</v>
@@ -18047,7 +18047,7 @@
         <v>34</v>
       </c>
       <c r="E284" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="F284" t="s">
         <v>173</v>
@@ -18062,7 +18062,7 @@
         <v>572</v>
       </c>
       <c r="J284" t="s">
-        <v>558</v>
+        <v>551</v>
       </c>
       <c r="K284" t="s">
         <v>271</v>
@@ -18336,10 +18336,10 @@
         <v>41</v>
       </c>
       <c r="H289" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="I289" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="J289" t="s">
         <v>176</v>
@@ -18360,7 +18360,7 @@
         <v>153</v>
       </c>
       <c r="P289" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="Q289" t="s">
         <v>45</v>
@@ -18902,7 +18902,7 @@
         <v>655</v>
       </c>
       <c r="J299" t="s">
-        <v>558</v>
+        <v>551</v>
       </c>
       <c r="K299" t="s">
         <v>81</v>
@@ -19167,7 +19167,7 @@
         <v>33</v>
       </c>
       <c r="E304" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="F304" t="s">
         <v>173</v>
@@ -19182,7 +19182,7 @@
         <v>674</v>
       </c>
       <c r="J304" t="s">
-        <v>558</v>
+        <v>551</v>
       </c>
       <c r="K304" t="s">
         <v>271</v>
@@ -19335,7 +19335,7 @@
         <v>33</v>
       </c>
       <c r="E307" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="F307" t="s">
         <v>173</v>
@@ -19350,7 +19350,7 @@
         <v>686</v>
       </c>
       <c r="J307" t="s">
-        <v>558</v>
+        <v>551</v>
       </c>
       <c r="K307" t="s">
         <v>687</v>
@@ -19462,7 +19462,7 @@
         <v>693</v>
       </c>
       <c r="J309" t="s">
-        <v>558</v>
+        <v>551</v>
       </c>
       <c r="K309" t="s">
         <v>81</v>
@@ -19630,10 +19630,10 @@
         <v>704</v>
       </c>
       <c r="J312" t="s">
-        <v>121</v>
+        <v>252</v>
       </c>
       <c r="K312" t="s">
-        <v>146</v>
+        <v>66</v>
       </c>
       <c r="L312" t="s">
         <v>705</v>
@@ -19692,7 +19692,7 @@
         <v>66</v>
       </c>
       <c r="L313" t="s">
-        <v>709</v>
+        <v>34</v>
       </c>
       <c r="M313" t="s">
         <v>697</v>
@@ -19727,7 +19727,7 @@
         <v>34</v>
       </c>
       <c r="E314" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="F314" t="s">
         <v>198</v>
@@ -19736,19 +19736,19 @@
         <v>41</v>
       </c>
       <c r="H314" t="s">
+        <v>710</v>
+      </c>
+      <c r="I314" t="s">
         <v>711</v>
       </c>
-      <c r="I314" t="s">
+      <c r="J314" t="s">
+        <v>121</v>
+      </c>
+      <c r="K314" t="s">
+        <v>146</v>
+      </c>
+      <c r="L314" t="s">
         <v>712</v>
-      </c>
-      <c r="J314" t="s">
-        <v>252</v>
-      </c>
-      <c r="K314" t="s">
-        <v>66</v>
-      </c>
-      <c r="L314" t="s">
-        <v>34</v>
       </c>
       <c r="M314" t="s">
         <v>697</v>
@@ -19760,7 +19760,7 @@
         <v>153</v>
       </c>
       <c r="P314" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="Q314" t="s">
         <v>45</v>
@@ -19839,7 +19839,7 @@
         <v>33</v>
       </c>
       <c r="E316" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="F316" t="s">
         <v>173</v>
@@ -19854,7 +19854,7 @@
         <v>718</v>
       </c>
       <c r="J316" t="s">
-        <v>558</v>
+        <v>551</v>
       </c>
       <c r="K316" t="s">
         <v>271</v>
@@ -19907,7 +19907,7 @@
         <v>722</v>
       </c>
       <c r="I317" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="J317" t="s">
         <v>682</v>
@@ -19928,7 +19928,7 @@
         <v>153</v>
       </c>
       <c r="P317" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="Q317" t="s">
         <v>45</v>
@@ -20078,13 +20078,13 @@
         <v>734</v>
       </c>
       <c r="J320" t="s">
-        <v>252</v>
+        <v>735</v>
       </c>
       <c r="K320" t="s">
         <v>271</v>
       </c>
       <c r="L320" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="M320" t="s">
         <v>732</v>
@@ -20119,7 +20119,7 @@
         <v>34</v>
       </c>
       <c r="E321" t="s">
-        <v>736</v>
+        <v>548</v>
       </c>
       <c r="F321" t="s">
         <v>173</v>
@@ -20128,13 +20128,13 @@
         <v>41</v>
       </c>
       <c r="H321" t="s">
-        <v>727</v>
+        <v>737</v>
       </c>
       <c r="I321" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="J321" t="s">
-        <v>738</v>
+        <v>275</v>
       </c>
       <c r="K321" t="s">
         <v>271</v>
@@ -20152,7 +20152,7 @@
         <v>153</v>
       </c>
       <c r="P321" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="Q321" t="s">
         <v>45</v>
@@ -20175,7 +20175,7 @@
         <v>34</v>
       </c>
       <c r="E322" t="s">
-        <v>552</v>
+        <v>740</v>
       </c>
       <c r="F322" t="s">
         <v>173</v>
@@ -20187,16 +20187,16 @@
         <v>727</v>
       </c>
       <c r="I322" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="J322" t="s">
-        <v>275</v>
+        <v>742</v>
       </c>
       <c r="K322" t="s">
-        <v>60</v>
+        <v>271</v>
       </c>
       <c r="L322" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="M322" t="s">
         <v>732</v>
@@ -20208,7 +20208,7 @@
         <v>153</v>
       </c>
       <c r="P322" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="Q322" t="s">
         <v>45</v>
@@ -20231,7 +20231,7 @@
         <v>34</v>
       </c>
       <c r="E323" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="F323" t="s">
         <v>173</v>
@@ -20243,16 +20243,16 @@
         <v>727</v>
       </c>
       <c r="I323" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="J323" t="s">
-        <v>738</v>
+        <v>252</v>
       </c>
       <c r="K323" t="s">
         <v>271</v>
       </c>
       <c r="L323" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="M323" t="s">
         <v>732</v>
@@ -20264,7 +20264,7 @@
         <v>153</v>
       </c>
       <c r="P323" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="Q323" t="s">
         <v>45</v>
@@ -20287,7 +20287,7 @@
         <v>34</v>
       </c>
       <c r="E324" t="s">
-        <v>552</v>
+        <v>747</v>
       </c>
       <c r="F324" t="s">
         <v>173</v>
@@ -20296,19 +20296,19 @@
         <v>41</v>
       </c>
       <c r="H324" t="s">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="I324" t="s">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="J324" t="s">
-        <v>275</v>
+        <v>750</v>
       </c>
       <c r="K324" t="s">
-        <v>271</v>
+        <v>751</v>
       </c>
       <c r="L324" t="s">
-        <v>747</v>
+        <v>752</v>
       </c>
       <c r="M324" t="s">
         <v>732</v>
@@ -20320,7 +20320,7 @@
         <v>153</v>
       </c>
       <c r="P324" t="s">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="Q324" t="s">
         <v>45</v>
@@ -20343,7 +20343,7 @@
         <v>34</v>
       </c>
       <c r="E325" t="s">
-        <v>748</v>
+        <v>753</v>
       </c>
       <c r="F325" t="s">
         <v>173</v>
@@ -20355,16 +20355,16 @@
         <v>727</v>
       </c>
       <c r="I325" t="s">
-        <v>749</v>
+        <v>754</v>
       </c>
       <c r="J325" t="s">
-        <v>750</v>
+        <v>742</v>
       </c>
       <c r="K325" t="s">
         <v>271</v>
       </c>
       <c r="L325" t="s">
-        <v>751</v>
+        <v>755</v>
       </c>
       <c r="M325" t="s">
         <v>732</v>
@@ -20376,7 +20376,7 @@
         <v>153</v>
       </c>
       <c r="P325" t="s">
-        <v>749</v>
+        <v>754</v>
       </c>
       <c r="Q325" t="s">
         <v>45</v>
@@ -20399,7 +20399,7 @@
         <v>34</v>
       </c>
       <c r="E326" t="s">
-        <v>752</v>
+        <v>548</v>
       </c>
       <c r="F326" t="s">
         <v>173</v>
@@ -20408,19 +20408,19 @@
         <v>41</v>
       </c>
       <c r="H326" t="s">
-        <v>753</v>
+        <v>727</v>
       </c>
       <c r="I326" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="J326" t="s">
-        <v>755</v>
+        <v>275</v>
       </c>
       <c r="K326" t="s">
-        <v>271</v>
+        <v>60</v>
       </c>
       <c r="L326" t="s">
-        <v>753</v>
+        <v>757</v>
       </c>
       <c r="M326" t="s">
         <v>732</v>
@@ -20432,7 +20432,7 @@
         <v>153</v>
       </c>
       <c r="P326" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="Q326" t="s">
         <v>45</v>
@@ -20455,7 +20455,7 @@
         <v>34</v>
       </c>
       <c r="E327" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="F327" t="s">
         <v>173</v>
@@ -20464,19 +20464,19 @@
         <v>41</v>
       </c>
       <c r="H327" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="I327" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="J327" t="s">
+        <v>761</v>
+      </c>
+      <c r="K327" t="s">
+        <v>271</v>
+      </c>
+      <c r="L327" t="s">
         <v>759</v>
-      </c>
-      <c r="K327" t="s">
-        <v>760</v>
-      </c>
-      <c r="L327" t="s">
-        <v>761</v>
       </c>
       <c r="M327" t="s">
         <v>732</v>
@@ -20488,7 +20488,7 @@
         <v>153</v>
       </c>
       <c r="P327" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="Q327" t="s">
         <v>45</v>
@@ -20735,7 +20735,7 @@
         <v>33</v>
       </c>
       <c r="E332" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="F332" t="s">
         <v>173</v>
@@ -20750,7 +20750,7 @@
         <v>781</v>
       </c>
       <c r="J332" t="s">
-        <v>558</v>
+        <v>551</v>
       </c>
       <c r="K332" t="s">
         <v>271</v>
@@ -20959,7 +20959,7 @@
         <v>33</v>
       </c>
       <c r="E336" t="s">
-        <v>552</v>
+        <v>653</v>
       </c>
       <c r="F336" t="s">
         <v>173</v>
@@ -20977,7 +20977,7 @@
         <v>558</v>
       </c>
       <c r="K336" t="s">
-        <v>271</v>
+        <v>163</v>
       </c>
       <c r="L336" t="s">
         <v>800</v>
@@ -21015,7 +21015,7 @@
         <v>34</v>
       </c>
       <c r="E337" t="s">
-        <v>653</v>
+        <v>548</v>
       </c>
       <c r="F337" t="s">
         <v>173</v>
@@ -21030,10 +21030,10 @@
         <v>802</v>
       </c>
       <c r="J337" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="K337" t="s">
-        <v>158</v>
+        <v>271</v>
       </c>
       <c r="L337" t="s">
         <v>803</v>
@@ -21071,7 +21071,7 @@
         <v>33</v>
       </c>
       <c r="E338" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="F338" t="s">
         <v>173</v>
@@ -21086,7 +21086,7 @@
         <v>807</v>
       </c>
       <c r="J338" t="s">
-        <v>750</v>
+        <v>735</v>
       </c>
       <c r="K338" t="s">
         <v>271</v>

--- a/xlsx/dre/DRE_08_2026.xlsx
+++ b/xlsx/dre/DRE_08_2026.xlsx
@@ -477,6 +477,24 @@
     <t>ADM</t>
   </si>
   <si>
+    <t>1/7</t>
+  </si>
+  <si>
+    <t>MP Interiores e Serv Ltda</t>
+  </si>
+  <si>
+    <t>R$  511,90</t>
+  </si>
+  <si>
+    <t>27/02/26</t>
+  </si>
+  <si>
+    <t>18/08/26</t>
+  </si>
+  <si>
+    <t>Digisac MP 2026</t>
+  </si>
+  <si>
     <t>38/1</t>
   </si>
   <si>
@@ -490,24 +508,6 @@
   </si>
   <si>
     <t>INSS</t>
-  </si>
-  <si>
-    <t>1/7</t>
-  </si>
-  <si>
-    <t>MP Interiores e Serv Ltda</t>
-  </si>
-  <si>
-    <t>R$  511,90</t>
-  </si>
-  <si>
-    <t>27/02/26</t>
-  </si>
-  <si>
-    <t>18/08/26</t>
-  </si>
-  <si>
-    <t>Digisac MP 2026</t>
   </si>
   <si>
     <t>4 CUSTOS E DESPESAS</t>
@@ -808,61 +808,43 @@
     <t>Mat estoque</t>
   </si>
   <si>
-    <t>69/2</t>
-  </si>
-  <si>
-    <t>R$  113,98</t>
-  </si>
-  <si>
-    <t>Leo madeiras</t>
+    <t>9/8</t>
+  </si>
+  <si>
+    <t>Mercado livre</t>
+  </si>
+  <si>
+    <t>R$  91,87</t>
+  </si>
+  <si>
+    <t>09/01/26</t>
+  </si>
+  <si>
+    <t>05/08/26</t>
+  </si>
+  <si>
+    <t>Grapa</t>
+  </si>
+  <si>
+    <t>72/8</t>
+  </si>
+  <si>
+    <t>R$  56,29</t>
+  </si>
+  <si>
+    <t>Perfil Led Abrafoton</t>
+  </si>
+  <si>
+    <t>80801Abrafoton</t>
   </si>
   <si>
     <t>67/2</t>
   </si>
   <si>
-    <t>Mercado livre</t>
-  </si>
-  <si>
     <t>R$  114,50</t>
   </si>
   <si>
     <t>31/07/26</t>
-  </si>
-  <si>
-    <t>05/08/26</t>
-  </si>
-  <si>
-    <t>Grapa</t>
-  </si>
-  <si>
-    <t>9/8</t>
-  </si>
-  <si>
-    <t>R$  91,87</t>
-  </si>
-  <si>
-    <t>09/01/26</t>
-  </si>
-  <si>
-    <t>72/8</t>
-  </si>
-  <si>
-    <t>R$  56,29</t>
-  </si>
-  <si>
-    <t>Perfil Led Abrafoton</t>
-  </si>
-  <si>
-    <t>80801Abrafoton</t>
-  </si>
-  <si>
-    <t>749/1</t>
-  </si>
-  <si>
-    <t>R$  71,83</t>
-  </si>
-  <si>
-    <t>aguas</t>
   </si>
   <si>
     <t>747/1</t>
@@ -879,6 +861,24 @@
 </t>
   </si>
   <si>
+    <t>69/1</t>
+  </si>
+  <si>
+    <t>R$  113,98</t>
+  </si>
+  <si>
+    <t>Leo madeiras</t>
+  </si>
+  <si>
+    <t>749/1</t>
+  </si>
+  <si>
+    <t>R$  71,83</t>
+  </si>
+  <si>
+    <t>aguas</t>
+  </si>
+  <si>
     <t>751/1</t>
   </si>
   <si>
@@ -891,9 +891,6 @@
 </t>
   </si>
   <si>
-    <t>69/1</t>
-  </si>
-  <si>
     <t>739/1</t>
   </si>
   <si>
@@ -921,6 +918,9 @@
     <t>Estoque</t>
   </si>
   <si>
+    <t>69/2</t>
+  </si>
+  <si>
     <t>4.02.02 CUSTO DE TRANSPORTE</t>
   </si>
   <si>
@@ -1140,54 +1140,54 @@
     <t>93701NELSONPC</t>
   </si>
   <si>
+    <t>R$  1.356,34</t>
+  </si>
+  <si>
+    <t>92901NELSONPC</t>
+  </si>
+  <si>
+    <t>R$  364,18</t>
+  </si>
+  <si>
+    <t>R$  432,64</t>
+  </si>
+  <si>
+    <t>MIRZACBL92401</t>
+  </si>
+  <si>
+    <t>R$  2.194,01</t>
+  </si>
+  <si>
+    <t>R$  346,86</t>
+  </si>
+  <si>
+    <t>R$  369,26</t>
+  </si>
+  <si>
+    <t>R$  611,00</t>
+  </si>
+  <si>
+    <t>R$  400,33</t>
+  </si>
+  <si>
+    <t>R$  396,91</t>
+  </si>
+  <si>
+    <t>96501LUCASPGM</t>
+  </si>
+  <si>
+    <t>R$  951,11</t>
+  </si>
+  <si>
+    <t>97401ALEXANDRE</t>
+  </si>
+  <si>
+    <t>R$  159,91</t>
+  </si>
+  <si>
     <t>R$  146,38</t>
   </si>
   <si>
-    <t>R$  364,18</t>
-  </si>
-  <si>
-    <t>R$  432,64</t>
-  </si>
-  <si>
-    <t>MIRZACBL92401</t>
-  </si>
-  <si>
-    <t>R$  2.194,01</t>
-  </si>
-  <si>
-    <t>R$  346,86</t>
-  </si>
-  <si>
-    <t>R$  369,26</t>
-  </si>
-  <si>
-    <t>R$  611,00</t>
-  </si>
-  <si>
-    <t>R$  400,33</t>
-  </si>
-  <si>
-    <t>R$  396,91</t>
-  </si>
-  <si>
-    <t>96501LUCASPGM</t>
-  </si>
-  <si>
-    <t>R$  951,11</t>
-  </si>
-  <si>
-    <t>97401ALEXANDRE</t>
-  </si>
-  <si>
-    <t>R$  159,91</t>
-  </si>
-  <si>
-    <t>R$  1.356,34</t>
-  </si>
-  <si>
-    <t>92901NELSONPC</t>
-  </si>
-  <si>
     <t>4.03.01.02.02 Comissões vendas</t>
   </si>
   <si>
@@ -1404,39 +1404,45 @@
     <t>R$  432,60</t>
   </si>
   <si>
+    <t>FERNANDA DOCHVAT SILVA</t>
+  </si>
+  <si>
+    <t>R$  2.193,79</t>
+  </si>
+  <si>
+    <t>R$  369,25</t>
+  </si>
+  <si>
+    <t>PPC</t>
+  </si>
+  <si>
+    <t>R$  159,90</t>
+  </si>
+  <si>
+    <t>R$  5,63</t>
+  </si>
+  <si>
+    <t>R$  1.358,25</t>
+  </si>
+  <si>
+    <t>88201/1</t>
+  </si>
+  <si>
+    <t>R$  294,73</t>
+  </si>
+  <si>
+    <t>88201BRUNORV</t>
+  </si>
+  <si>
     <t>90401/1</t>
   </si>
   <si>
-    <t>FERNANDA DOCHVAT SILVA</t>
-  </si>
-  <si>
     <t>R$  3.395,45</t>
   </si>
   <si>
     <t>89301JoaoMCC</t>
   </si>
   <si>
-    <t>PPC</t>
-  </si>
-  <si>
-    <t>R$  2.193,79</t>
-  </si>
-  <si>
-    <t>R$  369,25</t>
-  </si>
-  <si>
-    <t>R$  159,90</t>
-  </si>
-  <si>
-    <t>88201/1</t>
-  </si>
-  <si>
-    <t>R$  294,73</t>
-  </si>
-  <si>
-    <t>88201BRUNORV</t>
-  </si>
-  <si>
     <t>97901/2</t>
   </si>
   <si>
@@ -1452,27 +1458,36 @@
     <t>79601EduardoMF</t>
   </si>
   <si>
+    <t>R$  610,94</t>
+  </si>
+  <si>
+    <t>91001/1</t>
+  </si>
+  <si>
+    <t>R$  491,99</t>
+  </si>
+  <si>
+    <t>91001DABRURA</t>
+  </si>
+  <si>
+    <t>R$  92,96</t>
+  </si>
+  <si>
+    <t>90501/1</t>
+  </si>
+  <si>
+    <t>R$  314,79</t>
+  </si>
+  <si>
+    <t>90501TARLEYSO</t>
+  </si>
+  <si>
+    <t>R$  43,69</t>
+  </si>
+  <si>
     <t>R$  19,04</t>
   </si>
   <si>
-    <t>90501/1</t>
-  </si>
-  <si>
-    <t>R$  314,79</t>
-  </si>
-  <si>
-    <t>90501TARLEYSO</t>
-  </si>
-  <si>
-    <t>R$  92,96</t>
-  </si>
-  <si>
-    <t>R$  5,63</t>
-  </si>
-  <si>
-    <t>R$  43,69</t>
-  </si>
-  <si>
     <t>56101/1</t>
   </si>
   <si>
@@ -1482,21 +1497,6 @@
     <t>56101FELIXHS</t>
   </si>
   <si>
-    <t>91001/1</t>
-  </si>
-  <si>
-    <t>R$  491,99</t>
-  </si>
-  <si>
-    <t>91001DABRURA</t>
-  </si>
-  <si>
-    <t>R$  1.358,25</t>
-  </si>
-  <si>
-    <t>R$  610,94</t>
-  </si>
-  <si>
     <t>4.03.01.02.08 Comissões montagem - provisão</t>
   </si>
   <si>
@@ -1608,12 +1608,12 @@
     <t>4.03.03.02.05.02 Assistência técnica medição</t>
   </si>
   <si>
+    <t>PFP</t>
+  </si>
+  <si>
     <t>L E A Medicoes Tecnicas LTDA</t>
   </si>
   <si>
-    <t>PFP</t>
-  </si>
-  <si>
     <t>R$  360,00</t>
   </si>
   <si>
@@ -1668,9 +1668,30 @@
     <t>R$ 9.215,99</t>
   </si>
   <si>
+    <t>WEBGIGA SOLUCOES DIGITAIS LTDA</t>
+  </si>
+  <si>
+    <t>R$  4.642,50</t>
+  </si>
+  <si>
+    <t>18/02/26</t>
+  </si>
+  <si>
+    <t>Webgiga 2026</t>
+  </si>
+  <si>
     <t>12/8</t>
   </si>
   <si>
+    <t>Google</t>
+  </si>
+  <si>
+    <t>R$  14,99</t>
+  </si>
+  <si>
+    <t>Google 2026</t>
+  </si>
+  <si>
     <t>MARQUES MAIO MARKETING DIGITAL LTDA</t>
   </si>
   <si>
@@ -1683,27 +1704,6 @@
     <t>MHM - Honorários 2026</t>
   </si>
   <si>
-    <t>Google</t>
-  </si>
-  <si>
-    <t>R$  14,99</t>
-  </si>
-  <si>
-    <t>Google 2026</t>
-  </si>
-  <si>
-    <t>WEBGIGA SOLUCOES DIGITAIS LTDA</t>
-  </si>
-  <si>
-    <t>R$  4.642,50</t>
-  </si>
-  <si>
-    <t>18/02/26</t>
-  </si>
-  <si>
-    <t>Webgiga 2026</t>
-  </si>
-  <si>
     <t>1/6</t>
   </si>
   <si>
@@ -1761,6 +1761,72 @@
     <t>4.04.01.02.01.01 Salário fixo</t>
   </si>
   <si>
+    <t>SABRINA ALVES DE ABREU BRAUNBECK</t>
+  </si>
+  <si>
+    <t>R$  3.276,49</t>
+  </si>
+  <si>
+    <t>Sabrina Braunbeck - Pagamento 2026</t>
+  </si>
+  <si>
+    <t>Danielle Martins da Silva</t>
+  </si>
+  <si>
+    <t>R$  2.090,00</t>
+  </si>
+  <si>
+    <t>Danielle - Pagamento 2026</t>
+  </si>
+  <si>
+    <t>Rubens - Pagamento 2026</t>
+  </si>
+  <si>
+    <t>R$  2.536,00</t>
+  </si>
+  <si>
+    <t>19/02/26</t>
+  </si>
+  <si>
+    <t>Bianca Rodrigues - Salário fixo 2026</t>
+  </si>
+  <si>
+    <t>735/1</t>
+  </si>
+  <si>
+    <t>BIANCA RODRIGUES NASCIMENTO</t>
+  </si>
+  <si>
+    <t>Pemiação meta</t>
+  </si>
+  <si>
+    <t>GUTEMBERG DIAS GOMES</t>
+  </si>
+  <si>
+    <t>R$  6.500,00</t>
+  </si>
+  <si>
+    <t>Gutemberg Dias - Pagamento</t>
+  </si>
+  <si>
+    <t>R$  1.500,00</t>
+  </si>
+  <si>
+    <t>12/02/26</t>
+  </si>
+  <si>
+    <t>Fernanda Dochvat - Fixo 2026</t>
+  </si>
+  <si>
+    <t>Fixo ago26/1</t>
+  </si>
+  <si>
+    <t>R$  225,31</t>
+  </si>
+  <si>
+    <t>Estorno empréstimo</t>
+  </si>
+  <si>
     <t>CARINA PEREIRA</t>
   </si>
   <si>
@@ -1770,25 +1836,28 @@
     <t>Carina - Pagamento 2026</t>
   </si>
   <si>
-    <t>R$  1.500,00</t>
-  </si>
-  <si>
-    <t>12/02/26</t>
-  </si>
-  <si>
-    <t>Fernanda Dochvat - Fixo 2026</t>
-  </si>
-  <si>
-    <t>GUTEMBERG DIAS GOMES</t>
-  </si>
-  <si>
-    <t>R$  6.500,00</t>
-  </si>
-  <si>
-    <t>Gutemberg Dias - Pagamento</t>
-  </si>
-  <si>
-    <t>Rubens - Pagamento 2026</t>
+    <t>740/1</t>
+  </si>
+  <si>
+    <t>Eric Kevin de Souza Serpa</t>
+  </si>
+  <si>
+    <t>19/08/26</t>
+  </si>
+  <si>
+    <t>Salário Fixo -Eric Serpa 2026</t>
+  </si>
+  <si>
+    <t>Estorno empr ago26/1</t>
+  </si>
+  <si>
+    <t>R$  249,82</t>
+  </si>
+  <si>
+    <t>Teresinha Elvira Maximino de Menezes</t>
+  </si>
+  <si>
+    <t>Tucha - Fixo 2026</t>
   </si>
   <si>
     <t>Denny Lucas do Carmo Pereira</t>
@@ -1800,21 +1869,6 @@
     <t>Denny Lucas - Pagamento 2026</t>
   </si>
   <si>
-    <t>Danielle Martins da Silva</t>
-  </si>
-  <si>
-    <t>R$  2.090,00</t>
-  </si>
-  <si>
-    <t>Danielle - Pagamento 2026</t>
-  </si>
-  <si>
-    <t>Estorno empr ago26/1</t>
-  </si>
-  <si>
-    <t>R$  249,82</t>
-  </si>
-  <si>
     <t>R$  2.219,85</t>
   </si>
   <si>
@@ -1822,60 +1876,6 @@
   </si>
   <si>
     <t>Felipe Domingos - salário fixo 2026</t>
-  </si>
-  <si>
-    <t>SABRINA ALVES DE ABREU BRAUNBECK</t>
-  </si>
-  <si>
-    <t>R$  3.276,49</t>
-  </si>
-  <si>
-    <t>Sabrina Braunbeck - Pagamento 2026</t>
-  </si>
-  <si>
-    <t>R$  2.536,00</t>
-  </si>
-  <si>
-    <t>19/02/26</t>
-  </si>
-  <si>
-    <t>Bianca Rodrigues - Salário fixo 2026</t>
-  </si>
-  <si>
-    <t>Fixo ago26/1</t>
-  </si>
-  <si>
-    <t>R$  225,31</t>
-  </si>
-  <si>
-    <t>Estorno empréstimo</t>
-  </si>
-  <si>
-    <t>740/1</t>
-  </si>
-  <si>
-    <t>Eric Kevin de Souza Serpa</t>
-  </si>
-  <si>
-    <t>19/08/26</t>
-  </si>
-  <si>
-    <t>Salário Fixo -Eric Serpa 2026</t>
-  </si>
-  <si>
-    <t>Teresinha Elvira Maximino de Menezes</t>
-  </si>
-  <si>
-    <t>Tucha - Fixo 2026</t>
-  </si>
-  <si>
-    <t>735/1</t>
-  </si>
-  <si>
-    <t>BIANCA RODRIGUES NASCIMENTO</t>
-  </si>
-  <si>
-    <t>Pemiação meta</t>
   </si>
   <si>
     <t>4.04.01.02.05 IRRF sobre salários</t>
@@ -2130,6 +2130,18 @@
     <t xml:space="preserve">04/08/2026	•••• •••• •••• 0005497380066700654	SUPERMERCADO	Compra à vista		105,06	PAO DE ACUCAR 2409     	Materiais limpeza e pao de queijo
 25/08/2026	•••• •••• •••• 0005497380066700654	SUPERMERCADO	Compra à vista		307,33	PAO DE ACUCAR 2409	Materiais limpeza 
 </t>
+  </si>
+  <si>
+    <t>736/1</t>
+  </si>
+  <si>
+    <t>Casa de Bolos de Moema LTDA</t>
+  </si>
+  <si>
+    <t>R$  97,00</t>
+  </si>
+  <si>
+    <t>Bolo Bianca</t>
   </si>
   <si>
     <t>745/1</t>
@@ -2157,18 +2169,6 @@
     <t>R$  5,95</t>
   </si>
   <si>
-    <t>736/1</t>
-  </si>
-  <si>
-    <t>Casa de Bolos de Moema LTDA</t>
-  </si>
-  <si>
-    <t>R$  97,00</t>
-  </si>
-  <si>
-    <t>Bolo Bianca</t>
-  </si>
-  <si>
     <t>4.04.02.07 Informática</t>
   </si>
   <si>
@@ -2229,6 +2229,51 @@
     <t>4.04.02.08.03 Mensalidades e assinaturas - outros gastos</t>
   </si>
   <si>
+    <t>70/12</t>
+  </si>
+  <si>
+    <t>R$  188,22</t>
+  </si>
+  <si>
+    <t>Promob 26/5</t>
+  </si>
+  <si>
+    <t>63/3</t>
+  </si>
+  <si>
+    <t>R$  376,38</t>
+  </si>
+  <si>
+    <t>11/06/26</t>
+  </si>
+  <si>
+    <t>Promob 2026/4</t>
+  </si>
+  <si>
+    <t>R$  599,00</t>
+  </si>
+  <si>
+    <t>Promob 2026</t>
+  </si>
+  <si>
+    <t>62/3</t>
+  </si>
+  <si>
+    <t>R$  293,11</t>
+  </si>
+  <si>
+    <t>Promob 2026/3</t>
+  </si>
+  <si>
+    <t>D4 sign</t>
+  </si>
+  <si>
+    <t>R$  49,95</t>
+  </si>
+  <si>
+    <t>D4 sign 2026</t>
+  </si>
+  <si>
     <t>3/7</t>
   </si>
   <si>
@@ -2241,34 +2286,16 @@
     <t>Promob 2026/2</t>
   </si>
   <si>
-    <t>D4 sign</t>
-  </si>
-  <si>
-    <t>R$  49,95</t>
-  </si>
-  <si>
-    <t>D4 sign 2026</t>
-  </si>
-  <si>
-    <t>63/3</t>
-  </si>
-  <si>
-    <t>R$  376,38</t>
-  </si>
-  <si>
-    <t>11/06/26</t>
-  </si>
-  <si>
-    <t>Promob 2026/4</t>
-  </si>
-  <si>
-    <t>70/12</t>
-  </si>
-  <si>
-    <t>R$  188,22</t>
-  </si>
-  <si>
-    <t>Promob 26/5</t>
+    <t>61/4</t>
+  </si>
+  <si>
+    <t>Pipefy</t>
+  </si>
+  <si>
+    <t>R$  98,71</t>
+  </si>
+  <si>
+    <t>21/05/26</t>
   </si>
   <si>
     <t>64/3</t>
@@ -2287,33 +2314,6 @@
   </si>
   <si>
     <t>ISO Implantação -Saude ocupacional</t>
-  </si>
-  <si>
-    <t>62/3</t>
-  </si>
-  <si>
-    <t>R$  293,11</t>
-  </si>
-  <si>
-    <t>Promob 2026/3</t>
-  </si>
-  <si>
-    <t>R$  599,00</t>
-  </si>
-  <si>
-    <t>Promob 2026</t>
-  </si>
-  <si>
-    <t>61/4</t>
-  </si>
-  <si>
-    <t>Pipefy</t>
-  </si>
-  <si>
-    <t>R$  98,71</t>
-  </si>
-  <si>
-    <t>21/05/26</t>
   </si>
   <si>
     <t>4.04.02.11 Manutenção de predio e equipamentos</t>
@@ -2425,6 +2425,15 @@
     <t>R$ 400,33</t>
   </si>
   <si>
+    <t>Jackson Fernando de Araujo</t>
+  </si>
+  <si>
+    <t>R$  150,00</t>
+  </si>
+  <si>
+    <t>Segurança 2026</t>
+  </si>
+  <si>
     <t>VERISURE</t>
   </si>
   <si>
@@ -2432,15 +2441,6 @@
   </si>
   <si>
     <t>Verisure - Alarme 2026</t>
-  </si>
-  <si>
-    <t>Jackson Fernando de Araujo</t>
-  </si>
-  <si>
-    <t>R$  150,00</t>
-  </si>
-  <si>
-    <t>Segurança 2026</t>
   </si>
   <si>
     <t>4.04.02.14.08 Site e newsletter da loja</t>
@@ -4905,10 +4905,10 @@
         <v>157</v>
       </c>
       <c r="K49" t="s">
-        <v>88</v>
+        <v>158</v>
       </c>
       <c r="L49" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M49" t="s">
         <v>147</v>
@@ -4943,7 +4943,7 @@
         <v>34</v>
       </c>
       <c r="E50" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F50" t="s">
         <v>63</v>
@@ -4952,16 +4952,16 @@
         <v>41</v>
       </c>
       <c r="H50" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I50" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J50" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="K50" t="s">
-        <v>163</v>
+        <v>88</v>
       </c>
       <c r="L50" t="s">
         <v>164</v>
@@ -4976,7 +4976,7 @@
         <v>153</v>
       </c>
       <c r="P50" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q50" t="s">
         <v>45</v>
@@ -5223,7 +5223,7 @@
         <v>33</v>
       </c>
       <c r="E55" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="F55" t="s">
         <v>173</v>
@@ -6800,19 +6800,19 @@
         <v>41</v>
       </c>
       <c r="H83" t="s">
-        <v>245</v>
+        <v>265</v>
       </c>
       <c r="I83" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="J83" t="s">
-        <v>67</v>
+        <v>267</v>
       </c>
       <c r="K83" t="s">
-        <v>67</v>
+        <v>268</v>
       </c>
       <c r="L83" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="M83" t="s">
         <v>257</v>
@@ -6824,7 +6824,7 @@
         <v>153</v>
       </c>
       <c r="P83" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q83" t="s">
         <v>45</v>
@@ -6847,7 +6847,7 @@
         <v>34</v>
       </c>
       <c r="E84" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="F84" t="s">
         <v>173</v>
@@ -6856,16 +6856,16 @@
         <v>41</v>
       </c>
       <c r="H84" t="s">
+        <v>265</v>
+      </c>
+      <c r="I84" t="s">
+        <v>271</v>
+      </c>
+      <c r="J84" t="s">
         <v>268</v>
       </c>
-      <c r="I84" t="s">
-        <v>269</v>
-      </c>
-      <c r="J84" t="s">
-        <v>270</v>
-      </c>
       <c r="K84" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="L84" t="s">
         <v>272</v>
@@ -6877,10 +6877,10 @@
         <v>45</v>
       </c>
       <c r="O84" t="s">
-        <v>153</v>
+        <v>273</v>
       </c>
       <c r="P84" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q84" t="s">
         <v>45</v>
@@ -6903,7 +6903,7 @@
         <v>34</v>
       </c>
       <c r="E85" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F85" t="s">
         <v>173</v>
@@ -6912,19 +6912,19 @@
         <v>41</v>
       </c>
       <c r="H85" t="s">
+        <v>265</v>
+      </c>
+      <c r="I85" t="s">
+        <v>275</v>
+      </c>
+      <c r="J85" t="s">
+        <v>276</v>
+      </c>
+      <c r="K85" t="s">
         <v>268</v>
       </c>
-      <c r="I85" t="s">
-        <v>274</v>
-      </c>
-      <c r="J85" t="s">
-        <v>275</v>
-      </c>
-      <c r="K85" t="s">
-        <v>271</v>
-      </c>
       <c r="L85" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="M85" t="s">
         <v>257</v>
@@ -6936,7 +6936,7 @@
         <v>153</v>
       </c>
       <c r="P85" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q85" t="s">
         <v>45</v>
@@ -6959,28 +6959,28 @@
         <v>34</v>
       </c>
       <c r="E86" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F86" t="s">
-        <v>173</v>
+        <v>198</v>
       </c>
       <c r="G86" t="s">
         <v>41</v>
       </c>
       <c r="H86" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="I86" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J86" t="s">
-        <v>271</v>
+        <v>252</v>
       </c>
       <c r="K86" t="s">
-        <v>271</v>
+        <v>66</v>
       </c>
       <c r="L86" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M86" t="s">
         <v>257</v>
@@ -6989,10 +6989,10 @@
         <v>45</v>
       </c>
       <c r="O86" t="s">
-        <v>279</v>
+        <v>153</v>
       </c>
       <c r="P86" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q86" t="s">
         <v>45</v>
@@ -7018,22 +7018,22 @@
         <v>280</v>
       </c>
       <c r="F87" t="s">
-        <v>198</v>
+        <v>173</v>
       </c>
       <c r="G87" t="s">
         <v>41</v>
       </c>
       <c r="H87" t="s">
-        <v>268</v>
+        <v>245</v>
       </c>
       <c r="I87" t="s">
         <v>281</v>
       </c>
       <c r="J87" t="s">
-        <v>252</v>
+        <v>67</v>
       </c>
       <c r="K87" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="L87" t="s">
         <v>282</v>
@@ -7080,7 +7080,7 @@
         <v>41</v>
       </c>
       <c r="H88" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="I88" t="s">
         <v>284</v>
@@ -7136,7 +7136,7 @@
         <v>41</v>
       </c>
       <c r="H89" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="I89" t="s">
         <v>287</v>
@@ -7186,25 +7186,25 @@
         <v>289</v>
       </c>
       <c r="F90" t="s">
-        <v>173</v>
+        <v>198</v>
       </c>
       <c r="G90" t="s">
         <v>41</v>
       </c>
       <c r="H90" t="s">
-        <v>245</v>
+        <v>290</v>
       </c>
       <c r="I90" t="s">
-        <v>265</v>
+        <v>291</v>
       </c>
       <c r="J90" t="s">
-        <v>67</v>
+        <v>252</v>
       </c>
       <c r="K90" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="L90" t="s">
-        <v>266</v>
+        <v>34</v>
       </c>
       <c r="M90" t="s">
         <v>257</v>
@@ -7216,7 +7216,7 @@
         <v>153</v>
       </c>
       <c r="P90" t="s">
-        <v>265</v>
+        <v>291</v>
       </c>
       <c r="Q90" t="s">
         <v>45</v>
@@ -7239,28 +7239,28 @@
         <v>34</v>
       </c>
       <c r="E91" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="F91" t="s">
-        <v>198</v>
+        <v>173</v>
       </c>
       <c r="G91" t="s">
         <v>41</v>
       </c>
       <c r="H91" t="s">
-        <v>291</v>
+        <v>265</v>
       </c>
       <c r="I91" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="J91" t="s">
-        <v>252</v>
+        <v>188</v>
       </c>
       <c r="K91" t="s">
-        <v>66</v>
+        <v>188</v>
       </c>
       <c r="L91" t="s">
-        <v>34</v>
+        <v>294</v>
       </c>
       <c r="M91" t="s">
         <v>257</v>
@@ -7269,10 +7269,10 @@
         <v>45</v>
       </c>
       <c r="O91" t="s">
-        <v>153</v>
+        <v>273</v>
       </c>
       <c r="P91" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q91" t="s">
         <v>45</v>
@@ -7295,28 +7295,28 @@
         <v>34</v>
       </c>
       <c r="E92" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="F92" t="s">
-        <v>173</v>
+        <v>198</v>
       </c>
       <c r="G92" t="s">
         <v>41</v>
       </c>
       <c r="H92" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="I92" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="J92" t="s">
-        <v>188</v>
+        <v>158</v>
       </c>
       <c r="K92" t="s">
-        <v>188</v>
+        <v>88</v>
       </c>
       <c r="L92" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="M92" t="s">
         <v>257</v>
@@ -7325,10 +7325,10 @@
         <v>45</v>
       </c>
       <c r="O92" t="s">
-        <v>279</v>
+        <v>153</v>
       </c>
       <c r="P92" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q92" t="s">
         <v>45</v>
@@ -7351,28 +7351,28 @@
         <v>34</v>
       </c>
       <c r="E93" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F93" t="s">
-        <v>198</v>
+        <v>173</v>
       </c>
       <c r="G93" t="s">
         <v>41</v>
       </c>
       <c r="H93" t="s">
-        <v>260</v>
+        <v>245</v>
       </c>
       <c r="I93" t="s">
-        <v>297</v>
+        <v>281</v>
       </c>
       <c r="J93" t="s">
-        <v>163</v>
+        <v>67</v>
       </c>
       <c r="K93" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="L93" t="s">
-        <v>298</v>
+        <v>282</v>
       </c>
       <c r="M93" t="s">
         <v>257</v>
@@ -7384,7 +7384,7 @@
         <v>153</v>
       </c>
       <c r="P93" t="s">
-        <v>297</v>
+        <v>281</v>
       </c>
       <c r="Q93" t="s">
         <v>45</v>
@@ -9311,7 +9311,7 @@
         <v>34</v>
       </c>
       <c r="E128" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="F128" t="s">
         <v>211</v>
@@ -9341,7 +9341,7 @@
         <v>45</v>
       </c>
       <c r="O128" t="s">
-        <v>137</v>
+        <v>373</v>
       </c>
       <c r="P128" t="s">
         <v>372</v>
@@ -9379,7 +9379,7 @@
         <v>368</v>
       </c>
       <c r="I129" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="J129" t="s">
         <v>370</v>
@@ -9400,7 +9400,7 @@
         <v>329</v>
       </c>
       <c r="P129" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q129" t="s">
         <v>45</v>
@@ -9435,7 +9435,7 @@
         <v>368</v>
       </c>
       <c r="I130" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="J130" t="s">
         <v>370</v>
@@ -9453,10 +9453,10 @@
         <v>45</v>
       </c>
       <c r="O130" t="s">
+        <v>376</v>
+      </c>
+      <c r="P130" t="s">
         <v>375</v>
-      </c>
-      <c r="P130" t="s">
-        <v>374</v>
       </c>
       <c r="Q130" t="s">
         <v>45</v>
@@ -9491,7 +9491,7 @@
         <v>368</v>
       </c>
       <c r="I131" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="J131" t="s">
         <v>370</v>
@@ -9512,7 +9512,7 @@
         <v>243</v>
       </c>
       <c r="P131" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q131" t="s">
         <v>45</v>
@@ -9547,7 +9547,7 @@
         <v>368</v>
       </c>
       <c r="I132" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="J132" t="s">
         <v>370</v>
@@ -9568,7 +9568,7 @@
         <v>61</v>
       </c>
       <c r="P132" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q132" t="s">
         <v>45</v>
@@ -9603,7 +9603,7 @@
         <v>368</v>
       </c>
       <c r="I133" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="J133" t="s">
         <v>370</v>
@@ -9624,7 +9624,7 @@
         <v>326</v>
       </c>
       <c r="P133" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q133" t="s">
         <v>45</v>
@@ -9659,7 +9659,7 @@
         <v>368</v>
       </c>
       <c r="I134" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="J134" t="s">
         <v>370</v>
@@ -9680,7 +9680,7 @@
         <v>77</v>
       </c>
       <c r="P134" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Q134" t="s">
         <v>45</v>
@@ -9715,7 +9715,7 @@
         <v>368</v>
       </c>
       <c r="I135" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="J135" t="s">
         <v>370</v>
@@ -9736,7 +9736,7 @@
         <v>201</v>
       </c>
       <c r="P135" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Q135" t="s">
         <v>45</v>
@@ -9771,7 +9771,7 @@
         <v>368</v>
       </c>
       <c r="I136" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="J136" t="s">
         <v>370</v>
@@ -9789,10 +9789,10 @@
         <v>45</v>
       </c>
       <c r="O136" t="s">
+        <v>383</v>
+      </c>
+      <c r="P136" t="s">
         <v>382</v>
-      </c>
-      <c r="P136" t="s">
-        <v>381</v>
       </c>
       <c r="Q136" t="s">
         <v>45</v>
@@ -9827,7 +9827,7 @@
         <v>368</v>
       </c>
       <c r="I137" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="J137" t="s">
         <v>370</v>
@@ -9845,10 +9845,10 @@
         <v>45</v>
       </c>
       <c r="O137" t="s">
+        <v>385</v>
+      </c>
+      <c r="P137" t="s">
         <v>384</v>
-      </c>
-      <c r="P137" t="s">
-        <v>383</v>
       </c>
       <c r="Q137" t="s">
         <v>45</v>
@@ -9883,7 +9883,7 @@
         <v>368</v>
       </c>
       <c r="I138" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="J138" t="s">
         <v>370</v>
@@ -9904,7 +9904,7 @@
         <v>140</v>
       </c>
       <c r="P138" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Q138" t="s">
         <v>45</v>
@@ -9927,7 +9927,7 @@
         <v>34</v>
       </c>
       <c r="E139" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F139" t="s">
         <v>211</v>
@@ -9939,7 +9939,7 @@
         <v>368</v>
       </c>
       <c r="I139" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J139" t="s">
         <v>370</v>
@@ -9957,10 +9957,10 @@
         <v>45</v>
       </c>
       <c r="O139" t="s">
+        <v>137</v>
+      </c>
+      <c r="P139" t="s">
         <v>387</v>
-      </c>
-      <c r="P139" t="s">
-        <v>386</v>
       </c>
       <c r="Q139" t="s">
         <v>45</v>
@@ -10107,7 +10107,7 @@
         <v>394</v>
       </c>
       <c r="I142" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="J142" t="s">
         <v>370</v>
@@ -10128,7 +10128,7 @@
         <v>77</v>
       </c>
       <c r="P142" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Q142" t="s">
         <v>45</v>
@@ -10163,7 +10163,7 @@
         <v>394</v>
       </c>
       <c r="I143" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="J143" t="s">
         <v>370</v>
@@ -10184,7 +10184,7 @@
         <v>326</v>
       </c>
       <c r="P143" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q143" t="s">
         <v>45</v>
@@ -10219,7 +10219,7 @@
         <v>394</v>
       </c>
       <c r="I144" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="J144" t="s">
         <v>370</v>
@@ -10240,7 +10240,7 @@
         <v>61</v>
       </c>
       <c r="P144" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q144" t="s">
         <v>45</v>
@@ -10275,7 +10275,7 @@
         <v>394</v>
       </c>
       <c r="I145" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="J145" t="s">
         <v>370</v>
@@ -10296,7 +10296,7 @@
         <v>243</v>
       </c>
       <c r="P145" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q145" t="s">
         <v>45</v>
@@ -10331,7 +10331,7 @@
         <v>394</v>
       </c>
       <c r="I146" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="J146" t="s">
         <v>370</v>
@@ -10349,10 +10349,10 @@
         <v>45</v>
       </c>
       <c r="O146" t="s">
+        <v>376</v>
+      </c>
+      <c r="P146" t="s">
         <v>375</v>
-      </c>
-      <c r="P146" t="s">
-        <v>374</v>
       </c>
       <c r="Q146" t="s">
         <v>45</v>
@@ -10387,7 +10387,7 @@
         <v>394</v>
       </c>
       <c r="I147" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="J147" t="s">
         <v>370</v>
@@ -10408,7 +10408,7 @@
         <v>329</v>
       </c>
       <c r="P147" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q147" t="s">
         <v>45</v>
@@ -10443,7 +10443,7 @@
         <v>394</v>
       </c>
       <c r="I148" t="s">
-        <v>386</v>
+        <v>372</v>
       </c>
       <c r="J148" t="s">
         <v>370</v>
@@ -10461,10 +10461,10 @@
         <v>45</v>
       </c>
       <c r="O148" t="s">
-        <v>387</v>
+        <v>373</v>
       </c>
       <c r="P148" t="s">
-        <v>386</v>
+        <v>372</v>
       </c>
       <c r="Q148" t="s">
         <v>45</v>
@@ -10611,7 +10611,7 @@
         <v>394</v>
       </c>
       <c r="I151" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="J151" t="s">
         <v>370</v>
@@ -10632,7 +10632,7 @@
         <v>140</v>
       </c>
       <c r="P151" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Q151" t="s">
         <v>45</v>
@@ -10723,7 +10723,7 @@
         <v>394</v>
       </c>
       <c r="I153" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="J153" t="s">
         <v>370</v>
@@ -10741,10 +10741,10 @@
         <v>45</v>
       </c>
       <c r="O153" t="s">
+        <v>383</v>
+      </c>
+      <c r="P153" t="s">
         <v>382</v>
-      </c>
-      <c r="P153" t="s">
-        <v>381</v>
       </c>
       <c r="Q153" t="s">
         <v>45</v>
@@ -10835,7 +10835,7 @@
         <v>394</v>
       </c>
       <c r="I155" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="J155" t="s">
         <v>370</v>
@@ -10853,10 +10853,10 @@
         <v>45</v>
       </c>
       <c r="O155" t="s">
+        <v>385</v>
+      </c>
+      <c r="P155" t="s">
         <v>384</v>
-      </c>
-      <c r="P155" t="s">
-        <v>383</v>
       </c>
       <c r="Q155" t="s">
         <v>45</v>
@@ -11077,7 +11077,7 @@
         <v>45</v>
       </c>
       <c r="O159" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="P159" t="s">
         <v>405</v>
@@ -11133,7 +11133,7 @@
         <v>45</v>
       </c>
       <c r="O160" t="s">
-        <v>387</v>
+        <v>373</v>
       </c>
       <c r="P160" t="s">
         <v>407</v>
@@ -11525,7 +11525,7 @@
         <v>45</v>
       </c>
       <c r="O167" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="P167" t="s">
         <v>416</v>
@@ -11581,7 +11581,7 @@
         <v>45</v>
       </c>
       <c r="O168" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="P168" t="s">
         <v>417</v>
@@ -11973,7 +11973,7 @@
         <v>45</v>
       </c>
       <c r="O175" t="s">
-        <v>387</v>
+        <v>373</v>
       </c>
       <c r="P175" t="s">
         <v>427</v>
@@ -12253,7 +12253,7 @@
         <v>45</v>
       </c>
       <c r="O180" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="P180" t="s">
         <v>432</v>
@@ -12421,7 +12421,7 @@
         <v>45</v>
       </c>
       <c r="O183" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="P183" t="s">
         <v>435</v>
@@ -12477,7 +12477,7 @@
         <v>45</v>
       </c>
       <c r="O184" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="P184" t="s">
         <v>436</v>
@@ -12589,7 +12589,7 @@
         <v>45</v>
       </c>
       <c r="O186" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="P186" t="s">
         <v>438</v>
@@ -12801,7 +12801,7 @@
         <v>370</v>
       </c>
       <c r="K190" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="L190" t="s">
         <v>34</v>
@@ -12857,7 +12857,7 @@
         <v>370</v>
       </c>
       <c r="K191" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="L191" t="s">
         <v>34</v>
@@ -12913,7 +12913,7 @@
         <v>370</v>
       </c>
       <c r="K192" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="L192" t="s">
         <v>34</v>
@@ -13149,7 +13149,7 @@
         <v>45</v>
       </c>
       <c r="O196" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="P196" t="s">
         <v>455</v>
@@ -13205,7 +13205,7 @@
         <v>45</v>
       </c>
       <c r="O197" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="P197" t="s">
         <v>459</v>
@@ -13231,7 +13231,7 @@
         <v>34</v>
       </c>
       <c r="E198" t="s">
-        <v>460</v>
+        <v>239</v>
       </c>
       <c r="F198" t="s">
         <v>211</v>
@@ -13240,10 +13240,10 @@
         <v>41</v>
       </c>
       <c r="H198" t="s">
+        <v>460</v>
+      </c>
+      <c r="I198" t="s">
         <v>461</v>
-      </c>
-      <c r="I198" t="s">
-        <v>462</v>
       </c>
       <c r="J198" t="s">
         <v>370</v>
@@ -13261,10 +13261,10 @@
         <v>45</v>
       </c>
       <c r="O198" t="s">
-        <v>463</v>
+        <v>243</v>
       </c>
       <c r="P198" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="Q198" t="s">
         <v>45</v>
@@ -13287,25 +13287,25 @@
         <v>34</v>
       </c>
       <c r="E199" t="s">
-        <v>312</v>
+        <v>210</v>
       </c>
       <c r="F199" t="s">
-        <v>464</v>
+        <v>211</v>
       </c>
       <c r="G199" t="s">
         <v>41</v>
       </c>
       <c r="H199" t="s">
-        <v>204</v>
+        <v>460</v>
       </c>
       <c r="I199" t="s">
-        <v>383</v>
+        <v>462</v>
       </c>
       <c r="J199" t="s">
-        <v>130</v>
+        <v>370</v>
       </c>
       <c r="K199" t="s">
-        <v>130</v>
+        <v>55</v>
       </c>
       <c r="L199" t="s">
         <v>34</v>
@@ -13317,13 +13317,13 @@
         <v>45</v>
       </c>
       <c r="O199" t="s">
-        <v>34</v>
+        <v>326</v>
       </c>
       <c r="P199" t="s">
-        <v>34</v>
+        <v>462</v>
       </c>
       <c r="Q199" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R199" t="s">
         <v>34</v>
@@ -13343,25 +13343,25 @@
         <v>34</v>
       </c>
       <c r="E200" t="s">
-        <v>239</v>
+        <v>320</v>
       </c>
       <c r="F200" t="s">
-        <v>211</v>
+        <v>463</v>
       </c>
       <c r="G200" t="s">
         <v>41</v>
       </c>
       <c r="H200" t="s">
-        <v>461</v>
+        <v>392</v>
       </c>
       <c r="I200" t="s">
-        <v>465</v>
+        <v>387</v>
       </c>
       <c r="J200" t="s">
-        <v>370</v>
+        <v>130</v>
       </c>
       <c r="K200" t="s">
-        <v>55</v>
+        <v>130</v>
       </c>
       <c r="L200" t="s">
         <v>34</v>
@@ -13373,13 +13373,13 @@
         <v>45</v>
       </c>
       <c r="O200" t="s">
-        <v>243</v>
+        <v>34</v>
       </c>
       <c r="P200" t="s">
-        <v>465</v>
+        <v>34</v>
       </c>
       <c r="Q200" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="R200" t="s">
         <v>34</v>
@@ -13399,25 +13399,25 @@
         <v>34</v>
       </c>
       <c r="E201" t="s">
-        <v>210</v>
+        <v>316</v>
       </c>
       <c r="F201" t="s">
-        <v>211</v>
+        <v>463</v>
       </c>
       <c r="G201" t="s">
         <v>41</v>
       </c>
       <c r="H201" t="s">
-        <v>461</v>
+        <v>204</v>
       </c>
       <c r="I201" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="J201" t="s">
-        <v>370</v>
+        <v>118</v>
       </c>
       <c r="K201" t="s">
-        <v>55</v>
+        <v>118</v>
       </c>
       <c r="L201" t="s">
         <v>34</v>
@@ -13429,13 +13429,13 @@
         <v>45</v>
       </c>
       <c r="O201" t="s">
-        <v>326</v>
+        <v>34</v>
       </c>
       <c r="P201" t="s">
-        <v>466</v>
+        <v>34</v>
       </c>
       <c r="Q201" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="R201" t="s">
         <v>34</v>
@@ -13455,25 +13455,25 @@
         <v>34</v>
       </c>
       <c r="E202" t="s">
-        <v>316</v>
+        <v>206</v>
       </c>
       <c r="F202" t="s">
-        <v>464</v>
+        <v>211</v>
       </c>
       <c r="G202" t="s">
         <v>41</v>
       </c>
       <c r="H202" t="s">
-        <v>204</v>
+        <v>392</v>
       </c>
       <c r="I202" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="J202" t="s">
-        <v>118</v>
+        <v>370</v>
       </c>
       <c r="K202" t="s">
-        <v>118</v>
+        <v>55</v>
       </c>
       <c r="L202" t="s">
         <v>34</v>
@@ -13485,13 +13485,13 @@
         <v>45</v>
       </c>
       <c r="O202" t="s">
-        <v>34</v>
+        <v>400</v>
       </c>
       <c r="P202" t="s">
-        <v>34</v>
+        <v>465</v>
       </c>
       <c r="Q202" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R202" t="s">
         <v>34</v>
@@ -13511,25 +13511,25 @@
         <v>34</v>
       </c>
       <c r="E203" t="s">
-        <v>468</v>
+        <v>348</v>
       </c>
       <c r="F203" t="s">
-        <v>211</v>
+        <v>463</v>
       </c>
       <c r="G203" t="s">
         <v>41</v>
       </c>
       <c r="H203" t="s">
-        <v>392</v>
+        <v>204</v>
       </c>
       <c r="I203" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="J203" t="s">
-        <v>370</v>
+        <v>60</v>
       </c>
       <c r="K203" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="L203" t="s">
         <v>34</v>
@@ -13541,13 +13541,13 @@
         <v>45</v>
       </c>
       <c r="O203" t="s">
-        <v>470</v>
+        <v>34</v>
       </c>
       <c r="P203" t="s">
-        <v>469</v>
+        <v>34</v>
       </c>
       <c r="Q203" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="R203" t="s">
         <v>34</v>
@@ -13567,25 +13567,25 @@
         <v>34</v>
       </c>
       <c r="E204" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="F204" t="s">
-        <v>464</v>
+        <v>211</v>
       </c>
       <c r="G204" t="s">
         <v>41</v>
       </c>
       <c r="H204" t="s">
-        <v>204</v>
+        <v>392</v>
       </c>
       <c r="I204" t="s">
-        <v>402</v>
+        <v>468</v>
       </c>
       <c r="J204" t="s">
-        <v>44</v>
+        <v>370</v>
       </c>
       <c r="K204" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="L204" t="s">
         <v>34</v>
@@ -13597,13 +13597,13 @@
         <v>45</v>
       </c>
       <c r="O204" t="s">
-        <v>34</v>
+        <v>469</v>
       </c>
       <c r="P204" t="s">
-        <v>34</v>
+        <v>468</v>
       </c>
       <c r="Q204" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R204" t="s">
         <v>34</v>
@@ -13623,7 +13623,7 @@
         <v>34</v>
       </c>
       <c r="E205" t="s">
-        <v>219</v>
+        <v>470</v>
       </c>
       <c r="F205" t="s">
         <v>211</v>
@@ -13632,10 +13632,10 @@
         <v>41</v>
       </c>
       <c r="H205" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="I205" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="J205" t="s">
         <v>370</v>
@@ -13653,10 +13653,10 @@
         <v>45</v>
       </c>
       <c r="O205" t="s">
-        <v>329</v>
+        <v>472</v>
       </c>
       <c r="P205" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="Q205" t="s">
         <v>45</v>
@@ -13682,22 +13682,22 @@
         <v>473</v>
       </c>
       <c r="F206" t="s">
-        <v>211</v>
+        <v>463</v>
       </c>
       <c r="G206" t="s">
         <v>41</v>
       </c>
       <c r="H206" t="s">
-        <v>458</v>
+        <v>204</v>
       </c>
       <c r="I206" t="s">
-        <v>474</v>
+        <v>402</v>
       </c>
       <c r="J206" t="s">
-        <v>370</v>
+        <v>44</v>
       </c>
       <c r="K206" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="L206" t="s">
         <v>34</v>
@@ -13709,13 +13709,13 @@
         <v>45</v>
       </c>
       <c r="O206" t="s">
-        <v>475</v>
+        <v>34</v>
       </c>
       <c r="P206" t="s">
-        <v>474</v>
+        <v>34</v>
       </c>
       <c r="Q206" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="R206" t="s">
         <v>34</v>
@@ -13735,25 +13735,25 @@
         <v>34</v>
       </c>
       <c r="E207" t="s">
-        <v>446</v>
+        <v>307</v>
       </c>
       <c r="F207" t="s">
-        <v>211</v>
+        <v>463</v>
       </c>
       <c r="G207" t="s">
         <v>41</v>
       </c>
       <c r="H207" t="s">
-        <v>392</v>
+        <v>204</v>
       </c>
       <c r="I207" t="s">
-        <v>476</v>
+        <v>382</v>
       </c>
       <c r="J207" t="s">
-        <v>370</v>
+        <v>130</v>
       </c>
       <c r="K207" t="s">
-        <v>55</v>
+        <v>130</v>
       </c>
       <c r="L207" t="s">
         <v>34</v>
@@ -13765,13 +13765,13 @@
         <v>45</v>
       </c>
       <c r="O207" t="s">
-        <v>448</v>
+        <v>34</v>
       </c>
       <c r="P207" t="s">
-        <v>476</v>
+        <v>34</v>
       </c>
       <c r="Q207" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="R207" t="s">
         <v>34</v>
@@ -13791,25 +13791,25 @@
         <v>34</v>
       </c>
       <c r="E208" t="s">
-        <v>307</v>
+        <v>219</v>
       </c>
       <c r="F208" t="s">
-        <v>464</v>
+        <v>211</v>
       </c>
       <c r="G208" t="s">
         <v>41</v>
       </c>
       <c r="H208" t="s">
-        <v>204</v>
+        <v>458</v>
       </c>
       <c r="I208" t="s">
-        <v>381</v>
+        <v>474</v>
       </c>
       <c r="J208" t="s">
-        <v>130</v>
+        <v>370</v>
       </c>
       <c r="K208" t="s">
-        <v>130</v>
+        <v>55</v>
       </c>
       <c r="L208" t="s">
         <v>34</v>
@@ -13821,13 +13821,13 @@
         <v>45</v>
       </c>
       <c r="O208" t="s">
-        <v>34</v>
+        <v>329</v>
       </c>
       <c r="P208" t="s">
-        <v>34</v>
+        <v>474</v>
       </c>
       <c r="Q208" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R208" t="s">
         <v>34</v>
@@ -13847,25 +13847,25 @@
         <v>34</v>
       </c>
       <c r="E209" t="s">
-        <v>320</v>
+        <v>475</v>
       </c>
       <c r="F209" t="s">
-        <v>464</v>
+        <v>211</v>
       </c>
       <c r="G209" t="s">
         <v>41</v>
       </c>
       <c r="H209" t="s">
-        <v>392</v>
+        <v>458</v>
       </c>
       <c r="I209" t="s">
-        <v>372</v>
+        <v>476</v>
       </c>
       <c r="J209" t="s">
-        <v>130</v>
+        <v>370</v>
       </c>
       <c r="K209" t="s">
-        <v>130</v>
+        <v>55</v>
       </c>
       <c r="L209" t="s">
         <v>34</v>
@@ -13877,13 +13877,13 @@
         <v>45</v>
       </c>
       <c r="O209" t="s">
-        <v>34</v>
+        <v>477</v>
       </c>
       <c r="P209" t="s">
-        <v>34</v>
+        <v>476</v>
       </c>
       <c r="Q209" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R209" t="s">
         <v>34</v>
@@ -13903,25 +13903,25 @@
         <v>34</v>
       </c>
       <c r="E210" t="s">
-        <v>477</v>
+        <v>221</v>
       </c>
       <c r="F210" t="s">
-        <v>211</v>
+        <v>463</v>
       </c>
       <c r="G210" t="s">
         <v>41</v>
       </c>
       <c r="H210" t="s">
-        <v>458</v>
+        <v>204</v>
       </c>
       <c r="I210" t="s">
         <v>478</v>
       </c>
       <c r="J210" t="s">
-        <v>370</v>
+        <v>60</v>
       </c>
       <c r="K210" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="L210" t="s">
         <v>34</v>
@@ -13933,13 +13933,13 @@
         <v>45</v>
       </c>
       <c r="O210" t="s">
-        <v>479</v>
+        <v>34</v>
       </c>
       <c r="P210" t="s">
-        <v>478</v>
+        <v>34</v>
       </c>
       <c r="Q210" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="R210" t="s">
         <v>34</v>
@@ -13959,7 +13959,7 @@
         <v>34</v>
       </c>
       <c r="E211" t="s">
-        <v>202</v>
+        <v>479</v>
       </c>
       <c r="F211" t="s">
         <v>211</v>
@@ -13968,7 +13968,7 @@
         <v>41</v>
       </c>
       <c r="H211" t="s">
-        <v>392</v>
+        <v>422</v>
       </c>
       <c r="I211" t="s">
         <v>480</v>
@@ -13989,7 +13989,7 @@
         <v>45</v>
       </c>
       <c r="O211" t="s">
-        <v>51</v>
+        <v>481</v>
       </c>
       <c r="P211" t="s">
         <v>480</v>
@@ -14015,25 +14015,25 @@
         <v>34</v>
       </c>
       <c r="E212" t="s">
-        <v>206</v>
+        <v>359</v>
       </c>
       <c r="F212" t="s">
-        <v>211</v>
+        <v>463</v>
       </c>
       <c r="G212" t="s">
         <v>41</v>
       </c>
       <c r="H212" t="s">
-        <v>392</v>
+        <v>204</v>
       </c>
       <c r="I212" t="s">
-        <v>481</v>
+        <v>372</v>
       </c>
       <c r="J212" t="s">
-        <v>370</v>
+        <v>60</v>
       </c>
       <c r="K212" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="L212" t="s">
         <v>34</v>
@@ -14045,13 +14045,13 @@
         <v>45</v>
       </c>
       <c r="O212" t="s">
-        <v>400</v>
+        <v>34</v>
       </c>
       <c r="P212" t="s">
-        <v>481</v>
+        <v>34</v>
       </c>
       <c r="Q212" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="R212" t="s">
         <v>34</v>
@@ -14071,7 +14071,7 @@
         <v>34</v>
       </c>
       <c r="E213" t="s">
-        <v>255</v>
+        <v>202</v>
       </c>
       <c r="F213" t="s">
         <v>211</v>
@@ -14101,7 +14101,7 @@
         <v>45</v>
       </c>
       <c r="O213" t="s">
-        <v>89</v>
+        <v>51</v>
       </c>
       <c r="P213" t="s">
         <v>482</v>
@@ -14183,25 +14183,25 @@
         <v>34</v>
       </c>
       <c r="E215" t="s">
-        <v>486</v>
+        <v>312</v>
       </c>
       <c r="F215" t="s">
-        <v>211</v>
+        <v>463</v>
       </c>
       <c r="G215" t="s">
         <v>41</v>
       </c>
       <c r="H215" t="s">
-        <v>422</v>
+        <v>204</v>
       </c>
       <c r="I215" t="s">
-        <v>487</v>
+        <v>384</v>
       </c>
       <c r="J215" t="s">
-        <v>370</v>
+        <v>130</v>
       </c>
       <c r="K215" t="s">
-        <v>55</v>
+        <v>130</v>
       </c>
       <c r="L215" t="s">
         <v>34</v>
@@ -14213,13 +14213,13 @@
         <v>45</v>
       </c>
       <c r="O215" t="s">
-        <v>488</v>
+        <v>34</v>
       </c>
       <c r="P215" t="s">
-        <v>487</v>
+        <v>34</v>
       </c>
       <c r="Q215" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="R215" t="s">
         <v>34</v>
@@ -14239,25 +14239,25 @@
         <v>34</v>
       </c>
       <c r="E216" t="s">
-        <v>348</v>
+        <v>255</v>
       </c>
       <c r="F216" t="s">
-        <v>464</v>
+        <v>211</v>
       </c>
       <c r="G216" t="s">
         <v>41</v>
       </c>
       <c r="H216" t="s">
-        <v>204</v>
+        <v>392</v>
       </c>
       <c r="I216" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="J216" t="s">
-        <v>60</v>
+        <v>370</v>
       </c>
       <c r="K216" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="L216" t="s">
         <v>34</v>
@@ -14269,13 +14269,13 @@
         <v>45</v>
       </c>
       <c r="O216" t="s">
-        <v>34</v>
+        <v>89</v>
       </c>
       <c r="P216" t="s">
-        <v>34</v>
+        <v>486</v>
       </c>
       <c r="Q216" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R216" t="s">
         <v>34</v>
@@ -14295,25 +14295,25 @@
         <v>34</v>
       </c>
       <c r="E217" t="s">
-        <v>221</v>
+        <v>446</v>
       </c>
       <c r="F217" t="s">
-        <v>464</v>
+        <v>211</v>
       </c>
       <c r="G217" t="s">
         <v>41</v>
       </c>
       <c r="H217" t="s">
-        <v>204</v>
+        <v>392</v>
       </c>
       <c r="I217" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="J217" t="s">
-        <v>60</v>
+        <v>370</v>
       </c>
       <c r="K217" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="L217" t="s">
         <v>34</v>
@@ -14325,13 +14325,13 @@
         <v>45</v>
       </c>
       <c r="O217" t="s">
-        <v>34</v>
+        <v>448</v>
       </c>
       <c r="P217" t="s">
-        <v>34</v>
+        <v>487</v>
       </c>
       <c r="Q217" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R217" t="s">
         <v>34</v>
@@ -14351,25 +14351,25 @@
         <v>34</v>
       </c>
       <c r="E218" t="s">
-        <v>359</v>
+        <v>488</v>
       </c>
       <c r="F218" t="s">
-        <v>464</v>
+        <v>211</v>
       </c>
       <c r="G218" t="s">
         <v>41</v>
       </c>
       <c r="H218" t="s">
-        <v>204</v>
+        <v>458</v>
       </c>
       <c r="I218" t="s">
-        <v>386</v>
+        <v>489</v>
       </c>
       <c r="J218" t="s">
-        <v>60</v>
+        <v>370</v>
       </c>
       <c r="K218" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="L218" t="s">
         <v>34</v>
@@ -14381,13 +14381,13 @@
         <v>45</v>
       </c>
       <c r="O218" t="s">
-        <v>34</v>
+        <v>490</v>
       </c>
       <c r="P218" t="s">
-        <v>34</v>
+        <v>489</v>
       </c>
       <c r="Q218" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R218" t="s">
         <v>34</v>
@@ -14410,7 +14410,7 @@
         <v>228</v>
       </c>
       <c r="F219" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="G219" t="s">
         <v>41</v>
@@ -14522,7 +14522,7 @@
         <v>255</v>
       </c>
       <c r="F221" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="G221" t="s">
         <v>41</v>
@@ -14578,7 +14578,7 @@
         <v>202</v>
       </c>
       <c r="F222" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="G222" t="s">
         <v>41</v>
@@ -14634,7 +14634,7 @@
         <v>225</v>
       </c>
       <c r="F223" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="G223" t="s">
         <v>41</v>
@@ -14690,7 +14690,7 @@
         <v>239</v>
       </c>
       <c r="F224" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="G224" t="s">
         <v>41</v>
@@ -14746,7 +14746,7 @@
         <v>356</v>
       </c>
       <c r="F225" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="G225" t="s">
         <v>41</v>
@@ -14802,7 +14802,7 @@
         <v>223</v>
       </c>
       <c r="F226" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="G226" t="s">
         <v>41</v>
@@ -14858,7 +14858,7 @@
         <v>214</v>
       </c>
       <c r="F227" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="G227" t="s">
         <v>41</v>
@@ -14914,7 +14914,7 @@
         <v>197</v>
       </c>
       <c r="F228" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="G228" t="s">
         <v>41</v>
@@ -14970,7 +14970,7 @@
         <v>234</v>
       </c>
       <c r="F229" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="G229" t="s">
         <v>41</v>
@@ -15026,7 +15026,7 @@
         <v>226</v>
       </c>
       <c r="F230" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="G230" t="s">
         <v>41</v>
@@ -15082,7 +15082,7 @@
         <v>237</v>
       </c>
       <c r="F231" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="G231" t="s">
         <v>41</v>
@@ -15639,25 +15639,25 @@
         <v>33</v>
       </c>
       <c r="E241" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="F241" t="s">
-        <v>173</v>
+        <v>528</v>
       </c>
       <c r="G241" t="s">
         <v>41</v>
       </c>
       <c r="H241" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="I241" t="s">
         <v>251</v>
       </c>
       <c r="J241" t="s">
-        <v>67</v>
+        <v>118</v>
       </c>
       <c r="K241" t="s">
-        <v>67</v>
+        <v>118</v>
       </c>
       <c r="L241" t="s">
         <v>34</v>
@@ -15669,13 +15669,13 @@
         <v>45</v>
       </c>
       <c r="O241" t="s">
-        <v>329</v>
+        <v>34</v>
       </c>
       <c r="P241" t="s">
-        <v>251</v>
+        <v>34</v>
       </c>
       <c r="Q241" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="R241" t="s">
         <v>34</v>
@@ -15695,25 +15695,25 @@
         <v>34</v>
       </c>
       <c r="E242" t="s">
-        <v>237</v>
+        <v>216</v>
       </c>
       <c r="F242" t="s">
+        <v>173</v>
+      </c>
+      <c r="G242" t="s">
+        <v>41</v>
+      </c>
+      <c r="H242" t="s">
         <v>529</v>
-      </c>
-      <c r="G242" t="s">
-        <v>41</v>
-      </c>
-      <c r="H242" t="s">
-        <v>528</v>
       </c>
       <c r="I242" t="s">
         <v>251</v>
       </c>
       <c r="J242" t="s">
-        <v>118</v>
+        <v>67</v>
       </c>
       <c r="K242" t="s">
-        <v>118</v>
+        <v>67</v>
       </c>
       <c r="L242" t="s">
         <v>34</v>
@@ -15725,13 +15725,13 @@
         <v>45</v>
       </c>
       <c r="O242" t="s">
-        <v>34</v>
+        <v>243</v>
       </c>
       <c r="P242" t="s">
-        <v>34</v>
+        <v>251</v>
       </c>
       <c r="Q242" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R242" t="s">
         <v>34</v>
@@ -15751,25 +15751,25 @@
         <v>34</v>
       </c>
       <c r="E243" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="F243" t="s">
-        <v>173</v>
+        <v>528</v>
       </c>
       <c r="G243" t="s">
         <v>41</v>
       </c>
       <c r="H243" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="I243" t="s">
         <v>251</v>
       </c>
       <c r="J243" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="K243" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="L243" t="s">
         <v>34</v>
@@ -15781,13 +15781,13 @@
         <v>45</v>
       </c>
       <c r="O243" t="s">
-        <v>243</v>
+        <v>34</v>
       </c>
       <c r="P243" t="s">
-        <v>251</v>
+        <v>34</v>
       </c>
       <c r="Q243" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="R243" t="s">
         <v>34</v>
@@ -15807,7 +15807,7 @@
         <v>34</v>
       </c>
       <c r="E244" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="F244" t="s">
         <v>173</v>
@@ -15816,16 +15816,16 @@
         <v>41</v>
       </c>
       <c r="H244" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="I244" t="s">
         <v>251</v>
       </c>
       <c r="J244" t="s">
-        <v>130</v>
+        <v>60</v>
       </c>
       <c r="K244" t="s">
-        <v>130</v>
+        <v>60</v>
       </c>
       <c r="L244" t="s">
         <v>34</v>
@@ -15837,7 +15837,7 @@
         <v>45</v>
       </c>
       <c r="O244" t="s">
-        <v>137</v>
+        <v>61</v>
       </c>
       <c r="P244" t="s">
         <v>251</v>
@@ -15863,7 +15863,7 @@
         <v>34</v>
       </c>
       <c r="E245" t="s">
-        <v>208</v>
+        <v>255</v>
       </c>
       <c r="F245" t="s">
         <v>173</v>
@@ -15872,16 +15872,16 @@
         <v>41</v>
       </c>
       <c r="H245" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="I245" t="s">
         <v>251</v>
       </c>
       <c r="J245" t="s">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="K245" t="s">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="L245" t="s">
         <v>34</v>
@@ -15893,7 +15893,7 @@
         <v>45</v>
       </c>
       <c r="O245" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="P245" t="s">
         <v>251</v>
@@ -15919,25 +15919,25 @@
         <v>34</v>
       </c>
       <c r="E246" t="s">
-        <v>197</v>
+        <v>234</v>
       </c>
       <c r="F246" t="s">
-        <v>173</v>
+        <v>528</v>
       </c>
       <c r="G246" t="s">
         <v>41</v>
       </c>
       <c r="H246" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="I246" t="s">
         <v>251</v>
       </c>
       <c r="J246" t="s">
-        <v>108</v>
+        <v>130</v>
       </c>
       <c r="K246" t="s">
-        <v>108</v>
+        <v>130</v>
       </c>
       <c r="L246" t="s">
         <v>34</v>
@@ -15949,13 +15949,13 @@
         <v>45</v>
       </c>
       <c r="O246" t="s">
-        <v>201</v>
+        <v>34</v>
       </c>
       <c r="P246" t="s">
-        <v>251</v>
+        <v>34</v>
       </c>
       <c r="Q246" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="R246" t="s">
         <v>34</v>
@@ -15975,7 +15975,7 @@
         <v>34</v>
       </c>
       <c r="E247" t="s">
-        <v>239</v>
+        <v>210</v>
       </c>
       <c r="F247" t="s">
         <v>173</v>
@@ -15984,16 +15984,16 @@
         <v>41</v>
       </c>
       <c r="H247" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="I247" t="s">
-        <v>530</v>
+        <v>251</v>
       </c>
       <c r="J247" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="K247" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="L247" t="s">
         <v>34</v>
@@ -16005,10 +16005,10 @@
         <v>45</v>
       </c>
       <c r="O247" t="s">
-        <v>243</v>
+        <v>326</v>
       </c>
       <c r="P247" t="s">
-        <v>530</v>
+        <v>251</v>
       </c>
       <c r="Q247" t="s">
         <v>45</v>
@@ -16031,25 +16031,25 @@
         <v>34</v>
       </c>
       <c r="E248" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="F248" t="s">
+        <v>528</v>
+      </c>
+      <c r="G248" t="s">
+        <v>41</v>
+      </c>
+      <c r="H248" t="s">
         <v>529</v>
-      </c>
-      <c r="G248" t="s">
-        <v>41</v>
-      </c>
-      <c r="H248" t="s">
-        <v>528</v>
       </c>
       <c r="I248" t="s">
         <v>251</v>
       </c>
       <c r="J248" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="K248" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="L248" t="s">
         <v>34</v>
@@ -16087,25 +16087,25 @@
         <v>34</v>
       </c>
       <c r="E249" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="F249" t="s">
-        <v>173</v>
+        <v>528</v>
       </c>
       <c r="G249" t="s">
         <v>41</v>
       </c>
       <c r="H249" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="I249" t="s">
         <v>251</v>
       </c>
       <c r="J249" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="K249" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="L249" t="s">
         <v>34</v>
@@ -16117,13 +16117,13 @@
         <v>45</v>
       </c>
       <c r="O249" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="P249" t="s">
-        <v>251</v>
+        <v>34</v>
       </c>
       <c r="Q249" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="R249" t="s">
         <v>34</v>
@@ -16143,25 +16143,25 @@
         <v>34</v>
       </c>
       <c r="E250" t="s">
-        <v>234</v>
+        <v>197</v>
       </c>
       <c r="F250" t="s">
+        <v>173</v>
+      </c>
+      <c r="G250" t="s">
+        <v>41</v>
+      </c>
+      <c r="H250" t="s">
         <v>529</v>
-      </c>
-      <c r="G250" t="s">
-        <v>41</v>
-      </c>
-      <c r="H250" t="s">
-        <v>528</v>
       </c>
       <c r="I250" t="s">
         <v>251</v>
       </c>
       <c r="J250" t="s">
-        <v>130</v>
+        <v>108</v>
       </c>
       <c r="K250" t="s">
-        <v>130</v>
+        <v>108</v>
       </c>
       <c r="L250" t="s">
         <v>34</v>
@@ -16173,13 +16173,13 @@
         <v>45</v>
       </c>
       <c r="O250" t="s">
-        <v>34</v>
+        <v>201</v>
       </c>
       <c r="P250" t="s">
-        <v>34</v>
+        <v>251</v>
       </c>
       <c r="Q250" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R250" t="s">
         <v>34</v>
@@ -16199,25 +16199,25 @@
         <v>34</v>
       </c>
       <c r="E251" t="s">
-        <v>255</v>
+        <v>225</v>
       </c>
       <c r="F251" t="s">
-        <v>173</v>
+        <v>528</v>
       </c>
       <c r="G251" t="s">
         <v>41</v>
       </c>
       <c r="H251" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="I251" t="s">
         <v>251</v>
       </c>
       <c r="J251" t="s">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="K251" t="s">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="L251" t="s">
         <v>34</v>
@@ -16229,13 +16229,13 @@
         <v>45</v>
       </c>
       <c r="O251" t="s">
-        <v>89</v>
+        <v>34</v>
       </c>
       <c r="P251" t="s">
-        <v>251</v>
+        <v>34</v>
       </c>
       <c r="Q251" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="R251" t="s">
         <v>34</v>
@@ -16255,7 +16255,7 @@
         <v>34</v>
       </c>
       <c r="E252" t="s">
-        <v>210</v>
+        <v>239</v>
       </c>
       <c r="F252" t="s">
         <v>173</v>
@@ -16264,16 +16264,16 @@
         <v>41</v>
       </c>
       <c r="H252" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="I252" t="s">
-        <v>251</v>
+        <v>530</v>
       </c>
       <c r="J252" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="K252" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="L252" t="s">
         <v>34</v>
@@ -16285,10 +16285,10 @@
         <v>45</v>
       </c>
       <c r="O252" t="s">
-        <v>326</v>
+        <v>243</v>
       </c>
       <c r="P252" t="s">
-        <v>251</v>
+        <v>530</v>
       </c>
       <c r="Q252" t="s">
         <v>45</v>
@@ -16311,25 +16311,25 @@
         <v>34</v>
       </c>
       <c r="E253" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="F253" t="s">
+        <v>173</v>
+      </c>
+      <c r="G253" t="s">
+        <v>41</v>
+      </c>
+      <c r="H253" t="s">
         <v>529</v>
-      </c>
-      <c r="G253" t="s">
-        <v>41</v>
-      </c>
-      <c r="H253" t="s">
-        <v>528</v>
       </c>
       <c r="I253" t="s">
         <v>251</v>
       </c>
       <c r="J253" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="K253" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="L253" t="s">
         <v>34</v>
@@ -16341,13 +16341,13 @@
         <v>45</v>
       </c>
       <c r="O253" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="P253" t="s">
-        <v>34</v>
+        <v>251</v>
       </c>
       <c r="Q253" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R253" t="s">
         <v>34</v>
@@ -16367,25 +16367,25 @@
         <v>34</v>
       </c>
       <c r="E254" t="s">
-        <v>221</v>
+        <v>202</v>
       </c>
       <c r="F254" t="s">
+        <v>528</v>
+      </c>
+      <c r="G254" t="s">
+        <v>41</v>
+      </c>
+      <c r="H254" t="s">
         <v>529</v>
-      </c>
-      <c r="G254" t="s">
-        <v>41</v>
-      </c>
-      <c r="H254" t="s">
-        <v>528</v>
       </c>
       <c r="I254" t="s">
         <v>251</v>
       </c>
       <c r="J254" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="K254" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="L254" t="s">
         <v>34</v>
@@ -16423,25 +16423,25 @@
         <v>34</v>
       </c>
       <c r="E255" t="s">
-        <v>202</v>
+        <v>228</v>
       </c>
       <c r="F255" t="s">
+        <v>173</v>
+      </c>
+      <c r="G255" t="s">
+        <v>41</v>
+      </c>
+      <c r="H255" t="s">
         <v>529</v>
-      </c>
-      <c r="G255" t="s">
-        <v>41</v>
-      </c>
-      <c r="H255" t="s">
-        <v>528</v>
       </c>
       <c r="I255" t="s">
         <v>251</v>
       </c>
       <c r="J255" t="s">
-        <v>50</v>
+        <v>130</v>
       </c>
       <c r="K255" t="s">
-        <v>50</v>
+        <v>130</v>
       </c>
       <c r="L255" t="s">
         <v>34</v>
@@ -16453,13 +16453,13 @@
         <v>45</v>
       </c>
       <c r="O255" t="s">
-        <v>34</v>
+        <v>137</v>
       </c>
       <c r="P255" t="s">
-        <v>34</v>
+        <v>251</v>
       </c>
       <c r="Q255" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R255" t="s">
         <v>34</v>
@@ -16479,25 +16479,25 @@
         <v>34</v>
       </c>
       <c r="E256" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="F256" t="s">
+        <v>173</v>
+      </c>
+      <c r="G256" t="s">
+        <v>41</v>
+      </c>
+      <c r="H256" t="s">
         <v>529</v>
-      </c>
-      <c r="G256" t="s">
-        <v>41</v>
-      </c>
-      <c r="H256" t="s">
-        <v>528</v>
       </c>
       <c r="I256" t="s">
         <v>251</v>
       </c>
       <c r="J256" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="K256" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="L256" t="s">
         <v>34</v>
@@ -16509,13 +16509,13 @@
         <v>45</v>
       </c>
       <c r="O256" t="s">
-        <v>34</v>
+        <v>329</v>
       </c>
       <c r="P256" t="s">
-        <v>34</v>
+        <v>251</v>
       </c>
       <c r="Q256" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R256" t="s">
         <v>34</v>
@@ -16606,10 +16606,10 @@
         <v>536</v>
       </c>
       <c r="J258" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="K258" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="L258" t="s">
         <v>537</v>
@@ -16759,7 +16759,7 @@
         <v>33</v>
       </c>
       <c r="E261" t="s">
-        <v>548</v>
+        <v>154</v>
       </c>
       <c r="F261" t="s">
         <v>173</v>
@@ -16768,19 +16768,19 @@
         <v>41</v>
       </c>
       <c r="H261" t="s">
+        <v>548</v>
+      </c>
+      <c r="I261" t="s">
         <v>549</v>
       </c>
-      <c r="I261" t="s">
+      <c r="J261" t="s">
         <v>550</v>
       </c>
-      <c r="J261" t="s">
+      <c r="K261" t="s">
+        <v>158</v>
+      </c>
+      <c r="L261" t="s">
         <v>551</v>
-      </c>
-      <c r="K261" t="s">
-        <v>81</v>
-      </c>
-      <c r="L261" t="s">
-        <v>552</v>
       </c>
       <c r="M261" t="s">
         <v>546</v>
@@ -16792,7 +16792,7 @@
         <v>153</v>
       </c>
       <c r="P261" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="Q261" t="s">
         <v>45</v>
@@ -16815,7 +16815,7 @@
         <v>34</v>
       </c>
       <c r="E262" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="F262" t="s">
         <v>173</v>
@@ -16830,10 +16830,10 @@
         <v>554</v>
       </c>
       <c r="J262" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="K262" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="L262" t="s">
         <v>555</v>
@@ -16871,7 +16871,7 @@
         <v>34</v>
       </c>
       <c r="E263" t="s">
-        <v>159</v>
+        <v>552</v>
       </c>
       <c r="F263" t="s">
         <v>173</v>
@@ -16889,7 +16889,7 @@
         <v>558</v>
       </c>
       <c r="K263" t="s">
-        <v>163</v>
+        <v>81</v>
       </c>
       <c r="L263" t="s">
         <v>559</v>
@@ -17151,7 +17151,7 @@
         <v>33</v>
       </c>
       <c r="E268" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="F268" t="s">
         <v>173</v>
@@ -17166,10 +17166,10 @@
         <v>572</v>
       </c>
       <c r="J268" t="s">
-        <v>551</v>
+        <v>558</v>
       </c>
       <c r="K268" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="L268" t="s">
         <v>573</v>
@@ -17319,7 +17319,7 @@
         <v>33</v>
       </c>
       <c r="E271" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="F271" t="s">
         <v>173</v>
@@ -17334,10 +17334,10 @@
         <v>580</v>
       </c>
       <c r="J271" t="s">
-        <v>551</v>
+        <v>558</v>
       </c>
       <c r="K271" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="L271" t="s">
         <v>581</v>
@@ -17375,7 +17375,7 @@
         <v>34</v>
       </c>
       <c r="E272" t="s">
-        <v>159</v>
+        <v>552</v>
       </c>
       <c r="F272" t="s">
         <v>173</v>
@@ -17384,16 +17384,16 @@
         <v>41</v>
       </c>
       <c r="H272" t="s">
-        <v>461</v>
+        <v>582</v>
       </c>
       <c r="I272" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="J272" t="s">
-        <v>583</v>
+        <v>558</v>
       </c>
       <c r="K272" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="L272" t="s">
         <v>584</v>
@@ -17408,7 +17408,7 @@
         <v>153</v>
       </c>
       <c r="P272" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="Q272" t="s">
         <v>45</v>
@@ -17431,7 +17431,7 @@
         <v>34</v>
       </c>
       <c r="E273" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="F273" t="s">
         <v>173</v>
@@ -17440,19 +17440,19 @@
         <v>41</v>
       </c>
       <c r="H273" t="s">
+        <v>392</v>
+      </c>
+      <c r="I273" t="s">
+        <v>572</v>
+      </c>
+      <c r="J273" t="s">
+        <v>267</v>
+      </c>
+      <c r="K273" t="s">
+        <v>268</v>
+      </c>
+      <c r="L273" t="s">
         <v>585</v>
-      </c>
-      <c r="I273" t="s">
-        <v>586</v>
-      </c>
-      <c r="J273" t="s">
-        <v>551</v>
-      </c>
-      <c r="K273" t="s">
-        <v>271</v>
-      </c>
-      <c r="L273" t="s">
-        <v>587</v>
       </c>
       <c r="M273" t="s">
         <v>578</v>
@@ -17464,7 +17464,7 @@
         <v>153</v>
       </c>
       <c r="P273" t="s">
-        <v>586</v>
+        <v>572</v>
       </c>
       <c r="Q273" t="s">
         <v>45</v>
@@ -17487,7 +17487,7 @@
         <v>34</v>
       </c>
       <c r="E274" t="s">
-        <v>548</v>
+        <v>154</v>
       </c>
       <c r="F274" t="s">
         <v>173</v>
@@ -17496,16 +17496,16 @@
         <v>41</v>
       </c>
       <c r="H274" t="s">
-        <v>392</v>
+        <v>406</v>
       </c>
       <c r="I274" t="s">
-        <v>572</v>
+        <v>586</v>
       </c>
       <c r="J274" t="s">
-        <v>275</v>
+        <v>587</v>
       </c>
       <c r="K274" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="L274" t="s">
         <v>588</v>
@@ -17520,7 +17520,7 @@
         <v>153</v>
       </c>
       <c r="P274" t="s">
-        <v>572</v>
+        <v>586</v>
       </c>
       <c r="Q274" t="s">
         <v>45</v>
@@ -17543,25 +17543,25 @@
         <v>34</v>
       </c>
       <c r="E275" t="s">
-        <v>548</v>
+        <v>589</v>
       </c>
       <c r="F275" t="s">
-        <v>173</v>
+        <v>198</v>
       </c>
       <c r="G275" t="s">
         <v>41</v>
       </c>
       <c r="H275" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="I275" t="s">
-        <v>590</v>
+        <v>572</v>
       </c>
       <c r="J275" t="s">
-        <v>551</v>
+        <v>121</v>
       </c>
       <c r="K275" t="s">
-        <v>271</v>
+        <v>146</v>
       </c>
       <c r="L275" t="s">
         <v>591</v>
@@ -17576,7 +17576,7 @@
         <v>153</v>
       </c>
       <c r="P275" t="s">
-        <v>590</v>
+        <v>572</v>
       </c>
       <c r="Q275" t="s">
         <v>45</v>
@@ -17599,7 +17599,7 @@
         <v>34</v>
       </c>
       <c r="E276" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="F276" t="s">
         <v>173</v>
@@ -17614,10 +17614,10 @@
         <v>593</v>
       </c>
       <c r="J276" t="s">
-        <v>551</v>
+        <v>558</v>
       </c>
       <c r="K276" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="L276" t="s">
         <v>594</v>
@@ -17655,28 +17655,28 @@
         <v>34</v>
       </c>
       <c r="E277" t="s">
+        <v>154</v>
+      </c>
+      <c r="F277" t="s">
+        <v>173</v>
+      </c>
+      <c r="G277" t="s">
+        <v>41</v>
+      </c>
+      <c r="H277" t="s">
+        <v>460</v>
+      </c>
+      <c r="I277" t="s">
         <v>595</v>
       </c>
-      <c r="F277" t="s">
-        <v>198</v>
-      </c>
-      <c r="G277" t="s">
-        <v>41</v>
-      </c>
-      <c r="H277" t="s">
-        <v>515</v>
-      </c>
-      <c r="I277" t="s">
+      <c r="J277" t="s">
         <v>596</v>
       </c>
-      <c r="J277" t="s">
-        <v>66</v>
-      </c>
       <c r="K277" t="s">
-        <v>66</v>
+        <v>268</v>
       </c>
       <c r="L277" t="s">
-        <v>34</v>
+        <v>597</v>
       </c>
       <c r="M277" t="s">
         <v>578</v>
@@ -17688,7 +17688,7 @@
         <v>153</v>
       </c>
       <c r="P277" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="Q277" t="s">
         <v>45</v>
@@ -17711,10 +17711,10 @@
         <v>34</v>
       </c>
       <c r="E278" t="s">
-        <v>560</v>
+        <v>598</v>
       </c>
       <c r="F278" t="s">
-        <v>173</v>
+        <v>198</v>
       </c>
       <c r="G278" t="s">
         <v>41</v>
@@ -17723,16 +17723,16 @@
         <v>368</v>
       </c>
       <c r="I278" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="J278" t="s">
-        <v>598</v>
+        <v>55</v>
       </c>
       <c r="K278" t="s">
-        <v>271</v>
+        <v>55</v>
       </c>
       <c r="L278" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="M278" t="s">
         <v>578</v>
@@ -17744,7 +17744,7 @@
         <v>153</v>
       </c>
       <c r="P278" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="Q278" t="s">
         <v>45</v>
@@ -17767,7 +17767,7 @@
         <v>34</v>
       </c>
       <c r="E279" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="F279" t="s">
         <v>173</v>
@@ -17776,19 +17776,19 @@
         <v>41</v>
       </c>
       <c r="H279" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="I279" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="J279" t="s">
-        <v>551</v>
+        <v>558</v>
       </c>
       <c r="K279" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="L279" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="M279" t="s">
         <v>578</v>
@@ -17800,7 +17800,7 @@
         <v>153</v>
       </c>
       <c r="P279" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="Q279" t="s">
         <v>45</v>
@@ -17823,28 +17823,28 @@
         <v>34</v>
       </c>
       <c r="E280" t="s">
-        <v>159</v>
+        <v>604</v>
       </c>
       <c r="F280" t="s">
-        <v>173</v>
+        <v>198</v>
       </c>
       <c r="G280" t="s">
         <v>41</v>
       </c>
       <c r="H280" t="s">
-        <v>406</v>
+        <v>458</v>
       </c>
       <c r="I280" t="s">
-        <v>603</v>
+        <v>572</v>
       </c>
       <c r="J280" t="s">
-        <v>604</v>
+        <v>370</v>
       </c>
       <c r="K280" t="s">
-        <v>271</v>
+        <v>188</v>
       </c>
       <c r="L280" t="s">
-        <v>605</v>
+        <v>34</v>
       </c>
       <c r="M280" t="s">
         <v>578</v>
@@ -17856,7 +17856,7 @@
         <v>153</v>
       </c>
       <c r="P280" t="s">
-        <v>603</v>
+        <v>572</v>
       </c>
       <c r="Q280" t="s">
         <v>45</v>
@@ -17879,28 +17879,28 @@
         <v>34</v>
       </c>
       <c r="E281" t="s">
+        <v>154</v>
+      </c>
+      <c r="F281" t="s">
+        <v>173</v>
+      </c>
+      <c r="G281" t="s">
+        <v>41</v>
+      </c>
+      <c r="H281" t="s">
+        <v>605</v>
+      </c>
+      <c r="I281" t="s">
+        <v>586</v>
+      </c>
+      <c r="J281" t="s">
+        <v>587</v>
+      </c>
+      <c r="K281" t="s">
         <v>606</v>
       </c>
-      <c r="F281" t="s">
-        <v>198</v>
-      </c>
-      <c r="G281" t="s">
-        <v>41</v>
-      </c>
-      <c r="H281" t="s">
-        <v>368</v>
-      </c>
-      <c r="I281" t="s">
+      <c r="L281" t="s">
         <v>607</v>
-      </c>
-      <c r="J281" t="s">
-        <v>55</v>
-      </c>
-      <c r="K281" t="s">
-        <v>55</v>
-      </c>
-      <c r="L281" t="s">
-        <v>608</v>
       </c>
       <c r="M281" t="s">
         <v>578</v>
@@ -17912,7 +17912,7 @@
         <v>153</v>
       </c>
       <c r="P281" t="s">
-        <v>607</v>
+        <v>586</v>
       </c>
       <c r="Q281" t="s">
         <v>45</v>
@@ -17935,7 +17935,7 @@
         <v>34</v>
       </c>
       <c r="E282" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="F282" t="s">
         <v>198</v>
@@ -17944,16 +17944,16 @@
         <v>41</v>
       </c>
       <c r="H282" t="s">
-        <v>458</v>
+        <v>515</v>
       </c>
       <c r="I282" t="s">
-        <v>572</v>
+        <v>609</v>
       </c>
       <c r="J282" t="s">
-        <v>370</v>
+        <v>66</v>
       </c>
       <c r="K282" t="s">
-        <v>188</v>
+        <v>66</v>
       </c>
       <c r="L282" t="s">
         <v>34</v>
@@ -17968,7 +17968,7 @@
         <v>153</v>
       </c>
       <c r="P282" t="s">
-        <v>572</v>
+        <v>609</v>
       </c>
       <c r="Q282" t="s">
         <v>45</v>
@@ -17991,7 +17991,7 @@
         <v>34</v>
       </c>
       <c r="E283" t="s">
-        <v>159</v>
+        <v>552</v>
       </c>
       <c r="F283" t="s">
         <v>173</v>
@@ -18003,16 +18003,16 @@
         <v>610</v>
       </c>
       <c r="I283" t="s">
-        <v>603</v>
+        <v>572</v>
       </c>
       <c r="J283" t="s">
-        <v>604</v>
+        <v>558</v>
       </c>
       <c r="K283" t="s">
+        <v>268</v>
+      </c>
+      <c r="L283" t="s">
         <v>611</v>
-      </c>
-      <c r="L283" t="s">
-        <v>612</v>
       </c>
       <c r="M283" t="s">
         <v>578</v>
@@ -18024,7 +18024,7 @@
         <v>153</v>
       </c>
       <c r="P283" t="s">
-        <v>603</v>
+        <v>572</v>
       </c>
       <c r="Q283" t="s">
         <v>45</v>
@@ -18047,7 +18047,7 @@
         <v>34</v>
       </c>
       <c r="E284" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="F284" t="s">
         <v>173</v>
@@ -18056,16 +18056,16 @@
         <v>41</v>
       </c>
       <c r="H284" t="s">
+        <v>612</v>
+      </c>
+      <c r="I284" t="s">
         <v>613</v>
       </c>
-      <c r="I284" t="s">
-        <v>572</v>
-      </c>
       <c r="J284" t="s">
-        <v>551</v>
+        <v>558</v>
       </c>
       <c r="K284" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="L284" t="s">
         <v>614</v>
@@ -18080,7 +18080,7 @@
         <v>153</v>
       </c>
       <c r="P284" t="s">
-        <v>572</v>
+        <v>613</v>
       </c>
       <c r="Q284" t="s">
         <v>45</v>
@@ -18103,25 +18103,25 @@
         <v>34</v>
       </c>
       <c r="E285" t="s">
+        <v>560</v>
+      </c>
+      <c r="F285" t="s">
+        <v>173</v>
+      </c>
+      <c r="G285" t="s">
+        <v>41</v>
+      </c>
+      <c r="H285" t="s">
+        <v>368</v>
+      </c>
+      <c r="I285" t="s">
         <v>615</v>
       </c>
-      <c r="F285" t="s">
-        <v>198</v>
-      </c>
-      <c r="G285" t="s">
-        <v>41</v>
-      </c>
-      <c r="H285" t="s">
+      <c r="J285" t="s">
         <v>616</v>
       </c>
-      <c r="I285" t="s">
-        <v>572</v>
-      </c>
-      <c r="J285" t="s">
-        <v>121</v>
-      </c>
       <c r="K285" t="s">
-        <v>146</v>
+        <v>268</v>
       </c>
       <c r="L285" t="s">
         <v>617</v>
@@ -18136,7 +18136,7 @@
         <v>153</v>
       </c>
       <c r="P285" t="s">
-        <v>572</v>
+        <v>615</v>
       </c>
       <c r="Q285" t="s">
         <v>45</v>
@@ -18336,10 +18336,10 @@
         <v>41</v>
       </c>
       <c r="H289" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="I289" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="J289" t="s">
         <v>176</v>
@@ -18360,7 +18360,7 @@
         <v>153</v>
       </c>
       <c r="P289" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="Q289" t="s">
         <v>45</v>
@@ -18504,13 +18504,13 @@
         <v>41</v>
       </c>
       <c r="H292" t="s">
-        <v>579</v>
+        <v>601</v>
       </c>
       <c r="I292" t="s">
         <v>636</v>
       </c>
       <c r="J292" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="K292" t="s">
         <v>637</v>
@@ -18902,7 +18902,7 @@
         <v>655</v>
       </c>
       <c r="J299" t="s">
-        <v>551</v>
+        <v>558</v>
       </c>
       <c r="K299" t="s">
         <v>81</v>
@@ -19167,7 +19167,7 @@
         <v>33</v>
       </c>
       <c r="E304" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="F304" t="s">
         <v>173</v>
@@ -19182,10 +19182,10 @@
         <v>674</v>
       </c>
       <c r="J304" t="s">
-        <v>551</v>
+        <v>558</v>
       </c>
       <c r="K304" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="L304" t="s">
         <v>675</v>
@@ -19335,7 +19335,7 @@
         <v>33</v>
       </c>
       <c r="E307" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="F307" t="s">
         <v>173</v>
@@ -19350,7 +19350,7 @@
         <v>686</v>
       </c>
       <c r="J307" t="s">
-        <v>551</v>
+        <v>558</v>
       </c>
       <c r="K307" t="s">
         <v>687</v>
@@ -19462,7 +19462,7 @@
         <v>693</v>
       </c>
       <c r="J309" t="s">
-        <v>551</v>
+        <v>558</v>
       </c>
       <c r="K309" t="s">
         <v>81</v>
@@ -19630,10 +19630,10 @@
         <v>704</v>
       </c>
       <c r="J312" t="s">
-        <v>252</v>
+        <v>121</v>
       </c>
       <c r="K312" t="s">
-        <v>66</v>
+        <v>146</v>
       </c>
       <c r="L312" t="s">
         <v>705</v>
@@ -19692,7 +19692,7 @@
         <v>66</v>
       </c>
       <c r="L313" t="s">
-        <v>34</v>
+        <v>709</v>
       </c>
       <c r="M313" t="s">
         <v>697</v>
@@ -19727,7 +19727,7 @@
         <v>34</v>
       </c>
       <c r="E314" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="F314" t="s">
         <v>198</v>
@@ -19736,19 +19736,19 @@
         <v>41</v>
       </c>
       <c r="H314" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="I314" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="J314" t="s">
-        <v>121</v>
+        <v>252</v>
       </c>
       <c r="K314" t="s">
-        <v>146</v>
+        <v>66</v>
       </c>
       <c r="L314" t="s">
-        <v>712</v>
+        <v>34</v>
       </c>
       <c r="M314" t="s">
         <v>697</v>
@@ -19760,7 +19760,7 @@
         <v>153</v>
       </c>
       <c r="P314" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="Q314" t="s">
         <v>45</v>
@@ -19839,7 +19839,7 @@
         <v>33</v>
       </c>
       <c r="E316" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="F316" t="s">
         <v>173</v>
@@ -19854,10 +19854,10 @@
         <v>718</v>
       </c>
       <c r="J316" t="s">
-        <v>551</v>
+        <v>558</v>
       </c>
       <c r="K316" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="L316" t="s">
         <v>719</v>
@@ -19907,7 +19907,7 @@
         <v>722</v>
       </c>
       <c r="I317" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="J317" t="s">
         <v>682</v>
@@ -19928,7 +19928,7 @@
         <v>153</v>
       </c>
       <c r="P317" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="Q317" t="s">
         <v>45</v>
@@ -19969,7 +19969,7 @@
         <v>729</v>
       </c>
       <c r="K318" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="L318" t="s">
         <v>727</v>
@@ -20078,13 +20078,13 @@
         <v>734</v>
       </c>
       <c r="J320" t="s">
+        <v>252</v>
+      </c>
+      <c r="K320" t="s">
+        <v>268</v>
+      </c>
+      <c r="L320" t="s">
         <v>735</v>
-      </c>
-      <c r="K320" t="s">
-        <v>271</v>
-      </c>
-      <c r="L320" t="s">
-        <v>736</v>
       </c>
       <c r="M320" t="s">
         <v>732</v>
@@ -20119,7 +20119,7 @@
         <v>34</v>
       </c>
       <c r="E321" t="s">
-        <v>548</v>
+        <v>736</v>
       </c>
       <c r="F321" t="s">
         <v>173</v>
@@ -20128,16 +20128,16 @@
         <v>41</v>
       </c>
       <c r="H321" t="s">
+        <v>727</v>
+      </c>
+      <c r="I321" t="s">
         <v>737</v>
       </c>
-      <c r="I321" t="s">
+      <c r="J321" t="s">
         <v>738</v>
       </c>
-      <c r="J321" t="s">
-        <v>275</v>
-      </c>
       <c r="K321" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="L321" t="s">
         <v>739</v>
@@ -20152,7 +20152,7 @@
         <v>153</v>
       </c>
       <c r="P321" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="Q321" t="s">
         <v>45</v>
@@ -20175,7 +20175,7 @@
         <v>34</v>
       </c>
       <c r="E322" t="s">
-        <v>740</v>
+        <v>552</v>
       </c>
       <c r="F322" t="s">
         <v>173</v>
@@ -20187,16 +20187,16 @@
         <v>727</v>
       </c>
       <c r="I322" t="s">
+        <v>740</v>
+      </c>
+      <c r="J322" t="s">
+        <v>267</v>
+      </c>
+      <c r="K322" t="s">
+        <v>60</v>
+      </c>
+      <c r="L322" t="s">
         <v>741</v>
-      </c>
-      <c r="J322" t="s">
-        <v>742</v>
-      </c>
-      <c r="K322" t="s">
-        <v>271</v>
-      </c>
-      <c r="L322" t="s">
-        <v>743</v>
       </c>
       <c r="M322" t="s">
         <v>732</v>
@@ -20208,7 +20208,7 @@
         <v>153</v>
       </c>
       <c r="P322" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="Q322" t="s">
         <v>45</v>
@@ -20231,7 +20231,7 @@
         <v>34</v>
       </c>
       <c r="E323" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="F323" t="s">
         <v>173</v>
@@ -20243,16 +20243,16 @@
         <v>727</v>
       </c>
       <c r="I323" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="J323" t="s">
-        <v>252</v>
+        <v>738</v>
       </c>
       <c r="K323" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="L323" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="M323" t="s">
         <v>732</v>
@@ -20264,7 +20264,7 @@
         <v>153</v>
       </c>
       <c r="P323" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="Q323" t="s">
         <v>45</v>
@@ -20287,7 +20287,7 @@
         <v>34</v>
       </c>
       <c r="E324" t="s">
-        <v>747</v>
+        <v>552</v>
       </c>
       <c r="F324" t="s">
         <v>173</v>
@@ -20296,19 +20296,19 @@
         <v>41</v>
       </c>
       <c r="H324" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="I324" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="J324" t="s">
-        <v>750</v>
+        <v>267</v>
       </c>
       <c r="K324" t="s">
-        <v>751</v>
+        <v>268</v>
       </c>
       <c r="L324" t="s">
-        <v>752</v>
+        <v>747</v>
       </c>
       <c r="M324" t="s">
         <v>732</v>
@@ -20320,7 +20320,7 @@
         <v>153</v>
       </c>
       <c r="P324" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="Q324" t="s">
         <v>45</v>
@@ -20343,7 +20343,7 @@
         <v>34</v>
       </c>
       <c r="E325" t="s">
-        <v>753</v>
+        <v>748</v>
       </c>
       <c r="F325" t="s">
         <v>173</v>
@@ -20355,16 +20355,16 @@
         <v>727</v>
       </c>
       <c r="I325" t="s">
-        <v>754</v>
+        <v>749</v>
       </c>
       <c r="J325" t="s">
-        <v>742</v>
+        <v>750</v>
       </c>
       <c r="K325" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="L325" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="M325" t="s">
         <v>732</v>
@@ -20376,7 +20376,7 @@
         <v>153</v>
       </c>
       <c r="P325" t="s">
-        <v>754</v>
+        <v>749</v>
       </c>
       <c r="Q325" t="s">
         <v>45</v>
@@ -20399,7 +20399,7 @@
         <v>34</v>
       </c>
       <c r="E326" t="s">
-        <v>548</v>
+        <v>752</v>
       </c>
       <c r="F326" t="s">
         <v>173</v>
@@ -20408,19 +20408,19 @@
         <v>41</v>
       </c>
       <c r="H326" t="s">
-        <v>727</v>
+        <v>753</v>
       </c>
       <c r="I326" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="J326" t="s">
-        <v>275</v>
+        <v>755</v>
       </c>
       <c r="K326" t="s">
-        <v>60</v>
+        <v>268</v>
       </c>
       <c r="L326" t="s">
-        <v>757</v>
+        <v>753</v>
       </c>
       <c r="M326" t="s">
         <v>732</v>
@@ -20432,7 +20432,7 @@
         <v>153</v>
       </c>
       <c r="P326" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="Q326" t="s">
         <v>45</v>
@@ -20455,7 +20455,7 @@
         <v>34</v>
       </c>
       <c r="E327" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="F327" t="s">
         <v>173</v>
@@ -20464,19 +20464,19 @@
         <v>41</v>
       </c>
       <c r="H327" t="s">
+        <v>757</v>
+      </c>
+      <c r="I327" t="s">
+        <v>758</v>
+      </c>
+      <c r="J327" t="s">
         <v>759</v>
       </c>
-      <c r="I327" t="s">
+      <c r="K327" t="s">
         <v>760</v>
       </c>
-      <c r="J327" t="s">
+      <c r="L327" t="s">
         <v>761</v>
-      </c>
-      <c r="K327" t="s">
-        <v>271</v>
-      </c>
-      <c r="L327" t="s">
-        <v>759</v>
       </c>
       <c r="M327" t="s">
         <v>732</v>
@@ -20488,7 +20488,7 @@
         <v>153</v>
       </c>
       <c r="P327" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="Q327" t="s">
         <v>45</v>
@@ -20638,7 +20638,7 @@
         <v>775</v>
       </c>
       <c r="J330" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="K330" t="s">
         <v>637</v>
@@ -20735,7 +20735,7 @@
         <v>33</v>
       </c>
       <c r="E332" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="F332" t="s">
         <v>173</v>
@@ -20750,10 +20750,10 @@
         <v>781</v>
       </c>
       <c r="J332" t="s">
-        <v>551</v>
+        <v>558</v>
       </c>
       <c r="K332" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="L332" t="s">
         <v>782</v>
@@ -20918,7 +20918,7 @@
         <v>794</v>
       </c>
       <c r="J335" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="K335" t="s">
         <v>146</v>
@@ -20959,7 +20959,7 @@
         <v>33</v>
       </c>
       <c r="E336" t="s">
-        <v>653</v>
+        <v>552</v>
       </c>
       <c r="F336" t="s">
         <v>173</v>
@@ -20977,7 +20977,7 @@
         <v>558</v>
       </c>
       <c r="K336" t="s">
-        <v>163</v>
+        <v>268</v>
       </c>
       <c r="L336" t="s">
         <v>800</v>
@@ -21015,7 +21015,7 @@
         <v>34</v>
       </c>
       <c r="E337" t="s">
-        <v>548</v>
+        <v>653</v>
       </c>
       <c r="F337" t="s">
         <v>173</v>
@@ -21030,10 +21030,10 @@
         <v>802</v>
       </c>
       <c r="J337" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="K337" t="s">
-        <v>271</v>
+        <v>158</v>
       </c>
       <c r="L337" t="s">
         <v>803</v>
@@ -21071,7 +21071,7 @@
         <v>33</v>
       </c>
       <c r="E338" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="F338" t="s">
         <v>173</v>
@@ -21086,10 +21086,10 @@
         <v>807</v>
       </c>
       <c r="J338" t="s">
-        <v>735</v>
+        <v>750</v>
       </c>
       <c r="K338" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="L338" t="s">
         <v>808</v>
@@ -26297,7 +26297,7 @@
         <v>927</v>
       </c>
       <c r="K431" t="s">
-        <v>611</v>
+        <v>606</v>
       </c>
       <c r="L431" t="s">
         <v>928</v>
@@ -26409,7 +26409,7 @@
         <v>927</v>
       </c>
       <c r="K433" t="s">
-        <v>611</v>
+        <v>606</v>
       </c>
       <c r="L433" t="s">
         <v>934</v>
@@ -26574,10 +26574,10 @@
         <v>930</v>
       </c>
       <c r="J436" t="s">
-        <v>611</v>
+        <v>606</v>
       </c>
       <c r="K436" t="s">
-        <v>611</v>
+        <v>606</v>
       </c>
       <c r="L436" t="s">
         <v>928</v>

--- a/xlsx/dre/DRE_08_2026.xlsx
+++ b/xlsx/dre/DRE_08_2026.xlsx
@@ -513,7 +513,7 @@
     <t>4 CUSTOS E DESPESAS</t>
   </si>
   <si>
-    <t>R$ 584.195,62</t>
+    <t>R$ 577.612,89</t>
   </si>
   <si>
     <t>4.01 DEDUÇÕES DE RECEITA</t>
@@ -1404,69 +1404,96 @@
     <t>R$ 14.671,29</t>
   </si>
   <si>
+    <t>R$  5,63</t>
+  </si>
+  <si>
+    <t>FERNANDA DOCHVAT SILVA</t>
+  </si>
+  <si>
+    <t>R$  369,25</t>
+  </si>
+  <si>
+    <t>Jose Carlos de Carvalho</t>
+  </si>
+  <si>
+    <t>05/10/26</t>
+  </si>
+  <si>
+    <t>88201/1</t>
+  </si>
+  <si>
+    <t>R$  294,73</t>
+  </si>
+  <si>
+    <t>88201fERNANDOL</t>
+  </si>
+  <si>
+    <t>R$  364,20</t>
+  </si>
+  <si>
+    <t>R$  432,60</t>
+  </si>
+  <si>
+    <t>79601/1</t>
+  </si>
+  <si>
+    <t>R$  534,37</t>
+  </si>
+  <si>
+    <t>79601EduardoMF</t>
+  </si>
+  <si>
     <t>PPC</t>
   </si>
   <si>
     <t>R$  159,90</t>
   </si>
   <si>
-    <t>R$  5,63</t>
-  </si>
-  <si>
-    <t>Jose Carlos de Carvalho</t>
-  </si>
-  <si>
-    <t>05/10/26</t>
-  </si>
-  <si>
-    <t>FERNANDA DOCHVAT SILVA</t>
-  </si>
-  <si>
-    <t>R$  369,25</t>
+    <t>90501/1</t>
+  </si>
+  <si>
+    <t>R$  314,79</t>
+  </si>
+  <si>
+    <t>90501TARLEYSO</t>
+  </si>
+  <si>
+    <t>97901/2</t>
+  </si>
+  <si>
+    <t>R$  19,04</t>
+  </si>
+  <si>
+    <t>R$  43,69</t>
+  </si>
+  <si>
+    <t>R$  92,96</t>
+  </si>
+  <si>
+    <t>56101/1</t>
+  </si>
+  <si>
+    <t>R$  389,38</t>
+  </si>
+  <si>
+    <t>56101FELIXHS</t>
   </si>
   <si>
     <t>R$  2.193,79</t>
   </si>
   <si>
-    <t>R$  432,60</t>
+    <t>90401/1</t>
+  </si>
+  <si>
+    <t>R$  3.395,45</t>
+  </si>
+  <si>
+    <t>89301JoaoMCC</t>
   </si>
   <si>
     <t>R$  1.358,25</t>
   </si>
   <si>
-    <t>88201/1</t>
-  </si>
-  <si>
-    <t>R$  294,73</t>
-  </si>
-  <si>
-    <t>88201fERNANDOL</t>
-  </si>
-  <si>
-    <t>90401/1</t>
-  </si>
-  <si>
-    <t>R$  3.395,45</t>
-  </si>
-  <si>
-    <t>89301JoaoMCC</t>
-  </si>
-  <si>
-    <t>97901/2</t>
-  </si>
-  <si>
-    <t>R$  364,20</t>
-  </si>
-  <si>
-    <t>79601/1</t>
-  </si>
-  <si>
-    <t>R$  534,37</t>
-  </si>
-  <si>
-    <t>79601EduardoMF</t>
-  </si>
-  <si>
     <t>R$  610,94</t>
   </si>
   <si>
@@ -1479,33 +1506,6 @@
     <t>91001DABRURA</t>
   </si>
   <si>
-    <t>R$  92,96</t>
-  </si>
-  <si>
-    <t>90501/1</t>
-  </si>
-  <si>
-    <t>R$  314,79</t>
-  </si>
-  <si>
-    <t>90501TARLEYSO</t>
-  </si>
-  <si>
-    <t>R$  43,69</t>
-  </si>
-  <si>
-    <t>R$  19,04</t>
-  </si>
-  <si>
-    <t>56101/1</t>
-  </si>
-  <si>
-    <t>R$  389,38</t>
-  </si>
-  <si>
-    <t>56101FELIXHS</t>
-  </si>
-  <si>
     <t>4.03.01.02.08 Comissões montagem - provisão</t>
   </si>
   <si>
@@ -1833,6 +1833,57 @@
     <t>4.04.01.02.01.01 Salário fixo</t>
   </si>
   <si>
+    <t>CARINA PEREIRA</t>
+  </si>
+  <si>
+    <t>R$  2.365,00</t>
+  </si>
+  <si>
+    <t>Carina - Pagamento 2026</t>
+  </si>
+  <si>
+    <t>R$  1.500,00</t>
+  </si>
+  <si>
+    <t>12/02/26</t>
+  </si>
+  <si>
+    <t>Fernanda Dochvat - Fixo 2026</t>
+  </si>
+  <si>
+    <t>Rubens - Pagamento 2026</t>
+  </si>
+  <si>
+    <t>779/1</t>
+  </si>
+  <si>
+    <t>EFRAIM RIBEIRO</t>
+  </si>
+  <si>
+    <t>R$  1.060,00</t>
+  </si>
+  <si>
+    <t>788/1</t>
+  </si>
+  <si>
+    <t>R$  1.268,00</t>
+  </si>
+  <si>
+    <t>Estorno empr ago26/1</t>
+  </si>
+  <si>
+    <t>R$  249,82</t>
+  </si>
+  <si>
+    <t>R$  2.219,85</t>
+  </si>
+  <si>
+    <t>18/03/26</t>
+  </si>
+  <si>
+    <t>Felipe Domingos - salário fixo 2026</t>
+  </si>
+  <si>
     <t>R$  2.536,00</t>
   </si>
   <si>
@@ -1842,6 +1893,60 @@
     <t>Bianca Rodrigues - Salário fixo 2026</t>
   </si>
   <si>
+    <t>740/1</t>
+  </si>
+  <si>
+    <t>Eric Kevin de Souza Serpa</t>
+  </si>
+  <si>
+    <t>19/08/26</t>
+  </si>
+  <si>
+    <t>Salário Fixo -Eric Serpa 2026</t>
+  </si>
+  <si>
+    <t>Fixo ago26/1</t>
+  </si>
+  <si>
+    <t>R$  225,31</t>
+  </si>
+  <si>
+    <t>Estorno empréstimo</t>
+  </si>
+  <si>
+    <t>GUTEMBERG DIAS GOMES</t>
+  </si>
+  <si>
+    <t>R$  6.500,00</t>
+  </si>
+  <si>
+    <t>Gutemberg Dias - Pagamento</t>
+  </si>
+  <si>
+    <t>Denny Lucas do Carmo Pereira</t>
+  </si>
+  <si>
+    <t>R$  2.479,65</t>
+  </si>
+  <si>
+    <t>Denny Lucas - Pagamento 2026</t>
+  </si>
+  <si>
+    <t>Teresinha Elvira Maximino de Menezes</t>
+  </si>
+  <si>
+    <t>Tucha - Fixo 2026</t>
+  </si>
+  <si>
+    <t>SABRINA ALVES DE ABREU BRAUNBECK</t>
+  </si>
+  <si>
+    <t>R$  3.276,49</t>
+  </si>
+  <si>
+    <t>Sabrina Braunbeck - Pagamento 2026</t>
+  </si>
+  <si>
     <t>Danielle Martins da Silva</t>
   </si>
   <si>
@@ -1851,73 +1956,13 @@
     <t>Danielle - Pagamento 2026</t>
   </si>
   <si>
-    <t>788/1</t>
-  </si>
-  <si>
-    <t>R$  1.268,00</t>
-  </si>
-  <si>
-    <t>R$  2.219,85</t>
-  </si>
-  <si>
-    <t>18/03/26</t>
-  </si>
-  <si>
-    <t>Felipe Domingos - salário fixo 2026</t>
-  </si>
-  <si>
-    <t>Estorno empr ago26/1</t>
-  </si>
-  <si>
-    <t>R$  249,82</t>
-  </si>
-  <si>
-    <t>CARINA PEREIRA</t>
-  </si>
-  <si>
-    <t>R$  2.365,00</t>
-  </si>
-  <si>
-    <t>Carina - Pagamento 2026</t>
-  </si>
-  <si>
-    <t>779/1</t>
-  </si>
-  <si>
-    <t>EFRAIM RIBEIRO</t>
-  </si>
-  <si>
-    <t>R$  1.060,00</t>
-  </si>
-  <si>
-    <t>Denny Lucas do Carmo Pereira</t>
-  </si>
-  <si>
-    <t>R$  2.479,65</t>
-  </si>
-  <si>
-    <t>Denny Lucas - Pagamento 2026</t>
-  </si>
-  <si>
-    <t>SABRINA ALVES DE ABREU BRAUNBECK</t>
-  </si>
-  <si>
-    <t>R$  3.276,49</t>
-  </si>
-  <si>
-    <t>Sabrina Braunbeck - Pagamento 2026</t>
-  </si>
-  <si>
-    <t>Fixo ago26/1</t>
-  </si>
-  <si>
-    <t>R$  225,31</t>
-  </si>
-  <si>
-    <t>Estorno empréstimo</t>
-  </si>
-  <si>
-    <t>Rubens - Pagamento 2026</t>
+    <t>735/1</t>
+  </si>
+  <si>
+    <t>BIANCA RODRIGUES NASCIMENTO</t>
+  </si>
+  <si>
+    <t>Pemiação meta</t>
   </si>
   <si>
     <t>80/8</t>
@@ -1930,51 +1975,6 @@
   </si>
   <si>
     <t>Fixo Mayara</t>
-  </si>
-  <si>
-    <t>740/1</t>
-  </si>
-  <si>
-    <t>Eric Kevin de Souza Serpa</t>
-  </si>
-  <si>
-    <t>19/08/26</t>
-  </si>
-  <si>
-    <t>Salário Fixo -Eric Serpa 2026</t>
-  </si>
-  <si>
-    <t>R$  1.500,00</t>
-  </si>
-  <si>
-    <t>12/02/26</t>
-  </si>
-  <si>
-    <t>Fernanda Dochvat - Fixo 2026</t>
-  </si>
-  <si>
-    <t>Teresinha Elvira Maximino de Menezes</t>
-  </si>
-  <si>
-    <t>Tucha - Fixo 2026</t>
-  </si>
-  <si>
-    <t>GUTEMBERG DIAS GOMES</t>
-  </si>
-  <si>
-    <t>R$  6.500,00</t>
-  </si>
-  <si>
-    <t>Gutemberg Dias - Pagamento</t>
-  </si>
-  <si>
-    <t>735/1</t>
-  </si>
-  <si>
-    <t>BIANCA RODRIGUES NASCIMENTO</t>
-  </si>
-  <si>
-    <t>Pemiação meta</t>
   </si>
   <si>
     <t>4.04.01.02.05 IRRF sobre salários</t>
@@ -2581,7 +2581,7 @@
     <t>4.07 DESPESAS FINANCEIRAS VARIÁVEIS</t>
   </si>
   <si>
-    <t>R$ 126.158,67</t>
+    <t>R$ 119.575,94</t>
   </si>
   <si>
     <t>4.07.01 DESPESAS FINANCEIRAS VARIÁVEIS</t>
@@ -2611,6 +2611,12 @@
     <t>R$  7.042,50</t>
   </si>
   <si>
+    <t>PAGSEGURO</t>
+  </si>
+  <si>
+    <t>R$  13.790,00</t>
+  </si>
+  <si>
     <t>R$  9.451,77</t>
   </si>
   <si>
@@ -2632,12 +2638,6 @@
     <t>R$  321,78</t>
   </si>
   <si>
-    <t>PAGSEGURO</t>
-  </si>
-  <si>
-    <t>R$  20.372,73</t>
-  </si>
-  <si>
     <t>7.01 RECEITAS</t>
   </si>
   <si>
@@ -2773,7 +2773,7 @@
     <t>7.08 (-) DESPESAS E RECEITAS FINANCEIRAS</t>
   </si>
   <si>
-    <t>R$ 126.165,58</t>
+    <t>R$ 119.582,85</t>
   </si>
   <si>
     <t>7.08.01 Despesas e receitas financeiras fixas</t>
@@ -2791,7 +2791,7 @@
     <t>7.09 = RESULTADO OPERACIONAL</t>
   </si>
   <si>
-    <t>R$ 66.442,13</t>
+    <t>R$ 73.024,86</t>
   </si>
   <si>
     <t>7.11 = RESULTADO LÍQUIDO DO EXERCÍCIO</t>
@@ -2806,7 +2806,7 @@
     <t>7.50.02 TOTAL DOS CUSTOS VARIÁVEIS</t>
   </si>
   <si>
-    <t>R$ 509.818,29</t>
+    <t>R$ 503.235,56</t>
   </si>
   <si>
     <t>7.50.02.01 Deduções de receita</t>
@@ -2839,7 +2839,7 @@
     <t>7.60.02 TOTAL DE VENDAS - VALOR À VISTA</t>
   </si>
   <si>
-    <t>R$ 524.479,08</t>
+    <t>R$ 531.061,81</t>
   </si>
   <si>
     <t>7.60.03 TOTAL DE VENDAS - VALOR LÍQUIDO</t>
@@ -2869,7 +2869,7 @@
     <t>7.70 BREAK-EVEN POINT</t>
   </si>
   <si>
-    <t>R$ 343.650,65</t>
+    <t>R$ 328.303,80</t>
   </si>
   <si>
     <t>7.80.01 Mark Up Negociado</t>
@@ -2884,7 +2884,7 @@
     <t>7.80.02 Mark Up à Vista</t>
   </si>
   <si>
-    <t>2,64</t>
+    <t>2,67</t>
   </si>
   <si>
     <t>7.80.03 Mark Up Líquido</t>
@@ -13327,25 +13327,25 @@
         <v>33</v>
       </c>
       <c r="E198" t="s">
-        <v>318</v>
+        <v>204</v>
       </c>
       <c r="F198" t="s">
+        <v>209</v>
+      </c>
+      <c r="G198" t="s">
+        <v>41</v>
+      </c>
+      <c r="H198" t="s">
+        <v>394</v>
+      </c>
+      <c r="I198" t="s">
         <v>460</v>
       </c>
-      <c r="G198" t="s">
-        <v>41</v>
-      </c>
-      <c r="H198" t="s">
-        <v>202</v>
-      </c>
-      <c r="I198" t="s">
-        <v>461</v>
-      </c>
       <c r="J198" t="s">
-        <v>118</v>
+        <v>372</v>
       </c>
       <c r="K198" t="s">
-        <v>118</v>
+        <v>55</v>
       </c>
       <c r="L198" t="s">
         <v>34</v>
@@ -13357,13 +13357,13 @@
         <v>45</v>
       </c>
       <c r="O198" t="s">
-        <v>34</v>
+        <v>402</v>
       </c>
       <c r="P198" t="s">
-        <v>34</v>
+        <v>460</v>
       </c>
       <c r="Q198" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R198" t="s">
         <v>34</v>
@@ -13383,7 +13383,7 @@
         <v>34</v>
       </c>
       <c r="E199" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="F199" t="s">
         <v>209</v>
@@ -13392,7 +13392,7 @@
         <v>41</v>
       </c>
       <c r="H199" t="s">
-        <v>394</v>
+        <v>461</v>
       </c>
       <c r="I199" t="s">
         <v>462</v>
@@ -13413,7 +13413,7 @@
         <v>45</v>
       </c>
       <c r="O199" t="s">
-        <v>402</v>
+        <v>328</v>
       </c>
       <c r="P199" t="s">
         <v>462</v>
@@ -13607,7 +13607,7 @@
         <v>34</v>
       </c>
       <c r="E203" t="s">
-        <v>208</v>
+        <v>465</v>
       </c>
       <c r="F203" t="s">
         <v>209</v>
@@ -13616,7 +13616,7 @@
         <v>41</v>
       </c>
       <c r="H203" t="s">
-        <v>465</v>
+        <v>394</v>
       </c>
       <c r="I203" t="s">
         <v>466</v>
@@ -13637,7 +13637,7 @@
         <v>45</v>
       </c>
       <c r="O203" t="s">
-        <v>328</v>
+        <v>467</v>
       </c>
       <c r="P203" t="s">
         <v>466</v>
@@ -13663,7 +13663,7 @@
         <v>34</v>
       </c>
       <c r="E204" t="s">
-        <v>239</v>
+        <v>217</v>
       </c>
       <c r="F204" t="s">
         <v>209</v>
@@ -13672,10 +13672,10 @@
         <v>41</v>
       </c>
       <c r="H204" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="I204" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="J204" t="s">
         <v>372</v>
@@ -13693,10 +13693,10 @@
         <v>45</v>
       </c>
       <c r="O204" t="s">
-        <v>244</v>
+        <v>331</v>
       </c>
       <c r="P204" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="Q204" t="s">
         <v>45</v>
@@ -13731,7 +13731,7 @@
         <v>463</v>
       </c>
       <c r="I205" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="J205" t="s">
         <v>372</v>
@@ -13752,7 +13752,7 @@
         <v>378</v>
       </c>
       <c r="P205" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="Q205" t="s">
         <v>45</v>
@@ -13775,25 +13775,25 @@
         <v>34</v>
       </c>
       <c r="E206" t="s">
-        <v>350</v>
+        <v>470</v>
       </c>
       <c r="F206" t="s">
-        <v>460</v>
+        <v>209</v>
       </c>
       <c r="G206" t="s">
         <v>41</v>
       </c>
       <c r="H206" t="s">
-        <v>202</v>
+        <v>463</v>
       </c>
       <c r="I206" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="J206" t="s">
-        <v>60</v>
+        <v>372</v>
       </c>
       <c r="K206" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="L206" t="s">
         <v>34</v>
@@ -13805,13 +13805,13 @@
         <v>45</v>
       </c>
       <c r="O206" t="s">
-        <v>34</v>
+        <v>472</v>
       </c>
       <c r="P206" t="s">
-        <v>34</v>
+        <v>471</v>
       </c>
       <c r="Q206" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R206" t="s">
         <v>34</v>
@@ -13831,25 +13831,25 @@
         <v>34</v>
       </c>
       <c r="E207" t="s">
-        <v>470</v>
+        <v>318</v>
       </c>
       <c r="F207" t="s">
-        <v>209</v>
+        <v>473</v>
       </c>
       <c r="G207" t="s">
         <v>41</v>
       </c>
       <c r="H207" t="s">
-        <v>394</v>
+        <v>202</v>
       </c>
       <c r="I207" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="J207" t="s">
-        <v>372</v>
+        <v>118</v>
       </c>
       <c r="K207" t="s">
-        <v>55</v>
+        <v>118</v>
       </c>
       <c r="L207" t="s">
         <v>34</v>
@@ -13861,13 +13861,13 @@
         <v>45</v>
       </c>
       <c r="O207" t="s">
-        <v>472</v>
+        <v>34</v>
       </c>
       <c r="P207" t="s">
-        <v>471</v>
+        <v>34</v>
       </c>
       <c r="Q207" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="R207" t="s">
         <v>34</v>
@@ -13887,7 +13887,7 @@
         <v>34</v>
       </c>
       <c r="E208" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="F208" t="s">
         <v>209</v>
@@ -13896,10 +13896,10 @@
         <v>41</v>
       </c>
       <c r="H208" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="I208" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="J208" t="s">
         <v>372</v>
@@ -13917,10 +13917,10 @@
         <v>45</v>
       </c>
       <c r="O208" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="P208" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="Q208" t="s">
         <v>45</v>
@@ -13943,10 +13943,10 @@
         <v>34</v>
       </c>
       <c r="E209" t="s">
-        <v>476</v>
+        <v>314</v>
       </c>
       <c r="F209" t="s">
-        <v>460</v>
+        <v>473</v>
       </c>
       <c r="G209" t="s">
         <v>41</v>
@@ -13955,13 +13955,13 @@
         <v>202</v>
       </c>
       <c r="I209" t="s">
-        <v>404</v>
+        <v>386</v>
       </c>
       <c r="J209" t="s">
-        <v>44</v>
+        <v>130</v>
       </c>
       <c r="K209" t="s">
-        <v>44</v>
+        <v>130</v>
       </c>
       <c r="L209" t="s">
         <v>34</v>
@@ -14002,7 +14002,7 @@
         <v>309</v>
       </c>
       <c r="F210" t="s">
-        <v>460</v>
+        <v>473</v>
       </c>
       <c r="G210" t="s">
         <v>41</v>
@@ -14055,25 +14055,25 @@
         <v>34</v>
       </c>
       <c r="E211" t="s">
-        <v>217</v>
+        <v>478</v>
       </c>
       <c r="F211" t="s">
-        <v>209</v>
+        <v>473</v>
       </c>
       <c r="G211" t="s">
         <v>41</v>
       </c>
       <c r="H211" t="s">
-        <v>463</v>
+        <v>202</v>
       </c>
       <c r="I211" t="s">
-        <v>477</v>
+        <v>404</v>
       </c>
       <c r="J211" t="s">
-        <v>372</v>
+        <v>44</v>
       </c>
       <c r="K211" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="L211" t="s">
         <v>34</v>
@@ -14085,13 +14085,13 @@
         <v>45</v>
       </c>
       <c r="O211" t="s">
-        <v>331</v>
+        <v>34</v>
       </c>
       <c r="P211" t="s">
-        <v>477</v>
+        <v>34</v>
       </c>
       <c r="Q211" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="R211" t="s">
         <v>34</v>
@@ -14111,7 +14111,7 @@
         <v>34</v>
       </c>
       <c r="E212" t="s">
-        <v>478</v>
+        <v>448</v>
       </c>
       <c r="F212" t="s">
         <v>209</v>
@@ -14120,7 +14120,7 @@
         <v>41</v>
       </c>
       <c r="H212" t="s">
-        <v>463</v>
+        <v>394</v>
       </c>
       <c r="I212" t="s">
         <v>479</v>
@@ -14141,7 +14141,7 @@
         <v>45</v>
       </c>
       <c r="O212" t="s">
-        <v>480</v>
+        <v>450</v>
       </c>
       <c r="P212" t="s">
         <v>479</v>
@@ -14167,25 +14167,25 @@
         <v>34</v>
       </c>
       <c r="E213" t="s">
-        <v>219</v>
+        <v>257</v>
       </c>
       <c r="F213" t="s">
-        <v>460</v>
+        <v>209</v>
       </c>
       <c r="G213" t="s">
         <v>41</v>
       </c>
       <c r="H213" t="s">
-        <v>202</v>
+        <v>394</v>
       </c>
       <c r="I213" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="J213" t="s">
-        <v>60</v>
+        <v>372</v>
       </c>
       <c r="K213" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="L213" t="s">
         <v>34</v>
@@ -14197,13 +14197,13 @@
         <v>45</v>
       </c>
       <c r="O213" t="s">
-        <v>34</v>
+        <v>89</v>
       </c>
       <c r="P213" t="s">
-        <v>34</v>
+        <v>480</v>
       </c>
       <c r="Q213" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R213" t="s">
         <v>34</v>
@@ -14223,7 +14223,7 @@
         <v>34</v>
       </c>
       <c r="E214" t="s">
-        <v>482</v>
+        <v>200</v>
       </c>
       <c r="F214" t="s">
         <v>209</v>
@@ -14232,10 +14232,10 @@
         <v>41</v>
       </c>
       <c r="H214" t="s">
-        <v>424</v>
+        <v>394</v>
       </c>
       <c r="I214" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="J214" t="s">
         <v>372</v>
@@ -14253,10 +14253,10 @@
         <v>45</v>
       </c>
       <c r="O214" t="s">
-        <v>484</v>
+        <v>51</v>
       </c>
       <c r="P214" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="Q214" t="s">
         <v>45</v>
@@ -14279,25 +14279,25 @@
         <v>34</v>
       </c>
       <c r="E215" t="s">
-        <v>361</v>
+        <v>482</v>
       </c>
       <c r="F215" t="s">
-        <v>460</v>
+        <v>209</v>
       </c>
       <c r="G215" t="s">
         <v>41</v>
       </c>
       <c r="H215" t="s">
-        <v>202</v>
+        <v>463</v>
       </c>
       <c r="I215" t="s">
-        <v>374</v>
+        <v>483</v>
       </c>
       <c r="J215" t="s">
-        <v>60</v>
+        <v>372</v>
       </c>
       <c r="K215" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="L215" t="s">
         <v>34</v>
@@ -14309,13 +14309,13 @@
         <v>45</v>
       </c>
       <c r="O215" t="s">
-        <v>34</v>
+        <v>484</v>
       </c>
       <c r="P215" t="s">
-        <v>34</v>
+        <v>483</v>
       </c>
       <c r="Q215" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R215" t="s">
         <v>34</v>
@@ -14335,7 +14335,7 @@
         <v>34</v>
       </c>
       <c r="E216" t="s">
-        <v>200</v>
+        <v>239</v>
       </c>
       <c r="F216" t="s">
         <v>209</v>
@@ -14344,7 +14344,7 @@
         <v>41</v>
       </c>
       <c r="H216" t="s">
-        <v>394</v>
+        <v>461</v>
       </c>
       <c r="I216" t="s">
         <v>485</v>
@@ -14365,7 +14365,7 @@
         <v>45</v>
       </c>
       <c r="O216" t="s">
-        <v>51</v>
+        <v>244</v>
       </c>
       <c r="P216" t="s">
         <v>485</v>
@@ -14400,7 +14400,7 @@
         <v>41</v>
       </c>
       <c r="H217" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="I217" t="s">
         <v>487</v>
@@ -14447,10 +14447,10 @@
         <v>34</v>
       </c>
       <c r="E218" t="s">
-        <v>314</v>
+        <v>350</v>
       </c>
       <c r="F218" t="s">
-        <v>460</v>
+        <v>473</v>
       </c>
       <c r="G218" t="s">
         <v>41</v>
@@ -14459,13 +14459,13 @@
         <v>202</v>
       </c>
       <c r="I218" t="s">
-        <v>386</v>
+        <v>489</v>
       </c>
       <c r="J218" t="s">
-        <v>130</v>
+        <v>60</v>
       </c>
       <c r="K218" t="s">
-        <v>130</v>
+        <v>60</v>
       </c>
       <c r="L218" t="s">
         <v>34</v>
@@ -14503,25 +14503,25 @@
         <v>34</v>
       </c>
       <c r="E219" t="s">
-        <v>257</v>
+        <v>219</v>
       </c>
       <c r="F219" t="s">
-        <v>209</v>
+        <v>473</v>
       </c>
       <c r="G219" t="s">
         <v>41</v>
       </c>
       <c r="H219" t="s">
-        <v>394</v>
+        <v>202</v>
       </c>
       <c r="I219" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="J219" t="s">
-        <v>372</v>
+        <v>60</v>
       </c>
       <c r="K219" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="L219" t="s">
         <v>34</v>
@@ -14533,13 +14533,13 @@
         <v>45</v>
       </c>
       <c r="O219" t="s">
-        <v>89</v>
+        <v>34</v>
       </c>
       <c r="P219" t="s">
-        <v>489</v>
+        <v>34</v>
       </c>
       <c r="Q219" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="R219" t="s">
         <v>34</v>
@@ -14559,7 +14559,7 @@
         <v>34</v>
       </c>
       <c r="E220" t="s">
-        <v>448</v>
+        <v>491</v>
       </c>
       <c r="F220" t="s">
         <v>209</v>
@@ -14568,10 +14568,10 @@
         <v>41</v>
       </c>
       <c r="H220" t="s">
-        <v>394</v>
+        <v>424</v>
       </c>
       <c r="I220" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="J220" t="s">
         <v>372</v>
@@ -14589,10 +14589,10 @@
         <v>45</v>
       </c>
       <c r="O220" t="s">
-        <v>450</v>
+        <v>493</v>
       </c>
       <c r="P220" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="Q220" t="s">
         <v>45</v>
@@ -14615,25 +14615,25 @@
         <v>34</v>
       </c>
       <c r="E221" t="s">
-        <v>491</v>
+        <v>361</v>
       </c>
       <c r="F221" t="s">
-        <v>209</v>
+        <v>473</v>
       </c>
       <c r="G221" t="s">
         <v>41</v>
       </c>
       <c r="H221" t="s">
-        <v>463</v>
+        <v>202</v>
       </c>
       <c r="I221" t="s">
-        <v>492</v>
+        <v>374</v>
       </c>
       <c r="J221" t="s">
-        <v>372</v>
+        <v>60</v>
       </c>
       <c r="K221" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="L221" t="s">
         <v>34</v>
@@ -14645,13 +14645,13 @@
         <v>45</v>
       </c>
       <c r="O221" t="s">
-        <v>493</v>
+        <v>34</v>
       </c>
       <c r="P221" t="s">
-        <v>492</v>
+        <v>34</v>
       </c>
       <c r="Q221" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="R221" t="s">
         <v>34</v>
@@ -14786,7 +14786,7 @@
         <v>257</v>
       </c>
       <c r="F224" t="s">
-        <v>460</v>
+        <v>473</v>
       </c>
       <c r="G224" t="s">
         <v>41</v>
@@ -14842,7 +14842,7 @@
         <v>200</v>
       </c>
       <c r="F225" t="s">
-        <v>460</v>
+        <v>473</v>
       </c>
       <c r="G225" t="s">
         <v>41</v>
@@ -14898,7 +14898,7 @@
         <v>223</v>
       </c>
       <c r="F226" t="s">
-        <v>460</v>
+        <v>473</v>
       </c>
       <c r="G226" t="s">
         <v>41</v>
@@ -14954,7 +14954,7 @@
         <v>239</v>
       </c>
       <c r="F227" t="s">
-        <v>460</v>
+        <v>473</v>
       </c>
       <c r="G227" t="s">
         <v>41</v>
@@ -15010,7 +15010,7 @@
         <v>358</v>
       </c>
       <c r="F228" t="s">
-        <v>460</v>
+        <v>473</v>
       </c>
       <c r="G228" t="s">
         <v>41</v>
@@ -15066,7 +15066,7 @@
         <v>212</v>
       </c>
       <c r="F229" t="s">
-        <v>460</v>
+        <v>473</v>
       </c>
       <c r="G229" t="s">
         <v>41</v>
@@ -15122,7 +15122,7 @@
         <v>228</v>
       </c>
       <c r="F230" t="s">
-        <v>460</v>
+        <v>473</v>
       </c>
       <c r="G230" t="s">
         <v>41</v>
@@ -15178,7 +15178,7 @@
         <v>234</v>
       </c>
       <c r="F231" t="s">
-        <v>460</v>
+        <v>473</v>
       </c>
       <c r="G231" t="s">
         <v>41</v>
@@ -15234,7 +15234,7 @@
         <v>224</v>
       </c>
       <c r="F232" t="s">
-        <v>460</v>
+        <v>473</v>
       </c>
       <c r="G232" t="s">
         <v>41</v>
@@ -15290,7 +15290,7 @@
         <v>237</v>
       </c>
       <c r="F233" t="s">
-        <v>460</v>
+        <v>473</v>
       </c>
       <c r="G233" t="s">
         <v>41</v>
@@ -15346,7 +15346,7 @@
         <v>226</v>
       </c>
       <c r="F234" t="s">
-        <v>460</v>
+        <v>473</v>
       </c>
       <c r="G234" t="s">
         <v>41</v>
@@ -18143,7 +18143,7 @@
         <v>33</v>
       </c>
       <c r="E284" t="s">
-        <v>154</v>
+        <v>576</v>
       </c>
       <c r="F284" t="s">
         <v>173</v>
@@ -18152,13 +18152,13 @@
         <v>41</v>
       </c>
       <c r="H284" t="s">
-        <v>408</v>
+        <v>603</v>
       </c>
       <c r="I284" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="J284" t="s">
-        <v>604</v>
+        <v>582</v>
       </c>
       <c r="K284" t="s">
         <v>270</v>
@@ -18176,7 +18176,7 @@
         <v>153</v>
       </c>
       <c r="P284" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="Q284" t="s">
         <v>45</v>
@@ -18199,7 +18199,7 @@
         <v>34</v>
       </c>
       <c r="E285" t="s">
-        <v>576</v>
+        <v>154</v>
       </c>
       <c r="F285" t="s">
         <v>173</v>
@@ -18208,13 +18208,13 @@
         <v>41</v>
       </c>
       <c r="H285" t="s">
+        <v>461</v>
+      </c>
+      <c r="I285" t="s">
         <v>606</v>
       </c>
-      <c r="I285" t="s">
+      <c r="J285" t="s">
         <v>607</v>
-      </c>
-      <c r="J285" t="s">
-        <v>582</v>
       </c>
       <c r="K285" t="s">
         <v>270</v>
@@ -18232,7 +18232,7 @@
         <v>153</v>
       </c>
       <c r="P285" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="Q285" t="s">
         <v>45</v>
@@ -18255,28 +18255,28 @@
         <v>34</v>
       </c>
       <c r="E286" t="s">
+        <v>576</v>
+      </c>
+      <c r="F286" t="s">
+        <v>173</v>
+      </c>
+      <c r="G286" t="s">
+        <v>41</v>
+      </c>
+      <c r="H286" t="s">
+        <v>394</v>
+      </c>
+      <c r="I286" t="s">
+        <v>596</v>
+      </c>
+      <c r="J286" t="s">
+        <v>269</v>
+      </c>
+      <c r="K286" t="s">
+        <v>270</v>
+      </c>
+      <c r="L286" t="s">
         <v>609</v>
-      </c>
-      <c r="F286" t="s">
-        <v>197</v>
-      </c>
-      <c r="G286" t="s">
-        <v>41</v>
-      </c>
-      <c r="H286" t="s">
-        <v>424</v>
-      </c>
-      <c r="I286" t="s">
-        <v>610</v>
-      </c>
-      <c r="J286" t="s">
-        <v>372</v>
-      </c>
-      <c r="K286" t="s">
-        <v>55</v>
-      </c>
-      <c r="L286" t="s">
-        <v>34</v>
       </c>
       <c r="M286" t="s">
         <v>602</v>
@@ -18288,7 +18288,7 @@
         <v>153</v>
       </c>
       <c r="P286" t="s">
-        <v>610</v>
+        <v>596</v>
       </c>
       <c r="Q286" t="s">
         <v>45</v>
@@ -18311,28 +18311,28 @@
         <v>34</v>
       </c>
       <c r="E287" t="s">
-        <v>584</v>
+        <v>610</v>
       </c>
       <c r="F287" t="s">
-        <v>173</v>
+        <v>197</v>
       </c>
       <c r="G287" t="s">
         <v>41</v>
       </c>
       <c r="H287" t="s">
-        <v>370</v>
+        <v>611</v>
       </c>
       <c r="I287" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="J287" t="s">
-        <v>612</v>
+        <v>253</v>
       </c>
       <c r="K287" t="s">
         <v>270</v>
       </c>
       <c r="L287" t="s">
-        <v>613</v>
+        <v>34</v>
       </c>
       <c r="M287" t="s">
         <v>602</v>
@@ -18344,7 +18344,7 @@
         <v>153</v>
       </c>
       <c r="P287" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="Q287" t="s">
         <v>45</v>
@@ -18367,7 +18367,7 @@
         <v>34</v>
       </c>
       <c r="E288" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="F288" t="s">
         <v>197</v>
@@ -18376,16 +18376,16 @@
         <v>41</v>
       </c>
       <c r="H288" t="s">
-        <v>519</v>
+        <v>424</v>
       </c>
       <c r="I288" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="J288" t="s">
-        <v>66</v>
+        <v>372</v>
       </c>
       <c r="K288" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="L288" t="s">
         <v>34</v>
@@ -18400,7 +18400,7 @@
         <v>153</v>
       </c>
       <c r="P288" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="Q288" t="s">
         <v>45</v>
@@ -18423,28 +18423,28 @@
         <v>34</v>
       </c>
       <c r="E289" t="s">
-        <v>576</v>
+        <v>615</v>
       </c>
       <c r="F289" t="s">
-        <v>173</v>
+        <v>197</v>
       </c>
       <c r="G289" t="s">
         <v>41</v>
       </c>
       <c r="H289" t="s">
+        <v>519</v>
+      </c>
+      <c r="I289" t="s">
         <v>616</v>
       </c>
-      <c r="I289" t="s">
-        <v>617</v>
-      </c>
       <c r="J289" t="s">
-        <v>582</v>
+        <v>66</v>
       </c>
       <c r="K289" t="s">
-        <v>270</v>
+        <v>66</v>
       </c>
       <c r="L289" t="s">
-        <v>618</v>
+        <v>34</v>
       </c>
       <c r="M289" t="s">
         <v>602</v>
@@ -18456,7 +18456,7 @@
         <v>153</v>
       </c>
       <c r="P289" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="Q289" t="s">
         <v>45</v>
@@ -18479,28 +18479,28 @@
         <v>34</v>
       </c>
       <c r="E290" t="s">
-        <v>619</v>
+        <v>584</v>
       </c>
       <c r="F290" t="s">
-        <v>197</v>
+        <v>173</v>
       </c>
       <c r="G290" t="s">
         <v>41</v>
       </c>
       <c r="H290" t="s">
-        <v>620</v>
+        <v>370</v>
       </c>
       <c r="I290" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="J290" t="s">
-        <v>253</v>
+        <v>618</v>
       </c>
       <c r="K290" t="s">
         <v>270</v>
       </c>
       <c r="L290" t="s">
-        <v>34</v>
+        <v>619</v>
       </c>
       <c r="M290" t="s">
         <v>602</v>
@@ -18512,7 +18512,7 @@
         <v>153</v>
       </c>
       <c r="P290" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="Q290" t="s">
         <v>45</v>
@@ -18535,7 +18535,7 @@
         <v>34</v>
       </c>
       <c r="E291" t="s">
-        <v>576</v>
+        <v>154</v>
       </c>
       <c r="F291" t="s">
         <v>173</v>
@@ -18544,19 +18544,19 @@
         <v>41</v>
       </c>
       <c r="H291" t="s">
-        <v>622</v>
+        <v>408</v>
       </c>
       <c r="I291" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="J291" t="s">
-        <v>582</v>
+        <v>621</v>
       </c>
       <c r="K291" t="s">
         <v>270</v>
       </c>
       <c r="L291" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="M291" t="s">
         <v>602</v>
@@ -18568,7 +18568,7 @@
         <v>153</v>
       </c>
       <c r="P291" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="Q291" t="s">
         <v>45</v>
@@ -18591,28 +18591,28 @@
         <v>34</v>
       </c>
       <c r="E292" t="s">
-        <v>576</v>
+        <v>623</v>
       </c>
       <c r="F292" t="s">
-        <v>173</v>
+        <v>197</v>
       </c>
       <c r="G292" t="s">
         <v>41</v>
       </c>
       <c r="H292" t="s">
-        <v>625</v>
+        <v>463</v>
       </c>
       <c r="I292" t="s">
-        <v>626</v>
+        <v>596</v>
       </c>
       <c r="J292" t="s">
-        <v>582</v>
+        <v>372</v>
       </c>
       <c r="K292" t="s">
-        <v>270</v>
+        <v>188</v>
       </c>
       <c r="L292" t="s">
-        <v>627</v>
+        <v>34</v>
       </c>
       <c r="M292" t="s">
         <v>602</v>
@@ -18624,7 +18624,7 @@
         <v>153</v>
       </c>
       <c r="P292" t="s">
-        <v>626</v>
+        <v>596</v>
       </c>
       <c r="Q292" t="s">
         <v>45</v>
@@ -18647,28 +18647,28 @@
         <v>34</v>
       </c>
       <c r="E293" t="s">
-        <v>628</v>
+        <v>154</v>
       </c>
       <c r="F293" t="s">
-        <v>197</v>
+        <v>173</v>
       </c>
       <c r="G293" t="s">
         <v>41</v>
       </c>
       <c r="H293" t="s">
-        <v>370</v>
+        <v>624</v>
       </c>
       <c r="I293" t="s">
-        <v>629</v>
+        <v>620</v>
       </c>
       <c r="J293" t="s">
-        <v>55</v>
+        <v>621</v>
       </c>
       <c r="K293" t="s">
-        <v>55</v>
+        <v>625</v>
       </c>
       <c r="L293" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="M293" t="s">
         <v>602</v>
@@ -18680,7 +18680,7 @@
         <v>153</v>
       </c>
       <c r="P293" t="s">
-        <v>629</v>
+        <v>620</v>
       </c>
       <c r="Q293" t="s">
         <v>45</v>
@@ -18703,28 +18703,28 @@
         <v>34</v>
       </c>
       <c r="E294" t="s">
-        <v>576</v>
+        <v>627</v>
       </c>
       <c r="F294" t="s">
-        <v>173</v>
+        <v>197</v>
       </c>
       <c r="G294" t="s">
         <v>41</v>
       </c>
       <c r="H294" t="s">
-        <v>394</v>
+        <v>370</v>
       </c>
       <c r="I294" t="s">
-        <v>596</v>
+        <v>628</v>
       </c>
       <c r="J294" t="s">
-        <v>269</v>
+        <v>55</v>
       </c>
       <c r="K294" t="s">
-        <v>270</v>
+        <v>55</v>
       </c>
       <c r="L294" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="M294" t="s">
         <v>602</v>
@@ -18736,7 +18736,7 @@
         <v>153</v>
       </c>
       <c r="P294" t="s">
-        <v>596</v>
+        <v>628</v>
       </c>
       <c r="Q294" t="s">
         <v>45</v>
@@ -18759,7 +18759,7 @@
         <v>34</v>
       </c>
       <c r="E295" t="s">
-        <v>632</v>
+        <v>576</v>
       </c>
       <c r="F295" t="s">
         <v>173</v>
@@ -18768,19 +18768,19 @@
         <v>41</v>
       </c>
       <c r="H295" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="I295" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="J295" t="s">
-        <v>81</v>
+        <v>582</v>
       </c>
       <c r="K295" t="s">
-        <v>81</v>
+        <v>270</v>
       </c>
       <c r="L295" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="M295" t="s">
         <v>602</v>
@@ -18792,7 +18792,7 @@
         <v>153</v>
       </c>
       <c r="P295" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="Q295" t="s">
         <v>45</v>
@@ -18815,28 +18815,28 @@
         <v>34</v>
       </c>
       <c r="E296" t="s">
-        <v>636</v>
+        <v>576</v>
       </c>
       <c r="F296" t="s">
-        <v>197</v>
+        <v>173</v>
       </c>
       <c r="G296" t="s">
         <v>41</v>
       </c>
       <c r="H296" t="s">
-        <v>463</v>
+        <v>633</v>
       </c>
       <c r="I296" t="s">
-        <v>596</v>
+        <v>634</v>
       </c>
       <c r="J296" t="s">
-        <v>372</v>
+        <v>582</v>
       </c>
       <c r="K296" t="s">
-        <v>188</v>
+        <v>270</v>
       </c>
       <c r="L296" t="s">
-        <v>34</v>
+        <v>635</v>
       </c>
       <c r="M296" t="s">
         <v>602</v>
@@ -18848,7 +18848,7 @@
         <v>153</v>
       </c>
       <c r="P296" t="s">
-        <v>596</v>
+        <v>634</v>
       </c>
       <c r="Q296" t="s">
         <v>45</v>
@@ -18871,7 +18871,7 @@
         <v>34</v>
       </c>
       <c r="E297" t="s">
-        <v>154</v>
+        <v>576</v>
       </c>
       <c r="F297" t="s">
         <v>173</v>
@@ -18880,19 +18880,19 @@
         <v>41</v>
       </c>
       <c r="H297" t="s">
+        <v>636</v>
+      </c>
+      <c r="I297" t="s">
+        <v>596</v>
+      </c>
+      <c r="J297" t="s">
+        <v>582</v>
+      </c>
+      <c r="K297" t="s">
+        <v>270</v>
+      </c>
+      <c r="L297" t="s">
         <v>637</v>
-      </c>
-      <c r="I297" t="s">
-        <v>603</v>
-      </c>
-      <c r="J297" t="s">
-        <v>604</v>
-      </c>
-      <c r="K297" t="s">
-        <v>638</v>
-      </c>
-      <c r="L297" t="s">
-        <v>639</v>
       </c>
       <c r="M297" t="s">
         <v>602</v>
@@ -18904,7 +18904,7 @@
         <v>153</v>
       </c>
       <c r="P297" t="s">
-        <v>603</v>
+        <v>596</v>
       </c>
       <c r="Q297" t="s">
         <v>45</v>
@@ -18927,7 +18927,7 @@
         <v>34</v>
       </c>
       <c r="E298" t="s">
-        <v>154</v>
+        <v>576</v>
       </c>
       <c r="F298" t="s">
         <v>173</v>
@@ -18936,19 +18936,19 @@
         <v>41</v>
       </c>
       <c r="H298" t="s">
-        <v>465</v>
+        <v>638</v>
       </c>
       <c r="I298" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="J298" t="s">
-        <v>641</v>
+        <v>582</v>
       </c>
       <c r="K298" t="s">
         <v>270</v>
       </c>
       <c r="L298" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="M298" t="s">
         <v>602</v>
@@ -18960,7 +18960,7 @@
         <v>153</v>
       </c>
       <c r="P298" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="Q298" t="s">
         <v>45</v>
@@ -18992,10 +18992,10 @@
         <v>41</v>
       </c>
       <c r="H299" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="I299" t="s">
-        <v>596</v>
+        <v>642</v>
       </c>
       <c r="J299" t="s">
         <v>582</v>
@@ -19004,7 +19004,7 @@
         <v>270</v>
       </c>
       <c r="L299" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="M299" t="s">
         <v>602</v>
@@ -19016,7 +19016,7 @@
         <v>153</v>
       </c>
       <c r="P299" t="s">
-        <v>596</v>
+        <v>642</v>
       </c>
       <c r="Q299" t="s">
         <v>45</v>
@@ -19039,10 +19039,10 @@
         <v>34</v>
       </c>
       <c r="E300" t="s">
-        <v>576</v>
+        <v>644</v>
       </c>
       <c r="F300" t="s">
-        <v>173</v>
+        <v>197</v>
       </c>
       <c r="G300" t="s">
         <v>41</v>
@@ -19051,16 +19051,16 @@
         <v>645</v>
       </c>
       <c r="I300" t="s">
+        <v>596</v>
+      </c>
+      <c r="J300" t="s">
+        <v>121</v>
+      </c>
+      <c r="K300" t="s">
+        <v>146</v>
+      </c>
+      <c r="L300" t="s">
         <v>646</v>
-      </c>
-      <c r="J300" t="s">
-        <v>582</v>
-      </c>
-      <c r="K300" t="s">
-        <v>270</v>
-      </c>
-      <c r="L300" t="s">
-        <v>647</v>
       </c>
       <c r="M300" t="s">
         <v>602</v>
@@ -19072,7 +19072,7 @@
         <v>153</v>
       </c>
       <c r="P300" t="s">
-        <v>646</v>
+        <v>596</v>
       </c>
       <c r="Q300" t="s">
         <v>45</v>
@@ -19095,25 +19095,25 @@
         <v>34</v>
       </c>
       <c r="E301" t="s">
+        <v>647</v>
+      </c>
+      <c r="F301" t="s">
+        <v>173</v>
+      </c>
+      <c r="G301" t="s">
+        <v>41</v>
+      </c>
+      <c r="H301" t="s">
         <v>648</v>
       </c>
-      <c r="F301" t="s">
-        <v>197</v>
-      </c>
-      <c r="G301" t="s">
-        <v>41</v>
-      </c>
-      <c r="H301" t="s">
+      <c r="I301" t="s">
         <v>649</v>
       </c>
-      <c r="I301" t="s">
-        <v>596</v>
-      </c>
       <c r="J301" t="s">
-        <v>121</v>
+        <v>81</v>
       </c>
       <c r="K301" t="s">
-        <v>146</v>
+        <v>81</v>
       </c>
       <c r="L301" t="s">
         <v>650</v>
@@ -19128,7 +19128,7 @@
         <v>153</v>
       </c>
       <c r="P301" t="s">
-        <v>596</v>
+        <v>649</v>
       </c>
       <c r="Q301" t="s">
         <v>45</v>
@@ -19496,7 +19496,7 @@
         <v>41</v>
       </c>
       <c r="H308" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="I308" t="s">
         <v>669</v>
@@ -22735,7 +22735,7 @@
         <v>34</v>
       </c>
       <c r="E366" t="s">
-        <v>219</v>
+        <v>239</v>
       </c>
       <c r="F366" t="s">
         <v>209</v>
@@ -22744,16 +22744,16 @@
         <v>41</v>
       </c>
       <c r="H366" t="s">
-        <v>854</v>
+        <v>860</v>
       </c>
       <c r="I366" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="J366" t="s">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="K366" t="s">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="L366" t="s">
         <v>856</v>
@@ -22765,10 +22765,10 @@
         <v>45</v>
       </c>
       <c r="O366" t="s">
-        <v>77</v>
+        <v>244</v>
       </c>
       <c r="P366" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="Q366" t="s">
         <v>45</v>
@@ -22791,7 +22791,7 @@
         <v>34</v>
       </c>
       <c r="E367" t="s">
-        <v>234</v>
+        <v>219</v>
       </c>
       <c r="F367" t="s">
         <v>209</v>
@@ -22803,13 +22803,13 @@
         <v>854</v>
       </c>
       <c r="I367" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="J367" t="s">
-        <v>130</v>
+        <v>60</v>
       </c>
       <c r="K367" t="s">
-        <v>130</v>
+        <v>60</v>
       </c>
       <c r="L367" t="s">
         <v>856</v>
@@ -22821,10 +22821,10 @@
         <v>45</v>
       </c>
       <c r="O367" t="s">
-        <v>385</v>
+        <v>77</v>
       </c>
       <c r="P367" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="Q367" t="s">
         <v>45</v>
@@ -22847,7 +22847,7 @@
         <v>34</v>
       </c>
       <c r="E368" t="s">
-        <v>212</v>
+        <v>234</v>
       </c>
       <c r="F368" t="s">
         <v>209</v>
@@ -22859,13 +22859,13 @@
         <v>854</v>
       </c>
       <c r="I368" t="s">
-        <v>857</v>
+        <v>863</v>
       </c>
       <c r="J368" t="s">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="K368" t="s">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="L368" t="s">
         <v>856</v>
@@ -22877,10 +22877,10 @@
         <v>45</v>
       </c>
       <c r="O368" t="s">
-        <v>373</v>
+        <v>385</v>
       </c>
       <c r="P368" t="s">
-        <v>857</v>
+        <v>863</v>
       </c>
       <c r="Q368" t="s">
         <v>45</v>
@@ -22903,7 +22903,7 @@
         <v>34</v>
       </c>
       <c r="E369" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="F369" t="s">
         <v>209</v>
@@ -22915,13 +22915,13 @@
         <v>854</v>
       </c>
       <c r="I369" t="s">
-        <v>862</v>
+        <v>857</v>
       </c>
       <c r="J369" t="s">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="K369" t="s">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="L369" t="s">
         <v>856</v>
@@ -22933,10 +22933,10 @@
         <v>45</v>
       </c>
       <c r="O369" t="s">
-        <v>328</v>
+        <v>373</v>
       </c>
       <c r="P369" t="s">
-        <v>862</v>
+        <v>857</v>
       </c>
       <c r="Q369" t="s">
         <v>45</v>
@@ -22959,7 +22959,7 @@
         <v>34</v>
       </c>
       <c r="E370" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="F370" t="s">
         <v>209</v>
@@ -22971,13 +22971,13 @@
         <v>854</v>
       </c>
       <c r="I370" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="J370" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="K370" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="L370" t="s">
         <v>856</v>
@@ -22989,10 +22989,10 @@
         <v>45</v>
       </c>
       <c r="O370" t="s">
-        <v>216</v>
+        <v>328</v>
       </c>
       <c r="P370" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="Q370" t="s">
         <v>45</v>
@@ -23015,7 +23015,7 @@
         <v>34</v>
       </c>
       <c r="E371" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="F371" t="s">
         <v>209</v>
@@ -23027,13 +23027,13 @@
         <v>854</v>
       </c>
       <c r="I371" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="J371" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="K371" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="L371" t="s">
         <v>856</v>
@@ -23045,10 +23045,10 @@
         <v>45</v>
       </c>
       <c r="O371" t="s">
-        <v>61</v>
+        <v>216</v>
       </c>
       <c r="P371" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="Q371" t="s">
         <v>45</v>
@@ -23071,7 +23071,7 @@
         <v>34</v>
       </c>
       <c r="E372" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F372" t="s">
         <v>209</v>
@@ -23083,13 +23083,13 @@
         <v>854</v>
       </c>
       <c r="I372" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="J372" t="s">
-        <v>130</v>
+        <v>60</v>
       </c>
       <c r="K372" t="s">
-        <v>130</v>
+        <v>60</v>
       </c>
       <c r="L372" t="s">
         <v>856</v>
@@ -23101,10 +23101,10 @@
         <v>45</v>
       </c>
       <c r="O372" t="s">
-        <v>387</v>
+        <v>61</v>
       </c>
       <c r="P372" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="Q372" t="s">
         <v>45</v>
@@ -23127,7 +23127,7 @@
         <v>34</v>
       </c>
       <c r="E373" t="s">
-        <v>237</v>
+        <v>224</v>
       </c>
       <c r="F373" t="s">
         <v>209</v>
@@ -23139,13 +23139,13 @@
         <v>854</v>
       </c>
       <c r="I373" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="J373" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="K373" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="L373" t="s">
         <v>856</v>
@@ -23157,10 +23157,10 @@
         <v>45</v>
       </c>
       <c r="O373" t="s">
-        <v>140</v>
+        <v>387</v>
       </c>
       <c r="P373" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="Q373" t="s">
         <v>45</v>
@@ -23183,25 +23183,25 @@
         <v>34</v>
       </c>
       <c r="E374" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="F374" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="G374" t="s">
         <v>41</v>
       </c>
       <c r="H374" t="s">
-        <v>867</v>
+        <v>854</v>
       </c>
       <c r="I374" t="s">
         <v>868</v>
       </c>
       <c r="J374" t="s">
-        <v>88</v>
+        <v>118</v>
       </c>
       <c r="K374" t="s">
-        <v>88</v>
+        <v>118</v>
       </c>
       <c r="L374" t="s">
         <v>856</v>
@@ -23213,13 +23213,13 @@
         <v>45</v>
       </c>
       <c r="O374" t="s">
-        <v>34</v>
+        <v>140</v>
       </c>
       <c r="P374" t="s">
-        <v>34</v>
+        <v>868</v>
       </c>
       <c r="Q374" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R374" t="s">
         <v>34</v>
@@ -27289,7 +27289,7 @@
         <v>959</v>
       </c>
       <c r="K447" t="s">
-        <v>638</v>
+        <v>625</v>
       </c>
       <c r="L447" t="s">
         <v>960</v>
@@ -27401,7 +27401,7 @@
         <v>959</v>
       </c>
       <c r="K449" t="s">
-        <v>638</v>
+        <v>625</v>
       </c>
       <c r="L449" t="s">
         <v>966</v>
@@ -27566,10 +27566,10 @@
         <v>962</v>
       </c>
       <c r="J452" t="s">
-        <v>638</v>
+        <v>625</v>
       </c>
       <c r="K452" t="s">
-        <v>638</v>
+        <v>625</v>
       </c>
       <c r="L452" t="s">
         <v>960</v>
